--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G157"/>
+  <dimension ref="A1:G159"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="17.19921875" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -5926,6 +5926,76 @@
       <c r="G157" t="inlineStr">
         <is>
           <t>2025-08-22 09:02:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>서하니</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>representativec</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>12</v>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>대구 북구 공항로 16 105동 507호</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>2025-08-22 09:40:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>정시원</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>rushnice</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>13</v>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>대구연경초등학교</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>대구 동구 동화천로 369 101동 104호</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>2025-08-22 09:52:03</t>
         </is>
       </c>
     </row>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -424,7 +424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G159"/>
+  <dimension ref="A1:H169"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <cols>
     <col width="17.19921875" bestFit="1" customWidth="1" min="5" max="5"/>
@@ -465,6 +465,11 @@
       </c>
       <c r="G1" t="inlineStr">
         <is>
+          <t>학부모이름</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
           <t>가입일시</t>
         </is>
       </c>
@@ -498,7 +503,7 @@
           <t>대구 동구 아양로9길 35 102동 407호</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
+      <c r="H2" t="inlineStr">
         <is>
           <t>2025-08-18 09:08:11</t>
         </is>
@@ -533,7 +538,7 @@
           <t>대구 북구 침산남로 90 102동 504호</t>
         </is>
       </c>
-      <c r="G3" t="inlineStr">
+      <c r="H3" t="inlineStr">
         <is>
           <t>2025-08-18 09:10:48</t>
         </is>
@@ -568,7 +573,7 @@
           <t>대구 북구 학남로 60 나동 106호</t>
         </is>
       </c>
-      <c r="G4" t="inlineStr">
+      <c r="H4" t="inlineStr">
         <is>
           <t>2025-08-18 09:22:53</t>
         </is>
@@ -603,7 +608,7 @@
           <t>대구 북구 국우동 1080 505동 307호</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
+      <c r="H5" t="inlineStr">
         <is>
           <t>2025-08-18 09:32:47</t>
         </is>
@@ -638,7 +643,7 @@
           <t>대구 북구 침산로 163 104동 301호</t>
         </is>
       </c>
-      <c r="G6" t="inlineStr">
+      <c r="H6" t="inlineStr">
         <is>
           <t>2025-08-18 09:42:19</t>
         </is>
@@ -673,7 +678,7 @@
           <t>대구 북구 호암로 20 110동 101호</t>
         </is>
       </c>
-      <c r="G7" t="inlineStr">
+      <c r="H7" t="inlineStr">
         <is>
           <t>2025-08-18 09:52:49</t>
         </is>
@@ -708,7 +713,7 @@
           <t>대구 북구 침산남로 116 101동 406호</t>
         </is>
       </c>
-      <c r="G8" t="inlineStr">
+      <c r="H8" t="inlineStr">
         <is>
           <t>2025-08-18 10:04:28</t>
         </is>
@@ -743,7 +748,7 @@
           <t>대구 북구 침산남로19길 9 103동 306호</t>
         </is>
       </c>
-      <c r="G9" t="inlineStr">
+      <c r="H9" t="inlineStr">
         <is>
           <t>2025-08-18 10:13:42</t>
         </is>
@@ -778,7 +783,7 @@
           <t>대구 북구 침산로 163 104동 502호</t>
         </is>
       </c>
-      <c r="G10" t="inlineStr">
+      <c r="H10" t="inlineStr">
         <is>
           <t>2025-08-18 10:51:15</t>
         </is>
@@ -813,7 +818,7 @@
           <t>대구 북구 학남로 60 나동 108호</t>
         </is>
       </c>
-      <c r="G11" t="inlineStr">
+      <c r="H11" t="inlineStr">
         <is>
           <t>2025-08-18 11:00:54</t>
         </is>
@@ -848,7 +853,7 @@
           <t>대구 북구 매전로 50-42 202동 107호</t>
         </is>
       </c>
-      <c r="G12" t="inlineStr">
+      <c r="H12" t="inlineStr">
         <is>
           <t>2025-08-18 11:10:41</t>
         </is>
@@ -883,7 +888,7 @@
           <t>대구 북구 학남로 60 나동 101호</t>
         </is>
       </c>
-      <c r="G13" t="inlineStr">
+      <c r="H13" t="inlineStr">
         <is>
           <t>2025-08-18 11:21:00</t>
         </is>
@@ -918,7 +923,7 @@
           <t>대구 북구 구암서로 41 303동 507호</t>
         </is>
       </c>
-      <c r="G14" t="inlineStr">
+      <c r="H14" t="inlineStr">
         <is>
           <t>2025-08-18 11:31:25</t>
         </is>
@@ -953,7 +958,7 @@
           <t>대구 북구 공항로 84 102동 106호</t>
         </is>
       </c>
-      <c r="G15" t="inlineStr">
+      <c r="H15" t="inlineStr">
         <is>
           <t>2025-08-18 11:43:34</t>
         </is>
@@ -988,7 +993,7 @@
           <t>대구 북구 학정로110길 29 101동 302호</t>
         </is>
       </c>
-      <c r="G16" t="inlineStr">
+      <c r="H16" t="inlineStr">
         <is>
           <t>2025-08-18 11:53:56</t>
         </is>
@@ -1023,7 +1028,7 @@
           <t>대구 북구 학정로110길 29 101동 506호</t>
         </is>
       </c>
-      <c r="G17" t="inlineStr">
+      <c r="H17" t="inlineStr">
         <is>
           <t>2025-08-18 12:02:02</t>
         </is>
@@ -1058,7 +1063,7 @@
           <t>대구 북구 경대로5길 25 210동 506호</t>
         </is>
       </c>
-      <c r="G18" t="inlineStr">
+      <c r="H18" t="inlineStr">
         <is>
           <t>2025-08-18 12:13:52</t>
         </is>
@@ -1093,7 +1098,7 @@
           <t>대구 북구 칠성남로 101 107동 504호</t>
         </is>
       </c>
-      <c r="G19" t="inlineStr">
+      <c r="H19" t="inlineStr">
         <is>
           <t>2025-08-18 12:24:45</t>
         </is>
@@ -1128,7 +1133,7 @@
           <t>대구 동구 신성로 60 104동 407호</t>
         </is>
       </c>
-      <c r="G20" t="inlineStr">
+      <c r="H20" t="inlineStr">
         <is>
           <t>2025-08-18 12:34:38</t>
         </is>
@@ -1163,7 +1168,7 @@
           <t>대구 북구 칠성남로 101 107동 302호</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
+      <c r="H21" t="inlineStr">
         <is>
           <t>2025-08-18 14:40:45</t>
         </is>
@@ -1198,7 +1203,7 @@
           <t>대구 북구 매전로4길 9 212동 504호</t>
         </is>
       </c>
-      <c r="G22" t="inlineStr">
+      <c r="H22" t="inlineStr">
         <is>
           <t>2025-08-18 14:52:09</t>
         </is>
@@ -1233,7 +1238,7 @@
           <t>대구 동구 신성로 60 104동 404호</t>
         </is>
       </c>
-      <c r="G23" t="inlineStr">
+      <c r="H23" t="inlineStr">
         <is>
           <t>2025-08-18 15:02:15</t>
         </is>
@@ -1268,7 +1273,7 @@
           <t>대구 북구 침산로21길 24 103동 301호</t>
         </is>
       </c>
-      <c r="G24" t="inlineStr">
+      <c r="H24" t="inlineStr">
         <is>
           <t>2025-08-18 15:12:21</t>
         </is>
@@ -1303,7 +1308,7 @@
           <t>대구 북구 학정로110길 29 101동 105호</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="H25" t="inlineStr">
         <is>
           <t>2025-08-18 15:20:33</t>
         </is>
@@ -1338,7 +1343,7 @@
           <t>대구 북구 학남로 60 나동 501호</t>
         </is>
       </c>
-      <c r="G26" t="inlineStr">
+      <c r="H26" t="inlineStr">
         <is>
           <t>2025-08-18 15:28:55</t>
         </is>
@@ -1373,7 +1378,7 @@
           <t>대구 북구 침산남로19길 9 103동 106호</t>
         </is>
       </c>
-      <c r="G27" t="inlineStr">
+      <c r="H27" t="inlineStr">
         <is>
           <t>2025-08-18 15:39:10</t>
         </is>
@@ -1408,7 +1413,7 @@
           <t>대구 북구 구암서로 41 303동 307호</t>
         </is>
       </c>
-      <c r="G28" t="inlineStr">
+      <c r="H28" t="inlineStr">
         <is>
           <t>2025-08-18 15:47:22</t>
         </is>
@@ -1443,7 +1448,7 @@
           <t>대구 북구 경대로5길 25 210동 409호</t>
         </is>
       </c>
-      <c r="G29" t="inlineStr">
+      <c r="H29" t="inlineStr">
         <is>
           <t>2025-08-18 15:57:35</t>
         </is>
@@ -1478,7 +1483,7 @@
           <t>대구 북구 침산남로 90 102동 307호</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="H30" t="inlineStr">
         <is>
           <t>2025-08-18 16:06:11</t>
         </is>
@@ -1513,7 +1518,7 @@
           <t>대구 동구 신성로 60 104동 501호</t>
         </is>
       </c>
-      <c r="G31" t="inlineStr">
+      <c r="H31" t="inlineStr">
         <is>
           <t>2025-08-18 16:17:31</t>
         </is>
@@ -1548,7 +1553,7 @@
           <t>대구 북구 호암로 40 105동 306호</t>
         </is>
       </c>
-      <c r="G32" t="inlineStr">
+      <c r="H32" t="inlineStr">
         <is>
           <t>2025-08-18 16:29:03</t>
         </is>
@@ -1583,7 +1588,7 @@
           <t>대구 북구 학정동로 40 203동 504호</t>
         </is>
       </c>
-      <c r="G33" t="inlineStr">
+      <c r="H33" t="inlineStr">
         <is>
           <t>2025-08-18 16:37:57</t>
         </is>
@@ -1618,7 +1623,7 @@
           <t>대구 북구 침산남로 116 101동 401호</t>
         </is>
       </c>
-      <c r="G34" t="inlineStr">
+      <c r="H34" t="inlineStr">
         <is>
           <t>2025-08-18 16:48:59</t>
         </is>
@@ -1653,7 +1658,7 @@
           <t>대구 북구 구암로65길 9 307동 501호</t>
         </is>
       </c>
-      <c r="G35" t="inlineStr">
+      <c r="H35" t="inlineStr">
         <is>
           <t>2025-08-18 16:55:12</t>
         </is>
@@ -1688,7 +1693,7 @@
           <t>대구 북구 구암서로 41 303동 204호</t>
         </is>
       </c>
-      <c r="G36" t="inlineStr">
+      <c r="H36" t="inlineStr">
         <is>
           <t>2025-08-18 17:08:03</t>
         </is>
@@ -1723,7 +1728,7 @@
           <t>대구 동구 신성로 60 104동 205호</t>
         </is>
       </c>
-      <c r="G37" t="inlineStr">
+      <c r="H37" t="inlineStr">
         <is>
           <t>2025-08-18 17:24:23</t>
         </is>
@@ -1758,7 +1763,7 @@
           <t>대구 북구 침산로21길 24 103동 502호</t>
         </is>
       </c>
-      <c r="G38" t="inlineStr">
+      <c r="H38" t="inlineStr">
         <is>
           <t>2025-08-18 17:40:46</t>
         </is>
@@ -1793,7 +1798,7 @@
           <t>대구 북구 호암로 40 105동 106호</t>
         </is>
       </c>
-      <c r="G39" t="inlineStr">
+      <c r="H39" t="inlineStr">
         <is>
           <t>2025-08-18 17:53:28</t>
         </is>
@@ -1828,7 +1833,7 @@
           <t>대구 북구 침산남로 116 101동 204호</t>
         </is>
       </c>
-      <c r="G40" t="inlineStr">
+      <c r="H40" t="inlineStr">
         <is>
           <t>2025-08-18 18:09:02</t>
         </is>
@@ -1863,7 +1868,7 @@
           <t>대구 북구 옥산로17길 50 102동 205호</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="H41" t="inlineStr">
         <is>
           <t>2025-08-18 18:20:31</t>
         </is>
@@ -1898,7 +1903,7 @@
           <t>대구 북구 공항로 84 102동 308호</t>
         </is>
       </c>
-      <c r="G42" t="inlineStr">
+      <c r="H42" t="inlineStr">
         <is>
           <t>2025-08-18 18:35:47</t>
         </is>
@@ -1933,7 +1938,7 @@
           <t>대구 북구 학정동 980 106동 207호</t>
         </is>
       </c>
-      <c r="G43" t="inlineStr">
+      <c r="H43" t="inlineStr">
         <is>
           <t>2025-08-18 18:47:28</t>
         </is>
@@ -1968,7 +1973,7 @@
           <t>대구 북구 침산남로 116 101동 205호</t>
         </is>
       </c>
-      <c r="G44" t="inlineStr">
+      <c r="H44" t="inlineStr">
         <is>
           <t>2025-08-19 09:02:25</t>
         </is>
@@ -2003,7 +2008,7 @@
           <t>대구 북구 경대로5길 25 210동 304호</t>
         </is>
       </c>
-      <c r="G45" t="inlineStr">
+      <c r="H45" t="inlineStr">
         <is>
           <t>2025-08-19 09:16:16</t>
         </is>
@@ -2038,7 +2043,7 @@
           <t>대구 북구 학정동로 40 202동 506호</t>
         </is>
       </c>
-      <c r="G46" t="inlineStr">
+      <c r="H46" t="inlineStr">
         <is>
           <t>2025-08-19 09:30:49</t>
         </is>
@@ -2073,7 +2078,7 @@
           <t>대구 북구 매전로 50-42 202동 204호</t>
         </is>
       </c>
-      <c r="G47" t="inlineStr">
+      <c r="H47" t="inlineStr">
         <is>
           <t>2025-08-19 09:42:46</t>
         </is>
@@ -2108,7 +2113,7 @@
           <t>대구 북구 침산로 163 104동 206호</t>
         </is>
       </c>
-      <c r="G48" t="inlineStr">
+      <c r="H48" t="inlineStr">
         <is>
           <t>2025-08-19 09:55:46</t>
         </is>
@@ -2143,7 +2148,7 @@
           <t>대구 북구 국우동 1080 505동 408호</t>
         </is>
       </c>
-      <c r="G49" t="inlineStr">
+      <c r="H49" t="inlineStr">
         <is>
           <t>2025-08-19 10:07:59</t>
         </is>
@@ -2178,7 +2183,7 @@
           <t>대구 북구 구암로65길 9 307동 203호</t>
         </is>
       </c>
-      <c r="G50" t="inlineStr">
+      <c r="H50" t="inlineStr">
         <is>
           <t>2025-08-19 10:20:27</t>
         </is>
@@ -2213,7 +2218,7 @@
           <t>대구 북구 학정동로 40 202동 404호</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>2025-08-19 10:36:20</t>
         </is>
@@ -2248,7 +2253,7 @@
           <t>대구 북구 학정로110길 29 101동 508호</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="H52" t="inlineStr">
         <is>
           <t>2025-08-19 10:59:12</t>
         </is>
@@ -2283,7 +2288,7 @@
           <t>대구 북구 구암서로 70 203동 206호</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>2025-08-19 11:10:24</t>
         </is>
@@ -2318,7 +2323,7 @@
           <t>대구 북구 학정동로 40 202동 509호</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="H54" t="inlineStr">
         <is>
           <t>2025-08-19 11:21:06</t>
         </is>
@@ -2353,7 +2358,7 @@
           <t>대구 북구 침산남로19길 9 103동 406호</t>
         </is>
       </c>
-      <c r="G55" t="inlineStr">
+      <c r="H55" t="inlineStr">
         <is>
           <t>2025-08-19 11:36:11</t>
         </is>
@@ -2388,7 +2393,7 @@
           <t>대구 북구 학남로 60 나동 305호</t>
         </is>
       </c>
-      <c r="G56" t="inlineStr">
+      <c r="H56" t="inlineStr">
         <is>
           <t>2025-08-19 11:49:33</t>
         </is>
@@ -2423,7 +2428,7 @@
           <t>대구 동구 신성로 60 104동 201호</t>
         </is>
       </c>
-      <c r="G57" t="inlineStr">
+      <c r="H57" t="inlineStr">
         <is>
           <t>2025-08-19 12:04:10</t>
         </is>
@@ -2458,7 +2463,7 @@
           <t>대구 북구 매전로4길 9 212동 207호</t>
         </is>
       </c>
-      <c r="G58" t="inlineStr">
+      <c r="H58" t="inlineStr">
         <is>
           <t>2025-08-19 13:53:11</t>
         </is>
@@ -2493,7 +2498,7 @@
           <t>대구 북구 침산남로 116 101동 203호</t>
         </is>
       </c>
-      <c r="G59" t="inlineStr">
+      <c r="H59" t="inlineStr">
         <is>
           <t>2025-08-19 14:06:16</t>
         </is>
@@ -2528,7 +2533,7 @@
           <t>대구 북구 공항로 84 102동 104호</t>
         </is>
       </c>
-      <c r="G60" t="inlineStr">
+      <c r="H60" t="inlineStr">
         <is>
           <t>2025-08-19 14:17:33</t>
         </is>
@@ -2563,7 +2568,7 @@
           <t>대구 북구 학정동로 40 202동 109호</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
+      <c r="H61" t="inlineStr">
         <is>
           <t>2025-08-19 14:32:27</t>
         </is>
@@ -2598,7 +2603,7 @@
           <t>대구 북구 칠성남로 101 107동 502호</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>2025-08-19 14:48:17</t>
         </is>
@@ -2633,7 +2638,7 @@
           <t>대구 북구 학정동 980 106동 204호</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="H63" t="inlineStr">
         <is>
           <t>2025-08-19 14:59:26</t>
         </is>
@@ -2668,7 +2673,7 @@
           <t>대구 북구 구암서로 70 203동 108호</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
+      <c r="H64" t="inlineStr">
         <is>
           <t>2025-08-19 15:11:55</t>
         </is>
@@ -2703,7 +2708,7 @@
           <t>대구 북구 매전로4길 9 212동 107호</t>
         </is>
       </c>
-      <c r="G65" t="inlineStr">
+      <c r="H65" t="inlineStr">
         <is>
           <t>2025-08-19 15:23:39</t>
         </is>
@@ -2738,7 +2743,7 @@
           <t>대구 북구 옥산로17길 50 102동 504호</t>
         </is>
       </c>
-      <c r="G66" t="inlineStr">
+      <c r="H66" t="inlineStr">
         <is>
           <t>2025-08-19 15:37:05</t>
         </is>
@@ -2773,7 +2778,7 @@
           <t>대구 북구 구암로65길 9 307동 307호</t>
         </is>
       </c>
-      <c r="G67" t="inlineStr">
+      <c r="H67" t="inlineStr">
         <is>
           <t>2025-08-19 15:50:08</t>
         </is>
@@ -2808,7 +2813,7 @@
           <t>대구 북구 침산남로19길 9 103동 307호</t>
         </is>
       </c>
-      <c r="G68" t="inlineStr">
+      <c r="H68" t="inlineStr">
         <is>
           <t>2025-08-19 16:03:06</t>
         </is>
@@ -2843,7 +2848,7 @@
           <t>대구 북구 구암서로 70 203동 104호</t>
         </is>
       </c>
-      <c r="G69" t="inlineStr">
+      <c r="H69" t="inlineStr">
         <is>
           <t>2025-08-19 16:16:23</t>
         </is>
@@ -2878,7 +2883,7 @@
           <t>대구 북구 옥산로17길 50 102동 105호</t>
         </is>
       </c>
-      <c r="G70" t="inlineStr">
+      <c r="H70" t="inlineStr">
         <is>
           <t>2025-08-19 16:29:44</t>
         </is>
@@ -2913,7 +2918,7 @@
           <t>대구 북구 구암로65길 9 307동 402호</t>
         </is>
       </c>
-      <c r="G71" t="inlineStr">
+      <c r="H71" t="inlineStr">
         <is>
           <t>2025-08-19 16:46:05</t>
         </is>
@@ -2948,7 +2953,7 @@
           <t>대구 북구 매전로 50-42 202동 502호</t>
         </is>
       </c>
-      <c r="G72" t="inlineStr">
+      <c r="H72" t="inlineStr">
         <is>
           <t>2025-08-19 16:58:32</t>
         </is>
@@ -2983,7 +2988,7 @@
           <t>대구 북구 침산로21길 24 103동 208호</t>
         </is>
       </c>
-      <c r="G73" t="inlineStr">
+      <c r="H73" t="inlineStr">
         <is>
           <t>2025-08-19 17:17:12</t>
         </is>
@@ -3018,7 +3023,7 @@
           <t>대구 북구 공항로 16 105동 303호</t>
         </is>
       </c>
-      <c r="G74" t="inlineStr">
+      <c r="H74" t="inlineStr">
         <is>
           <t>2025-08-19 17:30:37</t>
         </is>
@@ -3053,7 +3058,7 @@
           <t>대구 북구 공항로 16 105동 207호</t>
         </is>
       </c>
-      <c r="G75" t="inlineStr">
+      <c r="H75" t="inlineStr">
         <is>
           <t>2025-08-19 17:45:00</t>
         </is>
@@ -3088,7 +3093,7 @@
           <t>대구 북구 호암로 40 105동 108호</t>
         </is>
       </c>
-      <c r="G76" t="inlineStr">
+      <c r="H76" t="inlineStr">
         <is>
           <t>2025-08-19 17:57:55</t>
         </is>
@@ -3123,7 +3128,7 @@
           <t>대구 북구 학정동로 40 202동 302호</t>
         </is>
       </c>
-      <c r="G77" t="inlineStr">
+      <c r="H77" t="inlineStr">
         <is>
           <t>2025-08-20 08:43:29</t>
         </is>
@@ -3158,7 +3163,7 @@
           <t>대구 북구 칠성남로 101 107동 404호</t>
         </is>
       </c>
-      <c r="G78" t="inlineStr">
+      <c r="H78" t="inlineStr">
         <is>
           <t>2025-08-20 08:54:56</t>
         </is>
@@ -3193,7 +3198,7 @@
           <t>대구 북구 호암로 20 110동 303호</t>
         </is>
       </c>
-      <c r="G79" t="inlineStr">
+      <c r="H79" t="inlineStr">
         <is>
           <t>2025-08-20 09:08:31</t>
         </is>
@@ -3228,7 +3233,7 @@
           <t>대구 북구 호암로 40 105동 202호</t>
         </is>
       </c>
-      <c r="G80" t="inlineStr">
+      <c r="H80" t="inlineStr">
         <is>
           <t>2025-08-20 09:22:45</t>
         </is>
@@ -3263,7 +3268,7 @@
           <t>대구 북구 복현동 241-1 106동 306호</t>
         </is>
       </c>
-      <c r="G81" t="inlineStr">
+      <c r="H81" t="inlineStr">
         <is>
           <t>2025-08-20 09:37:38</t>
         </is>
@@ -3298,7 +3303,7 @@
           <t>대구 북구 칠성남로 101 107동 505호</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
+      <c r="H82" t="inlineStr">
         <is>
           <t>2025-08-20 09:52:08</t>
         </is>
@@ -3333,7 +3338,7 @@
           <t>대구 북구 침산남로 116 101동 503호</t>
         </is>
       </c>
-      <c r="G83" t="inlineStr">
+      <c r="H83" t="inlineStr">
         <is>
           <t>2025-08-20 10:24:01</t>
         </is>
@@ -3368,7 +3373,7 @@
           <t>대구 북구 호암로 20 110동 106호</t>
         </is>
       </c>
-      <c r="G84" t="inlineStr">
+      <c r="H84" t="inlineStr">
         <is>
           <t>2025-08-20 10:36:42</t>
         </is>
@@ -3403,7 +3408,7 @@
           <t>대구 북구 공항로 84 102동 405호</t>
         </is>
       </c>
-      <c r="G85" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>2025-08-20 10:50:57</t>
         </is>
@@ -3438,7 +3443,7 @@
           <t>대구 북구 옥산로17길 50 102동 506호</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>2025-08-20 11:03:24</t>
         </is>
@@ -3473,7 +3478,7 @@
           <t>대구 북구 공항로 84 102동 205호</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>2025-08-20 11:17:24</t>
         </is>
@@ -3508,7 +3513,7 @@
           <t>대구 북구 옥산로17길 50 102동 308호</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>2025-08-20 11:31:31</t>
         </is>
@@ -3543,7 +3548,7 @@
           <t>대구 북구 침산로 163 104동 101호</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="H89" t="inlineStr">
         <is>
           <t>2025-08-20 11:45:11</t>
         </is>
@@ -3578,7 +3583,7 @@
           <t>대구 북구 호암로 20 110동 502호</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
+      <c r="H90" t="inlineStr">
         <is>
           <t>2025-08-20 12:00:17</t>
         </is>
@@ -3613,7 +3618,7 @@
           <t>대구 북구 경대로5길 25 210동 209호</t>
         </is>
       </c>
-      <c r="G91" t="inlineStr">
+      <c r="H91" t="inlineStr">
         <is>
           <t>2025-08-20 12:13:18</t>
         </is>
@@ -3648,7 +3653,7 @@
           <t>대구 북구 경대로5길 25 210동 107호</t>
         </is>
       </c>
-      <c r="G92" t="inlineStr">
+      <c r="H92" t="inlineStr">
         <is>
           <t>2025-08-20 12:26:41</t>
         </is>
@@ -3683,7 +3688,7 @@
           <t>대구 북구 구암서로 41 303동 403호</t>
         </is>
       </c>
-      <c r="G93" t="inlineStr">
+      <c r="H93" t="inlineStr">
         <is>
           <t>2025-08-20 12:39:28</t>
         </is>
@@ -3718,7 +3723,7 @@
           <t>대구 북구 학남로 60 나동 108호</t>
         </is>
       </c>
-      <c r="G94" t="inlineStr">
+      <c r="H94" t="inlineStr">
         <is>
           <t>2025-08-20 12:53:08</t>
         </is>
@@ -3753,7 +3758,7 @@
           <t>대구 북구 학남로 60 나동 303호</t>
         </is>
       </c>
-      <c r="G95" t="inlineStr">
+      <c r="H95" t="inlineStr">
         <is>
           <t>2025-08-20 13:06:35</t>
         </is>
@@ -3788,7 +3793,7 @@
           <t>대구 북구 침산로 163 104동 409호</t>
         </is>
       </c>
-      <c r="G96" t="inlineStr">
+      <c r="H96" t="inlineStr">
         <is>
           <t>2025-08-20 13:21:25</t>
         </is>
@@ -3823,7 +3828,7 @@
           <t>대구 동구 아양로9길 35 102동 308호</t>
         </is>
       </c>
-      <c r="G97" t="inlineStr">
+      <c r="H97" t="inlineStr">
         <is>
           <t>2025-08-20 13:33:30</t>
         </is>
@@ -3858,7 +3863,7 @@
           <t>대구 북구 침산남로 90 102동 409호</t>
         </is>
       </c>
-      <c r="G98" t="inlineStr">
+      <c r="H98" t="inlineStr">
         <is>
           <t>2025-08-20 13:44:55</t>
         </is>
@@ -3893,7 +3898,7 @@
           <t>대구 북구 구암로65길 9 307동 103호</t>
         </is>
       </c>
-      <c r="G99" t="inlineStr">
+      <c r="H99" t="inlineStr">
         <is>
           <t>2025-08-20 14:01:11</t>
         </is>
@@ -3928,7 +3933,7 @@
           <t>대구 북구 침산남로 116 101동 304호</t>
         </is>
       </c>
-      <c r="G100" t="inlineStr">
+      <c r="H100" t="inlineStr">
         <is>
           <t>2025-08-20 14:16:48</t>
         </is>
@@ -3963,7 +3968,7 @@
           <t>대구 북구 매전로4길 9 212동 204호</t>
         </is>
       </c>
-      <c r="G101" t="inlineStr">
+      <c r="H101" t="inlineStr">
         <is>
           <t>2025-08-20 14:33:13</t>
         </is>
@@ -3998,7 +4003,7 @@
           <t>대구 북구 구암서로 41 303동 106호</t>
         </is>
       </c>
-      <c r="G102" t="inlineStr">
+      <c r="H102" t="inlineStr">
         <is>
           <t>2025-08-20 14:49:18</t>
         </is>
@@ -4033,7 +4038,7 @@
           <t>대구 북구 침산남로 116 101동 501호</t>
         </is>
       </c>
-      <c r="G103" t="inlineStr">
+      <c r="H103" t="inlineStr">
         <is>
           <t>2025-08-20 15:05:37</t>
         </is>
@@ -4068,7 +4073,7 @@
           <t>대구 북구 구암로65길 9 307동 101호</t>
         </is>
       </c>
-      <c r="G104" t="inlineStr">
+      <c r="H104" t="inlineStr">
         <is>
           <t>2025-08-20 15:17:51</t>
         </is>
@@ -4103,7 +4108,7 @@
           <t>대구 북구 구암로65길 9 307동 208호</t>
         </is>
       </c>
-      <c r="G105" t="inlineStr">
+      <c r="H105" t="inlineStr">
         <is>
           <t>2025-08-20 15:32:47</t>
         </is>
@@ -4138,7 +4143,7 @@
           <t>대구 북구 침산로 163 104동 101호</t>
         </is>
       </c>
-      <c r="G106" t="inlineStr">
+      <c r="H106" t="inlineStr">
         <is>
           <t>2025-08-20 15:40:54</t>
         </is>
@@ -4173,7 +4178,7 @@
           <t>대구 북구 학정동 980 106동 203호</t>
         </is>
       </c>
-      <c r="G107" t="inlineStr">
+      <c r="H107" t="inlineStr">
         <is>
           <t>2025-08-20 15:52:30</t>
         </is>
@@ -4208,7 +4213,7 @@
           <t>대구 북구 국우동 1080 505동 503호</t>
         </is>
       </c>
-      <c r="G108" t="inlineStr">
+      <c r="H108" t="inlineStr">
         <is>
           <t>2025-08-20 16:03:54</t>
         </is>
@@ -4243,7 +4248,7 @@
           <t>대구 북구 침산남로 116 101동 407호</t>
         </is>
       </c>
-      <c r="G109" t="inlineStr">
+      <c r="H109" t="inlineStr">
         <is>
           <t>2025-08-20 16:17:52</t>
         </is>
@@ -4278,7 +4283,7 @@
           <t>대구 북구 옥산로17길 50 102동 109호</t>
         </is>
       </c>
-      <c r="G110" t="inlineStr">
+      <c r="H110" t="inlineStr">
         <is>
           <t>2025-08-20 16:29:38</t>
         </is>
@@ -4313,7 +4318,7 @@
           <t>대구 북구 학정동 980 106동 404호</t>
         </is>
       </c>
-      <c r="G111" t="inlineStr">
+      <c r="H111" t="inlineStr">
         <is>
           <t>2025-08-20 16:40:52</t>
         </is>
@@ -4348,7 +4353,7 @@
           <t>대구 북구 호암로 20 110동 402호</t>
         </is>
       </c>
-      <c r="G112" t="inlineStr">
+      <c r="H112" t="inlineStr">
         <is>
           <t>2025-08-20 16:56:02</t>
         </is>
@@ -4383,7 +4388,7 @@
           <t>대구 북구 학남로 60 나동 408호</t>
         </is>
       </c>
-      <c r="G113" t="inlineStr">
+      <c r="H113" t="inlineStr">
         <is>
           <t>2025-08-20 17:09:20</t>
         </is>
@@ -4418,7 +4423,7 @@
           <t>대구 북구 매전로4길 9 212동 203호</t>
         </is>
       </c>
-      <c r="G114" t="inlineStr">
+      <c r="H114" t="inlineStr">
         <is>
           <t>2025-08-20 17:23:57</t>
         </is>
@@ -4453,7 +4458,7 @@
           <t>대구 북구 국우동 1080 505동 109호</t>
         </is>
       </c>
-      <c r="G115" t="inlineStr">
+      <c r="H115" t="inlineStr">
         <is>
           <t>2025-08-20 17:35:04</t>
         </is>
@@ -4488,7 +4493,7 @@
           <t>대구 북구 매전로 50-42 202동 503호</t>
         </is>
       </c>
-      <c r="G116" t="inlineStr">
+      <c r="H116" t="inlineStr">
         <is>
           <t>2025-08-20 17:45:43</t>
         </is>
@@ -4523,7 +4528,7 @@
           <t>대구 북구 학정동로 40 203동 201호</t>
         </is>
       </c>
-      <c r="G117" t="inlineStr">
+      <c r="H117" t="inlineStr">
         <is>
           <t>2025-08-20 17:57:11</t>
         </is>
@@ -4558,7 +4563,7 @@
           <t>대구 북구 옥산로17길 50 102동 403호</t>
         </is>
       </c>
-      <c r="G118" t="inlineStr">
+      <c r="H118" t="inlineStr">
         <is>
           <t>2025-08-21 08:42:25</t>
         </is>
@@ -4593,7 +4598,7 @@
           <t>대구 북구 학정로110길 29 101동 503호</t>
         </is>
       </c>
-      <c r="G119" t="inlineStr">
+      <c r="H119" t="inlineStr">
         <is>
           <t>2025-08-21 08:56:25</t>
         </is>
@@ -4628,7 +4633,7 @@
           <t>대구 북구 매전로4길 31 203동 206호</t>
         </is>
       </c>
-      <c r="G120" t="inlineStr">
+      <c r="H120" t="inlineStr">
         <is>
           <t>2025-08-21 09:10:52</t>
         </is>
@@ -4663,7 +4668,7 @@
           <t>대구 북구 학정로110길 29 101동 307호</t>
         </is>
       </c>
-      <c r="G121" t="inlineStr">
+      <c r="H121" t="inlineStr">
         <is>
           <t>2025-08-21 09:25:14</t>
         </is>
@@ -4698,7 +4703,7 @@
           <t>대구 북구 공항로 16 105동 401호</t>
         </is>
       </c>
-      <c r="G122" t="inlineStr">
+      <c r="H122" t="inlineStr">
         <is>
           <t>2025-08-21 09:39:19</t>
         </is>
@@ -4733,7 +4738,7 @@
           <t>대구 북구 매전로4길 31 203동 508호</t>
         </is>
       </c>
-      <c r="G123" t="inlineStr">
+      <c r="H123" t="inlineStr">
         <is>
           <t>2025-08-21 09:50:43</t>
         </is>
@@ -4768,7 +4773,7 @@
           <t>대구 북구 구암로65길 9 307동 305호</t>
         </is>
       </c>
-      <c r="G124" t="inlineStr">
+      <c r="H124" t="inlineStr">
         <is>
           <t>2025-08-21 10:01:44</t>
         </is>
@@ -4803,7 +4808,7 @@
           <t>대구 북구 매전로4길 9 212동 505호</t>
         </is>
       </c>
-      <c r="G125" t="inlineStr">
+      <c r="H125" t="inlineStr">
         <is>
           <t>2025-08-21 10:15:17</t>
         </is>
@@ -4838,7 +4843,7 @@
           <t>대구 동구 신성로 60 104동 106호</t>
         </is>
       </c>
-      <c r="G126" t="inlineStr">
+      <c r="H126" t="inlineStr">
         <is>
           <t>2025-08-21 10:29:31</t>
         </is>
@@ -4873,7 +4878,7 @@
           <t>대구 동구 신성로 60 104동 402호</t>
         </is>
       </c>
-      <c r="G127" t="inlineStr">
+      <c r="H127" t="inlineStr">
         <is>
           <t>2025-08-21 10:45:08</t>
         </is>
@@ -4908,7 +4913,7 @@
           <t>대구 북구 매전로4길 9 212동 109호</t>
         </is>
       </c>
-      <c r="G128" t="inlineStr">
+      <c r="H128" t="inlineStr">
         <is>
           <t>2025-08-21 11:01:19</t>
         </is>
@@ -4943,7 +4948,7 @@
           <t>대구 북구 학정로110길 29 101동 207호</t>
         </is>
       </c>
-      <c r="G129" t="inlineStr">
+      <c r="H129" t="inlineStr">
         <is>
           <t>2025-08-21 11:14:50</t>
         </is>
@@ -4978,7 +4983,7 @@
           <t>대구 북구 침산남로 90 102동 104호</t>
         </is>
       </c>
-      <c r="G130" t="inlineStr">
+      <c r="H130" t="inlineStr">
         <is>
           <t>2025-08-21 11:30:08</t>
         </is>
@@ -5013,7 +5018,7 @@
           <t>대구 북구 칠성남로 101 107동 506호</t>
         </is>
       </c>
-      <c r="G131" t="inlineStr">
+      <c r="H131" t="inlineStr">
         <is>
           <t>2025-08-21 11:46:23</t>
         </is>
@@ -5048,7 +5053,7 @@
           <t>대구 북구 침산남로 90 102동 204호</t>
         </is>
       </c>
-      <c r="G132" t="inlineStr">
+      <c r="H132" t="inlineStr">
         <is>
           <t>2025-08-21 11:59:39</t>
         </is>
@@ -5083,7 +5088,7 @@
           <t>대구 동구 신성로 60 104동 501호</t>
         </is>
       </c>
-      <c r="G133" t="inlineStr">
+      <c r="H133" t="inlineStr">
         <is>
           <t>2025-08-21 12:12:27</t>
         </is>
@@ -5118,7 +5123,7 @@
           <t>대구 동구 아양로9길 35 102동 401호</t>
         </is>
       </c>
-      <c r="G134" t="inlineStr">
+      <c r="H134" t="inlineStr">
         <is>
           <t>2025-08-21 12:28:31</t>
         </is>
@@ -5153,7 +5158,7 @@
           <t>대구 북구 학정로110길 29 101동 508호</t>
         </is>
       </c>
-      <c r="G135" t="inlineStr">
+      <c r="H135" t="inlineStr">
         <is>
           <t>2025-08-21 12:40:34</t>
         </is>
@@ -5188,7 +5193,7 @@
           <t>대구 북구 학남로 60 나동 401호</t>
         </is>
       </c>
-      <c r="G136" t="inlineStr">
+      <c r="H136" t="inlineStr">
         <is>
           <t>2025-08-21 12:53:50</t>
         </is>
@@ -5223,7 +5228,7 @@
           <t>대구 북구 복현동 241-1 106동 404호</t>
         </is>
       </c>
-      <c r="G137" t="inlineStr">
+      <c r="H137" t="inlineStr">
         <is>
           <t>2025-08-21 13:07:21</t>
         </is>
@@ -5258,7 +5263,7 @@
           <t>대구 북구 칠성남로 101 107동 304호</t>
         </is>
       </c>
-      <c r="G138" t="inlineStr">
+      <c r="H138" t="inlineStr">
         <is>
           <t>2025-08-21 13:18:43</t>
         </is>
@@ -5293,7 +5298,7 @@
           <t>대구 북구 매전로4길 9 212동 202호</t>
         </is>
       </c>
-      <c r="G139" t="inlineStr">
+      <c r="H139" t="inlineStr">
         <is>
           <t>2025-08-21 13:31:17</t>
         </is>
@@ -5328,7 +5333,7 @@
           <t>대구 북구 구암서로 41 303동 204호</t>
         </is>
       </c>
-      <c r="G140" t="inlineStr">
+      <c r="H140" t="inlineStr">
         <is>
           <t>2025-08-21 13:42:59</t>
         </is>
@@ -5363,7 +5368,7 @@
           <t>대구 북구 학정로110길 29 101동 201호</t>
         </is>
       </c>
-      <c r="G141" t="inlineStr">
+      <c r="H141" t="inlineStr">
         <is>
           <t>2025-08-21 13:56:33</t>
         </is>
@@ -5398,7 +5403,7 @@
           <t>대구 북구 구암로65길 9 307동 401호</t>
         </is>
       </c>
-      <c r="G142" t="inlineStr">
+      <c r="H142" t="inlineStr">
         <is>
           <t>2025-08-21 14:08:41</t>
         </is>
@@ -5433,7 +5438,7 @@
           <t>대구 북구 매전로4길 9 212동 509호</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="H143" t="inlineStr">
         <is>
           <t>2025-08-21 14:20:39</t>
         </is>
@@ -5468,7 +5473,7 @@
           <t>대구 동구 아양로9길 35 102동 501호</t>
         </is>
       </c>
-      <c r="G144" t="inlineStr">
+      <c r="H144" t="inlineStr">
         <is>
           <t>2025-08-21 14:31:31</t>
         </is>
@@ -5503,7 +5508,7 @@
           <t>대구 북구 학정로110길 29 101동 205호</t>
         </is>
       </c>
-      <c r="G145" t="inlineStr">
+      <c r="H145" t="inlineStr">
         <is>
           <t>2025-08-21 14:59:58</t>
         </is>
@@ -5538,7 +5543,7 @@
           <t>대구 북구 구암서로 70 203동 305호</t>
         </is>
       </c>
-      <c r="G146" t="inlineStr">
+      <c r="H146" t="inlineStr">
         <is>
           <t>2025-08-21 15:13:23</t>
         </is>
@@ -5573,7 +5578,7 @@
           <t>대구 북구 구암서로 70 203동 405호</t>
         </is>
       </c>
-      <c r="G147" t="inlineStr">
+      <c r="H147" t="inlineStr">
         <is>
           <t>2025-08-21 15:28:47</t>
         </is>
@@ -5608,7 +5613,7 @@
           <t>대구 북구 구암로65길 9 307동 408호</t>
         </is>
       </c>
-      <c r="G148" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>2025-08-21 15:44:01</t>
         </is>
@@ -5643,7 +5648,7 @@
           <t>대구 북구 호암로 40 105동 104호</t>
         </is>
       </c>
-      <c r="G149" t="inlineStr">
+      <c r="H149" t="inlineStr">
         <is>
           <t>2025-08-21 16:00:07</t>
         </is>
@@ -5678,7 +5683,7 @@
           <t>대구 북구 학정동 980 106동 201호</t>
         </is>
       </c>
-      <c r="G150" t="inlineStr">
+      <c r="H150" t="inlineStr">
         <is>
           <t>2025-08-21 16:15:56</t>
         </is>
@@ -5713,7 +5718,7 @@
           <t>대구 북구 학남로 60 나동 106호</t>
         </is>
       </c>
-      <c r="G151" t="inlineStr">
+      <c r="H151" t="inlineStr">
         <is>
           <t>2025-08-21 16:28:06</t>
         </is>
@@ -5748,7 +5753,7 @@
           <t>대구 북구 호암로 20 110동 204호</t>
         </is>
       </c>
-      <c r="G152" t="inlineStr">
+      <c r="H152" t="inlineStr">
         <is>
           <t>2025-08-21 16:43:53</t>
         </is>
@@ -5783,7 +5788,7 @@
           <t>대구 북구 구암서로 70 203동 309호</t>
         </is>
       </c>
-      <c r="G153" t="inlineStr">
+      <c r="H153" t="inlineStr">
         <is>
           <t>2025-08-21 16:56:46</t>
         </is>
@@ -5818,7 +5823,7 @@
           <t>대구 북구 옥산로17길 50 102동 405호</t>
         </is>
       </c>
-      <c r="G154" t="inlineStr">
+      <c r="H154" t="inlineStr">
         <is>
           <t>2025-08-21 17:12:29</t>
         </is>
@@ -5853,7 +5858,7 @@
           <t>대구 북구 침산남로 90 102동 509호</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="H155" t="inlineStr">
         <is>
           <t>2025-08-21 17:24:37</t>
         </is>
@@ -5888,7 +5893,7 @@
           <t>대구 북구 구암서로 70 203동 406호</t>
         </is>
       </c>
-      <c r="G156" t="inlineStr">
+      <c r="H156" t="inlineStr">
         <is>
           <t>2025-08-21 17:35:40</t>
         </is>
@@ -5923,7 +5928,7 @@
           <t>대구 북구 학정동 980 106동 209호</t>
         </is>
       </c>
-      <c r="G157" t="inlineStr">
+      <c r="H157" t="inlineStr">
         <is>
           <t>2025-08-22 09:02:26</t>
         </is>
@@ -5958,7 +5963,7 @@
           <t>대구 북구 공항로 16 105동 507호</t>
         </is>
       </c>
-      <c r="G158" t="inlineStr">
+      <c r="H158" t="inlineStr">
         <is>
           <t>2025-08-22 09:40:20</t>
         </is>
@@ -5993,9 +5998,409 @@
           <t>대구 동구 동화천로 369 101동 104호</t>
         </is>
       </c>
-      <c r="G159" t="inlineStr">
+      <c r="H159" t="inlineStr">
         <is>
           <t>2025-08-22 09:52:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>류예담</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>adventurereduca</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>13</v>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>대구 북구 공항로 84 103동 101호</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>류재영</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>2025-08-22 10:03:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>강신</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>historycompassi</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>12</v>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>대구운암초등학교</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>대구 북구 대천로 101 101동 301호</t>
+        </is>
+      </c>
+      <c r="G161" t="inlineStr">
+        <is>
+          <t>심미령</t>
+        </is>
+      </c>
+      <c r="H161" t="inlineStr">
+        <is>
+          <t>2025-08-22 10:19:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>최은비</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>famguide6</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>13</v>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 49 105동 109호</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>최수정</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>2025-08-22 10:34:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>오세아</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>gosmash</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>13</v>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 205동 209호</t>
+        </is>
+      </c>
+      <c r="G163" t="inlineStr">
+        <is>
+          <t>오준호</t>
+        </is>
+      </c>
+      <c r="H163" t="inlineStr">
+        <is>
+          <t>2025-08-22 10:47:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>양채원</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>persistentempat</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>12</v>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>대구 북구 동북로 241 201동 102호</t>
+        </is>
+      </c>
+      <c r="G164" t="inlineStr">
+        <is>
+          <t>양민철</t>
+        </is>
+      </c>
+      <c r="H164" t="inlineStr">
+        <is>
+          <t>2025-08-22 11:01:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>박다온</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>bookwormadventu</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>11</v>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>대구 북구 학정로110길 29 102동 403호</t>
+        </is>
+      </c>
+      <c r="G165" t="inlineStr">
+        <is>
+          <t>장지안</t>
+        </is>
+      </c>
+      <c r="H165" t="inlineStr">
+        <is>
+          <t>2025-08-22 11:17:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>박동규</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>cool5</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>13</v>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>대구 북구 대천로 101 102동 404호</t>
+        </is>
+      </c>
+      <c r="G166" t="inlineStr">
+        <is>
+          <t>김혜선</t>
+        </is>
+      </c>
+      <c r="H166" t="inlineStr">
+        <is>
+          <t>2025-08-22 11:30:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>박나경</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>writing86</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>12</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>대구동변초등학교</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>대구 북구 동변로 55 102동 403호</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>박형종</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>2025-08-22 11:42:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>김혜리</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>minecraftmonkey</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>13</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>대구 북구 학정로110길 29 101동 504호</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>임윤서</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>2025-08-22 11:58:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>안영우</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>teeninnovator</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>11</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>대구연경초등학교</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>대구 북구 동화천로 315 202동 306호</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>안동인</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>2025-08-22 13:15:46</t>
         </is>
       </c>
     </row>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22095D2-453B-4B0B-9777-8E9E540E174E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2710AA9-70C2-44FB-8C3E-58D7A4EC2490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2883" uniqueCount="2001">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3156" uniqueCount="2191">
   <si>
     <t>이름</t>
   </si>
@@ -2319,6 +2319,9 @@
     <t>2025-08-22 17:47:59</t>
   </si>
   <si>
+    <t>성동준</t>
+  </si>
+  <si>
     <t>responsibility8</t>
   </si>
   <si>
@@ -3030,6 +3033,582 @@
     <t>2025-08-25 16:47:59</t>
   </si>
   <si>
+    <t>조리우</t>
+  </si>
+  <si>
+    <t>ghostingbookwor</t>
+  </si>
+  <si>
+    <t>대구 북구 내곡로 89 202동 406호</t>
+  </si>
+  <si>
+    <t>조재욱</t>
+  </si>
+  <si>
+    <t>2025-08-26 08:58:54</t>
+  </si>
+  <si>
+    <t>박혜림</t>
+  </si>
+  <si>
+    <t>optimistmega6</t>
+  </si>
+  <si>
+    <t>대구 북구 호암로 40 104동 402호</t>
+  </si>
+  <si>
+    <t>박민석</t>
+  </si>
+  <si>
+    <t>2025-08-26 08:59:23</t>
+  </si>
+  <si>
+    <t>이해성</t>
+  </si>
+  <si>
+    <t>zombieingrepres</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 156 102동 202호</t>
+  </si>
+  <si>
+    <t>정윤영</t>
+  </si>
+  <si>
+    <t>2025-08-26 09:28:30</t>
+  </si>
+  <si>
+    <t>김주혁</t>
+  </si>
+  <si>
+    <t>hobbiesfashion</t>
+  </si>
+  <si>
+    <t>대구 북구 호암로 40 104동 208호</t>
+  </si>
+  <si>
+    <t>박소희</t>
+  </si>
+  <si>
+    <t>2025-08-26 09:42:37</t>
+  </si>
+  <si>
+    <t>신민</t>
+  </si>
+  <si>
+    <t>legendmindfulne</t>
+  </si>
+  <si>
+    <t>최민희</t>
+  </si>
+  <si>
+    <t>2025-08-26 09:54:52</t>
+  </si>
+  <si>
+    <t>유재율</t>
+  </si>
+  <si>
+    <t>gamersnapchat</t>
+  </si>
+  <si>
+    <t>대구 북구 학정동로 40 201동 405호</t>
+  </si>
+  <si>
+    <t>장유미</t>
+  </si>
+  <si>
+    <t>2025-08-26 10:09:46</t>
+  </si>
+  <si>
+    <t>손승민</t>
+  </si>
+  <si>
+    <t>chef7</t>
+  </si>
+  <si>
+    <t>대구 북구 연경중앙로11길 19 103동 105호</t>
+  </si>
+  <si>
+    <t>손성하</t>
+  </si>
+  <si>
+    <t>2025-08-26 10:23:38</t>
+  </si>
+  <si>
+    <t>강로윤</t>
+  </si>
+  <si>
+    <t>integritybreadc</t>
+  </si>
+  <si>
+    <t>대구 북구 동변로 55 103동 403호</t>
+  </si>
+  <si>
+    <t>강성찬</t>
+  </si>
+  <si>
+    <t>2025-08-26 10:38:30</t>
+  </si>
+  <si>
+    <t>이하진</t>
+  </si>
+  <si>
+    <t>promoter0</t>
+  </si>
+  <si>
+    <t>대구 북구 국우동 1079 102동 503호</t>
+  </si>
+  <si>
+    <t>강지은</t>
+  </si>
+  <si>
+    <t>2025-08-26 10:49:06</t>
+  </si>
+  <si>
+    <t>박채령</t>
+  </si>
+  <si>
+    <t>strategistindep</t>
+  </si>
+  <si>
+    <t>대구 북구 연경중앙로 55 202동 403호</t>
+  </si>
+  <si>
+    <t>최유나</t>
+  </si>
+  <si>
+    <t>2025-08-26 11:01:07</t>
+  </si>
+  <si>
+    <t>강보경</t>
+  </si>
+  <si>
+    <t>bruhmusic7</t>
+  </si>
+  <si>
+    <t>대구 북구 도남길 148-51 101동 206호</t>
+  </si>
+  <si>
+    <t>박은진</t>
+  </si>
+  <si>
+    <t>2025-08-26 11:15:45</t>
+  </si>
+  <si>
+    <t>공윤오</t>
+  </si>
+  <si>
+    <t>empathyspeaker9</t>
+  </si>
+  <si>
+    <t>대구 북구 대천로 101 103동 301호</t>
+  </si>
+  <si>
+    <t>이윤정</t>
+  </si>
+  <si>
+    <t>2025-08-26 11:26:56</t>
+  </si>
+  <si>
+    <t>임건율</t>
+  </si>
+  <si>
+    <t>naruto06</t>
+  </si>
+  <si>
+    <t>대구광역시 북구 국우동 1079 105동 101호</t>
+  </si>
+  <si>
+    <t>임준일</t>
+  </si>
+  <si>
+    <t>2025-08-26 11:38:26</t>
+  </si>
+  <si>
+    <t>한혜원</t>
+  </si>
+  <si>
+    <t>equality09</t>
+  </si>
+  <si>
+    <t>대구 북구 대천로 101 101동 503호</t>
+  </si>
+  <si>
+    <t>김소정</t>
+  </si>
+  <si>
+    <t>2025-08-26 11:48:55</t>
+  </si>
+  <si>
+    <t>차한</t>
+  </si>
+  <si>
+    <t>stylekpop7</t>
+  </si>
+  <si>
+    <t>대구 동구 동화천로 369 101동 205호</t>
+  </si>
+  <si>
+    <t>박소미</t>
+  </si>
+  <si>
+    <t>2025-08-26 12:00:12</t>
+  </si>
+  <si>
+    <t>김나예</t>
+  </si>
+  <si>
+    <t>crazy26</t>
+  </si>
+  <si>
+    <t>대구 북구 학남로 60 103동 409호</t>
+  </si>
+  <si>
+    <t>전현숙</t>
+  </si>
+  <si>
+    <t>2025-08-26 12:11:49</t>
+  </si>
+  <si>
+    <t>김유환</t>
+  </si>
+  <si>
+    <t>pianolegend2</t>
+  </si>
+  <si>
+    <t>대구 북구 동북로 241 202동 409호</t>
+  </si>
+  <si>
+    <t>남미경</t>
+  </si>
+  <si>
+    <t>2025-08-26 12:24:16</t>
+  </si>
+  <si>
+    <t>송정인</t>
+  </si>
+  <si>
+    <t>imaginationguit</t>
+  </si>
+  <si>
+    <t>대구 북구 학정동로 40 205동 507호</t>
+  </si>
+  <si>
+    <t>송성규</t>
+  </si>
+  <si>
+    <t>2025-08-26 12:39:09</t>
+  </si>
+  <si>
+    <t>김미소</t>
+  </si>
+  <si>
+    <t>champ13</t>
+  </si>
+  <si>
+    <t>대구 북구 내곡로 89 203동 501호</t>
+  </si>
+  <si>
+    <t>배미정</t>
+  </si>
+  <si>
+    <t>2025-08-26 12:54:17</t>
+  </si>
+  <si>
+    <t>황수안</t>
+  </si>
+  <si>
+    <t>tea9</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 97 103동 107호</t>
+  </si>
+  <si>
+    <t>황동석</t>
+  </si>
+  <si>
+    <t>2025-08-26 13:06:01</t>
+  </si>
+  <si>
+    <t>지예린</t>
+  </si>
+  <si>
+    <t>learning34</t>
+  </si>
+  <si>
+    <t>대구 북구 공항로 16 106동 405호</t>
+  </si>
+  <si>
+    <t>임소진</t>
+  </si>
+  <si>
+    <t>2025-08-26 13:17:59</t>
+  </si>
+  <si>
+    <t>임규린</t>
+  </si>
+  <si>
+    <t>hobbiesinventor</t>
+  </si>
+  <si>
+    <t>대구 북구 호암로 20 105동 201호</t>
+  </si>
+  <si>
+    <t>김소연</t>
+  </si>
+  <si>
+    <t>2025-08-26 13:33:23</t>
+  </si>
+  <si>
+    <t>김소망</t>
+  </si>
+  <si>
+    <t>patient1</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 156 103동 404호</t>
+  </si>
+  <si>
+    <t>김현정</t>
+  </si>
+  <si>
+    <t>2025-08-26 13:39:42</t>
+  </si>
+  <si>
+    <t>김다나</t>
+  </si>
+  <si>
+    <t>learnergirl</t>
+  </si>
+  <si>
+    <t>대구 북구 동변로 50 103동 406호</t>
+  </si>
+  <si>
+    <t>김준영</t>
+  </si>
+  <si>
+    <t>2025-08-26 13:51:48</t>
+  </si>
+  <si>
+    <t>전도건</t>
+  </si>
+  <si>
+    <t>technologyfacil</t>
+  </si>
+  <si>
+    <t>대구 북구 학남로 60 103동 302호</t>
+  </si>
+  <si>
+    <t>전현영</t>
+  </si>
+  <si>
+    <t>2025-08-26 14:02:27</t>
+  </si>
+  <si>
+    <t>박담희</t>
+  </si>
+  <si>
+    <t>explorerhyper2</t>
+  </si>
+  <si>
+    <t>대구 북구 매전로4길 9 212동 102호</t>
+  </si>
+  <si>
+    <t>박준규</t>
+  </si>
+  <si>
+    <t>2025-08-26 14:17:00</t>
+  </si>
+  <si>
+    <t>김한솔</t>
+  </si>
+  <si>
+    <t>negotiator00</t>
+  </si>
+  <si>
+    <t>대구 북구 매전로 50-42 202동 405호</t>
+  </si>
+  <si>
+    <t>김현준</t>
+  </si>
+  <si>
+    <t>2025-08-26 14:31:09</t>
+  </si>
+  <si>
+    <t>고예봄</t>
+  </si>
+  <si>
+    <t>health8</t>
+  </si>
+  <si>
+    <t>대구 북구 구리로 254 201동 302호</t>
+  </si>
+  <si>
+    <t>고동일</t>
+  </si>
+  <si>
+    <t>2025-08-26 14:43:13</t>
+  </si>
+  <si>
+    <t>문강</t>
+  </si>
+  <si>
+    <t>responsibility6</t>
+  </si>
+  <si>
+    <t>문형규</t>
+  </si>
+  <si>
+    <t>2025-08-26 14:55:09</t>
+  </si>
+  <si>
+    <t>이진아</t>
+  </si>
+  <si>
+    <t>doctorconnector</t>
+  </si>
+  <si>
+    <t>대구 북구 연경중앙로 55 204동 308호</t>
+  </si>
+  <si>
+    <t>이형민</t>
+  </si>
+  <si>
+    <t>2025-08-26 15:09:27</t>
+  </si>
+  <si>
+    <t>임규원</t>
+  </si>
+  <si>
+    <t>fashionistaexpe</t>
+  </si>
+  <si>
+    <t>대구 북구 공항로 16 106동 501호</t>
+  </si>
+  <si>
+    <t>이혜진</t>
+  </si>
+  <si>
+    <t>2025-08-26 15:23:00</t>
+  </si>
+  <si>
+    <t>이서하</t>
+  </si>
+  <si>
+    <t>sinceresuper</t>
+  </si>
+  <si>
+    <t>대구 북구 호암로 40 108동 505호</t>
+  </si>
+  <si>
+    <t>김지연</t>
+  </si>
+  <si>
+    <t>2025-08-26 15:38:25</t>
+  </si>
+  <si>
+    <t>안성하</t>
+  </si>
+  <si>
+    <t>discoverymindfu</t>
+  </si>
+  <si>
+    <t>대구 북구 동북로 241 201동 208호</t>
+  </si>
+  <si>
+    <t>남지혜</t>
+  </si>
+  <si>
+    <t>2025-08-26 15:39:08</t>
+  </si>
+  <si>
+    <t>이해솔</t>
+  </si>
+  <si>
+    <t>snatchedmax</t>
+  </si>
+  <si>
+    <t>대구 북구 공항로 16 108동 208호</t>
+  </si>
+  <si>
+    <t>이형도</t>
+  </si>
+  <si>
+    <t>2025-08-26 15:51:51</t>
+  </si>
+  <si>
+    <t>정은설</t>
+  </si>
+  <si>
+    <t>crashy63</t>
+  </si>
+  <si>
+    <t>대구 북구 내곡로 89 201동 204호</t>
+  </si>
+  <si>
+    <t>연민경</t>
+  </si>
+  <si>
+    <t>2025-08-26 16:06:33</t>
+  </si>
+  <si>
+    <t>신서은</t>
+  </si>
+  <si>
+    <t>loyaltymotivati</t>
+  </si>
+  <si>
+    <t>대구 북구 호암로 20 105동 505호</t>
+  </si>
+  <si>
+    <t>신은주</t>
+  </si>
+  <si>
+    <t>2025-08-26 16:46:08</t>
+  </si>
+  <si>
+    <t>박지용</t>
+  </si>
+  <si>
+    <t>smashjustice</t>
+  </si>
+  <si>
+    <t>박동윤</t>
+  </si>
+  <si>
+    <t>2025-08-26 17:00:18</t>
+  </si>
+  <si>
+    <t>이정안</t>
+  </si>
+  <si>
+    <t>photographyadve</t>
+  </si>
+  <si>
+    <t>대구 북구 공항로 16 106동 506호</t>
+  </si>
+  <si>
+    <t>이성호</t>
+  </si>
+  <si>
+    <t>2025-08-26 17:15:12</t>
+  </si>
+  <si>
+    <t>한재하</t>
+  </si>
+  <si>
+    <t>motivatedexplor</t>
+  </si>
+  <si>
+    <t>대구 북구 동천로 156 101동 504호</t>
+  </si>
+  <si>
+    <t>한동민</t>
+  </si>
+  <si>
+    <t>2025-08-26 17:27:03</t>
+  </si>
+  <si>
     <t>홍도형</t>
   </si>
   <si>
@@ -4308,9 +4887,6 @@
     <t>happyexplorer</t>
   </si>
   <si>
-    <t>대구 북구 매전로 50-42 202동 405호</t>
-  </si>
-  <si>
     <t>2025-06-12 11:05:42</t>
   </si>
   <si>
@@ -5427,9 +6003,6 @@
     <t>2025-06-24 16:50:22</t>
   </si>
   <si>
-    <t>박민석</t>
-  </si>
-  <si>
     <t>musicianshining</t>
   </si>
   <si>
@@ -6022,10 +6595,6 @@
   </si>
   <si>
     <t>2025-06-25 17:52:17</t>
-  </si>
-  <si>
-    <t>성동준</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -6375,7 +6944,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:H268"/>
   <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
@@ -10643,10 +11212,10 @@
     </row>
     <row r="183" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>2000</v>
+        <v>765</v>
       </c>
       <c r="B183" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="C183">
         <v>12</v>
@@ -10658,21 +11227,21 @@
         <v>652</v>
       </c>
       <c r="F183" t="s">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="G183" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="H183" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
     </row>
     <row r="184" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="B184" t="s">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="C184">
         <v>13</v>
@@ -10681,24 +11250,24 @@
         <v>21</v>
       </c>
       <c r="E184" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F184" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="G184" t="s">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="H184" t="s">
-        <v>774</v>
+        <v>775</v>
       </c>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="B185" t="s">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="C185">
         <v>11</v>
@@ -10707,24 +11276,24 @@
         <v>21</v>
       </c>
       <c r="E185" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F185" t="s">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="G185" t="s">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="H185" t="s">
-        <v>780</v>
+        <v>781</v>
       </c>
     </row>
     <row r="186" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="B186" t="s">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="C186">
         <v>11</v>
@@ -10733,24 +11302,24 @@
         <v>21</v>
       </c>
       <c r="E186" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F186" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="G186" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="H186" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
     </row>
     <row r="187" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="B187" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C187">
         <v>13</v>
@@ -10759,24 +11328,24 @@
         <v>10</v>
       </c>
       <c r="E187" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F187" t="s">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="G187" t="s">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="H187" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="B188" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C188">
         <v>13</v>
@@ -10788,21 +11357,21 @@
         <v>642</v>
       </c>
       <c r="F188" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="G188" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="H188" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
     </row>
     <row r="189" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B189" t="s">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="C189">
         <v>12</v>
@@ -10814,21 +11383,21 @@
         <v>642</v>
       </c>
       <c r="F189" t="s">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="G189" t="s">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="H189" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
     </row>
     <row r="190" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A190" t="s">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="B190" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C190">
         <v>12</v>
@@ -10837,24 +11406,24 @@
         <v>10</v>
       </c>
       <c r="E190" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F190" t="s">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="G190" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="H190" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A191" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B191" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="C191">
         <v>11</v>
@@ -10863,24 +11432,24 @@
         <v>21</v>
       </c>
       <c r="E191" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F191" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="G191" t="s">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="H191" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
     </row>
     <row r="192" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A192" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B192" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="C192">
         <v>11</v>
@@ -10892,21 +11461,21 @@
         <v>706</v>
       </c>
       <c r="F192" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="G192" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="H192" t="s">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A193" t="s">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="B193" t="s">
-        <v>818</v>
+        <v>819</v>
       </c>
       <c r="C193">
         <v>13</v>
@@ -10915,24 +11484,24 @@
         <v>21</v>
       </c>
       <c r="E193" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="F193" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="G193" t="s">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="H193" t="s">
-        <v>821</v>
+        <v>822</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A194" t="s">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="B194" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C194">
         <v>13</v>
@@ -10941,24 +11510,24 @@
         <v>21</v>
       </c>
       <c r="E194" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F194" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="G194" t="s">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="H194" t="s">
-        <v>826</v>
+        <v>827</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A195" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B195" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="C195">
         <v>12</v>
@@ -10967,24 +11536,24 @@
         <v>21</v>
       </c>
       <c r="E195" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F195" t="s">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="G195" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="H195" t="s">
-        <v>832</v>
+        <v>833</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A196" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B196" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="C196">
         <v>13</v>
@@ -10993,24 +11562,24 @@
         <v>21</v>
       </c>
       <c r="E196" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F196" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="G196" t="s">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="H196" t="s">
-        <v>837</v>
+        <v>838</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A197" t="s">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="B197" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="C197">
         <v>13</v>
@@ -11019,24 +11588,24 @@
         <v>10</v>
       </c>
       <c r="E197" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F197" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="G197" t="s">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="H197" t="s">
-        <v>842</v>
+        <v>843</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A198" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B198" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="C198">
         <v>11</v>
@@ -11045,24 +11614,24 @@
         <v>10</v>
       </c>
       <c r="E198" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F198" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="G198" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="H198" t="s">
-        <v>847</v>
+        <v>848</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A199" t="s">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="B199" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C199">
         <v>11</v>
@@ -11074,21 +11643,21 @@
         <v>685</v>
       </c>
       <c r="F199" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="G199" t="s">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="H199" t="s">
-        <v>852</v>
+        <v>853</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A200" t="s">
-        <v>853</v>
+        <v>854</v>
       </c>
       <c r="B200" t="s">
-        <v>854</v>
+        <v>855</v>
       </c>
       <c r="C200">
         <v>13</v>
@@ -11100,21 +11669,21 @@
         <v>58</v>
       </c>
       <c r="F200" t="s">
-        <v>855</v>
+        <v>856</v>
       </c>
       <c r="G200" t="s">
-        <v>856</v>
+        <v>857</v>
       </c>
       <c r="H200" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A201" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="B201" t="s">
-        <v>859</v>
+        <v>860</v>
       </c>
       <c r="C201">
         <v>13</v>
@@ -11126,21 +11695,21 @@
         <v>706</v>
       </c>
       <c r="F201" t="s">
-        <v>860</v>
+        <v>861</v>
       </c>
       <c r="G201" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="H201" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A202" t="s">
-        <v>863</v>
+        <v>864</v>
       </c>
       <c r="B202" t="s">
-        <v>864</v>
+        <v>865</v>
       </c>
       <c r="C202">
         <v>12</v>
@@ -11152,21 +11721,21 @@
         <v>685</v>
       </c>
       <c r="F202" t="s">
-        <v>865</v>
+        <v>866</v>
       </c>
       <c r="G202" t="s">
-        <v>866</v>
+        <v>867</v>
       </c>
       <c r="H202" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A203" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="B203" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="C203">
         <v>12</v>
@@ -11178,21 +11747,21 @@
         <v>658</v>
       </c>
       <c r="F203" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="G203" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="H203" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A204" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B204" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="C204">
         <v>11</v>
@@ -11204,21 +11773,21 @@
         <v>642</v>
       </c>
       <c r="F204" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="G204" t="s">
-        <v>876</v>
+        <v>877</v>
       </c>
       <c r="H204" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A205" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="B205" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="C205">
         <v>12</v>
@@ -11227,24 +11796,24 @@
         <v>21</v>
       </c>
       <c r="E205" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="F205" t="s">
-        <v>880</v>
+        <v>881</v>
       </c>
       <c r="G205" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="H205" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A206" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B206" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="C206">
         <v>12</v>
@@ -11256,21 +11825,21 @@
         <v>72</v>
       </c>
       <c r="F206" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="G206" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="H206" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A207" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B207" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="C207">
         <v>11</v>
@@ -11279,24 +11848,24 @@
         <v>21</v>
       </c>
       <c r="E207" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F207" t="s">
-        <v>890</v>
+        <v>891</v>
       </c>
       <c r="G207" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="H207" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A208" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B208" t="s">
-        <v>894</v>
+        <v>895</v>
       </c>
       <c r="C208">
         <v>12</v>
@@ -11305,24 +11874,24 @@
         <v>21</v>
       </c>
       <c r="E208" t="s">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="F208" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="G208" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="H208" t="s">
-        <v>897</v>
+        <v>898</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A209" t="s">
-        <v>898</v>
+        <v>899</v>
       </c>
       <c r="B209" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="C209">
         <v>13</v>
@@ -11337,18 +11906,18 @@
         <v>653</v>
       </c>
       <c r="G209" t="s">
-        <v>900</v>
+        <v>901</v>
       </c>
       <c r="H209" t="s">
-        <v>901</v>
+        <v>902</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A210" t="s">
-        <v>902</v>
+        <v>903</v>
       </c>
       <c r="B210" t="s">
-        <v>903</v>
+        <v>904</v>
       </c>
       <c r="C210">
         <v>13</v>
@@ -11360,21 +11929,21 @@
         <v>22</v>
       </c>
       <c r="F210" t="s">
-        <v>904</v>
+        <v>905</v>
       </c>
       <c r="G210" t="s">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="H210" t="s">
-        <v>906</v>
+        <v>907</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A211" t="s">
-        <v>907</v>
+        <v>908</v>
       </c>
       <c r="B211" t="s">
-        <v>908</v>
+        <v>909</v>
       </c>
       <c r="C211">
         <v>13</v>
@@ -11386,21 +11955,21 @@
         <v>27</v>
       </c>
       <c r="F211" t="s">
-        <v>909</v>
+        <v>910</v>
       </c>
       <c r="G211" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="H211" t="s">
-        <v>911</v>
+        <v>912</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A212" t="s">
-        <v>912</v>
+        <v>913</v>
       </c>
       <c r="B212" t="s">
-        <v>913</v>
+        <v>914</v>
       </c>
       <c r="C212">
         <v>11</v>
@@ -11412,21 +11981,21 @@
         <v>27</v>
       </c>
       <c r="F212" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="G212" t="s">
-        <v>915</v>
+        <v>916</v>
       </c>
       <c r="H212" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A213" t="s">
-        <v>917</v>
+        <v>918</v>
       </c>
       <c r="B213" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="C213">
         <v>12</v>
@@ -11438,21 +12007,21 @@
         <v>652</v>
       </c>
       <c r="F213" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="G213" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="H213" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A214" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B214" t="s">
-        <v>923</v>
+        <v>924</v>
       </c>
       <c r="C214">
         <v>13</v>
@@ -11464,21 +12033,21 @@
         <v>706</v>
       </c>
       <c r="F214" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="G214" t="s">
-        <v>925</v>
+        <v>926</v>
       </c>
       <c r="H214" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A215" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="B215" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="C215">
         <v>11</v>
@@ -11490,21 +12059,21 @@
         <v>706</v>
       </c>
       <c r="F215" t="s">
-        <v>929</v>
+        <v>930</v>
       </c>
       <c r="G215" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="H215" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A216" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B216" t="s">
-        <v>933</v>
+        <v>934</v>
       </c>
       <c r="C216">
         <v>12</v>
@@ -11516,21 +12085,21 @@
         <v>679</v>
       </c>
       <c r="F216" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="G216" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="H216" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A217" t="s">
-        <v>937</v>
+        <v>938</v>
       </c>
       <c r="B217" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="C217">
         <v>11</v>
@@ -11542,21 +12111,21 @@
         <v>642</v>
       </c>
       <c r="F217" t="s">
-        <v>939</v>
+        <v>940</v>
       </c>
       <c r="G217" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="H217" t="s">
-        <v>941</v>
+        <v>942</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A218" t="s">
-        <v>942</v>
+        <v>943</v>
       </c>
       <c r="B218" t="s">
-        <v>943</v>
+        <v>944</v>
       </c>
       <c r="C218">
         <v>11</v>
@@ -11568,21 +12137,21 @@
         <v>679</v>
       </c>
       <c r="F218" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="G218" t="s">
-        <v>945</v>
+        <v>946</v>
       </c>
       <c r="H218" t="s">
-        <v>946</v>
+        <v>947</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A219" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="B219" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="C219">
         <v>11</v>
@@ -11594,21 +12163,21 @@
         <v>679</v>
       </c>
       <c r="F219" t="s">
-        <v>949</v>
+        <v>950</v>
       </c>
       <c r="G219" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="H219" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A220" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B220" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="C220">
         <v>13</v>
@@ -11620,21 +12189,21 @@
         <v>22</v>
       </c>
       <c r="F220" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="G220" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="H220" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A221" t="s">
-        <v>957</v>
+        <v>958</v>
       </c>
       <c r="B221" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="C221">
         <v>11</v>
@@ -11646,21 +12215,21 @@
         <v>679</v>
       </c>
       <c r="F221" t="s">
-        <v>959</v>
+        <v>960</v>
       </c>
       <c r="G221" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="H221" t="s">
-        <v>961</v>
+        <v>962</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A222" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B222" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="C222">
         <v>12</v>
@@ -11672,21 +12241,21 @@
         <v>642</v>
       </c>
       <c r="F222" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="G222" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="H222" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A223" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="B223" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="C223">
         <v>11</v>
@@ -11698,21 +12267,21 @@
         <v>27</v>
       </c>
       <c r="F223" t="s">
-        <v>969</v>
+        <v>970</v>
       </c>
       <c r="G223" t="s">
-        <v>970</v>
+        <v>971</v>
       </c>
       <c r="H223" t="s">
-        <v>971</v>
+        <v>972</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A224" t="s">
-        <v>972</v>
+        <v>973</v>
       </c>
       <c r="B224" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="C224">
         <v>13</v>
@@ -11721,24 +12290,24 @@
         <v>10</v>
       </c>
       <c r="E224" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="F224" t="s">
-        <v>974</v>
+        <v>975</v>
       </c>
       <c r="G224" t="s">
-        <v>975</v>
+        <v>976</v>
       </c>
       <c r="H224" t="s">
-        <v>976</v>
+        <v>977</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A225" t="s">
-        <v>977</v>
+        <v>978</v>
       </c>
       <c r="B225" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="C225">
         <v>13</v>
@@ -11750,21 +12319,21 @@
         <v>72</v>
       </c>
       <c r="F225" t="s">
-        <v>979</v>
+        <v>980</v>
       </c>
       <c r="G225" t="s">
-        <v>980</v>
+        <v>981</v>
       </c>
       <c r="H225" t="s">
-        <v>981</v>
+        <v>982</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A226" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="B226" t="s">
-        <v>983</v>
+        <v>984</v>
       </c>
       <c r="C226">
         <v>11</v>
@@ -11776,21 +12345,21 @@
         <v>652</v>
       </c>
       <c r="F226" t="s">
-        <v>984</v>
+        <v>985</v>
       </c>
       <c r="G226" t="s">
-        <v>985</v>
+        <v>986</v>
       </c>
       <c r="H226" t="s">
-        <v>986</v>
+        <v>987</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A227" t="s">
-        <v>987</v>
+        <v>988</v>
       </c>
       <c r="B227" t="s">
-        <v>988</v>
+        <v>989</v>
       </c>
       <c r="C227">
         <v>12</v>
@@ -11802,21 +12371,21 @@
         <v>642</v>
       </c>
       <c r="F227" t="s">
-        <v>989</v>
+        <v>990</v>
       </c>
       <c r="G227" t="s">
-        <v>990</v>
+        <v>991</v>
       </c>
       <c r="H227" t="s">
-        <v>991</v>
+        <v>992</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A228" t="s">
-        <v>992</v>
+        <v>993</v>
       </c>
       <c r="B228" t="s">
-        <v>993</v>
+        <v>994</v>
       </c>
       <c r="C228">
         <v>13</v>
@@ -11828,21 +12397,21 @@
         <v>58</v>
       </c>
       <c r="F228" t="s">
-        <v>994</v>
+        <v>995</v>
       </c>
       <c r="G228" t="s">
-        <v>995</v>
+        <v>996</v>
       </c>
       <c r="H228" t="s">
-        <v>996</v>
+        <v>997</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.4">
       <c r="A229" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="B229" t="s">
-        <v>998</v>
+        <v>999</v>
       </c>
       <c r="C229">
         <v>11</v>
@@ -11854,19 +12423,1033 @@
         <v>685</v>
       </c>
       <c r="F229" t="s">
-        <v>999</v>
+        <v>1000</v>
       </c>
       <c r="G229" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="H229" t="s">
-        <v>1001</v>
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A230" t="s">
+        <v>1003</v>
+      </c>
+      <c r="B230" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C230">
+        <v>13</v>
+      </c>
+      <c r="D230" t="s">
+        <v>10</v>
+      </c>
+      <c r="E230" t="s">
+        <v>789</v>
+      </c>
+      <c r="F230" t="s">
+        <v>1005</v>
+      </c>
+      <c r="G230" t="s">
+        <v>1006</v>
+      </c>
+      <c r="H230" t="s">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A231" t="s">
+        <v>1008</v>
+      </c>
+      <c r="B231" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C231">
+        <v>11</v>
+      </c>
+      <c r="D231" t="s">
+        <v>10</v>
+      </c>
+      <c r="E231" t="s">
+        <v>772</v>
+      </c>
+      <c r="F231" t="s">
+        <v>1010</v>
+      </c>
+      <c r="G231" t="s">
+        <v>1011</v>
+      </c>
+      <c r="H231" t="s">
+        <v>1012</v>
+      </c>
+    </row>
+    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A232" t="s">
+        <v>1013</v>
+      </c>
+      <c r="B232" t="s">
+        <v>1014</v>
+      </c>
+      <c r="C232">
+        <v>11</v>
+      </c>
+      <c r="D232" t="s">
+        <v>10</v>
+      </c>
+      <c r="E232" t="s">
+        <v>830</v>
+      </c>
+      <c r="F232" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G232" t="s">
+        <v>1016</v>
+      </c>
+      <c r="H232" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A233" t="s">
+        <v>1018</v>
+      </c>
+      <c r="B233" t="s">
+        <v>1019</v>
+      </c>
+      <c r="C233">
+        <v>11</v>
+      </c>
+      <c r="D233" t="s">
+        <v>10</v>
+      </c>
+      <c r="E233" t="s">
+        <v>772</v>
+      </c>
+      <c r="F233" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G233" t="s">
+        <v>1021</v>
+      </c>
+      <c r="H233" t="s">
+        <v>1022</v>
+      </c>
+    </row>
+    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A234" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B234" t="s">
+        <v>1024</v>
+      </c>
+      <c r="C234">
+        <v>13</v>
+      </c>
+      <c r="D234" t="s">
+        <v>10</v>
+      </c>
+      <c r="E234" t="s">
+        <v>830</v>
+      </c>
+      <c r="F234" t="s">
+        <v>910</v>
+      </c>
+      <c r="G234" t="s">
+        <v>1025</v>
+      </c>
+      <c r="H234" t="s">
+        <v>1026</v>
+      </c>
+    </row>
+    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A235" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B235" t="s">
+        <v>1028</v>
+      </c>
+      <c r="C235">
+        <v>12</v>
+      </c>
+      <c r="D235" t="s">
+        <v>10</v>
+      </c>
+      <c r="E235" t="s">
+        <v>22</v>
+      </c>
+      <c r="F235" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G235" t="s">
+        <v>1030</v>
+      </c>
+      <c r="H235" t="s">
+        <v>1031</v>
+      </c>
+    </row>
+    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A236" t="s">
+        <v>1032</v>
+      </c>
+      <c r="B236" t="s">
+        <v>1033</v>
+      </c>
+      <c r="C236">
+        <v>11</v>
+      </c>
+      <c r="D236" t="s">
+        <v>21</v>
+      </c>
+      <c r="E236" t="s">
+        <v>642</v>
+      </c>
+      <c r="F236" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G236" t="s">
+        <v>1035</v>
+      </c>
+      <c r="H236" t="s">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A237" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B237" t="s">
+        <v>1038</v>
+      </c>
+      <c r="C237">
+        <v>11</v>
+      </c>
+      <c r="D237" t="s">
+        <v>10</v>
+      </c>
+      <c r="E237" t="s">
+        <v>685</v>
+      </c>
+      <c r="F237" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G237" t="s">
+        <v>1040</v>
+      </c>
+      <c r="H237" t="s">
+        <v>1041</v>
+      </c>
+    </row>
+    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A238" t="s">
+        <v>1042</v>
+      </c>
+      <c r="B238" t="s">
+        <v>1043</v>
+      </c>
+      <c r="C238">
+        <v>13</v>
+      </c>
+      <c r="D238" t="s">
+        <v>21</v>
+      </c>
+      <c r="E238" t="s">
+        <v>22</v>
+      </c>
+      <c r="F238" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G238" t="s">
+        <v>1045</v>
+      </c>
+      <c r="H238" t="s">
+        <v>1046</v>
+      </c>
+    </row>
+    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A239" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B239" t="s">
+        <v>1048</v>
+      </c>
+      <c r="C239">
+        <v>12</v>
+      </c>
+      <c r="D239" t="s">
+        <v>21</v>
+      </c>
+      <c r="E239" t="s">
+        <v>642</v>
+      </c>
+      <c r="F239" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G239" t="s">
+        <v>1050</v>
+      </c>
+      <c r="H239" t="s">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A240" t="s">
+        <v>1052</v>
+      </c>
+      <c r="B240" t="s">
+        <v>1053</v>
+      </c>
+      <c r="C240">
+        <v>12</v>
+      </c>
+      <c r="D240" t="s">
+        <v>21</v>
+      </c>
+      <c r="E240" t="s">
+        <v>778</v>
+      </c>
+      <c r="F240" t="s">
+        <v>1054</v>
+      </c>
+      <c r="G240" t="s">
+        <v>1055</v>
+      </c>
+      <c r="H240" t="s">
+        <v>1056</v>
+      </c>
+    </row>
+    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A241" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B241" t="s">
+        <v>1058</v>
+      </c>
+      <c r="C241">
+        <v>11</v>
+      </c>
+      <c r="D241" t="s">
+        <v>10</v>
+      </c>
+      <c r="E241" t="s">
+        <v>679</v>
+      </c>
+      <c r="F241" t="s">
+        <v>1059</v>
+      </c>
+      <c r="G241" t="s">
+        <v>1060</v>
+      </c>
+      <c r="H241" t="s">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A242" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B242" t="s">
+        <v>1063</v>
+      </c>
+      <c r="C242">
+        <v>12</v>
+      </c>
+      <c r="D242" t="s">
+        <v>10</v>
+      </c>
+      <c r="E242" t="s">
+        <v>778</v>
+      </c>
+      <c r="F242" t="s">
+        <v>1064</v>
+      </c>
+      <c r="G242" t="s">
+        <v>1065</v>
+      </c>
+      <c r="H242" t="s">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A243" t="s">
+        <v>1067</v>
+      </c>
+      <c r="B243" t="s">
+        <v>1068</v>
+      </c>
+      <c r="C243">
+        <v>11</v>
+      </c>
+      <c r="D243" t="s">
+        <v>10</v>
+      </c>
+      <c r="E243" t="s">
+        <v>679</v>
+      </c>
+      <c r="F243" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G243" t="s">
+        <v>1070</v>
+      </c>
+      <c r="H243" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A244" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B244" t="s">
+        <v>1073</v>
+      </c>
+      <c r="C244">
+        <v>13</v>
+      </c>
+      <c r="D244" t="s">
+        <v>10</v>
+      </c>
+      <c r="E244" t="s">
+        <v>642</v>
+      </c>
+      <c r="F244" t="s">
+        <v>1074</v>
+      </c>
+      <c r="G244" t="s">
+        <v>1075</v>
+      </c>
+      <c r="H244" t="s">
+        <v>1076</v>
+      </c>
+    </row>
+    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A245" t="s">
+        <v>1077</v>
+      </c>
+      <c r="B245" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C245">
+        <v>13</v>
+      </c>
+      <c r="D245" t="s">
+        <v>10</v>
+      </c>
+      <c r="E245" t="s">
+        <v>830</v>
+      </c>
+      <c r="F245" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G245" t="s">
+        <v>1080</v>
+      </c>
+      <c r="H245" t="s">
+        <v>1081</v>
+      </c>
+    </row>
+    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A246" t="s">
+        <v>1082</v>
+      </c>
+      <c r="B246" t="s">
+        <v>1083</v>
+      </c>
+      <c r="C246">
+        <v>13</v>
+      </c>
+      <c r="D246" t="s">
+        <v>21</v>
+      </c>
+      <c r="E246" t="s">
+        <v>72</v>
+      </c>
+      <c r="F246" t="s">
+        <v>1084</v>
+      </c>
+      <c r="G246" t="s">
+        <v>1085</v>
+      </c>
+      <c r="H246" t="s">
+        <v>1086</v>
+      </c>
+    </row>
+    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A247" t="s">
+        <v>1087</v>
+      </c>
+      <c r="B247" t="s">
+        <v>1088</v>
+      </c>
+      <c r="C247">
+        <v>12</v>
+      </c>
+      <c r="D247" t="s">
+        <v>10</v>
+      </c>
+      <c r="E247" t="s">
+        <v>706</v>
+      </c>
+      <c r="F247" t="s">
+        <v>1089</v>
+      </c>
+      <c r="G247" t="s">
+        <v>1090</v>
+      </c>
+      <c r="H247" t="s">
+        <v>1091</v>
+      </c>
+    </row>
+    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A248" t="s">
+        <v>1092</v>
+      </c>
+      <c r="B248" t="s">
+        <v>1093</v>
+      </c>
+      <c r="C248">
+        <v>13</v>
+      </c>
+      <c r="D248" t="s">
+        <v>21</v>
+      </c>
+      <c r="E248" t="s">
+        <v>658</v>
+      </c>
+      <c r="F248" t="s">
+        <v>1094</v>
+      </c>
+      <c r="G248" t="s">
+        <v>1095</v>
+      </c>
+      <c r="H248" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A249" t="s">
+        <v>1097</v>
+      </c>
+      <c r="B249" t="s">
+        <v>1098</v>
+      </c>
+      <c r="C249">
+        <v>13</v>
+      </c>
+      <c r="D249" t="s">
+        <v>10</v>
+      </c>
+      <c r="E249" t="s">
+        <v>679</v>
+      </c>
+      <c r="F249" t="s">
+        <v>1099</v>
+      </c>
+      <c r="G249" t="s">
+        <v>1100</v>
+      </c>
+      <c r="H249" t="s">
+        <v>1101</v>
+      </c>
+    </row>
+    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A250" t="s">
+        <v>1102</v>
+      </c>
+      <c r="B250" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C250">
+        <v>13</v>
+      </c>
+      <c r="D250" t="s">
+        <v>10</v>
+      </c>
+      <c r="E250" t="s">
+        <v>72</v>
+      </c>
+      <c r="F250" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G250" t="s">
+        <v>1105</v>
+      </c>
+      <c r="H250" t="s">
+        <v>1106</v>
+      </c>
+    </row>
+    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A251" t="s">
+        <v>1107</v>
+      </c>
+      <c r="B251" t="s">
+        <v>1108</v>
+      </c>
+      <c r="C251">
+        <v>12</v>
+      </c>
+      <c r="D251" t="s">
+        <v>21</v>
+      </c>
+      <c r="E251" t="s">
+        <v>772</v>
+      </c>
+      <c r="F251" t="s">
+        <v>1109</v>
+      </c>
+      <c r="G251" t="s">
+        <v>1110</v>
+      </c>
+      <c r="H251" t="s">
+        <v>1111</v>
+      </c>
+    </row>
+    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A252" t="s">
+        <v>1112</v>
+      </c>
+      <c r="B252" t="s">
+        <v>1113</v>
+      </c>
+      <c r="C252">
+        <v>11</v>
+      </c>
+      <c r="D252" t="s">
+        <v>10</v>
+      </c>
+      <c r="E252" t="s">
+        <v>679</v>
+      </c>
+      <c r="F252" t="s">
+        <v>1114</v>
+      </c>
+      <c r="G252" t="s">
+        <v>1115</v>
+      </c>
+      <c r="H252" t="s">
+        <v>1116</v>
+      </c>
+    </row>
+    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A253" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B253" t="s">
+        <v>1118</v>
+      </c>
+      <c r="C253">
+        <v>11</v>
+      </c>
+      <c r="D253" t="s">
+        <v>21</v>
+      </c>
+      <c r="E253" t="s">
+        <v>685</v>
+      </c>
+      <c r="F253" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G253" t="s">
+        <v>1120</v>
+      </c>
+      <c r="H253" t="s">
+        <v>1121</v>
+      </c>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A254" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B254" t="s">
+        <v>1123</v>
+      </c>
+      <c r="C254">
+        <v>11</v>
+      </c>
+      <c r="D254" t="s">
+        <v>21</v>
+      </c>
+      <c r="E254" t="s">
+        <v>830</v>
+      </c>
+      <c r="F254" t="s">
+        <v>1124</v>
+      </c>
+      <c r="G254" t="s">
+        <v>1125</v>
+      </c>
+      <c r="H254" t="s">
+        <v>1126</v>
+      </c>
+    </row>
+    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A255" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B255" t="s">
+        <v>1128</v>
+      </c>
+      <c r="C255">
+        <v>11</v>
+      </c>
+      <c r="D255" t="s">
+        <v>21</v>
+      </c>
+      <c r="E255" t="s">
+        <v>58</v>
+      </c>
+      <c r="F255" t="s">
+        <v>1129</v>
+      </c>
+      <c r="G255" t="s">
+        <v>1130</v>
+      </c>
+      <c r="H255" t="s">
+        <v>1131</v>
+      </c>
+    </row>
+    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A256" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B256" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C256">
+        <v>11</v>
+      </c>
+      <c r="D256" t="s">
+        <v>10</v>
+      </c>
+      <c r="E256" t="s">
+        <v>58</v>
+      </c>
+      <c r="F256" t="s">
+        <v>1134</v>
+      </c>
+      <c r="G256" t="s">
+        <v>1135</v>
+      </c>
+      <c r="H256" t="s">
+        <v>1136</v>
+      </c>
+    </row>
+    <row r="257" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A257" t="s">
+        <v>1137</v>
+      </c>
+      <c r="B257" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C257">
+        <v>13</v>
+      </c>
+      <c r="D257" t="s">
+        <v>21</v>
+      </c>
+      <c r="E257" t="s">
+        <v>778</v>
+      </c>
+      <c r="F257" t="s">
+        <v>1139</v>
+      </c>
+      <c r="G257" t="s">
+        <v>1140</v>
+      </c>
+      <c r="H257" t="s">
+        <v>1141</v>
+      </c>
+    </row>
+    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A258" t="s">
+        <v>1142</v>
+      </c>
+      <c r="B258" t="s">
+        <v>1143</v>
+      </c>
+      <c r="C258">
+        <v>12</v>
+      </c>
+      <c r="D258" t="s">
+        <v>10</v>
+      </c>
+      <c r="E258" t="s">
+        <v>830</v>
+      </c>
+      <c r="F258" t="s">
+        <v>935</v>
+      </c>
+      <c r="G258" t="s">
+        <v>1144</v>
+      </c>
+      <c r="H258" t="s">
+        <v>1145</v>
+      </c>
+    </row>
+    <row r="259" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A259" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B259" t="s">
+        <v>1147</v>
+      </c>
+      <c r="C259">
+        <v>11</v>
+      </c>
+      <c r="D259" t="s">
+        <v>10</v>
+      </c>
+      <c r="E259" t="s">
+        <v>642</v>
+      </c>
+      <c r="F259" t="s">
+        <v>1148</v>
+      </c>
+      <c r="G259" t="s">
+        <v>1149</v>
+      </c>
+      <c r="H259" t="s">
+        <v>1150</v>
+      </c>
+    </row>
+    <row r="260" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A260" t="s">
+        <v>1151</v>
+      </c>
+      <c r="B260" t="s">
+        <v>1152</v>
+      </c>
+      <c r="C260">
+        <v>11</v>
+      </c>
+      <c r="D260" t="s">
+        <v>10</v>
+      </c>
+      <c r="E260" t="s">
+        <v>72</v>
+      </c>
+      <c r="F260" t="s">
+        <v>1153</v>
+      </c>
+      <c r="G260" t="s">
+        <v>1154</v>
+      </c>
+      <c r="H260" t="s">
+        <v>1155</v>
+      </c>
+    </row>
+    <row r="261" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A261" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B261" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C261">
+        <v>13</v>
+      </c>
+      <c r="D261" t="s">
+        <v>10</v>
+      </c>
+      <c r="E261" t="s">
+        <v>772</v>
+      </c>
+      <c r="F261" t="s">
+        <v>1158</v>
+      </c>
+      <c r="G261" t="s">
+        <v>1159</v>
+      </c>
+      <c r="H261" t="s">
+        <v>1160</v>
+      </c>
+    </row>
+    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A262" t="s">
+        <v>1161</v>
+      </c>
+      <c r="B262" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C262">
+        <v>12</v>
+      </c>
+      <c r="D262" t="s">
+        <v>10</v>
+      </c>
+      <c r="E262" t="s">
+        <v>72</v>
+      </c>
+      <c r="F262" t="s">
+        <v>1163</v>
+      </c>
+      <c r="G262" t="s">
+        <v>1164</v>
+      </c>
+      <c r="H262" t="s">
+        <v>1165</v>
+      </c>
+    </row>
+    <row r="263" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A263" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B263" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C263">
+        <v>12</v>
+      </c>
+      <c r="D263" t="s">
+        <v>10</v>
+      </c>
+      <c r="E263" t="s">
+        <v>72</v>
+      </c>
+      <c r="F263" t="s">
+        <v>1168</v>
+      </c>
+      <c r="G263" t="s">
+        <v>1169</v>
+      </c>
+      <c r="H263" t="s">
+        <v>1170</v>
+      </c>
+    </row>
+    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A264" t="s">
+        <v>1171</v>
+      </c>
+      <c r="B264" t="s">
+        <v>1172</v>
+      </c>
+      <c r="C264">
+        <v>11</v>
+      </c>
+      <c r="D264" t="s">
+        <v>10</v>
+      </c>
+      <c r="E264" t="s">
+        <v>789</v>
+      </c>
+      <c r="F264" t="s">
+        <v>1173</v>
+      </c>
+      <c r="G264" t="s">
+        <v>1174</v>
+      </c>
+      <c r="H264" t="s">
+        <v>1175</v>
+      </c>
+    </row>
+    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A265" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B265" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C265">
+        <v>11</v>
+      </c>
+      <c r="D265" t="s">
+        <v>10</v>
+      </c>
+      <c r="E265" t="s">
+        <v>772</v>
+      </c>
+      <c r="F265" t="s">
+        <v>1178</v>
+      </c>
+      <c r="G265" t="s">
+        <v>1179</v>
+      </c>
+      <c r="H265" t="s">
+        <v>1180</v>
+      </c>
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A266" t="s">
+        <v>1181</v>
+      </c>
+      <c r="B266" t="s">
+        <v>1182</v>
+      </c>
+      <c r="C266">
+        <v>12</v>
+      </c>
+      <c r="D266" t="s">
+        <v>21</v>
+      </c>
+      <c r="E266" t="s">
+        <v>679</v>
+      </c>
+      <c r="F266" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G266" t="s">
+        <v>1183</v>
+      </c>
+      <c r="H266" t="s">
+        <v>1184</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A267" t="s">
+        <v>1185</v>
+      </c>
+      <c r="B267" t="s">
+        <v>1186</v>
+      </c>
+      <c r="C267">
+        <v>11</v>
+      </c>
+      <c r="D267" t="s">
+        <v>21</v>
+      </c>
+      <c r="E267" t="s">
+        <v>72</v>
+      </c>
+      <c r="F267" t="s">
+        <v>1187</v>
+      </c>
+      <c r="G267" t="s">
+        <v>1188</v>
+      </c>
+      <c r="H267" t="s">
+        <v>1189</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
+      <c r="A268" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B268" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C268">
+        <v>11</v>
+      </c>
+      <c r="D268" t="s">
+        <v>21</v>
+      </c>
+      <c r="E268" t="s">
+        <v>679</v>
+      </c>
+      <c r="F268" t="s">
+        <v>1192</v>
+      </c>
+      <c r="G268" t="s">
+        <v>1193</v>
+      </c>
+      <c r="H268" t="s">
+        <v>1194</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11904,1451 +13487,1451 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" s="1" t="s">
-        <v>1002</v>
+        <v>1195</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1003</v>
+        <v>1196</v>
       </c>
       <c r="C2" s="1">
         <v>11</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1005</v>
+        <v>1198</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1006</v>
+        <v>1199</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" s="1" t="s">
-        <v>1007</v>
+        <v>1200</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1008</v>
+        <v>1201</v>
       </c>
       <c r="C3" s="1">
         <v>12</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1010</v>
+        <v>1203</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1011</v>
+        <v>1204</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" s="1" t="s">
-        <v>1012</v>
+        <v>1205</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1013</v>
+        <v>1206</v>
       </c>
       <c r="C4" s="1">
         <v>11</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1015</v>
+        <v>1208</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1016</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" s="1" t="s">
-        <v>1017</v>
+        <v>1210</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1018</v>
+        <v>1211</v>
       </c>
       <c r="C5" s="1">
         <v>13</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1020</v>
+        <v>1213</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1021</v>
+        <v>1214</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" s="1" t="s">
-        <v>1022</v>
+        <v>1215</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1023</v>
+        <v>1216</v>
       </c>
       <c r="C6" s="1">
         <v>13</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1025</v>
+        <v>1218</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1026</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" s="1" t="s">
-        <v>1027</v>
+        <v>1220</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1028</v>
+        <v>1221</v>
       </c>
       <c r="C7" s="1">
         <v>11</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1030</v>
+        <v>1223</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1031</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" s="1" t="s">
-        <v>1032</v>
+        <v>1225</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1033</v>
+        <v>1226</v>
       </c>
       <c r="C8" s="1">
         <v>13</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1035</v>
+        <v>1228</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1036</v>
+        <v>1229</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" s="1" t="s">
-        <v>1037</v>
+        <v>1230</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1038</v>
+        <v>1231</v>
       </c>
       <c r="C9" s="1">
         <v>12</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>1039</v>
+        <v>1232</v>
       </c>
       <c r="G9" s="1" t="s">
-        <v>1040</v>
+        <v>1233</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" s="1" t="s">
-        <v>1041</v>
+        <v>1234</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1042</v>
+        <v>1235</v>
       </c>
       <c r="C10" s="1">
         <v>12</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1044</v>
+        <v>1237</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1045</v>
+        <v>1238</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A11" s="1" t="s">
-        <v>1046</v>
+        <v>1239</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1047</v>
+        <v>1240</v>
       </c>
       <c r="C11" s="1">
         <v>13</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1048</v>
+        <v>1241</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1049</v>
+        <v>1242</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" s="1" t="s">
-        <v>1050</v>
+        <v>1243</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1051</v>
+        <v>1244</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1053</v>
+        <v>1246</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1054</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" s="1" t="s">
-        <v>1055</v>
+        <v>1248</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1056</v>
+        <v>1249</v>
       </c>
       <c r="C13" s="1">
         <v>13</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1057</v>
+        <v>1250</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1058</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" s="1" t="s">
-        <v>1059</v>
+        <v>1252</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1060</v>
+        <v>1253</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1061</v>
+        <v>1254</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1062</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" s="1" t="s">
-        <v>1063</v>
+        <v>1256</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1064</v>
+        <v>1257</v>
       </c>
       <c r="C15" s="1">
         <v>13</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>1065</v>
+        <v>1258</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1066</v>
+        <v>1259</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1067</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" s="1" t="s">
-        <v>1068</v>
+        <v>1261</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1069</v>
+        <v>1262</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1070</v>
+        <v>1263</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1071</v>
+        <v>1264</v>
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A17" s="1" t="s">
-        <v>1072</v>
+        <v>1265</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1073</v>
+        <v>1266</v>
       </c>
       <c r="C17" s="1">
         <v>13</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1074</v>
+        <v>1267</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1075</v>
+        <v>1268</v>
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A18" s="1" t="s">
-        <v>1076</v>
+        <v>1269</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1077</v>
+        <v>1270</v>
       </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1078</v>
+        <v>1271</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1079</v>
+        <v>1272</v>
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A19" s="1" t="s">
-        <v>1080</v>
+        <v>1273</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1081</v>
+        <v>1274</v>
       </c>
       <c r="C19" s="1">
         <v>11</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1082</v>
+        <v>1275</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1083</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A20" s="1" t="s">
-        <v>1084</v>
+        <v>1277</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1085</v>
+        <v>1278</v>
       </c>
       <c r="C20" s="1">
         <v>13</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1086</v>
+        <v>1279</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1087</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A21" s="1" t="s">
-        <v>1088</v>
+        <v>1281</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1089</v>
+        <v>1282</v>
       </c>
       <c r="C21" s="1">
         <v>13</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1090</v>
+        <v>1283</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1091</v>
+        <v>1284</v>
       </c>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A22" s="1" t="s">
-        <v>1092</v>
+        <v>1285</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1093</v>
+        <v>1286</v>
       </c>
       <c r="C22" s="1">
         <v>12</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1094</v>
+        <v>1287</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1095</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A23" s="1" t="s">
-        <v>1096</v>
+        <v>1289</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1097</v>
+        <v>1290</v>
       </c>
       <c r="C23" s="1">
         <v>13</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1098</v>
+        <v>1291</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1099</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A24" s="1" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1100</v>
+        <v>1293</v>
       </c>
       <c r="C24" s="1">
         <v>11</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1101</v>
+        <v>1294</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1102</v>
+        <v>1295</v>
       </c>
     </row>
     <row r="25" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A25" s="1" t="s">
-        <v>1103</v>
+        <v>1296</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1104</v>
+        <v>1297</v>
       </c>
       <c r="C25" s="1">
         <v>13</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1105</v>
+        <v>1298</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1106</v>
+        <v>1299</v>
       </c>
     </row>
     <row r="26" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A26" s="1" t="s">
-        <v>1107</v>
+        <v>1300</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1108</v>
+        <v>1301</v>
       </c>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1109</v>
+        <v>1302</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1110</v>
+        <v>1303</v>
       </c>
     </row>
     <row r="27" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A27" s="1" t="s">
-        <v>1111</v>
+        <v>1304</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1112</v>
+        <v>1305</v>
       </c>
       <c r="C27" s="1">
         <v>12</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1113</v>
+        <v>1306</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1114</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="28" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A28" s="1" t="s">
-        <v>1115</v>
+        <v>1308</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1116</v>
+        <v>1309</v>
       </c>
       <c r="C28" s="1">
         <v>13</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1117</v>
+        <v>1310</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1118</v>
+        <v>1311</v>
       </c>
     </row>
     <row r="29" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A29" s="1" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1119</v>
+        <v>1312</v>
       </c>
       <c r="C29" s="1">
         <v>11</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1120</v>
+        <v>1313</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1121</v>
+        <v>1314</v>
       </c>
     </row>
     <row r="30" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A30" s="1" t="s">
-        <v>1122</v>
+        <v>1315</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1123</v>
+        <v>1316</v>
       </c>
       <c r="C30" s="1">
         <v>11</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1124</v>
+        <v>1317</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1125</v>
+        <v>1318</v>
       </c>
     </row>
     <row r="31" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A31" s="1" t="s">
-        <v>1126</v>
+        <v>1319</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1127</v>
+        <v>1320</v>
       </c>
       <c r="C31" s="1">
         <v>11</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1128</v>
+        <v>1321</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1129</v>
+        <v>1322</v>
       </c>
     </row>
     <row r="32" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A32" s="1" t="s">
-        <v>1130</v>
+        <v>1323</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1131</v>
+        <v>1324</v>
       </c>
       <c r="C32" s="1">
         <v>11</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1132</v>
+        <v>1325</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1133</v>
+        <v>1326</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" s="1" t="s">
-        <v>1134</v>
+        <v>1327</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1135</v>
+        <v>1328</v>
       </c>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1136</v>
+        <v>1329</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1137</v>
+        <v>1330</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" s="1" t="s">
-        <v>1138</v>
+        <v>1331</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1139</v>
+        <v>1332</v>
       </c>
       <c r="C34" s="1">
         <v>11</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1140</v>
+        <v>1333</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1141</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" s="1" t="s">
-        <v>1142</v>
+        <v>1335</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1143</v>
+        <v>1336</v>
       </c>
       <c r="C35" s="1">
         <v>13</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1144</v>
+        <v>1337</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1145</v>
+        <v>1338</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" s="1" t="s">
-        <v>1146</v>
+        <v>1339</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1147</v>
+        <v>1340</v>
       </c>
       <c r="C36" s="1">
         <v>11</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1148</v>
+        <v>1341</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1149</v>
+        <v>1342</v>
       </c>
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" s="1" t="s">
-        <v>1150</v>
+        <v>1343</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1151</v>
+        <v>1344</v>
       </c>
       <c r="C37" s="1">
         <v>11</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1152</v>
+        <v>1345</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1153</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" s="1" t="s">
-        <v>1154</v>
+        <v>1347</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1155</v>
+        <v>1348</v>
       </c>
       <c r="C38" s="1">
         <v>12</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1156</v>
+        <v>1349</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1157</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" s="1" t="s">
-        <v>1158</v>
+        <v>1351</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1159</v>
+        <v>1352</v>
       </c>
       <c r="C39" s="1">
         <v>12</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1160</v>
+        <v>1353</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1161</v>
+        <v>1354</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" s="1" t="s">
-        <v>1162</v>
+        <v>1355</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1163</v>
+        <v>1356</v>
       </c>
       <c r="C40" s="1">
         <v>12</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1164</v>
+        <v>1357</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1165</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" s="1" t="s">
-        <v>1166</v>
+        <v>1359</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1167</v>
+        <v>1360</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1168</v>
+        <v>1361</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1169</v>
+        <v>1362</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" s="1" t="s">
-        <v>1170</v>
+        <v>1363</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1171</v>
+        <v>1364</v>
       </c>
       <c r="C42" s="1">
         <v>13</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1172</v>
+        <v>1365</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1173</v>
+        <v>1366</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" s="1" t="s">
-        <v>1174</v>
+        <v>1367</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1175</v>
+        <v>1368</v>
       </c>
       <c r="C43" s="1">
         <v>13</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1176</v>
+        <v>1369</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1177</v>
+        <v>1370</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" s="1" t="s">
-        <v>1178</v>
+        <v>1371</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1179</v>
+        <v>1372</v>
       </c>
       <c r="C44" s="1">
         <v>13</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1180</v>
+        <v>1373</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1181</v>
+        <v>1374</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" s="1" t="s">
-        <v>1182</v>
+        <v>1375</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1183</v>
+        <v>1376</v>
       </c>
       <c r="C45" s="1">
         <v>13</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1184</v>
+        <v>1377</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1185</v>
+        <v>1378</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" s="1" t="s">
-        <v>1186</v>
+        <v>1379</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1187</v>
+        <v>1380</v>
       </c>
       <c r="C46" s="1">
         <v>13</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1188</v>
+        <v>1381</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1189</v>
+        <v>1382</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" s="1" t="s">
-        <v>1190</v>
+        <v>1383</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1191</v>
+        <v>1384</v>
       </c>
       <c r="C47" s="1">
         <v>11</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1192</v>
+        <v>1385</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1193</v>
+        <v>1386</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" s="1" t="s">
-        <v>1194</v>
+        <v>1387</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1195</v>
+        <v>1388</v>
       </c>
       <c r="C48" s="1">
         <v>12</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1196</v>
+        <v>1389</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1197</v>
+        <v>1390</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" s="1" t="s">
-        <v>1198</v>
+        <v>1391</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1199</v>
+        <v>1392</v>
       </c>
       <c r="C49" s="1">
         <v>13</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1200</v>
+        <v>1393</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1201</v>
+        <v>1394</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" s="1" t="s">
-        <v>1202</v>
+        <v>1395</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1203</v>
+        <v>1396</v>
       </c>
       <c r="C50" s="1">
         <v>12</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1204</v>
+        <v>1397</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1205</v>
+        <v>1398</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" s="1" t="s">
-        <v>1206</v>
+        <v>1399</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1207</v>
+        <v>1400</v>
       </c>
       <c r="C51" s="1">
         <v>13</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1208</v>
+        <v>1401</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1209</v>
+        <v>1402</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" s="1" t="s">
-        <v>1210</v>
+        <v>1403</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1211</v>
+        <v>1404</v>
       </c>
       <c r="C52" s="1">
         <v>13</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1212</v>
+        <v>1405</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1213</v>
+        <v>1406</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" s="1" t="s">
-        <v>1214</v>
+        <v>1407</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1215</v>
+        <v>1408</v>
       </c>
       <c r="C53" s="1">
         <v>11</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1216</v>
+        <v>1409</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1217</v>
+        <v>1410</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" s="1" t="s">
-        <v>1218</v>
+        <v>1411</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1219</v>
+        <v>1412</v>
       </c>
       <c r="C54" s="1">
         <v>13</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1220</v>
+        <v>1413</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1221</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" s="1" t="s">
-        <v>1222</v>
+        <v>1415</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1223</v>
+        <v>1416</v>
       </c>
       <c r="C55" s="1">
         <v>11</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1224</v>
+        <v>1417</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1225</v>
+        <v>1418</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" s="1" t="s">
-        <v>1226</v>
+        <v>1419</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1227</v>
+        <v>1420</v>
       </c>
       <c r="C56" s="1">
         <v>13</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1228</v>
+        <v>1421</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1229</v>
+        <v>1422</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" s="1" t="s">
-        <v>1230</v>
+        <v>1423</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1231</v>
+        <v>1424</v>
       </c>
       <c r="C57" s="1">
         <v>13</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1232</v>
+        <v>1425</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1233</v>
+        <v>1426</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" s="1" t="s">
-        <v>1234</v>
+        <v>1427</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1235</v>
+        <v>1428</v>
       </c>
       <c r="C58" s="1">
         <v>13</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1236</v>
+        <v>1429</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1237</v>
+        <v>1430</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" s="1" t="s">
-        <v>1238</v>
+        <v>1431</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1239</v>
+        <v>1432</v>
       </c>
       <c r="C59" s="1">
         <v>12</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1240</v>
+        <v>1433</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1241</v>
+        <v>1434</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" s="1" t="s">
-        <v>1242</v>
+        <v>1435</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1243</v>
+        <v>1436</v>
       </c>
       <c r="C60" s="1">
         <v>13</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1244</v>
+        <v>1437</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1245</v>
+        <v>1438</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" s="1" t="s">
-        <v>1246</v>
+        <v>1439</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1247</v>
+        <v>1440</v>
       </c>
       <c r="C61" s="1">
         <v>13</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1248</v>
+        <v>1441</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1249</v>
+        <v>1442</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" s="1" t="s">
-        <v>1250</v>
+        <v>1443</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1251</v>
+        <v>1444</v>
       </c>
       <c r="C62" s="1">
         <v>11</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1252</v>
+        <v>1445</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1253</v>
+        <v>1446</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" s="1" t="s">
-        <v>1254</v>
+        <v>1447</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1255</v>
+        <v>1448</v>
       </c>
       <c r="C63" s="1">
         <v>11</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1256</v>
+        <v>1449</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1257</v>
+        <v>1450</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" s="1" t="s">
-        <v>1258</v>
+        <v>1451</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1259</v>
+        <v>1452</v>
       </c>
       <c r="C64" s="1">
         <v>13</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1061</v>
+        <v>1254</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1260</v>
+        <v>1453</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" s="1" t="s">
-        <v>1261</v>
+        <v>1454</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1262</v>
+        <v>1455</v>
       </c>
       <c r="C65" s="1">
         <v>13</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
-        <v>1052</v>
+        <v>1245</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1263</v>
+        <v>1456</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1264</v>
+        <v>1457</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" s="1" t="s">
-        <v>1265</v>
+        <v>1458</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1266</v>
+        <v>1459</v>
       </c>
       <c r="C66" s="1">
         <v>11</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1267</v>
+        <v>1460</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1268</v>
+        <v>1461</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" s="1" t="s">
-        <v>1269</v>
+        <v>1462</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1270</v>
+        <v>1463</v>
       </c>
       <c r="C67" s="1">
         <v>13</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1271</v>
+        <v>1464</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1272</v>
+        <v>1465</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" s="1" t="s">
-        <v>1273</v>
+        <v>1466</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1274</v>
+        <v>1467</v>
       </c>
       <c r="C68" s="1">
         <v>12</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1275</v>
+        <v>1468</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1276</v>
+        <v>1469</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" s="1" t="s">
-        <v>1277</v>
+        <v>1470</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1278</v>
+        <v>1471</v>
       </c>
       <c r="C69" s="1">
         <v>12</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1" t="s">
-        <v>1009</v>
+        <v>1202</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1279</v>
+        <v>1472</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1280</v>
+        <v>1473</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" s="1" t="s">
-        <v>1281</v>
+        <v>1474</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1282</v>
+        <v>1475</v>
       </c>
       <c r="C70" s="1">
         <v>13</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1283</v>
+        <v>1476</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1284</v>
+        <v>1477</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
@@ -13356,209 +14939,209 @@
         <v>91</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1285</v>
+        <v>1478</v>
       </c>
       <c r="C71" s="1">
         <v>11</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>1065</v>
+        <v>1258</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1286</v>
+        <v>1479</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1287</v>
+        <v>1480</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" s="1" t="s">
-        <v>1288</v>
+        <v>1481</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1289</v>
+        <v>1482</v>
       </c>
       <c r="C72" s="1">
         <v>12</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1290</v>
+        <v>1483</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1291</v>
+        <v>1484</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" s="1" t="s">
-        <v>1292</v>
+        <v>1485</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1293</v>
+        <v>1486</v>
       </c>
       <c r="C73" s="1">
         <v>12</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1" t="s">
-        <v>1004</v>
+        <v>1197</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1294</v>
+        <v>1487</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1295</v>
+        <v>1488</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" s="1" t="s">
-        <v>1296</v>
+        <v>1489</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1297</v>
+        <v>1490</v>
       </c>
       <c r="C74" s="1">
         <v>11</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1" t="s">
-        <v>1014</v>
+        <v>1207</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1298</v>
+        <v>1491</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1299</v>
+        <v>1492</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A75" s="1" t="s">
-        <v>1300</v>
+        <v>1493</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1301</v>
+        <v>1494</v>
       </c>
       <c r="C75" s="1">
         <v>12</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1" t="s">
-        <v>1029</v>
+        <v>1222</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1302</v>
+        <v>1495</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1303</v>
+        <v>1496</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A76" s="1" t="s">
-        <v>1304</v>
+        <v>1497</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1305</v>
+        <v>1498</v>
       </c>
       <c r="C76" s="1">
         <v>13</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1" t="s">
-        <v>1034</v>
+        <v>1227</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1306</v>
+        <v>1499</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1307</v>
+        <v>1500</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A77" s="1" t="s">
-        <v>1308</v>
+        <v>1501</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1309</v>
+        <v>1502</v>
       </c>
       <c r="C77" s="1">
         <v>13</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1" t="s">
-        <v>1065</v>
+        <v>1258</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1310</v>
+        <v>1503</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1311</v>
+        <v>1504</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" s="1" t="s">
-        <v>1312</v>
+        <v>1505</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1313</v>
+        <v>1506</v>
       </c>
       <c r="C78" s="1">
         <v>13</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>1019</v>
+        <v>1212</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1314</v>
+        <v>1507</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1315</v>
+        <v>1508</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" s="1" t="s">
-        <v>1316</v>
+        <v>1509</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1317</v>
+        <v>1510</v>
       </c>
       <c r="C79" s="1">
         <v>12</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>1024</v>
+        <v>1217</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1318</v>
+        <v>1511</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1319</v>
+        <v>1512</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A80" s="1" t="s">
-        <v>1320</v>
+        <v>1513</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1321</v>
+        <v>1514</v>
       </c>
       <c r="C80" s="1">
         <v>13</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1" t="s">
-        <v>1043</v>
+        <v>1236</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1322</v>
+        <v>1515</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1323</v>
+        <v>1516</v>
       </c>
     </row>
   </sheetData>
@@ -13602,10 +15185,10 @@
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A2" t="s">
-        <v>1324</v>
+        <v>1517</v>
       </c>
       <c r="B2" t="s">
-        <v>1325</v>
+        <v>1518</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -13614,15 +15197,15 @@
         <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>1326</v>
+        <v>1519</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A3" t="s">
-        <v>1327</v>
+        <v>1520</v>
       </c>
       <c r="B3" t="s">
-        <v>1328</v>
+        <v>1521</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -13631,15 +15214,15 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>1329</v>
+        <v>1522</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A4" t="s">
-        <v>1330</v>
+        <v>1523</v>
       </c>
       <c r="B4" t="s">
-        <v>1331</v>
+        <v>1524</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -13648,15 +15231,15 @@
         <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>1332</v>
+        <v>1525</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A5" t="s">
-        <v>1333</v>
+        <v>1526</v>
       </c>
       <c r="B5" t="s">
-        <v>1334</v>
+        <v>1527</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -13665,15 +15248,15 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
-        <v>1335</v>
+        <v>1528</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A6" t="s">
-        <v>1336</v>
+        <v>1529</v>
       </c>
       <c r="B6" t="s">
-        <v>1337</v>
+        <v>1530</v>
       </c>
       <c r="C6">
         <v>11</v>
@@ -13682,15 +15265,15 @@
         <v>11</v>
       </c>
       <c r="F6" t="s">
-        <v>1338</v>
+        <v>1531</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A7" t="s">
-        <v>1339</v>
+        <v>1532</v>
       </c>
       <c r="B7" t="s">
-        <v>1340</v>
+        <v>1533</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -13699,15 +15282,15 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>1341</v>
+        <v>1534</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A8" t="s">
-        <v>1342</v>
+        <v>1535</v>
       </c>
       <c r="B8" t="s">
-        <v>1343</v>
+        <v>1536</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -13716,15 +15299,15 @@
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>1344</v>
+        <v>1537</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A9" t="s">
-        <v>1345</v>
+        <v>1538</v>
       </c>
       <c r="B9" t="s">
-        <v>1346</v>
+        <v>1539</v>
       </c>
       <c r="C9">
         <v>11</v>
@@ -13733,15 +15316,15 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>1347</v>
+        <v>1540</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A10" t="s">
-        <v>1348</v>
+        <v>1541</v>
       </c>
       <c r="B10" t="s">
-        <v>1349</v>
+        <v>1542</v>
       </c>
       <c r="C10">
         <v>12</v>
@@ -13750,7 +15333,7 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>1350</v>
+        <v>1543</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.4">
@@ -13758,7 +15341,7 @@
         <v>733</v>
       </c>
       <c r="B11" t="s">
-        <v>1351</v>
+        <v>1544</v>
       </c>
       <c r="C11">
         <v>12</v>
@@ -13767,15 +15350,15 @@
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>1352</v>
+        <v>1545</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A12" t="s">
-        <v>1353</v>
+        <v>1546</v>
       </c>
       <c r="B12" t="s">
-        <v>1354</v>
+        <v>1547</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -13784,15 +15367,15 @@
         <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>1355</v>
+        <v>1548</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A13" t="s">
-        <v>1356</v>
+        <v>1549</v>
       </c>
       <c r="B13" t="s">
-        <v>1357</v>
+        <v>1550</v>
       </c>
       <c r="C13">
         <v>13</v>
@@ -13801,15 +15384,15 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>1358</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A14" t="s">
-        <v>1359</v>
+        <v>1552</v>
       </c>
       <c r="B14" t="s">
-        <v>1360</v>
+        <v>1553</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -13818,15 +15401,15 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>1361</v>
+        <v>1554</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A15" t="s">
-        <v>1362</v>
+        <v>1555</v>
       </c>
       <c r="B15" t="s">
-        <v>1363</v>
+        <v>1556</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -13835,15 +15418,15 @@
         <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>1364</v>
+        <v>1557</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A16" t="s">
-        <v>1365</v>
+        <v>1558</v>
       </c>
       <c r="B16" t="s">
-        <v>1366</v>
+        <v>1559</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -13852,15 +15435,15 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>1367</v>
+        <v>1560</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A17" t="s">
-        <v>1368</v>
+        <v>1561</v>
       </c>
       <c r="B17" t="s">
-        <v>1369</v>
+        <v>1562</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -13869,15 +15452,15 @@
         <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>1370</v>
+        <v>1563</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A18" t="s">
-        <v>1371</v>
+        <v>1564</v>
       </c>
       <c r="B18" t="s">
-        <v>1372</v>
+        <v>1565</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -13886,15 +15469,15 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>1358</v>
+        <v>1551</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A19" t="s">
-        <v>1373</v>
+        <v>1566</v>
       </c>
       <c r="B19" t="s">
-        <v>1374</v>
+        <v>1567</v>
       </c>
       <c r="C19">
         <v>13</v>
@@ -13903,15 +15486,15 @@
         <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>1375</v>
+        <v>1568</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A20" t="s">
-        <v>1376</v>
+        <v>1569</v>
       </c>
       <c r="B20" t="s">
-        <v>1377</v>
+        <v>1570</v>
       </c>
       <c r="C20">
         <v>12</v>
@@ -13920,15 +15503,15 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>1378</v>
+        <v>1571</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A21" t="s">
-        <v>1379</v>
+        <v>1572</v>
       </c>
       <c r="B21" t="s">
-        <v>1380</v>
+        <v>1573</v>
       </c>
       <c r="C21">
         <v>12</v>
@@ -13937,15 +15520,15 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>1381</v>
+        <v>1574</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A22" t="s">
-        <v>1382</v>
+        <v>1575</v>
       </c>
       <c r="B22" t="s">
-        <v>1383</v>
+        <v>1576</v>
       </c>
       <c r="C22">
         <v>13</v>
@@ -13959,10 +15542,10 @@
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A23" t="s">
-        <v>1384</v>
+        <v>1577</v>
       </c>
       <c r="B23" t="s">
-        <v>1385</v>
+        <v>1578</v>
       </c>
       <c r="C23">
         <v>13</v>
@@ -13971,15 +15554,15 @@
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>1386</v>
+        <v>1579</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A24" t="s">
-        <v>1387</v>
+        <v>1580</v>
       </c>
       <c r="B24" t="s">
-        <v>1388</v>
+        <v>1581</v>
       </c>
       <c r="C24">
         <v>13</v>
@@ -13988,15 +15571,15 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>1389</v>
+        <v>1582</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A25" t="s">
-        <v>1390</v>
+        <v>1583</v>
       </c>
       <c r="B25" t="s">
-        <v>1391</v>
+        <v>1584</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -14005,15 +15588,15 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>1392</v>
+        <v>1585</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A26" t="s">
-        <v>1393</v>
+        <v>1586</v>
       </c>
       <c r="B26" t="s">
-        <v>1394</v>
+        <v>1587</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -14022,15 +15605,15 @@
         <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>1395</v>
+        <v>1588</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A27" t="s">
-        <v>1304</v>
+        <v>1497</v>
       </c>
       <c r="B27" t="s">
-        <v>1396</v>
+        <v>1589</v>
       </c>
       <c r="C27">
         <v>12</v>
@@ -14039,15 +15622,15 @@
         <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>1397</v>
+        <v>1590</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A28" t="s">
-        <v>1398</v>
+        <v>1591</v>
       </c>
       <c r="B28" t="s">
-        <v>1399</v>
+        <v>1592</v>
       </c>
       <c r="C28">
         <v>11</v>
@@ -14056,15 +15639,15 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>1400</v>
+        <v>1593</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A29" t="s">
-        <v>1401</v>
+        <v>1594</v>
       </c>
       <c r="B29" t="s">
-        <v>1402</v>
+        <v>1595</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -14073,15 +15656,15 @@
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>1403</v>
+        <v>1596</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A30" t="s">
-        <v>1261</v>
+        <v>1454</v>
       </c>
       <c r="B30" t="s">
-        <v>1404</v>
+        <v>1597</v>
       </c>
       <c r="C30">
         <v>11</v>
@@ -14090,15 +15673,15 @@
         <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>1405</v>
+        <v>1598</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A31" t="s">
-        <v>1406</v>
+        <v>1599</v>
       </c>
       <c r="B31" t="s">
-        <v>1407</v>
+        <v>1600</v>
       </c>
       <c r="C31">
         <v>13</v>
@@ -14107,15 +15690,15 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>1408</v>
+        <v>1601</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.4">
       <c r="A32" t="s">
-        <v>1409</v>
+        <v>1602</v>
       </c>
       <c r="B32" t="s">
-        <v>1410</v>
+        <v>1603</v>
       </c>
       <c r="C32">
         <v>13</v>
@@ -14124,15 +15707,15 @@
         <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>1411</v>
+        <v>1604</v>
       </c>
     </row>
     <row r="33" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A33" t="s">
-        <v>1412</v>
+        <v>1605</v>
       </c>
       <c r="B33" t="s">
-        <v>1413</v>
+        <v>1606</v>
       </c>
       <c r="C33">
         <v>11</v>
@@ -14141,15 +15724,15 @@
         <v>67</v>
       </c>
       <c r="F33" t="s">
-        <v>1414</v>
+        <v>1607</v>
       </c>
     </row>
     <row r="34" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A34" t="s">
-        <v>1415</v>
+        <v>1608</v>
       </c>
       <c r="B34" t="s">
-        <v>1416</v>
+        <v>1609</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -14158,15 +15741,15 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>1417</v>
+        <v>1610</v>
       </c>
     </row>
     <row r="35" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A35" t="s">
-        <v>1418</v>
+        <v>1611</v>
       </c>
       <c r="B35" t="s">
-        <v>1419</v>
+        <v>1612</v>
       </c>
       <c r="C35">
         <v>13</v>
@@ -14175,15 +15758,15 @@
         <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>1420</v>
+        <v>1613</v>
       </c>
     </row>
     <row r="36" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A36" t="s">
-        <v>1421</v>
+        <v>1614</v>
       </c>
       <c r="B36" t="s">
-        <v>1422</v>
+        <v>1615</v>
       </c>
       <c r="C36">
         <v>13</v>
@@ -14197,10 +15780,10 @@
     </row>
     <row r="37" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A37" t="s">
-        <v>1423</v>
+        <v>1616</v>
       </c>
       <c r="B37" t="s">
-        <v>1424</v>
+        <v>1617</v>
       </c>
       <c r="C37">
         <v>11</v>
@@ -14209,15 +15792,15 @@
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>1425</v>
+        <v>1618</v>
       </c>
     </row>
     <row r="38" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A38" t="s">
-        <v>1426</v>
+        <v>1619</v>
       </c>
       <c r="B38" t="s">
-        <v>1427</v>
+        <v>1620</v>
       </c>
       <c r="C38">
         <v>12</v>
@@ -14226,18 +15809,18 @@
         <v>58</v>
       </c>
       <c r="F38" t="s">
-        <v>1428</v>
+        <v>1134</v>
       </c>
       <c r="G38" t="s">
-        <v>1429</v>
+        <v>1621</v>
       </c>
     </row>
     <row r="39" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A39" t="s">
-        <v>1430</v>
+        <v>1622</v>
       </c>
       <c r="B39" t="s">
-        <v>1431</v>
+        <v>1623</v>
       </c>
       <c r="C39">
         <v>11</v>
@@ -14249,15 +15832,15 @@
         <v>268</v>
       </c>
       <c r="G39" t="s">
-        <v>1432</v>
+        <v>1624</v>
       </c>
     </row>
     <row r="40" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A40" t="s">
-        <v>1433</v>
+        <v>1625</v>
       </c>
       <c r="B40" t="s">
-        <v>1434</v>
+        <v>1626</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -14266,18 +15849,18 @@
         <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>1435</v>
+        <v>1627</v>
       </c>
       <c r="G40" t="s">
-        <v>1436</v>
+        <v>1628</v>
       </c>
     </row>
     <row r="41" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A41" t="s">
-        <v>1437</v>
+        <v>1629</v>
       </c>
       <c r="B41" t="s">
-        <v>1438</v>
+        <v>1630</v>
       </c>
       <c r="C41">
         <v>13</v>
@@ -14286,18 +15869,18 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>1439</v>
+        <v>1631</v>
       </c>
       <c r="G41" t="s">
-        <v>1440</v>
+        <v>1632</v>
       </c>
     </row>
     <row r="42" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A42" t="s">
-        <v>1441</v>
+        <v>1633</v>
       </c>
       <c r="B42" t="s">
-        <v>1442</v>
+        <v>1634</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -14306,18 +15889,18 @@
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>1443</v>
+        <v>1635</v>
       </c>
       <c r="G42" t="s">
-        <v>1444</v>
+        <v>1636</v>
       </c>
     </row>
     <row r="43" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A43" t="s">
-        <v>1445</v>
+        <v>1637</v>
       </c>
       <c r="B43" t="s">
-        <v>1446</v>
+        <v>1638</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -14326,18 +15909,18 @@
         <v>36</v>
       </c>
       <c r="F43" t="s">
-        <v>1447</v>
+        <v>1639</v>
       </c>
       <c r="G43" t="s">
-        <v>1448</v>
+        <v>1640</v>
       </c>
     </row>
     <row r="44" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A44" t="s">
-        <v>1449</v>
+        <v>1641</v>
       </c>
       <c r="B44" t="s">
-        <v>1450</v>
+        <v>1642</v>
       </c>
       <c r="C44">
         <v>13</v>
@@ -14346,18 +15929,18 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>1451</v>
+        <v>1643</v>
       </c>
       <c r="G44" t="s">
-        <v>1452</v>
+        <v>1644</v>
       </c>
     </row>
     <row r="45" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A45" t="s">
-        <v>1453</v>
+        <v>1645</v>
       </c>
       <c r="B45" t="s">
-        <v>1454</v>
+        <v>1646</v>
       </c>
       <c r="C45">
         <v>12</v>
@@ -14366,18 +15949,18 @@
         <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>1455</v>
+        <v>1647</v>
       </c>
       <c r="G45" t="s">
-        <v>1456</v>
+        <v>1648</v>
       </c>
     </row>
     <row r="46" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A46" t="s">
-        <v>1457</v>
+        <v>1649</v>
       </c>
       <c r="B46" t="s">
-        <v>1458</v>
+        <v>1650</v>
       </c>
       <c r="C46">
         <v>11</v>
@@ -14386,18 +15969,18 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>1459</v>
+        <v>1651</v>
       </c>
       <c r="G46" t="s">
-        <v>1460</v>
+        <v>1652</v>
       </c>
     </row>
     <row r="47" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A47" t="s">
-        <v>1461</v>
+        <v>1653</v>
       </c>
       <c r="B47" t="s">
-        <v>1462</v>
+        <v>1654</v>
       </c>
       <c r="C47">
         <v>12</v>
@@ -14406,18 +15989,18 @@
         <v>58</v>
       </c>
       <c r="F47" t="s">
-        <v>1463</v>
+        <v>1655</v>
       </c>
       <c r="G47" t="s">
-        <v>1464</v>
+        <v>1656</v>
       </c>
     </row>
     <row r="48" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A48" t="s">
-        <v>1465</v>
+        <v>1657</v>
       </c>
       <c r="B48" t="s">
-        <v>1466</v>
+        <v>1658</v>
       </c>
       <c r="C48">
         <v>12</v>
@@ -14426,18 +16009,18 @@
         <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>1467</v>
+        <v>1659</v>
       </c>
       <c r="G48" t="s">
-        <v>1468</v>
+        <v>1660</v>
       </c>
     </row>
     <row r="49" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A49" t="s">
-        <v>1469</v>
+        <v>1661</v>
       </c>
       <c r="B49" t="s">
-        <v>1470</v>
+        <v>1662</v>
       </c>
       <c r="C49">
         <v>11</v>
@@ -14446,18 +16029,18 @@
         <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>1471</v>
+        <v>1663</v>
       </c>
       <c r="G49" t="s">
-        <v>1472</v>
+        <v>1664</v>
       </c>
     </row>
     <row r="50" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A50" t="s">
-        <v>1473</v>
+        <v>1665</v>
       </c>
       <c r="B50" t="s">
-        <v>1474</v>
+        <v>1666</v>
       </c>
       <c r="C50">
         <v>12</v>
@@ -14466,18 +16049,18 @@
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>1475</v>
+        <v>1667</v>
       </c>
       <c r="G50" t="s">
-        <v>1476</v>
+        <v>1668</v>
       </c>
     </row>
     <row r="51" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A51" t="s">
-        <v>1477</v>
+        <v>1669</v>
       </c>
       <c r="B51" t="s">
-        <v>1478</v>
+        <v>1670</v>
       </c>
       <c r="C51">
         <v>11</v>
@@ -14486,18 +16069,18 @@
         <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>1479</v>
+        <v>1671</v>
       </c>
       <c r="G51" t="s">
-        <v>1480</v>
+        <v>1672</v>
       </c>
     </row>
     <row r="52" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A52" t="s">
-        <v>1421</v>
+        <v>1614</v>
       </c>
       <c r="B52" t="s">
-        <v>1481</v>
+        <v>1673</v>
       </c>
       <c r="C52">
         <v>11</v>
@@ -14509,15 +16092,15 @@
         <v>466</v>
       </c>
       <c r="G52" t="s">
-        <v>1482</v>
+        <v>1674</v>
       </c>
     </row>
     <row r="53" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A53" t="s">
-        <v>1483</v>
+        <v>1675</v>
       </c>
       <c r="B53" t="s">
-        <v>1484</v>
+        <v>1676</v>
       </c>
       <c r="C53">
         <v>11</v>
@@ -14526,18 +16109,18 @@
         <v>72</v>
       </c>
       <c r="F53" t="s">
-        <v>1485</v>
+        <v>1677</v>
       </c>
       <c r="G53" t="s">
-        <v>1486</v>
+        <v>1678</v>
       </c>
     </row>
     <row r="54" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A54" t="s">
-        <v>1487</v>
+        <v>1679</v>
       </c>
       <c r="B54" t="s">
-        <v>1488</v>
+        <v>1680</v>
       </c>
       <c r="C54">
         <v>12</v>
@@ -14546,18 +16129,18 @@
         <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>1489</v>
+        <v>1681</v>
       </c>
       <c r="G54" t="s">
-        <v>1490</v>
+        <v>1682</v>
       </c>
     </row>
     <row r="55" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A55" t="s">
-        <v>1491</v>
+        <v>1683</v>
       </c>
       <c r="B55" t="s">
-        <v>1492</v>
+        <v>1684</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -14566,18 +16149,18 @@
         <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>1493</v>
+        <v>1685</v>
       </c>
       <c r="G55" t="s">
-        <v>1494</v>
+        <v>1686</v>
       </c>
     </row>
     <row r="56" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A56" t="s">
-        <v>1495</v>
+        <v>1687</v>
       </c>
       <c r="B56" t="s">
-        <v>1496</v>
+        <v>1688</v>
       </c>
       <c r="C56">
         <v>11</v>
@@ -14586,18 +16169,18 @@
         <v>67</v>
       </c>
       <c r="F56" t="s">
-        <v>1497</v>
+        <v>1689</v>
       </c>
       <c r="G56" t="s">
-        <v>1498</v>
+        <v>1690</v>
       </c>
     </row>
     <row r="57" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A57" t="s">
-        <v>1499</v>
+        <v>1691</v>
       </c>
       <c r="B57" t="s">
-        <v>1500</v>
+        <v>1692</v>
       </c>
       <c r="C57">
         <v>13</v>
@@ -14606,18 +16189,18 @@
         <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>1501</v>
+        <v>1693</v>
       </c>
       <c r="G57" t="s">
-        <v>1502</v>
+        <v>1694</v>
       </c>
     </row>
     <row r="58" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A58" t="s">
-        <v>1503</v>
+        <v>1695</v>
       </c>
       <c r="B58" t="s">
-        <v>1504</v>
+        <v>1696</v>
       </c>
       <c r="C58">
         <v>11</v>
@@ -14626,18 +16209,18 @@
         <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>1505</v>
+        <v>1697</v>
       </c>
       <c r="G58" t="s">
-        <v>1506</v>
+        <v>1698</v>
       </c>
     </row>
     <row r="59" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A59" t="s">
-        <v>1507</v>
+        <v>1699</v>
       </c>
       <c r="B59" t="s">
-        <v>1508</v>
+        <v>1700</v>
       </c>
       <c r="C59">
         <v>11</v>
@@ -14646,18 +16229,18 @@
         <v>58</v>
       </c>
       <c r="F59" t="s">
-        <v>1509</v>
+        <v>1701</v>
       </c>
       <c r="G59" t="s">
-        <v>1510</v>
+        <v>1702</v>
       </c>
     </row>
     <row r="60" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A60" t="s">
-        <v>1511</v>
+        <v>1703</v>
       </c>
       <c r="B60" t="s">
-        <v>1512</v>
+        <v>1704</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -14666,18 +16249,18 @@
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>1397</v>
+        <v>1590</v>
       </c>
       <c r="G60" t="s">
-        <v>1513</v>
+        <v>1705</v>
       </c>
     </row>
     <row r="61" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A61" t="s">
-        <v>1514</v>
+        <v>1706</v>
       </c>
       <c r="B61" t="s">
-        <v>1515</v>
+        <v>1707</v>
       </c>
       <c r="C61">
         <v>11</v>
@@ -14686,18 +16269,18 @@
         <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>1516</v>
+        <v>1708</v>
       </c>
       <c r="G61" t="s">
-        <v>1517</v>
+        <v>1709</v>
       </c>
     </row>
     <row r="62" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A62" t="s">
-        <v>1518</v>
+        <v>1710</v>
       </c>
       <c r="B62" t="s">
-        <v>1519</v>
+        <v>1711</v>
       </c>
       <c r="C62">
         <v>13</v>
@@ -14706,18 +16289,18 @@
         <v>72</v>
       </c>
       <c r="F62" t="s">
-        <v>1520</v>
+        <v>1712</v>
       </c>
       <c r="G62" t="s">
-        <v>1521</v>
+        <v>1713</v>
       </c>
     </row>
     <row r="63" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A63" t="s">
-        <v>1522</v>
+        <v>1714</v>
       </c>
       <c r="B63" t="s">
-        <v>1523</v>
+        <v>1715</v>
       </c>
       <c r="C63">
         <v>12</v>
@@ -14726,18 +16309,18 @@
         <v>41</v>
       </c>
       <c r="F63" t="s">
-        <v>1524</v>
+        <v>1716</v>
       </c>
       <c r="G63" t="s">
-        <v>1525</v>
+        <v>1717</v>
       </c>
     </row>
     <row r="64" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A64" t="s">
-        <v>1526</v>
+        <v>1718</v>
       </c>
       <c r="B64" t="s">
-        <v>1527</v>
+        <v>1719</v>
       </c>
       <c r="C64">
         <v>12</v>
@@ -14746,18 +16329,18 @@
         <v>58</v>
       </c>
       <c r="F64" t="s">
-        <v>1528</v>
+        <v>1720</v>
       </c>
       <c r="G64" t="s">
-        <v>1529</v>
+        <v>1721</v>
       </c>
     </row>
     <row r="65" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A65" t="s">
-        <v>1530</v>
+        <v>1722</v>
       </c>
       <c r="B65" t="s">
-        <v>1531</v>
+        <v>1723</v>
       </c>
       <c r="C65">
         <v>13</v>
@@ -14766,18 +16349,18 @@
         <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>1532</v>
+        <v>1724</v>
       </c>
       <c r="G65" t="s">
-        <v>1533</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="66" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A66" t="s">
-        <v>1534</v>
+        <v>1726</v>
       </c>
       <c r="B66" t="s">
-        <v>1535</v>
+        <v>1727</v>
       </c>
       <c r="C66">
         <v>11</v>
@@ -14789,18 +16372,18 @@
         <v>679</v>
       </c>
       <c r="F66" t="s">
-        <v>1536</v>
+        <v>1728</v>
       </c>
       <c r="G66" t="s">
-        <v>1537</v>
+        <v>1729</v>
       </c>
     </row>
     <row r="67" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A67" t="s">
-        <v>1538</v>
+        <v>1730</v>
       </c>
       <c r="B67" t="s">
-        <v>1539</v>
+        <v>1731</v>
       </c>
       <c r="C67">
         <v>12</v>
@@ -14812,18 +16395,18 @@
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>1540</v>
+        <v>1732</v>
       </c>
       <c r="G67" t="s">
-        <v>1541</v>
+        <v>1733</v>
       </c>
     </row>
     <row r="68" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A68" t="s">
-        <v>1542</v>
+        <v>1734</v>
       </c>
       <c r="B68" t="s">
-        <v>1543</v>
+        <v>1735</v>
       </c>
       <c r="C68">
         <v>12</v>
@@ -14838,15 +16421,15 @@
         <v>212</v>
       </c>
       <c r="G68" t="s">
-        <v>1544</v>
+        <v>1736</v>
       </c>
     </row>
     <row r="69" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A69" t="s">
-        <v>1545</v>
+        <v>1737</v>
       </c>
       <c r="B69" t="s">
-        <v>1546</v>
+        <v>1738</v>
       </c>
       <c r="C69">
         <v>12</v>
@@ -14861,15 +16444,15 @@
         <v>545</v>
       </c>
       <c r="G69" t="s">
-        <v>1547</v>
+        <v>1739</v>
       </c>
     </row>
     <row r="70" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A70" t="s">
-        <v>1548</v>
+        <v>1740</v>
       </c>
       <c r="B70" t="s">
-        <v>1549</v>
+        <v>1741</v>
       </c>
       <c r="C70">
         <v>12</v>
@@ -14881,18 +16464,18 @@
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>1550</v>
+        <v>1742</v>
       </c>
       <c r="G70" t="s">
-        <v>1551</v>
+        <v>1743</v>
       </c>
     </row>
     <row r="71" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A71" t="s">
-        <v>1552</v>
+        <v>1744</v>
       </c>
       <c r="B71" t="s">
-        <v>1553</v>
+        <v>1745</v>
       </c>
       <c r="C71">
         <v>13</v>
@@ -14904,18 +16487,18 @@
         <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>1554</v>
+        <v>1746</v>
       </c>
       <c r="G71" t="s">
-        <v>1555</v>
+        <v>1747</v>
       </c>
     </row>
     <row r="72" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A72" t="s">
-        <v>1556</v>
+        <v>1748</v>
       </c>
       <c r="B72" t="s">
-        <v>1557</v>
+        <v>1749</v>
       </c>
       <c r="C72">
         <v>11</v>
@@ -14927,18 +16510,18 @@
         <v>36</v>
       </c>
       <c r="F72" t="s">
-        <v>1447</v>
+        <v>1639</v>
       </c>
       <c r="G72" t="s">
-        <v>1558</v>
+        <v>1750</v>
       </c>
     </row>
     <row r="73" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A73" t="s">
-        <v>1559</v>
+        <v>1751</v>
       </c>
       <c r="B73" t="s">
-        <v>1560</v>
+        <v>1752</v>
       </c>
       <c r="C73">
         <v>11</v>
@@ -14950,18 +16533,18 @@
         <v>11</v>
       </c>
       <c r="F73" t="s">
-        <v>1561</v>
+        <v>1753</v>
       </c>
       <c r="G73" t="s">
-        <v>1562</v>
+        <v>1754</v>
       </c>
     </row>
     <row r="74" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A74" t="s">
-        <v>1563</v>
+        <v>1755</v>
       </c>
       <c r="B74" t="s">
-        <v>1564</v>
+        <v>1756</v>
       </c>
       <c r="C74">
         <v>12</v>
@@ -14976,15 +16559,15 @@
         <v>141</v>
       </c>
       <c r="G74" t="s">
-        <v>1565</v>
+        <v>1757</v>
       </c>
     </row>
     <row r="75" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A75" t="s">
-        <v>1566</v>
+        <v>1758</v>
       </c>
       <c r="B75" t="s">
-        <v>1567</v>
+        <v>1759</v>
       </c>
       <c r="C75">
         <v>11</v>
@@ -14999,15 +16582,15 @@
         <v>68</v>
       </c>
       <c r="G75" t="s">
-        <v>1568</v>
+        <v>1760</v>
       </c>
     </row>
     <row r="76" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A76" t="s">
-        <v>1569</v>
+        <v>1761</v>
       </c>
       <c r="B76" t="s">
-        <v>1570</v>
+        <v>1762</v>
       </c>
       <c r="C76">
         <v>11</v>
@@ -15019,18 +16602,18 @@
         <v>58</v>
       </c>
       <c r="F76" t="s">
-        <v>1571</v>
+        <v>1763</v>
       </c>
       <c r="G76" t="s">
-        <v>1572</v>
+        <v>1764</v>
       </c>
     </row>
     <row r="77" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A77" t="s">
-        <v>1573</v>
+        <v>1765</v>
       </c>
       <c r="B77" t="s">
-        <v>1574</v>
+        <v>1766</v>
       </c>
       <c r="C77">
         <v>13</v>
@@ -15042,18 +16625,18 @@
         <v>58</v>
       </c>
       <c r="F77" t="s">
-        <v>1575</v>
+        <v>1767</v>
       </c>
       <c r="G77" t="s">
-        <v>1576</v>
+        <v>1768</v>
       </c>
     </row>
     <row r="78" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A78" t="s">
-        <v>1577</v>
+        <v>1769</v>
       </c>
       <c r="B78" t="s">
-        <v>1578</v>
+        <v>1770</v>
       </c>
       <c r="C78">
         <v>13</v>
@@ -15065,18 +16648,18 @@
         <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>1579</v>
+        <v>1771</v>
       </c>
       <c r="G78" t="s">
-        <v>1580</v>
+        <v>1772</v>
       </c>
     </row>
     <row r="79" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A79" t="s">
-        <v>1581</v>
+        <v>1773</v>
       </c>
       <c r="B79" t="s">
-        <v>1582</v>
+        <v>1774</v>
       </c>
       <c r="C79">
         <v>12</v>
@@ -15091,15 +16674,15 @@
         <v>696</v>
       </c>
       <c r="G79" t="s">
-        <v>1583</v>
+        <v>1775</v>
       </c>
     </row>
     <row r="80" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A80" t="s">
-        <v>1584</v>
+        <v>1776</v>
       </c>
       <c r="B80" t="s">
-        <v>1585</v>
+        <v>1777</v>
       </c>
       <c r="C80">
         <v>13</v>
@@ -15111,18 +16694,18 @@
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>1586</v>
+        <v>1778</v>
       </c>
       <c r="G80" t="s">
-        <v>1587</v>
+        <v>1779</v>
       </c>
     </row>
     <row r="81" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A81" t="s">
-        <v>1588</v>
+        <v>1780</v>
       </c>
       <c r="B81" t="s">
-        <v>1589</v>
+        <v>1781</v>
       </c>
       <c r="C81">
         <v>12</v>
@@ -15134,18 +16717,18 @@
         <v>67</v>
       </c>
       <c r="F81" t="s">
-        <v>1590</v>
+        <v>1782</v>
       </c>
       <c r="G81" t="s">
-        <v>1591</v>
+        <v>1783</v>
       </c>
     </row>
     <row r="82" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A82" t="s">
-        <v>1592</v>
+        <v>1784</v>
       </c>
       <c r="B82" t="s">
-        <v>1593</v>
+        <v>1785</v>
       </c>
       <c r="C82">
         <v>13</v>
@@ -15157,18 +16740,18 @@
         <v>22</v>
       </c>
       <c r="F82" t="s">
-        <v>1594</v>
+        <v>1786</v>
       </c>
       <c r="G82" t="s">
-        <v>1595</v>
+        <v>1787</v>
       </c>
     </row>
     <row r="83" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A83" t="s">
-        <v>1596</v>
+        <v>1788</v>
       </c>
       <c r="B83" t="s">
-        <v>1597</v>
+        <v>1789</v>
       </c>
       <c r="C83">
         <v>12</v>
@@ -15180,18 +16763,18 @@
         <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>1598</v>
+        <v>1790</v>
       </c>
       <c r="G83" t="s">
-        <v>1599</v>
+        <v>1791</v>
       </c>
     </row>
     <row r="84" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A84" t="s">
-        <v>1600</v>
+        <v>1792</v>
       </c>
       <c r="B84" t="s">
-        <v>1601</v>
+        <v>1793</v>
       </c>
       <c r="C84">
         <v>12</v>
@@ -15203,18 +16786,18 @@
         <v>58</v>
       </c>
       <c r="F84" t="s">
-        <v>1602</v>
+        <v>1794</v>
       </c>
       <c r="G84" t="s">
-        <v>1603</v>
+        <v>1795</v>
       </c>
     </row>
     <row r="85" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A85" t="s">
-        <v>1604</v>
+        <v>1796</v>
       </c>
       <c r="B85" t="s">
-        <v>1605</v>
+        <v>1797</v>
       </c>
       <c r="C85">
         <v>13</v>
@@ -15226,18 +16809,18 @@
         <v>72</v>
       </c>
       <c r="F85" t="s">
-        <v>1606</v>
+        <v>1798</v>
       </c>
       <c r="G85" t="s">
-        <v>1607</v>
+        <v>1799</v>
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A86" t="s">
-        <v>1608</v>
+        <v>1800</v>
       </c>
       <c r="B86" t="s">
-        <v>1609</v>
+        <v>1801</v>
       </c>
       <c r="C86">
         <v>12</v>
@@ -15249,18 +16832,18 @@
         <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>1610</v>
+        <v>1802</v>
       </c>
       <c r="G86" t="s">
-        <v>1611</v>
+        <v>1803</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A87" t="s">
-        <v>1612</v>
+        <v>1804</v>
       </c>
       <c r="B87" t="s">
-        <v>1613</v>
+        <v>1805</v>
       </c>
       <c r="C87">
         <v>13</v>
@@ -15272,18 +16855,18 @@
         <v>679</v>
       </c>
       <c r="F87" t="s">
-        <v>1614</v>
+        <v>1806</v>
       </c>
       <c r="G87" t="s">
-        <v>1615</v>
+        <v>1807</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A88" t="s">
-        <v>1616</v>
+        <v>1808</v>
       </c>
       <c r="B88" t="s">
-        <v>1617</v>
+        <v>1809</v>
       </c>
       <c r="C88">
         <v>12</v>
@@ -15295,18 +16878,18 @@
         <v>41</v>
       </c>
       <c r="F88" t="s">
-        <v>1475</v>
+        <v>1667</v>
       </c>
       <c r="G88" t="s">
-        <v>1618</v>
+        <v>1810</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A89" t="s">
-        <v>1619</v>
+        <v>1811</v>
       </c>
       <c r="B89" t="s">
-        <v>1620</v>
+        <v>1812</v>
       </c>
       <c r="C89">
         <v>11</v>
@@ -15318,18 +16901,18 @@
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>1621</v>
+        <v>1813</v>
       </c>
       <c r="G89" t="s">
-        <v>1622</v>
+        <v>1814</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A90" t="s">
-        <v>1623</v>
+        <v>1815</v>
       </c>
       <c r="B90" t="s">
-        <v>1624</v>
+        <v>1816</v>
       </c>
       <c r="C90">
         <v>12</v>
@@ -15341,18 +16924,18 @@
         <v>72</v>
       </c>
       <c r="F90" t="s">
-        <v>1625</v>
+        <v>1817</v>
       </c>
       <c r="G90" t="s">
-        <v>1626</v>
+        <v>1818</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A91" t="s">
-        <v>1627</v>
+        <v>1819</v>
       </c>
       <c r="B91" t="s">
-        <v>1628</v>
+        <v>1820</v>
       </c>
       <c r="C91">
         <v>13</v>
@@ -15367,15 +16950,15 @@
         <v>560</v>
       </c>
       <c r="G91" t="s">
-        <v>1629</v>
+        <v>1821</v>
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A92" t="s">
-        <v>1630</v>
+        <v>1822</v>
       </c>
       <c r="B92" t="s">
-        <v>1631</v>
+        <v>1823</v>
       </c>
       <c r="C92">
         <v>13</v>
@@ -15387,18 +16970,18 @@
         <v>67</v>
       </c>
       <c r="F92" t="s">
-        <v>1632</v>
+        <v>1824</v>
       </c>
       <c r="G92" t="s">
-        <v>1633</v>
+        <v>1825</v>
       </c>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A93" t="s">
-        <v>1634</v>
+        <v>1826</v>
       </c>
       <c r="B93" t="s">
-        <v>1635</v>
+        <v>1827</v>
       </c>
       <c r="C93">
         <v>12</v>
@@ -15410,18 +16993,18 @@
         <v>679</v>
       </c>
       <c r="F93" t="s">
-        <v>1614</v>
+        <v>1806</v>
       </c>
       <c r="G93" t="s">
-        <v>1636</v>
+        <v>1828</v>
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A94" t="s">
-        <v>1637</v>
+        <v>1829</v>
       </c>
       <c r="B94" t="s">
-        <v>1638</v>
+        <v>1830</v>
       </c>
       <c r="C94">
         <v>13</v>
@@ -15433,18 +17016,18 @@
         <v>22</v>
       </c>
       <c r="F94" t="s">
-        <v>1639</v>
+        <v>1831</v>
       </c>
       <c r="G94" t="s">
-        <v>1640</v>
+        <v>1832</v>
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A95" t="s">
-        <v>1641</v>
+        <v>1833</v>
       </c>
       <c r="B95" t="s">
-        <v>1642</v>
+        <v>1834</v>
       </c>
       <c r="C95">
         <v>13</v>
@@ -15456,18 +17039,18 @@
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>1643</v>
+        <v>1835</v>
       </c>
       <c r="G95" t="s">
-        <v>1644</v>
+        <v>1836</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A96" t="s">
-        <v>1645</v>
+        <v>1837</v>
       </c>
       <c r="B96" t="s">
-        <v>1646</v>
+        <v>1838</v>
       </c>
       <c r="C96">
         <v>12</v>
@@ -15479,18 +17062,18 @@
         <v>22</v>
       </c>
       <c r="F96" t="s">
-        <v>1647</v>
+        <v>1839</v>
       </c>
       <c r="G96" t="s">
-        <v>1648</v>
+        <v>1840</v>
       </c>
     </row>
     <row r="97" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A97" t="s">
-        <v>1649</v>
+        <v>1841</v>
       </c>
       <c r="B97" t="s">
-        <v>1650</v>
+        <v>1842</v>
       </c>
       <c r="C97">
         <v>12</v>
@@ -15502,18 +17085,18 @@
         <v>36</v>
       </c>
       <c r="F97" t="s">
-        <v>1651</v>
+        <v>1843</v>
       </c>
       <c r="G97" t="s">
-        <v>1652</v>
+        <v>1844</v>
       </c>
     </row>
     <row r="98" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A98" t="s">
-        <v>1653</v>
+        <v>1845</v>
       </c>
       <c r="B98" t="s">
-        <v>1654</v>
+        <v>1846</v>
       </c>
       <c r="C98">
         <v>12</v>
@@ -15525,18 +17108,18 @@
         <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>1655</v>
+        <v>1847</v>
       </c>
       <c r="G98" t="s">
-        <v>1656</v>
+        <v>1848</v>
       </c>
     </row>
     <row r="99" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A99" t="s">
-        <v>1657</v>
+        <v>1849</v>
       </c>
       <c r="B99" t="s">
-        <v>1658</v>
+        <v>1850</v>
       </c>
       <c r="C99">
         <v>12</v>
@@ -15551,15 +17134,15 @@
         <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>1659</v>
+        <v>1851</v>
       </c>
     </row>
     <row r="100" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A100" t="s">
-        <v>1660</v>
+        <v>1852</v>
       </c>
       <c r="B100" t="s">
-        <v>1661</v>
+        <v>1853</v>
       </c>
       <c r="C100">
         <v>11</v>
@@ -15571,18 +17154,18 @@
         <v>67</v>
       </c>
       <c r="F100" t="s">
-        <v>1662</v>
+        <v>1854</v>
       </c>
       <c r="G100" t="s">
-        <v>1663</v>
+        <v>1855</v>
       </c>
     </row>
     <row r="101" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A101" t="s">
-        <v>1664</v>
+        <v>1856</v>
       </c>
       <c r="B101" t="s">
-        <v>1665</v>
+        <v>1857</v>
       </c>
       <c r="C101">
         <v>12</v>
@@ -15594,18 +17177,18 @@
         <v>679</v>
       </c>
       <c r="F101" t="s">
-        <v>1666</v>
+        <v>1858</v>
       </c>
       <c r="G101" t="s">
-        <v>1667</v>
+        <v>1859</v>
       </c>
     </row>
     <row r="102" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A102" t="s">
-        <v>1668</v>
+        <v>1860</v>
       </c>
       <c r="B102" t="s">
-        <v>1669</v>
+        <v>1861</v>
       </c>
       <c r="C102">
         <v>13</v>
@@ -15617,18 +17200,18 @@
         <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>1670</v>
+        <v>1862</v>
       </c>
       <c r="G102" t="s">
-        <v>1671</v>
+        <v>1863</v>
       </c>
     </row>
     <row r="103" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A103" t="s">
-        <v>1672</v>
+        <v>1864</v>
       </c>
       <c r="B103" t="s">
-        <v>1673</v>
+        <v>1865</v>
       </c>
       <c r="C103">
         <v>11</v>
@@ -15640,18 +17223,18 @@
         <v>27</v>
       </c>
       <c r="F103" t="s">
-        <v>1674</v>
+        <v>1866</v>
       </c>
       <c r="G103" t="s">
-        <v>1675</v>
+        <v>1867</v>
       </c>
     </row>
     <row r="104" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A104" t="s">
-        <v>1676</v>
+        <v>1868</v>
       </c>
       <c r="B104" t="s">
-        <v>1677</v>
+        <v>1869</v>
       </c>
       <c r="C104">
         <v>13</v>
@@ -15663,18 +17246,18 @@
         <v>67</v>
       </c>
       <c r="F104" t="s">
-        <v>1678</v>
+        <v>1870</v>
       </c>
       <c r="G104" t="s">
-        <v>1679</v>
+        <v>1871</v>
       </c>
     </row>
     <row r="105" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A105" t="s">
-        <v>1680</v>
+        <v>1872</v>
       </c>
       <c r="B105" t="s">
-        <v>1681</v>
+        <v>1873</v>
       </c>
       <c r="C105">
         <v>12</v>
@@ -15686,18 +17269,18 @@
         <v>36</v>
       </c>
       <c r="F105" t="s">
-        <v>1682</v>
+        <v>1874</v>
       </c>
       <c r="G105" t="s">
-        <v>1683</v>
+        <v>1875</v>
       </c>
     </row>
     <row r="106" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A106" t="s">
-        <v>1684</v>
+        <v>1876</v>
       </c>
       <c r="B106" t="s">
-        <v>1685</v>
+        <v>1877</v>
       </c>
       <c r="C106">
         <v>12</v>
@@ -15712,15 +17295,15 @@
         <v>607</v>
       </c>
       <c r="G106" t="s">
-        <v>1686</v>
+        <v>1878</v>
       </c>
     </row>
     <row r="107" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A107" t="s">
-        <v>1202</v>
+        <v>1395</v>
       </c>
       <c r="B107" t="s">
-        <v>1687</v>
+        <v>1879</v>
       </c>
       <c r="C107">
         <v>13</v>
@@ -15732,18 +17315,18 @@
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>1688</v>
+        <v>1880</v>
       </c>
       <c r="G107" t="s">
-        <v>1689</v>
+        <v>1881</v>
       </c>
     </row>
     <row r="108" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A108" t="s">
-        <v>1690</v>
+        <v>1882</v>
       </c>
       <c r="B108" t="s">
-        <v>1691</v>
+        <v>1883</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -15755,18 +17338,18 @@
         <v>22</v>
       </c>
       <c r="F108" t="s">
-        <v>1692</v>
+        <v>1884</v>
       </c>
       <c r="G108" t="s">
-        <v>1693</v>
+        <v>1885</v>
       </c>
     </row>
     <row r="109" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A109" t="s">
-        <v>1694</v>
+        <v>1886</v>
       </c>
       <c r="B109" t="s">
-        <v>1695</v>
+        <v>1887</v>
       </c>
       <c r="C109">
         <v>13</v>
@@ -15778,18 +17361,18 @@
         <v>41</v>
       </c>
       <c r="F109" t="s">
-        <v>1696</v>
+        <v>1888</v>
       </c>
       <c r="G109" t="s">
-        <v>1697</v>
+        <v>1889</v>
       </c>
     </row>
     <row r="110" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A110" t="s">
-        <v>1698</v>
+        <v>1890</v>
       </c>
       <c r="B110" t="s">
-        <v>1699</v>
+        <v>1891</v>
       </c>
       <c r="C110">
         <v>11</v>
@@ -15801,18 +17384,18 @@
         <v>41</v>
       </c>
       <c r="F110" t="s">
-        <v>1700</v>
+        <v>1892</v>
       </c>
       <c r="G110" t="s">
-        <v>1701</v>
+        <v>1893</v>
       </c>
     </row>
     <row r="111" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A111" t="s">
-        <v>1702</v>
+        <v>1894</v>
       </c>
       <c r="B111" t="s">
-        <v>1703</v>
+        <v>1895</v>
       </c>
       <c r="C111">
         <v>11</v>
@@ -15827,15 +17410,15 @@
         <v>482</v>
       </c>
       <c r="G111" t="s">
-        <v>1704</v>
+        <v>1896</v>
       </c>
     </row>
     <row r="112" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A112" t="s">
-        <v>1705</v>
+        <v>1897</v>
       </c>
       <c r="B112" t="s">
-        <v>1706</v>
+        <v>1898</v>
       </c>
       <c r="C112">
         <v>13</v>
@@ -15847,18 +17430,18 @@
         <v>58</v>
       </c>
       <c r="F112" t="s">
-        <v>1707</v>
+        <v>1899</v>
       </c>
       <c r="G112" t="s">
-        <v>1708</v>
+        <v>1900</v>
       </c>
     </row>
     <row r="113" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A113" t="s">
-        <v>1709</v>
+        <v>1901</v>
       </c>
       <c r="B113" t="s">
-        <v>1710</v>
+        <v>1902</v>
       </c>
       <c r="C113">
         <v>12</v>
@@ -15870,18 +17453,18 @@
         <v>36</v>
       </c>
       <c r="F113" t="s">
-        <v>1711</v>
+        <v>1903</v>
       </c>
       <c r="G113" t="s">
-        <v>1712</v>
+        <v>1904</v>
       </c>
     </row>
     <row r="114" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A114" t="s">
-        <v>1713</v>
+        <v>1905</v>
       </c>
       <c r="B114" t="s">
-        <v>1714</v>
+        <v>1906</v>
       </c>
       <c r="C114">
         <v>11</v>
@@ -15893,18 +17476,18 @@
         <v>67</v>
       </c>
       <c r="F114" t="s">
-        <v>1715</v>
+        <v>1907</v>
       </c>
       <c r="G114" t="s">
-        <v>1716</v>
+        <v>1908</v>
       </c>
     </row>
     <row r="115" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A115" t="s">
-        <v>1717</v>
+        <v>1909</v>
       </c>
       <c r="B115" t="s">
-        <v>1718</v>
+        <v>1910</v>
       </c>
       <c r="C115">
         <v>13</v>
@@ -15916,18 +17499,18 @@
         <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>1719</v>
+        <v>1911</v>
       </c>
       <c r="G115" t="s">
-        <v>1720</v>
+        <v>1912</v>
       </c>
     </row>
     <row r="116" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A116" t="s">
-        <v>1721</v>
+        <v>1913</v>
       </c>
       <c r="B116" t="s">
-        <v>1722</v>
+        <v>1914</v>
       </c>
       <c r="C116">
         <v>12</v>
@@ -15939,18 +17522,18 @@
         <v>58</v>
       </c>
       <c r="F116" t="s">
-        <v>1723</v>
+        <v>1915</v>
       </c>
       <c r="G116" t="s">
-        <v>1724</v>
+        <v>1916</v>
       </c>
     </row>
     <row r="117" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A117" t="s">
-        <v>1725</v>
+        <v>1917</v>
       </c>
       <c r="B117" t="s">
-        <v>1726</v>
+        <v>1918</v>
       </c>
       <c r="C117">
         <v>13</v>
@@ -15962,18 +17545,18 @@
         <v>72</v>
       </c>
       <c r="F117" t="s">
-        <v>1727</v>
+        <v>1919</v>
       </c>
       <c r="G117" t="s">
-        <v>1728</v>
+        <v>1920</v>
       </c>
     </row>
     <row r="118" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A118" t="s">
-        <v>1729</v>
+        <v>1921</v>
       </c>
       <c r="B118" t="s">
-        <v>1730</v>
+        <v>1922</v>
       </c>
       <c r="C118">
         <v>11</v>
@@ -15985,18 +17568,18 @@
         <v>36</v>
       </c>
       <c r="F118" t="s">
-        <v>1731</v>
+        <v>1923</v>
       </c>
       <c r="G118" t="s">
-        <v>1732</v>
+        <v>1924</v>
       </c>
     </row>
     <row r="119" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A119" t="s">
-        <v>1733</v>
+        <v>1925</v>
       </c>
       <c r="B119" t="s">
-        <v>1734</v>
+        <v>1926</v>
       </c>
       <c r="C119">
         <v>13</v>
@@ -16008,18 +17591,18 @@
         <v>67</v>
       </c>
       <c r="F119" t="s">
-        <v>1735</v>
+        <v>1927</v>
       </c>
       <c r="G119" t="s">
-        <v>1736</v>
+        <v>1928</v>
       </c>
     </row>
     <row r="120" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A120" t="s">
-        <v>1737</v>
+        <v>1929</v>
       </c>
       <c r="B120" t="s">
-        <v>1738</v>
+        <v>1930</v>
       </c>
       <c r="C120">
         <v>12</v>
@@ -16031,18 +17614,18 @@
         <v>22</v>
       </c>
       <c r="F120" t="s">
-        <v>1739</v>
+        <v>1931</v>
       </c>
       <c r="G120" t="s">
-        <v>1740</v>
+        <v>1932</v>
       </c>
     </row>
     <row r="121" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A121" t="s">
-        <v>1741</v>
+        <v>1933</v>
       </c>
       <c r="B121" t="s">
-        <v>1742</v>
+        <v>1934</v>
       </c>
       <c r="C121">
         <v>12</v>
@@ -16054,18 +17637,18 @@
         <v>36</v>
       </c>
       <c r="F121" t="s">
-        <v>1743</v>
+        <v>1935</v>
       </c>
       <c r="G121" t="s">
-        <v>1744</v>
+        <v>1936</v>
       </c>
     </row>
     <row r="122" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A122" t="s">
-        <v>1745</v>
+        <v>1937</v>
       </c>
       <c r="B122" t="s">
-        <v>1746</v>
+        <v>1938</v>
       </c>
       <c r="C122">
         <v>11</v>
@@ -16077,18 +17660,18 @@
         <v>67</v>
       </c>
       <c r="F122" t="s">
-        <v>1747</v>
+        <v>1939</v>
       </c>
       <c r="G122" t="s">
-        <v>1748</v>
+        <v>1940</v>
       </c>
     </row>
     <row r="123" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A123" t="s">
-        <v>1749</v>
+        <v>1941</v>
       </c>
       <c r="B123" t="s">
-        <v>1750</v>
+        <v>1942</v>
       </c>
       <c r="C123">
         <v>13</v>
@@ -16100,18 +17683,18 @@
         <v>679</v>
       </c>
       <c r="F123" t="s">
-        <v>1751</v>
+        <v>1943</v>
       </c>
       <c r="G123" t="s">
-        <v>1752</v>
+        <v>1944</v>
       </c>
     </row>
     <row r="124" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A124" t="s">
-        <v>1753</v>
+        <v>1945</v>
       </c>
       <c r="B124" t="s">
-        <v>1754</v>
+        <v>1946</v>
       </c>
       <c r="C124">
         <v>12</v>
@@ -16123,18 +17706,18 @@
         <v>11</v>
       </c>
       <c r="F124" t="s">
-        <v>1755</v>
+        <v>1947</v>
       </c>
       <c r="G124" t="s">
-        <v>1756</v>
+        <v>1948</v>
       </c>
     </row>
     <row r="125" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A125" t="s">
-        <v>1757</v>
+        <v>1949</v>
       </c>
       <c r="B125" t="s">
-        <v>1758</v>
+        <v>1950</v>
       </c>
       <c r="C125">
         <v>13</v>
@@ -16146,18 +17729,18 @@
         <v>11</v>
       </c>
       <c r="F125" t="s">
-        <v>1759</v>
+        <v>1951</v>
       </c>
       <c r="G125" t="s">
-        <v>1760</v>
+        <v>1952</v>
       </c>
     </row>
     <row r="126" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A126" t="s">
-        <v>1761</v>
+        <v>1953</v>
       </c>
       <c r="B126" t="s">
-        <v>1762</v>
+        <v>1954</v>
       </c>
       <c r="C126">
         <v>13</v>
@@ -16169,18 +17752,18 @@
         <v>22</v>
       </c>
       <c r="F126" t="s">
-        <v>1763</v>
+        <v>1955</v>
       </c>
       <c r="G126" t="s">
-        <v>1764</v>
+        <v>1956</v>
       </c>
     </row>
     <row r="127" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A127" t="s">
-        <v>1765</v>
+        <v>1957</v>
       </c>
       <c r="B127" t="s">
-        <v>1766</v>
+        <v>1958</v>
       </c>
       <c r="C127">
         <v>12</v>
@@ -16192,18 +17775,18 @@
         <v>36</v>
       </c>
       <c r="F127" t="s">
-        <v>1767</v>
+        <v>1959</v>
       </c>
       <c r="G127" t="s">
-        <v>1768</v>
+        <v>1960</v>
       </c>
     </row>
     <row r="128" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A128" t="s">
-        <v>1769</v>
+        <v>1961</v>
       </c>
       <c r="B128" t="s">
-        <v>1770</v>
+        <v>1962</v>
       </c>
       <c r="C128">
         <v>12</v>
@@ -16215,18 +17798,18 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>1771</v>
+        <v>1963</v>
       </c>
       <c r="G128" t="s">
-        <v>1772</v>
+        <v>1964</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A129" t="s">
-        <v>1773</v>
+        <v>1965</v>
       </c>
       <c r="B129" t="s">
-        <v>1774</v>
+        <v>1966</v>
       </c>
       <c r="C129">
         <v>11</v>
@@ -16238,18 +17821,18 @@
         <v>67</v>
       </c>
       <c r="F129" t="s">
-        <v>1775</v>
+        <v>1967</v>
       </c>
       <c r="G129" t="s">
-        <v>1776</v>
+        <v>1968</v>
       </c>
     </row>
     <row r="130" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A130" t="s">
-        <v>1777</v>
+        <v>1969</v>
       </c>
       <c r="B130" t="s">
-        <v>1778</v>
+        <v>1970</v>
       </c>
       <c r="C130">
         <v>13</v>
@@ -16261,18 +17844,18 @@
         <v>22</v>
       </c>
       <c r="F130" t="s">
-        <v>1779</v>
+        <v>1971</v>
       </c>
       <c r="G130" t="s">
-        <v>1780</v>
+        <v>1972</v>
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A131" t="s">
-        <v>1721</v>
+        <v>1913</v>
       </c>
       <c r="B131" t="s">
-        <v>1781</v>
+        <v>1973</v>
       </c>
       <c r="C131">
         <v>11</v>
@@ -16284,18 +17867,18 @@
         <v>41</v>
       </c>
       <c r="F131" t="s">
-        <v>1782</v>
+        <v>1974</v>
       </c>
       <c r="G131" t="s">
-        <v>1783</v>
+        <v>1975</v>
       </c>
     </row>
     <row r="132" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A132" t="s">
-        <v>1784</v>
+        <v>1976</v>
       </c>
       <c r="B132" t="s">
-        <v>1785</v>
+        <v>1977</v>
       </c>
       <c r="C132">
         <v>13</v>
@@ -16307,18 +17890,18 @@
         <v>11</v>
       </c>
       <c r="F132" t="s">
-        <v>1786</v>
+        <v>1978</v>
       </c>
       <c r="G132" t="s">
-        <v>1787</v>
+        <v>1979</v>
       </c>
     </row>
     <row r="133" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A133" t="s">
-        <v>1788</v>
+        <v>1980</v>
       </c>
       <c r="B133" t="s">
-        <v>1789</v>
+        <v>1981</v>
       </c>
       <c r="C133">
         <v>13</v>
@@ -16330,18 +17913,18 @@
         <v>72</v>
       </c>
       <c r="F133" t="s">
-        <v>1395</v>
+        <v>1588</v>
       </c>
       <c r="G133" t="s">
-        <v>1790</v>
+        <v>1982</v>
       </c>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A134" t="s">
-        <v>1791</v>
+        <v>1983</v>
       </c>
       <c r="B134" t="s">
-        <v>1792</v>
+        <v>1984</v>
       </c>
       <c r="C134">
         <v>11</v>
@@ -16353,18 +17936,18 @@
         <v>11</v>
       </c>
       <c r="F134" t="s">
-        <v>1793</v>
+        <v>1985</v>
       </c>
       <c r="G134" t="s">
-        <v>1794</v>
+        <v>1986</v>
       </c>
     </row>
     <row r="135" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A135" t="s">
-        <v>1795</v>
+        <v>1987</v>
       </c>
       <c r="B135" t="s">
-        <v>1796</v>
+        <v>1988</v>
       </c>
       <c r="C135">
         <v>13</v>
@@ -16376,10 +17959,10 @@
         <v>11</v>
       </c>
       <c r="F135" t="s">
-        <v>1797</v>
+        <v>1989</v>
       </c>
       <c r="G135" t="s">
-        <v>1798</v>
+        <v>1990</v>
       </c>
     </row>
     <row r="136" spans="1:7" x14ac:dyDescent="0.4">
@@ -16387,7 +17970,7 @@
         <v>484</v>
       </c>
       <c r="B136" t="s">
-        <v>1799</v>
+        <v>1991</v>
       </c>
       <c r="C136">
         <v>13</v>
@@ -16402,15 +17985,15 @@
         <v>587</v>
       </c>
       <c r="G136" t="s">
-        <v>1800</v>
+        <v>1992</v>
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A137" t="s">
-        <v>1801</v>
+        <v>1011</v>
       </c>
       <c r="B137" t="s">
-        <v>1802</v>
+        <v>1993</v>
       </c>
       <c r="C137">
         <v>12</v>
@@ -16422,18 +18005,18 @@
         <v>27</v>
       </c>
       <c r="F137" t="s">
-        <v>1803</v>
+        <v>1994</v>
       </c>
       <c r="G137" t="s">
-        <v>1804</v>
+        <v>1995</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A138" t="s">
-        <v>1805</v>
+        <v>1996</v>
       </c>
       <c r="B138" t="s">
-        <v>1806</v>
+        <v>1997</v>
       </c>
       <c r="C138">
         <v>13</v>
@@ -16448,15 +18031,15 @@
         <v>272</v>
       </c>
       <c r="G138" t="s">
-        <v>1807</v>
+        <v>1998</v>
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A139" t="s">
-        <v>1808</v>
+        <v>1999</v>
       </c>
       <c r="B139" t="s">
-        <v>1809</v>
+        <v>2000</v>
       </c>
       <c r="C139">
         <v>13</v>
@@ -16468,18 +18051,18 @@
         <v>58</v>
       </c>
       <c r="F139" t="s">
-        <v>1428</v>
+        <v>1134</v>
       </c>
       <c r="G139" t="s">
-        <v>1810</v>
+        <v>2001</v>
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A140" t="s">
-        <v>1811</v>
+        <v>2002</v>
       </c>
       <c r="B140" t="s">
-        <v>1812</v>
+        <v>2003</v>
       </c>
       <c r="C140">
         <v>11</v>
@@ -16491,18 +18074,18 @@
         <v>67</v>
       </c>
       <c r="F140" t="s">
-        <v>1813</v>
+        <v>2004</v>
       </c>
       <c r="G140" t="s">
-        <v>1814</v>
+        <v>2005</v>
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A141" t="s">
-        <v>1815</v>
+        <v>2006</v>
       </c>
       <c r="B141" t="s">
-        <v>1816</v>
+        <v>2007</v>
       </c>
       <c r="C141">
         <v>12</v>
@@ -16514,18 +18097,18 @@
         <v>67</v>
       </c>
       <c r="F141" t="s">
-        <v>1817</v>
+        <v>2008</v>
       </c>
       <c r="G141" t="s">
-        <v>1818</v>
+        <v>2009</v>
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A142" t="s">
-        <v>1819</v>
+        <v>2010</v>
       </c>
       <c r="B142" t="s">
-        <v>1820</v>
+        <v>2011</v>
       </c>
       <c r="C142">
         <v>11</v>
@@ -16540,15 +18123,15 @@
         <v>376</v>
       </c>
       <c r="G142" t="s">
-        <v>1821</v>
+        <v>2012</v>
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A143" t="s">
-        <v>1822</v>
+        <v>2013</v>
       </c>
       <c r="B143" t="s">
-        <v>1823</v>
+        <v>2014</v>
       </c>
       <c r="C143">
         <v>12</v>
@@ -16560,18 +18143,18 @@
         <v>22</v>
       </c>
       <c r="F143" t="s">
-        <v>1505</v>
+        <v>1697</v>
       </c>
       <c r="G143" t="s">
-        <v>1824</v>
+        <v>2015</v>
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A144" t="s">
-        <v>1825</v>
+        <v>2016</v>
       </c>
       <c r="B144" t="s">
-        <v>1826</v>
+        <v>2017</v>
       </c>
       <c r="C144">
         <v>13</v>
@@ -16583,18 +18166,18 @@
         <v>72</v>
       </c>
       <c r="F144" t="s">
-        <v>1827</v>
+        <v>2018</v>
       </c>
       <c r="G144" t="s">
-        <v>1828</v>
+        <v>2019</v>
       </c>
     </row>
     <row r="145" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A145" t="s">
-        <v>1829</v>
+        <v>2020</v>
       </c>
       <c r="B145" t="s">
-        <v>1830</v>
+        <v>2021</v>
       </c>
       <c r="C145">
         <v>11</v>
@@ -16609,15 +18192,15 @@
         <v>117</v>
       </c>
       <c r="G145" t="s">
-        <v>1831</v>
+        <v>2022</v>
       </c>
     </row>
     <row r="146" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A146" t="s">
-        <v>1832</v>
+        <v>2023</v>
       </c>
       <c r="B146" t="s">
-        <v>1833</v>
+        <v>2024</v>
       </c>
       <c r="C146">
         <v>12</v>
@@ -16629,18 +18212,18 @@
         <v>72</v>
       </c>
       <c r="F146" t="s">
-        <v>1834</v>
+        <v>2025</v>
       </c>
       <c r="G146" t="s">
-        <v>1835</v>
+        <v>2026</v>
       </c>
     </row>
     <row r="147" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A147" t="s">
-        <v>1836</v>
+        <v>2027</v>
       </c>
       <c r="B147" t="s">
-        <v>1837</v>
+        <v>2028</v>
       </c>
       <c r="C147">
         <v>13</v>
@@ -16652,18 +18235,18 @@
         <v>11</v>
       </c>
       <c r="F147" t="s">
-        <v>1838</v>
+        <v>2029</v>
       </c>
       <c r="G147" t="s">
-        <v>1839</v>
+        <v>2030</v>
       </c>
     </row>
     <row r="148" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A148" t="s">
-        <v>1840</v>
+        <v>2031</v>
       </c>
       <c r="B148" t="s">
-        <v>1841</v>
+        <v>2032</v>
       </c>
       <c r="C148">
         <v>11</v>
@@ -16675,18 +18258,18 @@
         <v>22</v>
       </c>
       <c r="F148" t="s">
-        <v>1842</v>
+        <v>2033</v>
       </c>
       <c r="G148" t="s">
-        <v>1843</v>
+        <v>2034</v>
       </c>
     </row>
     <row r="149" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A149" t="s">
-        <v>1844</v>
+        <v>2035</v>
       </c>
       <c r="B149" t="s">
-        <v>1845</v>
+        <v>2036</v>
       </c>
       <c r="C149">
         <v>11</v>
@@ -16698,18 +18281,18 @@
         <v>11</v>
       </c>
       <c r="F149" t="s">
-        <v>1846</v>
+        <v>2037</v>
       </c>
       <c r="G149" t="s">
-        <v>1847</v>
+        <v>2038</v>
       </c>
     </row>
     <row r="150" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A150" t="s">
-        <v>1848</v>
+        <v>2039</v>
       </c>
       <c r="B150" t="s">
-        <v>1849</v>
+        <v>2040</v>
       </c>
       <c r="C150">
         <v>11</v>
@@ -16721,18 +18304,18 @@
         <v>27</v>
       </c>
       <c r="F150" t="s">
-        <v>1850</v>
+        <v>2041</v>
       </c>
       <c r="G150" t="s">
-        <v>1851</v>
+        <v>2042</v>
       </c>
     </row>
     <row r="151" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A151" t="s">
-        <v>1852</v>
+        <v>2043</v>
       </c>
       <c r="B151" t="s">
-        <v>1853</v>
+        <v>2044</v>
       </c>
       <c r="C151">
         <v>12</v>
@@ -16744,18 +18327,18 @@
         <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>1854</v>
+        <v>2045</v>
       </c>
       <c r="G151" t="s">
-        <v>1855</v>
+        <v>2046</v>
       </c>
     </row>
     <row r="152" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A152" t="s">
-        <v>1856</v>
+        <v>2047</v>
       </c>
       <c r="B152" t="s">
-        <v>1857</v>
+        <v>2048</v>
       </c>
       <c r="C152">
         <v>12</v>
@@ -16767,18 +18350,18 @@
         <v>72</v>
       </c>
       <c r="F152" t="s">
-        <v>1485</v>
+        <v>1677</v>
       </c>
       <c r="G152" t="s">
-        <v>1858</v>
+        <v>2049</v>
       </c>
     </row>
     <row r="153" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A153" t="s">
-        <v>1859</v>
+        <v>2050</v>
       </c>
       <c r="B153" t="s">
-        <v>1860</v>
+        <v>2051</v>
       </c>
       <c r="C153">
         <v>12</v>
@@ -16790,18 +18373,18 @@
         <v>16</v>
       </c>
       <c r="F153" t="s">
-        <v>1861</v>
+        <v>2052</v>
       </c>
       <c r="G153" t="s">
-        <v>1862</v>
+        <v>2053</v>
       </c>
     </row>
     <row r="154" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A154" t="s">
-        <v>1863</v>
+        <v>2054</v>
       </c>
       <c r="B154" t="s">
-        <v>1864</v>
+        <v>2055</v>
       </c>
       <c r="C154">
         <v>13</v>
@@ -16813,18 +18396,18 @@
         <v>41</v>
       </c>
       <c r="F154" t="s">
-        <v>1865</v>
+        <v>2056</v>
       </c>
       <c r="G154" t="s">
-        <v>1866</v>
+        <v>2057</v>
       </c>
     </row>
     <row r="155" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A155" t="s">
-        <v>1867</v>
+        <v>2058</v>
       </c>
       <c r="B155" t="s">
-        <v>1868</v>
+        <v>2059</v>
       </c>
       <c r="C155">
         <v>13</v>
@@ -16839,15 +18422,15 @@
         <v>196</v>
       </c>
       <c r="G155" t="s">
-        <v>1869</v>
+        <v>2060</v>
       </c>
     </row>
     <row r="156" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A156" t="s">
-        <v>1870</v>
+        <v>2061</v>
       </c>
       <c r="B156" t="s">
-        <v>1871</v>
+        <v>2062</v>
       </c>
       <c r="C156">
         <v>11</v>
@@ -16859,18 +18442,18 @@
         <v>58</v>
       </c>
       <c r="F156" t="s">
-        <v>1872</v>
+        <v>2063</v>
       </c>
       <c r="G156" t="s">
-        <v>1873</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="157" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A157" t="s">
-        <v>1874</v>
+        <v>2065</v>
       </c>
       <c r="B157" t="s">
-        <v>1875</v>
+        <v>2066</v>
       </c>
       <c r="C157">
         <v>11</v>
@@ -16882,18 +18465,18 @@
         <v>67</v>
       </c>
       <c r="F157" t="s">
-        <v>1876</v>
+        <v>2067</v>
       </c>
       <c r="G157" t="s">
-        <v>1877</v>
+        <v>2068</v>
       </c>
     </row>
     <row r="158" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A158" t="s">
-        <v>1878</v>
+        <v>2069</v>
       </c>
       <c r="B158" t="s">
-        <v>1879</v>
+        <v>2070</v>
       </c>
       <c r="C158">
         <v>11</v>
@@ -16905,18 +18488,18 @@
         <v>11</v>
       </c>
       <c r="F158" t="s">
-        <v>1688</v>
+        <v>1880</v>
       </c>
       <c r="G158" t="s">
-        <v>1880</v>
+        <v>2071</v>
       </c>
     </row>
     <row r="159" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A159" t="s">
-        <v>1881</v>
+        <v>2072</v>
       </c>
       <c r="B159" t="s">
-        <v>1882</v>
+        <v>2073</v>
       </c>
       <c r="C159">
         <v>12</v>
@@ -16928,18 +18511,18 @@
         <v>58</v>
       </c>
       <c r="F159" t="s">
-        <v>1883</v>
+        <v>2074</v>
       </c>
       <c r="G159" t="s">
-        <v>1884</v>
+        <v>2075</v>
       </c>
     </row>
     <row r="160" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A160" t="s">
-        <v>1885</v>
+        <v>2076</v>
       </c>
       <c r="B160" t="s">
-        <v>1886</v>
+        <v>2077</v>
       </c>
       <c r="C160">
         <v>12</v>
@@ -16951,18 +18534,18 @@
         <v>36</v>
       </c>
       <c r="F160" t="s">
-        <v>1887</v>
+        <v>2078</v>
       </c>
       <c r="G160" t="s">
-        <v>1888</v>
+        <v>2079</v>
       </c>
     </row>
     <row r="161" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A161" t="s">
-        <v>1889</v>
+        <v>2080</v>
       </c>
       <c r="B161" t="s">
-        <v>1890</v>
+        <v>2081</v>
       </c>
       <c r="C161">
         <v>12</v>
@@ -16974,18 +18557,18 @@
         <v>16</v>
       </c>
       <c r="F161" t="s">
-        <v>1891</v>
+        <v>2082</v>
       </c>
       <c r="G161" t="s">
-        <v>1892</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="162" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A162" t="s">
-        <v>1893</v>
+        <v>2084</v>
       </c>
       <c r="B162" t="s">
-        <v>1894</v>
+        <v>2085</v>
       </c>
       <c r="C162">
         <v>12</v>
@@ -16997,18 +18580,18 @@
         <v>41</v>
       </c>
       <c r="F162" t="s">
-        <v>1895</v>
+        <v>2086</v>
       </c>
       <c r="G162" t="s">
-        <v>1896</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="163" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A163" t="s">
-        <v>1897</v>
+        <v>2088</v>
       </c>
       <c r="B163" t="s">
-        <v>1898</v>
+        <v>2089</v>
       </c>
       <c r="C163">
         <v>12</v>
@@ -17020,18 +18603,18 @@
         <v>41</v>
       </c>
       <c r="F163" t="s">
-        <v>1899</v>
+        <v>2090</v>
       </c>
       <c r="G163" t="s">
-        <v>1900</v>
+        <v>2091</v>
       </c>
     </row>
     <row r="164" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A164" t="s">
-        <v>1901</v>
+        <v>2092</v>
       </c>
       <c r="B164" t="s">
-        <v>1902</v>
+        <v>2093</v>
       </c>
       <c r="C164">
         <v>13</v>
@@ -17046,15 +18629,15 @@
         <v>595</v>
       </c>
       <c r="G164" t="s">
-        <v>1903</v>
+        <v>2094</v>
       </c>
     </row>
     <row r="165" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A165" t="s">
-        <v>1904</v>
+        <v>2095</v>
       </c>
       <c r="B165" t="s">
-        <v>1905</v>
+        <v>2096</v>
       </c>
       <c r="C165">
         <v>11</v>
@@ -17066,18 +18649,18 @@
         <v>22</v>
       </c>
       <c r="F165" t="s">
-        <v>1906</v>
+        <v>2097</v>
       </c>
       <c r="G165" t="s">
-        <v>1907</v>
+        <v>2098</v>
       </c>
     </row>
     <row r="166" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A166" t="s">
-        <v>1218</v>
+        <v>1411</v>
       </c>
       <c r="B166" t="s">
-        <v>1908</v>
+        <v>2099</v>
       </c>
       <c r="C166">
         <v>12</v>
@@ -17089,18 +18672,18 @@
         <v>41</v>
       </c>
       <c r="F166" t="s">
-        <v>1909</v>
+        <v>2100</v>
       </c>
       <c r="G166" t="s">
-        <v>1910</v>
+        <v>2101</v>
       </c>
     </row>
     <row r="167" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A167" t="s">
-        <v>1911</v>
+        <v>2102</v>
       </c>
       <c r="B167" t="s">
-        <v>1912</v>
+        <v>2103</v>
       </c>
       <c r="C167">
         <v>13</v>
@@ -17112,18 +18695,18 @@
         <v>72</v>
       </c>
       <c r="F167" t="s">
-        <v>1913</v>
+        <v>2104</v>
       </c>
       <c r="G167" t="s">
-        <v>1914</v>
+        <v>2105</v>
       </c>
     </row>
     <row r="168" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A168" t="s">
-        <v>1915</v>
+        <v>2106</v>
       </c>
       <c r="B168" t="s">
-        <v>1916</v>
+        <v>2107</v>
       </c>
       <c r="C168">
         <v>12</v>
@@ -17135,18 +18718,18 @@
         <v>11</v>
       </c>
       <c r="F168" t="s">
-        <v>1917</v>
+        <v>2108</v>
       </c>
       <c r="G168" t="s">
-        <v>1918</v>
+        <v>2109</v>
       </c>
     </row>
     <row r="169" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A169" t="s">
-        <v>1919</v>
+        <v>2110</v>
       </c>
       <c r="B169" t="s">
-        <v>1920</v>
+        <v>2111</v>
       </c>
       <c r="C169">
         <v>11</v>
@@ -17158,18 +18741,18 @@
         <v>72</v>
       </c>
       <c r="F169" t="s">
-        <v>1921</v>
+        <v>2112</v>
       </c>
       <c r="G169" t="s">
-        <v>1922</v>
+        <v>2113</v>
       </c>
     </row>
     <row r="170" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A170" t="s">
-        <v>1923</v>
+        <v>2114</v>
       </c>
       <c r="B170" t="s">
-        <v>1924</v>
+        <v>2115</v>
       </c>
       <c r="C170">
         <v>13</v>
@@ -17181,18 +18764,18 @@
         <v>41</v>
       </c>
       <c r="F170" t="s">
-        <v>1925</v>
+        <v>2116</v>
       </c>
       <c r="G170" t="s">
-        <v>1926</v>
+        <v>2117</v>
       </c>
     </row>
     <row r="171" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A171" t="s">
-        <v>1927</v>
+        <v>2118</v>
       </c>
       <c r="B171" t="s">
-        <v>1928</v>
+        <v>2119</v>
       </c>
       <c r="C171">
         <v>12</v>
@@ -17204,18 +18787,18 @@
         <v>58</v>
       </c>
       <c r="F171" t="s">
-        <v>1929</v>
+        <v>2120</v>
       </c>
       <c r="G171" t="s">
-        <v>1930</v>
+        <v>2121</v>
       </c>
     </row>
     <row r="172" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A172" t="s">
-        <v>1931</v>
+        <v>2122</v>
       </c>
       <c r="B172" t="s">
-        <v>1932</v>
+        <v>2123</v>
       </c>
       <c r="C172">
         <v>12</v>
@@ -17227,18 +18810,18 @@
         <v>41</v>
       </c>
       <c r="F172" t="s">
-        <v>1933</v>
+        <v>2124</v>
       </c>
       <c r="G172" t="s">
-        <v>1934</v>
+        <v>2125</v>
       </c>
     </row>
     <row r="173" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A173" t="s">
-        <v>1935</v>
+        <v>2126</v>
       </c>
       <c r="B173" t="s">
-        <v>1936</v>
+        <v>2127</v>
       </c>
       <c r="C173">
         <v>12</v>
@@ -17250,18 +18833,18 @@
         <v>27</v>
       </c>
       <c r="F173" t="s">
-        <v>1937</v>
+        <v>2128</v>
       </c>
       <c r="G173" t="s">
-        <v>1938</v>
+        <v>2129</v>
       </c>
     </row>
     <row r="174" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A174" t="s">
-        <v>1939</v>
+        <v>2130</v>
       </c>
       <c r="B174" t="s">
-        <v>1940</v>
+        <v>2131</v>
       </c>
       <c r="C174">
         <v>11</v>
@@ -17276,15 +18859,15 @@
         <v>46</v>
       </c>
       <c r="G174" t="s">
-        <v>1941</v>
+        <v>2132</v>
       </c>
     </row>
     <row r="175" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A175" t="s">
-        <v>1942</v>
+        <v>2133</v>
       </c>
       <c r="B175" t="s">
-        <v>1943</v>
+        <v>2134</v>
       </c>
       <c r="C175">
         <v>12</v>
@@ -17296,18 +18879,18 @@
         <v>67</v>
       </c>
       <c r="F175" t="s">
-        <v>1944</v>
+        <v>2135</v>
       </c>
       <c r="G175" t="s">
-        <v>1945</v>
+        <v>2136</v>
       </c>
     </row>
     <row r="176" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A176" t="s">
-        <v>1946</v>
+        <v>2137</v>
       </c>
       <c r="B176" t="s">
-        <v>1947</v>
+        <v>2138</v>
       </c>
       <c r="C176">
         <v>13</v>
@@ -17322,15 +18905,15 @@
         <v>595</v>
       </c>
       <c r="G176" t="s">
-        <v>1948</v>
+        <v>2139</v>
       </c>
     </row>
     <row r="177" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A177" t="s">
-        <v>1949</v>
+        <v>2140</v>
       </c>
       <c r="B177" t="s">
-        <v>1950</v>
+        <v>2141</v>
       </c>
       <c r="C177">
         <v>13</v>
@@ -17342,18 +18925,18 @@
         <v>67</v>
       </c>
       <c r="F177" t="s">
-        <v>1951</v>
+        <v>2142</v>
       </c>
       <c r="G177" t="s">
-        <v>1952</v>
+        <v>2143</v>
       </c>
     </row>
     <row r="178" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A178" t="s">
-        <v>1953</v>
+        <v>2144</v>
       </c>
       <c r="B178" t="s">
-        <v>1954</v>
+        <v>2145</v>
       </c>
       <c r="C178">
         <v>13</v>
@@ -17365,18 +18948,18 @@
         <v>27</v>
       </c>
       <c r="F178" t="s">
-        <v>1955</v>
+        <v>2146</v>
       </c>
       <c r="G178" t="s">
-        <v>1956</v>
+        <v>2147</v>
       </c>
     </row>
     <row r="179" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A179" t="s">
-        <v>1957</v>
+        <v>2148</v>
       </c>
       <c r="B179" t="s">
-        <v>1958</v>
+        <v>2149</v>
       </c>
       <c r="C179">
         <v>13</v>
@@ -17388,18 +18971,18 @@
         <v>27</v>
       </c>
       <c r="F179" t="s">
-        <v>1959</v>
+        <v>2150</v>
       </c>
       <c r="G179" t="s">
-        <v>1960</v>
+        <v>2151</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A180" t="s">
-        <v>1961</v>
+        <v>2152</v>
       </c>
       <c r="B180" t="s">
-        <v>1962</v>
+        <v>2153</v>
       </c>
       <c r="C180">
         <v>13</v>
@@ -17411,18 +18994,18 @@
         <v>22</v>
       </c>
       <c r="F180" t="s">
-        <v>1963</v>
+        <v>2154</v>
       </c>
       <c r="G180" t="s">
-        <v>1964</v>
+        <v>2155</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A181" t="s">
-        <v>1965</v>
+        <v>2156</v>
       </c>
       <c r="B181" t="s">
-        <v>1966</v>
+        <v>2157</v>
       </c>
       <c r="C181">
         <v>11</v>
@@ -17434,18 +19017,18 @@
         <v>11</v>
       </c>
       <c r="F181" t="s">
-        <v>1967</v>
+        <v>2158</v>
       </c>
       <c r="G181" t="s">
-        <v>1968</v>
+        <v>2159</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A182" t="s">
-        <v>1969</v>
+        <v>2160</v>
       </c>
       <c r="B182" t="s">
-        <v>1970</v>
+        <v>2161</v>
       </c>
       <c r="C182">
         <v>11</v>
@@ -17457,18 +19040,18 @@
         <v>22</v>
       </c>
       <c r="F182" t="s">
-        <v>1842</v>
+        <v>2033</v>
       </c>
       <c r="G182" t="s">
-        <v>1971</v>
+        <v>2162</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A183" t="s">
-        <v>1972</v>
+        <v>2163</v>
       </c>
       <c r="B183" t="s">
-        <v>1973</v>
+        <v>2164</v>
       </c>
       <c r="C183">
         <v>12</v>
@@ -17480,18 +19063,18 @@
         <v>36</v>
       </c>
       <c r="F183" t="s">
-        <v>1974</v>
+        <v>2165</v>
       </c>
       <c r="G183" t="s">
-        <v>1975</v>
+        <v>2166</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A184" t="s">
-        <v>1976</v>
+        <v>2167</v>
       </c>
       <c r="B184" t="s">
-        <v>1977</v>
+        <v>2168</v>
       </c>
       <c r="C184">
         <v>12</v>
@@ -17503,18 +19086,18 @@
         <v>22</v>
       </c>
       <c r="F184" t="s">
-        <v>1978</v>
+        <v>2169</v>
       </c>
       <c r="G184" t="s">
-        <v>1979</v>
+        <v>2170</v>
       </c>
     </row>
     <row r="185" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A185" t="s">
-        <v>1980</v>
+        <v>2171</v>
       </c>
       <c r="B185" t="s">
-        <v>1981</v>
+        <v>2172</v>
       </c>
       <c r="C185">
         <v>13</v>
@@ -17526,18 +19109,18 @@
         <v>72</v>
       </c>
       <c r="F185" t="s">
-        <v>1982</v>
+        <v>2173</v>
       </c>
       <c r="G185" t="s">
-        <v>1983</v>
+        <v>2174</v>
       </c>
     </row>
     <row r="186" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A186" t="s">
-        <v>1984</v>
+        <v>2175</v>
       </c>
       <c r="B186" t="s">
-        <v>1985</v>
+        <v>2176</v>
       </c>
       <c r="C186">
         <v>13</v>
@@ -17549,18 +19132,18 @@
         <v>36</v>
       </c>
       <c r="F186" t="s">
-        <v>1986</v>
+        <v>2177</v>
       </c>
       <c r="G186" t="s">
-        <v>1987</v>
+        <v>2178</v>
       </c>
     </row>
     <row r="187" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A187" t="s">
-        <v>1988</v>
+        <v>2179</v>
       </c>
       <c r="B187" t="s">
-        <v>1989</v>
+        <v>2180</v>
       </c>
       <c r="C187">
         <v>11</v>
@@ -17572,18 +19155,18 @@
         <v>41</v>
       </c>
       <c r="F187" t="s">
-        <v>1990</v>
+        <v>2181</v>
       </c>
       <c r="G187" t="s">
-        <v>1991</v>
+        <v>2182</v>
       </c>
     </row>
     <row r="188" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A188" t="s">
-        <v>1992</v>
+        <v>2183</v>
       </c>
       <c r="B188" t="s">
-        <v>1993</v>
+        <v>2184</v>
       </c>
       <c r="C188">
         <v>11</v>
@@ -17595,18 +19178,18 @@
         <v>36</v>
       </c>
       <c r="F188" t="s">
-        <v>1994</v>
+        <v>2185</v>
       </c>
       <c r="G188" t="s">
-        <v>1995</v>
+        <v>2186</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.4">
       <c r="A189" t="s">
-        <v>1996</v>
+        <v>2187</v>
       </c>
       <c r="B189" t="s">
-        <v>1997</v>
+        <v>2188</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -17618,10 +19201,10 @@
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>1998</v>
+        <v>2189</v>
       </c>
       <c r="G189" t="s">
-        <v>1999</v>
+        <v>2190</v>
       </c>
     </row>
   </sheetData>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -5,19 +5,32 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D22095D2-453B-4B0B-9777-8E9E540E174E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AB914C8F-171A-415A-A297-DB2ECDF6017E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30" yWindow="750" windowWidth="28770" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
     <sheet name="PH" sheetId="2" r:id="rId2"/>
     <sheet name="BG1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -6376,14 +6389,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H229"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6409,7 +6422,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -6432,7 +6445,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -6455,7 +6468,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -6478,7 +6491,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -6501,7 +6514,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -6524,7 +6537,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -6547,7 +6560,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -6570,7 +6583,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -6593,7 +6606,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -6616,7 +6629,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -6639,7 +6652,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -6662,7 +6675,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -6685,7 +6698,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -6708,7 +6721,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -6731,7 +6744,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -6754,7 +6767,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -6777,7 +6790,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -6800,7 +6813,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -6823,7 +6836,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -6846,7 +6859,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -6869,7 +6882,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -6892,7 +6905,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -6915,7 +6928,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>107</v>
       </c>
@@ -6938,7 +6951,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -6961,7 +6974,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -6984,7 +6997,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>119</v>
       </c>
@@ -7007,7 +7020,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -7030,7 +7043,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -7053,7 +7066,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -7076,7 +7089,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -7099,7 +7112,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -7122,7 +7135,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -7145,7 +7158,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -7168,7 +7181,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -7191,7 +7204,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -7214,7 +7227,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -7237,7 +7250,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>162</v>
       </c>
@@ -7260,7 +7273,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -7283,7 +7296,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>170</v>
       </c>
@@ -7306,7 +7319,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>174</v>
       </c>
@@ -7329,7 +7342,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>178</v>
       </c>
@@ -7352,7 +7365,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -7375,7 +7388,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -7398,7 +7411,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>190</v>
       </c>
@@ -7421,7 +7434,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -7444,7 +7457,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>198</v>
       </c>
@@ -7467,7 +7480,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -7490,7 +7503,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -7513,7 +7526,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -7536,7 +7549,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>214</v>
       </c>
@@ -7559,7 +7572,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>218</v>
       </c>
@@ -7582,7 +7595,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -7605,7 +7618,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>226</v>
       </c>
@@ -7628,7 +7641,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>230</v>
       </c>
@@ -7651,7 +7664,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
@@ -7674,7 +7687,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>238</v>
       </c>
@@ -7697,7 +7710,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>242</v>
       </c>
@@ -7720,7 +7733,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>246</v>
       </c>
@@ -7743,7 +7756,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -7766,7 +7779,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>254</v>
       </c>
@@ -7789,7 +7802,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -7812,7 +7825,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>262</v>
       </c>
@@ -7835,7 +7848,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>266</v>
       </c>
@@ -7858,7 +7871,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>270</v>
       </c>
@@ -7881,7 +7894,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>274</v>
       </c>
@@ -7904,7 +7917,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>278</v>
       </c>
@@ -7927,7 +7940,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -7950,7 +7963,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>286</v>
       </c>
@@ -7973,7 +7986,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>290</v>
       </c>
@@ -7996,7 +8009,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>294</v>
       </c>
@@ -8019,7 +8032,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>298</v>
       </c>
@@ -8042,7 +8055,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>302</v>
       </c>
@@ -8065,7 +8078,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>306</v>
       </c>
@@ -8088,7 +8101,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>310</v>
       </c>
@@ -8111,7 +8124,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>314</v>
       </c>
@@ -8134,7 +8147,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>318</v>
       </c>
@@ -8157,7 +8170,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>322</v>
       </c>
@@ -8180,7 +8193,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>326</v>
       </c>
@@ -8203,7 +8216,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>330</v>
       </c>
@@ -8226,7 +8239,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>334</v>
       </c>
@@ -8249,7 +8262,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>338</v>
       </c>
@@ -8272,7 +8285,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>342</v>
       </c>
@@ -8295,7 +8308,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>346</v>
       </c>
@@ -8318,7 +8331,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>350</v>
       </c>
@@ -8341,7 +8354,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>354</v>
       </c>
@@ -8364,7 +8377,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>358</v>
       </c>
@@ -8387,7 +8400,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>362</v>
       </c>
@@ -8410,7 +8423,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>366</v>
       </c>
@@ -8433,7 +8446,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>370</v>
       </c>
@@ -8456,7 +8469,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>374</v>
       </c>
@@ -8479,7 +8492,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>378</v>
       </c>
@@ -8502,7 +8515,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>382</v>
       </c>
@@ -8525,7 +8538,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>386</v>
       </c>
@@ -8548,7 +8561,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>389</v>
       </c>
@@ -8571,7 +8584,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>393</v>
       </c>
@@ -8594,7 +8607,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>397</v>
       </c>
@@ -8617,7 +8630,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>401</v>
       </c>
@@ -8640,7 +8653,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>405</v>
       </c>
@@ -8663,7 +8676,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>409</v>
       </c>
@@ -8686,7 +8699,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>413</v>
       </c>
@@ -8709,7 +8722,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>417</v>
       </c>
@@ -8732,7 +8745,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>421</v>
       </c>
@@ -8755,7 +8768,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>425</v>
       </c>
@@ -8778,7 +8791,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>429</v>
       </c>
@@ -8801,7 +8814,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>433</v>
       </c>
@@ -8824,7 +8837,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>436</v>
       </c>
@@ -8847,7 +8860,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>440</v>
       </c>
@@ -8870,7 +8883,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>444</v>
       </c>
@@ -8893,7 +8906,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>448</v>
       </c>
@@ -8916,7 +8929,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>452</v>
       </c>
@@ -8939,7 +8952,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>456</v>
       </c>
@@ -8962,7 +8975,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>460</v>
       </c>
@@ -8985,7 +8998,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>464</v>
       </c>
@@ -9008,7 +9021,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>468</v>
       </c>
@@ -9031,7 +9044,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>472</v>
       </c>
@@ -9054,7 +9067,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>476</v>
       </c>
@@ -9077,7 +9090,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>480</v>
       </c>
@@ -9100,7 +9113,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>484</v>
       </c>
@@ -9123,7 +9136,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>488</v>
       </c>
@@ -9146,7 +9159,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>492</v>
       </c>
@@ -9169,7 +9182,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>496</v>
       </c>
@@ -9192,7 +9205,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>500</v>
       </c>
@@ -9215,7 +9228,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>504</v>
       </c>
@@ -9238,7 +9251,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>508</v>
       </c>
@@ -9261,7 +9274,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>512</v>
       </c>
@@ -9284,7 +9297,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>516</v>
       </c>
@@ -9307,7 +9320,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>520</v>
       </c>
@@ -9330,7 +9343,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>524</v>
       </c>
@@ -9353,7 +9366,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>528</v>
       </c>
@@ -9376,7 +9389,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>532</v>
       </c>
@@ -9399,7 +9412,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>536</v>
       </c>
@@ -9422,7 +9435,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>540</v>
       </c>
@@ -9445,7 +9458,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>543</v>
       </c>
@@ -9468,7 +9481,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>547</v>
       </c>
@@ -9491,7 +9504,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>550</v>
       </c>
@@ -9514,7 +9527,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>554</v>
       </c>
@@ -9537,7 +9550,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>558</v>
       </c>
@@ -9560,7 +9573,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>562</v>
       </c>
@@ -9583,7 +9596,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>566</v>
       </c>
@@ -9606,7 +9619,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>569</v>
       </c>
@@ -9629,7 +9642,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>573</v>
       </c>
@@ -9652,7 +9665,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>577</v>
       </c>
@@ -9675,7 +9688,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>581</v>
       </c>
@@ -9698,7 +9711,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>585</v>
       </c>
@@ -9721,7 +9734,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>589</v>
       </c>
@@ -9744,7 +9757,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>593</v>
       </c>
@@ -9767,7 +9780,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>597</v>
       </c>
@@ -9790,7 +9803,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>601</v>
       </c>
@@ -9813,7 +9826,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>605</v>
       </c>
@@ -9836,7 +9849,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>609</v>
       </c>
@@ -9859,7 +9872,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>612</v>
       </c>
@@ -9882,7 +9895,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>616</v>
       </c>
@@ -9905,7 +9918,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>620</v>
       </c>
@@ -9928,7 +9941,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>624</v>
       </c>
@@ -9951,7 +9964,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>628</v>
       </c>
@@ -9974,7 +9987,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>632</v>
       </c>
@@ -9997,7 +10010,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>636</v>
       </c>
@@ -10020,7 +10033,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>640</v>
       </c>
@@ -10043,7 +10056,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>645</v>
       </c>
@@ -10069,7 +10082,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>650</v>
       </c>
@@ -10095,7 +10108,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>656</v>
       </c>
@@ -10121,7 +10134,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>662</v>
       </c>
@@ -10147,7 +10160,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>667</v>
       </c>
@@ -10173,7 +10186,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>672</v>
       </c>
@@ -10199,7 +10212,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>677</v>
       </c>
@@ -10225,7 +10238,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>683</v>
       </c>
@@ -10251,7 +10264,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>689</v>
       </c>
@@ -10277,7 +10290,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>694</v>
       </c>
@@ -10303,7 +10316,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>699</v>
       </c>
@@ -10329,7 +10342,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>704</v>
       </c>
@@ -10355,7 +10368,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>710</v>
       </c>
@@ -10381,7 +10394,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>715</v>
       </c>
@@ -10407,7 +10420,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>720</v>
       </c>
@@ -10433,7 +10446,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>725</v>
       </c>
@@ -10459,7 +10472,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>730</v>
       </c>
@@ -10485,7 +10498,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>735</v>
       </c>
@@ -10511,7 +10524,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>740</v>
       </c>
@@ -10537,7 +10550,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>745</v>
       </c>
@@ -10563,7 +10576,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>750</v>
       </c>
@@ -10589,7 +10602,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>755</v>
       </c>
@@ -10615,7 +10628,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>760</v>
       </c>
@@ -10641,7 +10654,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>2000</v>
       </c>
@@ -10667,7 +10680,7 @@
         <v>768</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>769</v>
       </c>
@@ -10693,7 +10706,7 @@
         <v>774</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>775</v>
       </c>
@@ -10719,7 +10732,7 @@
         <v>780</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>781</v>
       </c>
@@ -10745,7 +10758,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>786</v>
       </c>
@@ -10771,7 +10784,7 @@
         <v>791</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>792</v>
       </c>
@@ -10797,7 +10810,7 @@
         <v>796</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>797</v>
       </c>
@@ -10823,7 +10836,7 @@
         <v>801</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>802</v>
       </c>
@@ -10849,7 +10862,7 @@
         <v>806</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>807</v>
       </c>
@@ -10875,7 +10888,7 @@
         <v>811</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>812</v>
       </c>
@@ -10901,7 +10914,7 @@
         <v>816</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>817</v>
       </c>
@@ -10927,7 +10940,7 @@
         <v>821</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>822</v>
       </c>
@@ -10953,7 +10966,7 @@
         <v>826</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>827</v>
       </c>
@@ -10979,7 +10992,7 @@
         <v>832</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>833</v>
       </c>
@@ -11005,7 +11018,7 @@
         <v>837</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>838</v>
       </c>
@@ -11031,7 +11044,7 @@
         <v>842</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>843</v>
       </c>
@@ -11057,7 +11070,7 @@
         <v>847</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>848</v>
       </c>
@@ -11083,7 +11096,7 @@
         <v>852</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>853</v>
       </c>
@@ -11109,7 +11122,7 @@
         <v>857</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>858</v>
       </c>
@@ -11135,7 +11148,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>863</v>
       </c>
@@ -11161,7 +11174,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>868</v>
       </c>
@@ -11187,7 +11200,7 @@
         <v>872</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>873</v>
       </c>
@@ -11213,7 +11226,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>878</v>
       </c>
@@ -11239,7 +11252,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>883</v>
       </c>
@@ -11265,7 +11278,7 @@
         <v>887</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>888</v>
       </c>
@@ -11291,7 +11304,7 @@
         <v>892</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>893</v>
       </c>
@@ -11317,7 +11330,7 @@
         <v>897</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>898</v>
       </c>
@@ -11343,7 +11356,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>902</v>
       </c>
@@ -11369,7 +11382,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>907</v>
       </c>
@@ -11395,7 +11408,7 @@
         <v>911</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>912</v>
       </c>
@@ -11421,7 +11434,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>917</v>
       </c>
@@ -11447,7 +11460,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>922</v>
       </c>
@@ -11473,7 +11486,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>927</v>
       </c>
@@ -11499,7 +11512,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>932</v>
       </c>
@@ -11525,7 +11538,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>937</v>
       </c>
@@ -11551,7 +11564,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>942</v>
       </c>
@@ -11577,7 +11590,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>947</v>
       </c>
@@ -11603,7 +11616,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>952</v>
       </c>
@@ -11629,7 +11642,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>957</v>
       </c>
@@ -11655,7 +11668,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>962</v>
       </c>
@@ -11681,7 +11694,7 @@
         <v>966</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>967</v>
       </c>
@@ -11707,7 +11720,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>972</v>
       </c>
@@ -11733,7 +11746,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>977</v>
       </c>
@@ -11759,7 +11772,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>982</v>
       </c>
@@ -11785,7 +11798,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>987</v>
       </c>
@@ -11811,7 +11824,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>992</v>
       </c>
@@ -11837,7 +11850,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>997</v>
       </c>
@@ -11873,13 +11886,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G80"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -11902,7 +11915,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
         <v>1002</v>
       </c>
@@ -11923,7 +11936,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
         <v>1007</v>
       </c>
@@ -11944,7 +11957,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
         <v>1012</v>
       </c>
@@ -11965,7 +11978,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
         <v>1017</v>
       </c>
@@ -11986,7 +11999,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
         <v>1022</v>
       </c>
@@ -12007,7 +12020,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
         <v>1027</v>
       </c>
@@ -12028,7 +12041,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
         <v>1032</v>
       </c>
@@ -12049,7 +12062,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
         <v>1037</v>
       </c>
@@ -12070,7 +12083,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
         <v>1041</v>
       </c>
@@ -12091,7 +12104,7 @@
         <v>1045</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
         <v>1046</v>
       </c>
@@ -12112,7 +12125,7 @@
         <v>1049</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
         <v>1050</v>
       </c>
@@ -12133,7 +12146,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
         <v>1055</v>
       </c>
@@ -12154,7 +12167,7 @@
         <v>1058</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
         <v>1059</v>
       </c>
@@ -12175,7 +12188,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
         <v>1063</v>
       </c>
@@ -12196,7 +12209,7 @@
         <v>1067</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
         <v>1068</v>
       </c>
@@ -12217,7 +12230,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
         <v>1072</v>
       </c>
@@ -12238,7 +12251,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
         <v>1076</v>
       </c>
@@ -12259,7 +12272,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
         <v>1080</v>
       </c>
@@ -12280,7 +12293,7 @@
         <v>1083</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
         <v>1084</v>
       </c>
@@ -12301,7 +12314,7 @@
         <v>1087</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
         <v>1088</v>
       </c>
@@ -12322,7 +12335,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
         <v>1092</v>
       </c>
@@ -12343,7 +12356,7 @@
         <v>1095</v>
       </c>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
         <v>1096</v>
       </c>
@@ -12364,7 +12377,7 @@
         <v>1099</v>
       </c>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>896</v>
       </c>
@@ -12385,7 +12398,7 @@
         <v>1102</v>
       </c>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
         <v>1103</v>
       </c>
@@ -12406,7 +12419,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
         <v>1107</v>
       </c>
@@ -12427,7 +12440,7 @@
         <v>1110</v>
       </c>
     </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
         <v>1111</v>
       </c>
@@ -12448,7 +12461,7 @@
         <v>1114</v>
       </c>
     </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
         <v>1115</v>
       </c>
@@ -12469,7 +12482,7 @@
         <v>1118</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>940</v>
       </c>
@@ -12490,7 +12503,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
         <v>1122</v>
       </c>
@@ -12511,7 +12524,7 @@
         <v>1125</v>
       </c>
     </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
         <v>1126</v>
       </c>
@@ -12532,7 +12545,7 @@
         <v>1129</v>
       </c>
     </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
         <v>1130</v>
       </c>
@@ -12553,7 +12566,7 @@
         <v>1133</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
         <v>1134</v>
       </c>
@@ -12574,7 +12587,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
         <v>1138</v>
       </c>
@@ -12595,7 +12608,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
         <v>1142</v>
       </c>
@@ -12616,7 +12629,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
         <v>1146</v>
       </c>
@@ -12637,7 +12650,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
         <v>1150</v>
       </c>
@@ -12658,7 +12671,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
         <v>1154</v>
       </c>
@@ -12679,7 +12692,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
         <v>1158</v>
       </c>
@@ -12700,7 +12713,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
         <v>1162</v>
       </c>
@@ -12721,7 +12734,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
         <v>1166</v>
       </c>
@@ -12742,7 +12755,7 @@
         <v>1169</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
         <v>1170</v>
       </c>
@@ -12763,7 +12776,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
         <v>1174</v>
       </c>
@@ -12784,7 +12797,7 @@
         <v>1177</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
         <v>1178</v>
       </c>
@@ -12805,7 +12818,7 @@
         <v>1181</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
         <v>1182</v>
       </c>
@@ -12826,7 +12839,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
         <v>1186</v>
       </c>
@@ -12847,7 +12860,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
         <v>1190</v>
       </c>
@@ -12868,7 +12881,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
         <v>1194</v>
       </c>
@@ -12889,7 +12902,7 @@
         <v>1197</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
         <v>1198</v>
       </c>
@@ -12910,7 +12923,7 @@
         <v>1201</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
         <v>1202</v>
       </c>
@@ -12931,7 +12944,7 @@
         <v>1205</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
         <v>1206</v>
       </c>
@@ -12952,7 +12965,7 @@
         <v>1209</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
         <v>1210</v>
       </c>
@@ -12973,7 +12986,7 @@
         <v>1213</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
         <v>1214</v>
       </c>
@@ -12994,7 +13007,7 @@
         <v>1217</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
         <v>1218</v>
       </c>
@@ -13015,7 +13028,7 @@
         <v>1221</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
         <v>1222</v>
       </c>
@@ -13036,7 +13049,7 @@
         <v>1225</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
         <v>1226</v>
       </c>
@@ -13057,7 +13070,7 @@
         <v>1229</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
         <v>1230</v>
       </c>
@@ -13078,7 +13091,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
         <v>1234</v>
       </c>
@@ -13099,7 +13112,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
         <v>1238</v>
       </c>
@@ -13120,7 +13133,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
         <v>1242</v>
       </c>
@@ -13141,7 +13154,7 @@
         <v>1245</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
         <v>1246</v>
       </c>
@@ -13162,7 +13175,7 @@
         <v>1249</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
         <v>1250</v>
       </c>
@@ -13183,7 +13196,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
         <v>1254</v>
       </c>
@@ -13204,7 +13217,7 @@
         <v>1257</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
         <v>1258</v>
       </c>
@@ -13225,7 +13238,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
         <v>1261</v>
       </c>
@@ -13246,7 +13259,7 @@
         <v>1264</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
         <v>1265</v>
       </c>
@@ -13267,7 +13280,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
         <v>1269</v>
       </c>
@@ -13288,7 +13301,7 @@
         <v>1272</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
         <v>1273</v>
       </c>
@@ -13309,7 +13322,7 @@
         <v>1276</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
         <v>1277</v>
       </c>
@@ -13330,7 +13343,7 @@
         <v>1280</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
         <v>1281</v>
       </c>
@@ -13351,7 +13364,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>91</v>
       </c>
@@ -13372,7 +13385,7 @@
         <v>1287</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
         <v>1288</v>
       </c>
@@ -13393,7 +13406,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
         <v>1292</v>
       </c>
@@ -13414,7 +13427,7 @@
         <v>1295</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
         <v>1296</v>
       </c>
@@ -13435,7 +13448,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
         <v>1300</v>
       </c>
@@ -13456,7 +13469,7 @@
         <v>1303</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
         <v>1304</v>
       </c>
@@ -13477,7 +13490,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
         <v>1308</v>
       </c>
@@ -13498,7 +13511,7 @@
         <v>1311</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
         <v>1312</v>
       </c>
@@ -13519,7 +13532,7 @@
         <v>1315</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
         <v>1316</v>
       </c>
@@ -13540,7 +13553,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
         <v>1320</v>
       </c>
@@ -13570,14 +13583,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G189"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -13600,7 +13613,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1324</v>
       </c>
@@ -13617,7 +13630,7 @@
         <v>1326</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1327</v>
       </c>
@@ -13634,7 +13647,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1330</v>
       </c>
@@ -13651,7 +13664,7 @@
         <v>1332</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1333</v>
       </c>
@@ -13668,7 +13681,7 @@
         <v>1335</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>1336</v>
       </c>
@@ -13685,7 +13698,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>1339</v>
       </c>
@@ -13702,7 +13715,7 @@
         <v>1341</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>1342</v>
       </c>
@@ -13719,7 +13732,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1345</v>
       </c>
@@ -13736,7 +13749,7 @@
         <v>1347</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1348</v>
       </c>
@@ -13753,7 +13766,7 @@
         <v>1350</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>733</v>
       </c>
@@ -13770,7 +13783,7 @@
         <v>1352</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1353</v>
       </c>
@@ -13787,7 +13800,7 @@
         <v>1355</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1356</v>
       </c>
@@ -13804,7 +13817,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1359</v>
       </c>
@@ -13821,7 +13834,7 @@
         <v>1361</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1362</v>
       </c>
@@ -13838,7 +13851,7 @@
         <v>1364</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1365</v>
       </c>
@@ -13855,7 +13868,7 @@
         <v>1367</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1368</v>
       </c>
@@ -13872,7 +13885,7 @@
         <v>1370</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1371</v>
       </c>
@@ -13889,7 +13902,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1373</v>
       </c>
@@ -13906,7 +13919,7 @@
         <v>1375</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1376</v>
       </c>
@@ -13923,7 +13936,7 @@
         <v>1378</v>
       </c>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1379</v>
       </c>
@@ -13940,7 +13953,7 @@
         <v>1381</v>
       </c>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1382</v>
       </c>
@@ -13957,7 +13970,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1384</v>
       </c>
@@ -13974,7 +13987,7 @@
         <v>1386</v>
       </c>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>1387</v>
       </c>
@@ -13991,7 +14004,7 @@
         <v>1389</v>
       </c>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>1390</v>
       </c>
@@ -14008,7 +14021,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>1393</v>
       </c>
@@ -14025,7 +14038,7 @@
         <v>1395</v>
       </c>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>1304</v>
       </c>
@@ -14042,7 +14055,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>1398</v>
       </c>
@@ -14059,7 +14072,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>1401</v>
       </c>
@@ -14076,7 +14089,7 @@
         <v>1403</v>
       </c>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>1261</v>
       </c>
@@ -14093,7 +14106,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>1406</v>
       </c>
@@ -14110,7 +14123,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>1409</v>
       </c>
@@ -14127,7 +14140,7 @@
         <v>1411</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>1412</v>
       </c>
@@ -14144,7 +14157,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>1415</v>
       </c>
@@ -14161,7 +14174,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>1418</v>
       </c>
@@ -14178,7 +14191,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>1421</v>
       </c>
@@ -14195,7 +14208,7 @@
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>1423</v>
       </c>
@@ -14212,7 +14225,7 @@
         <v>1425</v>
       </c>
     </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>1426</v>
       </c>
@@ -14232,7 +14245,7 @@
         <v>1429</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>1430</v>
       </c>
@@ -14252,7 +14265,7 @@
         <v>1432</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1433</v>
       </c>
@@ -14272,7 +14285,7 @@
         <v>1436</v>
       </c>
     </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1437</v>
       </c>
@@ -14292,7 +14305,7 @@
         <v>1440</v>
       </c>
     </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1441</v>
       </c>
@@ -14312,7 +14325,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1445</v>
       </c>
@@ -14332,7 +14345,7 @@
         <v>1448</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1449</v>
       </c>
@@ -14352,7 +14365,7 @@
         <v>1452</v>
       </c>
     </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1453</v>
       </c>
@@ -14372,7 +14385,7 @@
         <v>1456</v>
       </c>
     </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1457</v>
       </c>
@@ -14392,7 +14405,7 @@
         <v>1460</v>
       </c>
     </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1461</v>
       </c>
@@ -14412,7 +14425,7 @@
         <v>1464</v>
       </c>
     </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1465</v>
       </c>
@@ -14432,7 +14445,7 @@
         <v>1468</v>
       </c>
     </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1469</v>
       </c>
@@ -14452,7 +14465,7 @@
         <v>1472</v>
       </c>
     </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1473</v>
       </c>
@@ -14472,7 +14485,7 @@
         <v>1476</v>
       </c>
     </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1477</v>
       </c>
@@ -14492,7 +14505,7 @@
         <v>1480</v>
       </c>
     </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>1421</v>
       </c>
@@ -14512,7 +14525,7 @@
         <v>1482</v>
       </c>
     </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>1483</v>
       </c>
@@ -14532,7 +14545,7 @@
         <v>1486</v>
       </c>
     </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>1487</v>
       </c>
@@ -14552,7 +14565,7 @@
         <v>1490</v>
       </c>
     </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>1491</v>
       </c>
@@ -14572,7 +14585,7 @@
         <v>1494</v>
       </c>
     </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>1495</v>
       </c>
@@ -14592,7 +14605,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>1499</v>
       </c>
@@ -14612,7 +14625,7 @@
         <v>1502</v>
       </c>
     </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>1503</v>
       </c>
@@ -14632,7 +14645,7 @@
         <v>1506</v>
       </c>
     </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>1507</v>
       </c>
@@ -14652,7 +14665,7 @@
         <v>1510</v>
       </c>
     </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>1511</v>
       </c>
@@ -14672,7 +14685,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>1514</v>
       </c>
@@ -14692,7 +14705,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>1518</v>
       </c>
@@ -14712,7 +14725,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>1522</v>
       </c>
@@ -14732,7 +14745,7 @@
         <v>1525</v>
       </c>
     </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>1526</v>
       </c>
@@ -14752,7 +14765,7 @@
         <v>1529</v>
       </c>
     </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>1530</v>
       </c>
@@ -14772,7 +14785,7 @@
         <v>1533</v>
       </c>
     </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>1534</v>
       </c>
@@ -14795,7 +14808,7 @@
         <v>1537</v>
       </c>
     </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>1538</v>
       </c>
@@ -14818,7 +14831,7 @@
         <v>1541</v>
       </c>
     </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>1542</v>
       </c>
@@ -14841,7 +14854,7 @@
         <v>1544</v>
       </c>
     </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>1545</v>
       </c>
@@ -14864,7 +14877,7 @@
         <v>1547</v>
       </c>
     </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>1548</v>
       </c>
@@ -14887,7 +14900,7 @@
         <v>1551</v>
       </c>
     </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>1552</v>
       </c>
@@ -14910,7 +14923,7 @@
         <v>1555</v>
       </c>
     </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>1556</v>
       </c>
@@ -14933,7 +14946,7 @@
         <v>1558</v>
       </c>
     </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>1559</v>
       </c>
@@ -14956,7 +14969,7 @@
         <v>1562</v>
       </c>
     </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1563</v>
       </c>
@@ -14979,7 +14992,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1566</v>
       </c>
@@ -15002,7 +15015,7 @@
         <v>1568</v>
       </c>
     </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1569</v>
       </c>
@@ -15025,7 +15038,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1573</v>
       </c>
@@ -15048,7 +15061,7 @@
         <v>1576</v>
       </c>
     </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1577</v>
       </c>
@@ -15071,7 +15084,7 @@
         <v>1580</v>
       </c>
     </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1581</v>
       </c>
@@ -15094,7 +15107,7 @@
         <v>1583</v>
       </c>
     </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1584</v>
       </c>
@@ -15117,7 +15130,7 @@
         <v>1587</v>
       </c>
     </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1588</v>
       </c>
@@ -15140,7 +15153,7 @@
         <v>1591</v>
       </c>
     </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1592</v>
       </c>
@@ -15163,7 +15176,7 @@
         <v>1595</v>
       </c>
     </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1596</v>
       </c>
@@ -15186,7 +15199,7 @@
         <v>1599</v>
       </c>
     </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1600</v>
       </c>
@@ -15209,7 +15222,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1604</v>
       </c>
@@ -15232,7 +15245,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1608</v>
       </c>
@@ -15255,7 +15268,7 @@
         <v>1611</v>
       </c>
     </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1612</v>
       </c>
@@ -15278,7 +15291,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1616</v>
       </c>
@@ -15301,7 +15314,7 @@
         <v>1618</v>
       </c>
     </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>1619</v>
       </c>
@@ -15324,7 +15337,7 @@
         <v>1622</v>
       </c>
     </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>1623</v>
       </c>
@@ -15347,7 +15360,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>1627</v>
       </c>
@@ -15370,7 +15383,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>1630</v>
       </c>
@@ -15393,7 +15406,7 @@
         <v>1633</v>
       </c>
     </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>1634</v>
       </c>
@@ -15416,7 +15429,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>1637</v>
       </c>
@@ -15439,7 +15452,7 @@
         <v>1640</v>
       </c>
     </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>1641</v>
       </c>
@@ -15462,7 +15475,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>1645</v>
       </c>
@@ -15485,7 +15498,7 @@
         <v>1648</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>1649</v>
       </c>
@@ -15508,7 +15521,7 @@
         <v>1652</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>1653</v>
       </c>
@@ -15531,7 +15544,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>1657</v>
       </c>
@@ -15554,7 +15567,7 @@
         <v>1659</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>1660</v>
       </c>
@@ -15577,7 +15590,7 @@
         <v>1663</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1664</v>
       </c>
@@ -15600,7 +15613,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1668</v>
       </c>
@@ -15623,7 +15636,7 @@
         <v>1671</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1672</v>
       </c>
@@ -15646,7 +15659,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1676</v>
       </c>
@@ -15669,7 +15682,7 @@
         <v>1679</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1680</v>
       </c>
@@ -15692,7 +15705,7 @@
         <v>1683</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1684</v>
       </c>
@@ -15715,7 +15728,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1202</v>
       </c>
@@ -15738,7 +15751,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1690</v>
       </c>
@@ -15761,7 +15774,7 @@
         <v>1693</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>1694</v>
       </c>
@@ -15784,7 +15797,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>1698</v>
       </c>
@@ -15807,7 +15820,7 @@
         <v>1701</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>1702</v>
       </c>
@@ -15830,7 +15843,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>1705</v>
       </c>
@@ -15853,7 +15866,7 @@
         <v>1708</v>
       </c>
     </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>1709</v>
       </c>
@@ -15876,7 +15889,7 @@
         <v>1712</v>
       </c>
     </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>1713</v>
       </c>
@@ -15899,7 +15912,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>1717</v>
       </c>
@@ -15922,7 +15935,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>1721</v>
       </c>
@@ -15945,7 +15958,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>1725</v>
       </c>
@@ -15968,7 +15981,7 @@
         <v>1728</v>
       </c>
     </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>1729</v>
       </c>
@@ -15991,7 +16004,7 @@
         <v>1732</v>
       </c>
     </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>1733</v>
       </c>
@@ -16014,7 +16027,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>1737</v>
       </c>
@@ -16037,7 +16050,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>1741</v>
       </c>
@@ -16060,7 +16073,7 @@
         <v>1744</v>
       </c>
     </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>1745</v>
       </c>
@@ -16083,7 +16096,7 @@
         <v>1748</v>
       </c>
     </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>1749</v>
       </c>
@@ -16106,7 +16119,7 @@
         <v>1752</v>
       </c>
     </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1753</v>
       </c>
@@ -16129,7 +16142,7 @@
         <v>1756</v>
       </c>
     </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>1757</v>
       </c>
@@ -16152,7 +16165,7 @@
         <v>1760</v>
       </c>
     </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>1761</v>
       </c>
@@ -16175,7 +16188,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>1765</v>
       </c>
@@ -16198,7 +16211,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>1769</v>
       </c>
@@ -16221,7 +16234,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>1773</v>
       </c>
@@ -16244,7 +16257,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>1777</v>
       </c>
@@ -16267,7 +16280,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>1721</v>
       </c>
@@ -16290,7 +16303,7 @@
         <v>1783</v>
       </c>
     </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>1784</v>
       </c>
@@ -16313,7 +16326,7 @@
         <v>1787</v>
       </c>
     </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>1788</v>
       </c>
@@ -16336,7 +16349,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>1791</v>
       </c>
@@ -16359,7 +16372,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>1795</v>
       </c>
@@ -16382,7 +16395,7 @@
         <v>1798</v>
       </c>
     </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>484</v>
       </c>
@@ -16405,7 +16418,7 @@
         <v>1800</v>
       </c>
     </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>1801</v>
       </c>
@@ -16428,7 +16441,7 @@
         <v>1804</v>
       </c>
     </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>1805</v>
       </c>
@@ -16451,7 +16464,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>1808</v>
       </c>
@@ -16474,7 +16487,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>1811</v>
       </c>
@@ -16497,7 +16510,7 @@
         <v>1814</v>
       </c>
     </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>1815</v>
       </c>
@@ -16520,7 +16533,7 @@
         <v>1818</v>
       </c>
     </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>1819</v>
       </c>
@@ -16543,7 +16556,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>1822</v>
       </c>
@@ -16566,7 +16579,7 @@
         <v>1824</v>
       </c>
     </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>1825</v>
       </c>
@@ -16589,7 +16602,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1829</v>
       </c>
@@ -16612,7 +16625,7 @@
         <v>1831</v>
       </c>
     </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1832</v>
       </c>
@@ -16635,7 +16648,7 @@
         <v>1835</v>
       </c>
     </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1836</v>
       </c>
@@ -16658,7 +16671,7 @@
         <v>1839</v>
       </c>
     </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>1840</v>
       </c>
@@ -16681,7 +16694,7 @@
         <v>1843</v>
       </c>
     </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>1844</v>
       </c>
@@ -16704,7 +16717,7 @@
         <v>1847</v>
       </c>
     </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>1848</v>
       </c>
@@ -16727,7 +16740,7 @@
         <v>1851</v>
       </c>
     </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>1852</v>
       </c>
@@ -16750,7 +16763,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>1856</v>
       </c>
@@ -16773,7 +16786,7 @@
         <v>1858</v>
       </c>
     </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>1859</v>
       </c>
@@ -16796,7 +16809,7 @@
         <v>1862</v>
       </c>
     </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>1863</v>
       </c>
@@ -16819,7 +16832,7 @@
         <v>1866</v>
       </c>
     </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>1867</v>
       </c>
@@ -16842,7 +16855,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>1870</v>
       </c>
@@ -16865,7 +16878,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>1874</v>
       </c>
@@ -16888,7 +16901,7 @@
         <v>1877</v>
       </c>
     </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>1878</v>
       </c>
@@ -16911,7 +16924,7 @@
         <v>1880</v>
       </c>
     </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>1881</v>
       </c>
@@ -16934,7 +16947,7 @@
         <v>1884</v>
       </c>
     </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1885</v>
       </c>
@@ -16957,7 +16970,7 @@
         <v>1888</v>
       </c>
     </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1889</v>
       </c>
@@ -16980,7 +16993,7 @@
         <v>1892</v>
       </c>
     </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1893</v>
       </c>
@@ -17003,7 +17016,7 @@
         <v>1896</v>
       </c>
     </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1897</v>
       </c>
@@ -17026,7 +17039,7 @@
         <v>1900</v>
       </c>
     </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1901</v>
       </c>
@@ -17049,7 +17062,7 @@
         <v>1903</v>
       </c>
     </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1904</v>
       </c>
@@ -17072,7 +17085,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1218</v>
       </c>
@@ -17095,7 +17108,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1911</v>
       </c>
@@ -17118,7 +17131,7 @@
         <v>1914</v>
       </c>
     </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1915</v>
       </c>
@@ -17141,7 +17154,7 @@
         <v>1918</v>
       </c>
     </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1919</v>
       </c>
@@ -17164,7 +17177,7 @@
         <v>1922</v>
       </c>
     </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1923</v>
       </c>
@@ -17187,7 +17200,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1927</v>
       </c>
@@ -17210,7 +17223,7 @@
         <v>1930</v>
       </c>
     </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1931</v>
       </c>
@@ -17233,7 +17246,7 @@
         <v>1934</v>
       </c>
     </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>1935</v>
       </c>
@@ -17256,7 +17269,7 @@
         <v>1938</v>
       </c>
     </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>1939</v>
       </c>
@@ -17279,7 +17292,7 @@
         <v>1941</v>
       </c>
     </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>1942</v>
       </c>
@@ -17302,7 +17315,7 @@
         <v>1945</v>
       </c>
     </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>1946</v>
       </c>
@@ -17325,7 +17338,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>1949</v>
       </c>
@@ -17348,7 +17361,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>1953</v>
       </c>
@@ -17371,7 +17384,7 @@
         <v>1956</v>
       </c>
     </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>1957</v>
       </c>
@@ -17394,7 +17407,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>1961</v>
       </c>
@@ -17417,7 +17430,7 @@
         <v>1964</v>
       </c>
     </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>1965</v>
       </c>
@@ -17440,7 +17453,7 @@
         <v>1968</v>
       </c>
     </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>1969</v>
       </c>
@@ -17463,7 +17476,7 @@
         <v>1971</v>
       </c>
     </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>1972</v>
       </c>
@@ -17486,7 +17499,7 @@
         <v>1975</v>
       </c>
     </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>1976</v>
       </c>
@@ -17509,7 +17522,7 @@
         <v>1979</v>
       </c>
     </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>1980</v>
       </c>
@@ -17532,7 +17545,7 @@
         <v>1983</v>
       </c>
     </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>1984</v>
       </c>
@@ -17555,7 +17568,7 @@
         <v>1987</v>
       </c>
     </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>1988</v>
       </c>
@@ -17578,7 +17591,7 @@
         <v>1991</v>
       </c>
     </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>1992</v>
       </c>
@@ -17601,7 +17614,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>1996</v>
       </c>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -5,24 +5,37 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2710AA9-70C2-44FB-8C3E-58D7A4EC2490}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C8E04E8A-D600-41C1-B3B5-FBC8A0407525}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="30930" yWindow="2685" windowWidth="36465" windowHeight="15450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
     <sheet name="PH" sheetId="2" r:id="rId2"/>
     <sheet name="BG1" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3156" uniqueCount="2191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3149" uniqueCount="2186">
   <si>
     <t>이름</t>
   </si>
@@ -3490,21 +3503,6 @@
   </si>
   <si>
     <t>2025-08-26 15:23:00</t>
-  </si>
-  <si>
-    <t>이서하</t>
-  </si>
-  <si>
-    <t>sinceresuper</t>
-  </si>
-  <si>
-    <t>대구 북구 호암로 40 108동 505호</t>
-  </si>
-  <si>
-    <t>김지연</t>
-  </si>
-  <si>
-    <t>2025-08-26 15:38:25</t>
   </si>
   <si>
     <t>안성하</t>
@@ -6944,15 +6942,15 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H268"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:H267"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.3984375" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -6978,7 +6976,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -7001,7 +6999,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>14</v>
       </c>
@@ -7024,7 +7022,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -7047,7 +7045,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>25</v>
       </c>
@@ -7070,7 +7068,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>30</v>
       </c>
@@ -7093,7 +7091,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>34</v>
       </c>
@@ -7116,7 +7114,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>39</v>
       </c>
@@ -7139,7 +7137,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>44</v>
       </c>
@@ -7162,7 +7160,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>48</v>
       </c>
@@ -7185,7 +7183,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>52</v>
       </c>
@@ -7208,7 +7206,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>56</v>
       </c>
@@ -7231,7 +7229,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>61</v>
       </c>
@@ -7254,7 +7252,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>65</v>
       </c>
@@ -7277,7 +7275,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>70</v>
       </c>
@@ -7300,7 +7298,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>75</v>
       </c>
@@ -7323,7 +7321,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>79</v>
       </c>
@@ -7346,7 +7344,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>83</v>
       </c>
@@ -7369,7 +7367,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>87</v>
       </c>
@@ -7392,7 +7390,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>91</v>
       </c>
@@ -7415,7 +7413,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>95</v>
       </c>
@@ -7438,7 +7436,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>99</v>
       </c>
@@ -7461,7 +7459,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>103</v>
       </c>
@@ -7484,7 +7482,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>107</v>
       </c>
@@ -7507,7 +7505,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>111</v>
       </c>
@@ -7530,7 +7528,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>115</v>
       </c>
@@ -7553,7 +7551,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>119</v>
       </c>
@@ -7576,7 +7574,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>123</v>
       </c>
@@ -7599,7 +7597,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>127</v>
       </c>
@@ -7622,7 +7620,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>131</v>
       </c>
@@ -7645,7 +7643,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>135</v>
       </c>
@@ -7668,7 +7666,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>139</v>
       </c>
@@ -7691,7 +7689,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>143</v>
       </c>
@@ -7714,7 +7712,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>147</v>
       </c>
@@ -7737,7 +7735,7 @@
         <v>150</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>151</v>
       </c>
@@ -7760,7 +7758,7 @@
         <v>154</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>155</v>
       </c>
@@ -7783,7 +7781,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>103</v>
       </c>
@@ -7806,7 +7804,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>162</v>
       </c>
@@ -7829,7 +7827,7 @@
         <v>165</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>166</v>
       </c>
@@ -7852,7 +7850,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>170</v>
       </c>
@@ -7875,7 +7873,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>174</v>
       </c>
@@ -7898,7 +7896,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>178</v>
       </c>
@@ -7921,7 +7919,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>182</v>
       </c>
@@ -7944,7 +7942,7 @@
         <v>185</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>186</v>
       </c>
@@ -7967,7 +7965,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>190</v>
       </c>
@@ -7990,7 +7988,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>194</v>
       </c>
@@ -8013,7 +8011,7 @@
         <v>197</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>198</v>
       </c>
@@ -8036,7 +8034,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>202</v>
       </c>
@@ -8059,7 +8057,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>206</v>
       </c>
@@ -8082,7 +8080,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>210</v>
       </c>
@@ -8105,7 +8103,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>214</v>
       </c>
@@ -8128,7 +8126,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>218</v>
       </c>
@@ -8151,7 +8149,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>222</v>
       </c>
@@ -8174,7 +8172,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>226</v>
       </c>
@@ -8197,7 +8195,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>230</v>
       </c>
@@ -8220,7 +8218,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>234</v>
       </c>
@@ -8243,7 +8241,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>238</v>
       </c>
@@ -8266,7 +8264,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>242</v>
       </c>
@@ -8289,7 +8287,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>246</v>
       </c>
@@ -8312,7 +8310,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>250</v>
       </c>
@@ -8335,7 +8333,7 @@
         <v>253</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>254</v>
       </c>
@@ -8358,7 +8356,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>258</v>
       </c>
@@ -8381,7 +8379,7 @@
         <v>261</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>262</v>
       </c>
@@ -8404,7 +8402,7 @@
         <v>265</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>266</v>
       </c>
@@ -8427,7 +8425,7 @@
         <v>269</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>270</v>
       </c>
@@ -8450,7 +8448,7 @@
         <v>273</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>274</v>
       </c>
@@ -8473,7 +8471,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>278</v>
       </c>
@@ -8496,7 +8494,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>282</v>
       </c>
@@ -8519,7 +8517,7 @@
         <v>285</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>286</v>
       </c>
@@ -8542,7 +8540,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>290</v>
       </c>
@@ -8565,7 +8563,7 @@
         <v>293</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>294</v>
       </c>
@@ -8588,7 +8586,7 @@
         <v>297</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>298</v>
       </c>
@@ -8611,7 +8609,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>302</v>
       </c>
@@ -8634,7 +8632,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>306</v>
       </c>
@@ -8657,7 +8655,7 @@
         <v>309</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>310</v>
       </c>
@@ -8680,7 +8678,7 @@
         <v>313</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>314</v>
       </c>
@@ -8703,7 +8701,7 @@
         <v>317</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>318</v>
       </c>
@@ -8726,7 +8724,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>322</v>
       </c>
@@ -8749,7 +8747,7 @@
         <v>325</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>326</v>
       </c>
@@ -8772,7 +8770,7 @@
         <v>329</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>330</v>
       </c>
@@ -8795,7 +8793,7 @@
         <v>333</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>334</v>
       </c>
@@ -8818,7 +8816,7 @@
         <v>337</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>338</v>
       </c>
@@ -8841,7 +8839,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>342</v>
       </c>
@@ -8864,7 +8862,7 @@
         <v>345</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>346</v>
       </c>
@@ -8887,7 +8885,7 @@
         <v>349</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>350</v>
       </c>
@@ -8910,7 +8908,7 @@
         <v>353</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>354</v>
       </c>
@@ -8933,7 +8931,7 @@
         <v>357</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>358</v>
       </c>
@@ -8956,7 +8954,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>362</v>
       </c>
@@ -8979,7 +8977,7 @@
         <v>365</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>366</v>
       </c>
@@ -9002,7 +9000,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>370</v>
       </c>
@@ -9025,7 +9023,7 @@
         <v>373</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>374</v>
       </c>
@@ -9048,7 +9046,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>378</v>
       </c>
@@ -9071,7 +9069,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>382</v>
       </c>
@@ -9094,7 +9092,7 @@
         <v>385</v>
       </c>
     </row>
-    <row r="94" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="94" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>386</v>
       </c>
@@ -9117,7 +9115,7 @@
         <v>388</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="95" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>389</v>
       </c>
@@ -9140,7 +9138,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>393</v>
       </c>
@@ -9163,7 +9161,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="97" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>397</v>
       </c>
@@ -9186,7 +9184,7 @@
         <v>400</v>
       </c>
     </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="98" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>401</v>
       </c>
@@ -9209,7 +9207,7 @@
         <v>404</v>
       </c>
     </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="99" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>405</v>
       </c>
@@ -9232,7 +9230,7 @@
         <v>408</v>
       </c>
     </row>
-    <row r="100" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="100" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>409</v>
       </c>
@@ -9255,7 +9253,7 @@
         <v>412</v>
       </c>
     </row>
-    <row r="101" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="101" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>413</v>
       </c>
@@ -9278,7 +9276,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="102" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="102" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>417</v>
       </c>
@@ -9301,7 +9299,7 @@
         <v>420</v>
       </c>
     </row>
-    <row r="103" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="103" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>421</v>
       </c>
@@ -9324,7 +9322,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="104" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="104" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>425</v>
       </c>
@@ -9347,7 +9345,7 @@
         <v>428</v>
       </c>
     </row>
-    <row r="105" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="105" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>429</v>
       </c>
@@ -9370,7 +9368,7 @@
         <v>432</v>
       </c>
     </row>
-    <row r="106" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="106" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>433</v>
       </c>
@@ -9393,7 +9391,7 @@
         <v>435</v>
       </c>
     </row>
-    <row r="107" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="107" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>436</v>
       </c>
@@ -9416,7 +9414,7 @@
         <v>439</v>
       </c>
     </row>
-    <row r="108" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="108" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>440</v>
       </c>
@@ -9439,7 +9437,7 @@
         <v>443</v>
       </c>
     </row>
-    <row r="109" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="109" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>444</v>
       </c>
@@ -9462,7 +9460,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="110" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>448</v>
       </c>
@@ -9485,7 +9483,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="111" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="111" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>452</v>
       </c>
@@ -9508,7 +9506,7 @@
         <v>455</v>
       </c>
     </row>
-    <row r="112" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="112" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>456</v>
       </c>
@@ -9531,7 +9529,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="113" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="113" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>460</v>
       </c>
@@ -9554,7 +9552,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="114" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="114" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>464</v>
       </c>
@@ -9577,7 +9575,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="115" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="115" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>468</v>
       </c>
@@ -9600,7 +9598,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="116" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="116" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>472</v>
       </c>
@@ -9623,7 +9621,7 @@
         <v>475</v>
       </c>
     </row>
-    <row r="117" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="117" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>476</v>
       </c>
@@ -9646,7 +9644,7 @@
         <v>479</v>
       </c>
     </row>
-    <row r="118" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="118" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>480</v>
       </c>
@@ -9669,7 +9667,7 @@
         <v>483</v>
       </c>
     </row>
-    <row r="119" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="119" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>484</v>
       </c>
@@ -9692,7 +9690,7 @@
         <v>487</v>
       </c>
     </row>
-    <row r="120" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="120" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>488</v>
       </c>
@@ -9715,7 +9713,7 @@
         <v>491</v>
       </c>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="121" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>492</v>
       </c>
@@ -9738,7 +9736,7 @@
         <v>495</v>
       </c>
     </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="122" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>496</v>
       </c>
@@ -9761,7 +9759,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="123" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="123" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>500</v>
       </c>
@@ -9784,7 +9782,7 @@
         <v>503</v>
       </c>
     </row>
-    <row r="124" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="124" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>504</v>
       </c>
@@ -9807,7 +9805,7 @@
         <v>507</v>
       </c>
     </row>
-    <row r="125" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="125" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>508</v>
       </c>
@@ -9830,7 +9828,7 @@
         <v>511</v>
       </c>
     </row>
-    <row r="126" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="126" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>512</v>
       </c>
@@ -9853,7 +9851,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="127" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="127" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>516</v>
       </c>
@@ -9876,7 +9874,7 @@
         <v>519</v>
       </c>
     </row>
-    <row r="128" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="128" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>520</v>
       </c>
@@ -9899,7 +9897,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="129" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>524</v>
       </c>
@@ -9922,7 +9920,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="130" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="130" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>528</v>
       </c>
@@ -9945,7 +9943,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="131" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="131" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>532</v>
       </c>
@@ -9968,7 +9966,7 @@
         <v>535</v>
       </c>
     </row>
-    <row r="132" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="132" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>536</v>
       </c>
@@ -9991,7 +9989,7 @@
         <v>539</v>
       </c>
     </row>
-    <row r="133" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="133" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>540</v>
       </c>
@@ -10014,7 +10012,7 @@
         <v>542</v>
       </c>
     </row>
-    <row r="134" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="134" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>543</v>
       </c>
@@ -10037,7 +10035,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="135" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="135" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>547</v>
       </c>
@@ -10060,7 +10058,7 @@
         <v>549</v>
       </c>
     </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="136" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>550</v>
       </c>
@@ -10083,7 +10081,7 @@
         <v>553</v>
       </c>
     </row>
-    <row r="137" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="137" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>554</v>
       </c>
@@ -10106,7 +10104,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="138" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="138" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>558</v>
       </c>
@@ -10129,7 +10127,7 @@
         <v>561</v>
       </c>
     </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="139" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>562</v>
       </c>
@@ -10152,7 +10150,7 @@
         <v>565</v>
       </c>
     </row>
-    <row r="140" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="140" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>566</v>
       </c>
@@ -10175,7 +10173,7 @@
         <v>568</v>
       </c>
     </row>
-    <row r="141" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="141" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>569</v>
       </c>
@@ -10198,7 +10196,7 @@
         <v>572</v>
       </c>
     </row>
-    <row r="142" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="142" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>573</v>
       </c>
@@ -10221,7 +10219,7 @@
         <v>576</v>
       </c>
     </row>
-    <row r="143" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="143" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>577</v>
       </c>
@@ -10244,7 +10242,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="144" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="144" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>581</v>
       </c>
@@ -10267,7 +10265,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="145" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="145" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>585</v>
       </c>
@@ -10290,7 +10288,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="146" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="146" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>589</v>
       </c>
@@ -10313,7 +10311,7 @@
         <v>592</v>
       </c>
     </row>
-    <row r="147" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="147" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>593</v>
       </c>
@@ -10336,7 +10334,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="148" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="148" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>597</v>
       </c>
@@ -10359,7 +10357,7 @@
         <v>600</v>
       </c>
     </row>
-    <row r="149" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="149" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>601</v>
       </c>
@@ -10382,7 +10380,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="150" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>605</v>
       </c>
@@ -10405,7 +10403,7 @@
         <v>608</v>
       </c>
     </row>
-    <row r="151" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="151" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>609</v>
       </c>
@@ -10428,7 +10426,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="152" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="152" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>612</v>
       </c>
@@ -10451,7 +10449,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="153" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="153" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>616</v>
       </c>
@@ -10474,7 +10472,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="154" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="154" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>620</v>
       </c>
@@ -10497,7 +10495,7 @@
         <v>623</v>
       </c>
     </row>
-    <row r="155" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="155" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>624</v>
       </c>
@@ -10520,7 +10518,7 @@
         <v>627</v>
       </c>
     </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="156" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>628</v>
       </c>
@@ -10543,7 +10541,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="157" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="157" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>632</v>
       </c>
@@ -10566,7 +10564,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="158" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="158" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>636</v>
       </c>
@@ -10589,7 +10587,7 @@
         <v>639</v>
       </c>
     </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="159" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>640</v>
       </c>
@@ -10612,7 +10610,7 @@
         <v>644</v>
       </c>
     </row>
-    <row r="160" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="160" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>645</v>
       </c>
@@ -10638,7 +10636,7 @@
         <v>649</v>
       </c>
     </row>
-    <row r="161" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="161" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>650</v>
       </c>
@@ -10664,7 +10662,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="162" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>656</v>
       </c>
@@ -10690,7 +10688,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="163" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="163" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>662</v>
       </c>
@@ -10716,7 +10714,7 @@
         <v>666</v>
       </c>
     </row>
-    <row r="164" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="164" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>667</v>
       </c>
@@ -10742,7 +10740,7 @@
         <v>671</v>
       </c>
     </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="165" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>672</v>
       </c>
@@ -10768,7 +10766,7 @@
         <v>676</v>
       </c>
     </row>
-    <row r="166" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="166" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>677</v>
       </c>
@@ -10794,7 +10792,7 @@
         <v>682</v>
       </c>
     </row>
-    <row r="167" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="167" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>683</v>
       </c>
@@ -10820,7 +10818,7 @@
         <v>688</v>
       </c>
     </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="168" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>689</v>
       </c>
@@ -10846,7 +10844,7 @@
         <v>693</v>
       </c>
     </row>
-    <row r="169" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="169" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>694</v>
       </c>
@@ -10872,7 +10870,7 @@
         <v>698</v>
       </c>
     </row>
-    <row r="170" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="170" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>699</v>
       </c>
@@ -10898,7 +10896,7 @@
         <v>703</v>
       </c>
     </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="171" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>704</v>
       </c>
@@ -10924,7 +10922,7 @@
         <v>709</v>
       </c>
     </row>
-    <row r="172" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="172" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>710</v>
       </c>
@@ -10950,7 +10948,7 @@
         <v>714</v>
       </c>
     </row>
-    <row r="173" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="173" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>715</v>
       </c>
@@ -10976,7 +10974,7 @@
         <v>719</v>
       </c>
     </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="174" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>720</v>
       </c>
@@ -11002,7 +11000,7 @@
         <v>724</v>
       </c>
     </row>
-    <row r="175" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="175" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>725</v>
       </c>
@@ -11028,7 +11026,7 @@
         <v>729</v>
       </c>
     </row>
-    <row r="176" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="176" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>730</v>
       </c>
@@ -11054,7 +11052,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="177" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>735</v>
       </c>
@@ -11080,7 +11078,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="178" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="178" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>740</v>
       </c>
@@ -11106,7 +11104,7 @@
         <v>744</v>
       </c>
     </row>
-    <row r="179" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="179" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>745</v>
       </c>
@@ -11132,7 +11130,7 @@
         <v>749</v>
       </c>
     </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="180" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>750</v>
       </c>
@@ -11158,7 +11156,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="181" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="181" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>755</v>
       </c>
@@ -11184,7 +11182,7 @@
         <v>759</v>
       </c>
     </row>
-    <row r="182" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="182" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>760</v>
       </c>
@@ -11210,7 +11208,7 @@
         <v>764</v>
       </c>
     </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="183" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>765</v>
       </c>
@@ -11236,7 +11234,7 @@
         <v>769</v>
       </c>
     </row>
-    <row r="184" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="184" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>770</v>
       </c>
@@ -11262,7 +11260,7 @@
         <v>775</v>
       </c>
     </row>
-    <row r="185" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="185" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>776</v>
       </c>
@@ -11288,7 +11286,7 @@
         <v>781</v>
       </c>
     </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="186" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>782</v>
       </c>
@@ -11314,7 +11312,7 @@
         <v>786</v>
       </c>
     </row>
-    <row r="187" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="187" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>787</v>
       </c>
@@ -11340,7 +11338,7 @@
         <v>792</v>
       </c>
     </row>
-    <row r="188" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="188" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>793</v>
       </c>
@@ -11366,7 +11364,7 @@
         <v>797</v>
       </c>
     </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="189" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>798</v>
       </c>
@@ -11392,7 +11390,7 @@
         <v>802</v>
       </c>
     </row>
-    <row r="190" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="190" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>803</v>
       </c>
@@ -11418,7 +11416,7 @@
         <v>807</v>
       </c>
     </row>
-    <row r="191" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="191" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>808</v>
       </c>
@@ -11444,7 +11442,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="192" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>813</v>
       </c>
@@ -11470,7 +11468,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="193" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="193" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>818</v>
       </c>
@@ -11496,7 +11494,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="194" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="194" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>823</v>
       </c>
@@ -11522,7 +11520,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="195" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>828</v>
       </c>
@@ -11548,7 +11546,7 @@
         <v>833</v>
       </c>
     </row>
-    <row r="196" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="196" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>834</v>
       </c>
@@ -11574,7 +11572,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="197" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="197" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>839</v>
       </c>
@@ -11600,7 +11598,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="198" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="198" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>844</v>
       </c>
@@ -11626,7 +11624,7 @@
         <v>848</v>
       </c>
     </row>
-    <row r="199" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="199" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>849</v>
       </c>
@@ -11652,7 +11650,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="200" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="200" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>854</v>
       </c>
@@ -11678,7 +11676,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="201" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="201" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>859</v>
       </c>
@@ -11704,7 +11702,7 @@
         <v>863</v>
       </c>
     </row>
-    <row r="202" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="202" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>864</v>
       </c>
@@ -11730,7 +11728,7 @@
         <v>868</v>
       </c>
     </row>
-    <row r="203" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="203" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>869</v>
       </c>
@@ -11756,7 +11754,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="204" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="204" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>874</v>
       </c>
@@ -11782,7 +11780,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="205" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="205" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>879</v>
       </c>
@@ -11808,7 +11806,7 @@
         <v>883</v>
       </c>
     </row>
-    <row r="206" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="206" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>884</v>
       </c>
@@ -11834,7 +11832,7 @@
         <v>888</v>
       </c>
     </row>
-    <row r="207" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="207" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>889</v>
       </c>
@@ -11860,7 +11858,7 @@
         <v>893</v>
       </c>
     </row>
-    <row r="208" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="208" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A208" t="s">
         <v>894</v>
       </c>
@@ -11886,7 +11884,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="209" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="209" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>899</v>
       </c>
@@ -11912,7 +11910,7 @@
         <v>902</v>
       </c>
     </row>
-    <row r="210" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="210" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>903</v>
       </c>
@@ -11938,7 +11936,7 @@
         <v>907</v>
       </c>
     </row>
-    <row r="211" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="211" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>908</v>
       </c>
@@ -11964,7 +11962,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="212" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="212" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>913</v>
       </c>
@@ -11990,7 +11988,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="213" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="213" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>918</v>
       </c>
@@ -12016,7 +12014,7 @@
         <v>922</v>
       </c>
     </row>
-    <row r="214" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="214" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>923</v>
       </c>
@@ -12042,7 +12040,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="215" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="215" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>928</v>
       </c>
@@ -12068,7 +12066,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="216" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="216" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>933</v>
       </c>
@@ -12094,7 +12092,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="217" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="217" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>938</v>
       </c>
@@ -12120,7 +12118,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="218" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="218" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>943</v>
       </c>
@@ -12146,7 +12144,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="219" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="219" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>948</v>
       </c>
@@ -12172,7 +12170,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="220" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="220" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>953</v>
       </c>
@@ -12198,7 +12196,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="221" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="221" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>958</v>
       </c>
@@ -12224,7 +12222,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="222" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="222" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>963</v>
       </c>
@@ -12250,7 +12248,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="223" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="223" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>968</v>
       </c>
@@ -12276,7 +12274,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="224" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="224" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>973</v>
       </c>
@@ -12302,7 +12300,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="225" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="225" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>978</v>
       </c>
@@ -12328,7 +12326,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="226" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="226" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>983</v>
       </c>
@@ -12354,7 +12352,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="227" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A227" t="s">
         <v>988</v>
       </c>
@@ -12380,7 +12378,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="228" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="228" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>993</v>
       </c>
@@ -12406,7 +12404,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="229" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="229" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>998</v>
       </c>
@@ -12432,7 +12430,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="230" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>1003</v>
       </c>
@@ -12458,7 +12456,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="231" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="231" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>1008</v>
       </c>
@@ -12484,7 +12482,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="232" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>1013</v>
       </c>
@@ -12510,7 +12508,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="233" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="233" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>1018</v>
       </c>
@@ -12536,7 +12534,7 @@
         <v>1022</v>
       </c>
     </row>
-    <row r="234" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="234" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>1023</v>
       </c>
@@ -12562,7 +12560,7 @@
         <v>1026</v>
       </c>
     </row>
-    <row r="235" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="235" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>1027</v>
       </c>
@@ -12588,7 +12586,7 @@
         <v>1031</v>
       </c>
     </row>
-    <row r="236" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="236" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>1032</v>
       </c>
@@ -12614,7 +12612,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="237" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="237" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>1037</v>
       </c>
@@ -12640,7 +12638,7 @@
         <v>1041</v>
       </c>
     </row>
-    <row r="238" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="238" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>1042</v>
       </c>
@@ -12666,7 +12664,7 @@
         <v>1046</v>
       </c>
     </row>
-    <row r="239" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="239" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>1047</v>
       </c>
@@ -12692,7 +12690,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="240" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="240" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>1052</v>
       </c>
@@ -12718,7 +12716,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="241" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="241" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>1057</v>
       </c>
@@ -12744,7 +12742,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="242" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="242" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>1062</v>
       </c>
@@ -12770,7 +12768,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="243" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="243" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>1067</v>
       </c>
@@ -12796,7 +12794,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="244" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="244" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>1072</v>
       </c>
@@ -12822,7 +12820,7 @@
         <v>1076</v>
       </c>
     </row>
-    <row r="245" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="245" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>1077</v>
       </c>
@@ -12848,7 +12846,7 @@
         <v>1081</v>
       </c>
     </row>
-    <row r="246" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="246" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>1082</v>
       </c>
@@ -12874,7 +12872,7 @@
         <v>1086</v>
       </c>
     </row>
-    <row r="247" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="247" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>1087</v>
       </c>
@@ -12900,7 +12898,7 @@
         <v>1091</v>
       </c>
     </row>
-    <row r="248" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="248" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>1092</v>
       </c>
@@ -12926,7 +12924,7 @@
         <v>1096</v>
       </c>
     </row>
-    <row r="249" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="249" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>1097</v>
       </c>
@@ -12952,7 +12950,7 @@
         <v>1101</v>
       </c>
     </row>
-    <row r="250" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="250" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>1102</v>
       </c>
@@ -12978,7 +12976,7 @@
         <v>1106</v>
       </c>
     </row>
-    <row r="251" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="251" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>1107</v>
       </c>
@@ -13004,7 +13002,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="252" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>1112</v>
       </c>
@@ -13030,7 +13028,7 @@
         <v>1116</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="253" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>1117</v>
       </c>
@@ -13056,7 +13054,7 @@
         <v>1121</v>
       </c>
     </row>
-    <row r="254" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="254" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>1122</v>
       </c>
@@ -13082,7 +13080,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="255" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A255" t="s">
         <v>1127</v>
       </c>
@@ -13108,7 +13106,7 @@
         <v>1131</v>
       </c>
     </row>
-    <row r="256" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="256" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A256" t="s">
         <v>1132</v>
       </c>
@@ -13134,7 +13132,7 @@
         <v>1136</v>
       </c>
     </row>
-    <row r="257" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="257" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A257" t="s">
         <v>1137</v>
       </c>
@@ -13160,7 +13158,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="258" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="258" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A258" t="s">
         <v>1142</v>
       </c>
@@ -13186,7 +13184,7 @@
         <v>1145</v>
       </c>
     </row>
-    <row r="259" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="259" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A259" t="s">
         <v>1146</v>
       </c>
@@ -13212,7 +13210,7 @@
         <v>1150</v>
       </c>
     </row>
-    <row r="260" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="260" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>1151</v>
       </c>
@@ -13238,7 +13236,7 @@
         <v>1155</v>
       </c>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="261" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>1156</v>
       </c>
@@ -13246,13 +13244,13 @@
         <v>1157</v>
       </c>
       <c r="C261">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D261" t="s">
         <v>10</v>
       </c>
       <c r="E261" t="s">
-        <v>772</v>
+        <v>72</v>
       </c>
       <c r="F261" t="s">
         <v>1158</v>
@@ -13264,7 +13262,7 @@
         <v>1160</v>
       </c>
     </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="262" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A262" t="s">
         <v>1161</v>
       </c>
@@ -13290,7 +13288,7 @@
         <v>1165</v>
       </c>
     </row>
-    <row r="263" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="263" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A263" t="s">
         <v>1166</v>
       </c>
@@ -13298,13 +13296,13 @@
         <v>1167</v>
       </c>
       <c r="C263">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D263" t="s">
         <v>10</v>
       </c>
       <c r="E263" t="s">
-        <v>72</v>
+        <v>789</v>
       </c>
       <c r="F263" t="s">
         <v>1168</v>
@@ -13316,7 +13314,7 @@
         <v>1170</v>
       </c>
     </row>
-    <row r="264" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="264" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A264" t="s">
         <v>1171</v>
       </c>
@@ -13330,7 +13328,7 @@
         <v>10</v>
       </c>
       <c r="E264" t="s">
-        <v>789</v>
+        <v>772</v>
       </c>
       <c r="F264" t="s">
         <v>1173</v>
@@ -13342,7 +13340,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="265" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="265" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A265" t="s">
         <v>1176</v>
       </c>
@@ -13350,42 +13348,42 @@
         <v>1177</v>
       </c>
       <c r="C265">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D265" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="E265" t="s">
-        <v>772</v>
+        <v>679</v>
       </c>
       <c r="F265" t="s">
+        <v>1069</v>
+      </c>
+      <c r="G265" t="s">
         <v>1178</v>
       </c>
-      <c r="G265" t="s">
+      <c r="H265" t="s">
         <v>1179</v>
       </c>
-      <c r="H265" t="s">
+    </row>
+    <row r="266" spans="1:8" x14ac:dyDescent="0.3">
+      <c r="A266" t="s">
         <v>1180</v>
       </c>
-    </row>
-    <row r="266" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A266" t="s">
+      <c r="B266" t="s">
         <v>1181</v>
       </c>
-      <c r="B266" t="s">
-        <v>1182</v>
-      </c>
       <c r="C266">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="D266" t="s">
         <v>21</v>
       </c>
       <c r="E266" t="s">
-        <v>679</v>
+        <v>72</v>
       </c>
       <c r="F266" t="s">
-        <v>1069</v>
+        <v>1182</v>
       </c>
       <c r="G266" t="s">
         <v>1183</v>
@@ -13394,7 +13392,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="267" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="267" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>1185</v>
       </c>
@@ -13408,7 +13406,7 @@
         <v>21</v>
       </c>
       <c r="E267" t="s">
-        <v>72</v>
+        <v>679</v>
       </c>
       <c r="F267" t="s">
         <v>1187</v>
@@ -13418,32 +13416,6 @@
       </c>
       <c r="H267" t="s">
         <v>1189</v>
-      </c>
-    </row>
-    <row r="268" spans="1:8" x14ac:dyDescent="0.4">
-      <c r="A268" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B268" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C268">
-        <v>11</v>
-      </c>
-      <c r="D268" t="s">
-        <v>21</v>
-      </c>
-      <c r="E268" t="s">
-        <v>679</v>
-      </c>
-      <c r="F268" t="s">
-        <v>1192</v>
-      </c>
-      <c r="G268" t="s">
-        <v>1193</v>
-      </c>
-      <c r="H268" t="s">
-        <v>1194</v>
       </c>
     </row>
   </sheetData>
@@ -13456,13 +13428,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G80"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -13485,1663 +13457,1663 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" s="1" t="s">
-        <v>1195</v>
+        <v>1190</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>1196</v>
+        <v>1191</v>
       </c>
       <c r="C2" s="1">
         <v>11</v>
       </c>
       <c r="D2" s="1"/>
       <c r="E2" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>1198</v>
+        <v>1193</v>
       </c>
       <c r="G2" s="1" t="s">
-        <v>1199</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1194</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" s="1" t="s">
-        <v>1200</v>
+        <v>1195</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>1201</v>
+        <v>1196</v>
       </c>
       <c r="C3" s="1">
         <v>12</v>
       </c>
       <c r="D3" s="1"/>
       <c r="E3" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F3" s="1" t="s">
-        <v>1203</v>
+        <v>1198</v>
       </c>
       <c r="G3" s="1" t="s">
-        <v>1204</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1199</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" s="1" t="s">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>1206</v>
+        <v>1201</v>
       </c>
       <c r="C4" s="1">
         <v>11</v>
       </c>
       <c r="D4" s="1"/>
       <c r="E4" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F4" s="1" t="s">
-        <v>1208</v>
+        <v>1203</v>
       </c>
       <c r="G4" s="1" t="s">
-        <v>1209</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1204</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
-        <v>1210</v>
+        <v>1205</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>1211</v>
+        <v>1206</v>
       </c>
       <c r="C5" s="1">
         <v>13</v>
       </c>
       <c r="D5" s="1"/>
       <c r="E5" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>1213</v>
+        <v>1208</v>
       </c>
       <c r="G5" s="1" t="s">
-        <v>1214</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1209</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A6" s="1" t="s">
-        <v>1215</v>
+        <v>1210</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>1216</v>
+        <v>1211</v>
       </c>
       <c r="C6" s="1">
         <v>13</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>1218</v>
+        <v>1213</v>
       </c>
       <c r="G6" s="1" t="s">
-        <v>1219</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1214</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A7" s="1" t="s">
-        <v>1220</v>
+        <v>1215</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>1221</v>
+        <v>1216</v>
       </c>
       <c r="C7" s="1">
         <v>11</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>1223</v>
+        <v>1218</v>
       </c>
       <c r="G7" s="1" t="s">
-        <v>1224</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1219</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="1" t="s">
-        <v>1225</v>
+        <v>1220</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>1226</v>
+        <v>1221</v>
       </c>
       <c r="C8" s="1">
         <v>13</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>1228</v>
+        <v>1223</v>
       </c>
       <c r="G8" s="1" t="s">
-        <v>1229</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1224</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" s="1" t="s">
-        <v>1230</v>
+        <v>1225</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>1231</v>
+        <v>1226</v>
       </c>
       <c r="C9" s="1">
         <v>12</v>
       </c>
       <c r="D9" s="1"/>
       <c r="E9" s="1" t="s">
+        <v>1222</v>
+      </c>
+      <c r="F9" s="1" t="s">
         <v>1227</v>
       </c>
-      <c r="F9" s="1" t="s">
-        <v>1232</v>
-      </c>
       <c r="G9" s="1" t="s">
-        <v>1233</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1228</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" s="1" t="s">
-        <v>1234</v>
+        <v>1229</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>1235</v>
+        <v>1230</v>
       </c>
       <c r="C10" s="1">
         <v>12</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F10" s="1" t="s">
-        <v>1237</v>
+        <v>1232</v>
       </c>
       <c r="G10" s="1" t="s">
-        <v>1238</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1233</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" s="1" t="s">
-        <v>1239</v>
+        <v>1234</v>
       </c>
       <c r="B11" s="1" t="s">
-        <v>1240</v>
+        <v>1235</v>
       </c>
       <c r="C11" s="1">
         <v>13</v>
       </c>
       <c r="D11" s="1"/>
       <c r="E11" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F11" s="1" t="s">
-        <v>1241</v>
+        <v>1236</v>
       </c>
       <c r="G11" s="1" t="s">
-        <v>1242</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1237</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" s="1" t="s">
-        <v>1243</v>
+        <v>1238</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>1244</v>
+        <v>1239</v>
       </c>
       <c r="C12" s="1">
         <v>11</v>
       </c>
       <c r="D12" s="1"/>
       <c r="E12" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>1246</v>
+        <v>1241</v>
       </c>
       <c r="G12" s="1" t="s">
-        <v>1247</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1242</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="1" t="s">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>1249</v>
+        <v>1244</v>
       </c>
       <c r="C13" s="1">
         <v>13</v>
       </c>
       <c r="D13" s="1"/>
       <c r="E13" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>1250</v>
+        <v>1245</v>
       </c>
       <c r="G13" s="1" t="s">
-        <v>1251</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1246</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" s="1" t="s">
-        <v>1252</v>
+        <v>1247</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>1253</v>
+        <v>1248</v>
       </c>
       <c r="C14" s="1">
         <v>13</v>
       </c>
       <c r="D14" s="1"/>
       <c r="E14" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="G14" s="1" t="s">
-        <v>1255</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1250</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" s="1" t="s">
-        <v>1256</v>
+        <v>1251</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>1257</v>
+        <v>1252</v>
       </c>
       <c r="C15" s="1">
         <v>13</v>
       </c>
       <c r="D15" s="1"/>
       <c r="E15" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>1259</v>
+        <v>1254</v>
       </c>
       <c r="G15" s="1" t="s">
-        <v>1260</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1255</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="1" t="s">
-        <v>1261</v>
+        <v>1256</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>1262</v>
+        <v>1257</v>
       </c>
       <c r="C16" s="1">
         <v>12</v>
       </c>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F16" s="1" t="s">
-        <v>1263</v>
+        <v>1258</v>
       </c>
       <c r="G16" s="1" t="s">
-        <v>1264</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1259</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A17" s="1" t="s">
-        <v>1265</v>
+        <v>1260</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>1266</v>
+        <v>1261</v>
       </c>
       <c r="C17" s="1">
         <v>13</v>
       </c>
       <c r="D17" s="1"/>
       <c r="E17" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F17" s="1" t="s">
-        <v>1267</v>
+        <v>1262</v>
       </c>
       <c r="G17" s="1" t="s">
-        <v>1268</v>
-      </c>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1263</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A18" s="1" t="s">
-        <v>1269</v>
+        <v>1264</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>1270</v>
+        <v>1265</v>
       </c>
       <c r="C18" s="1">
         <v>13</v>
       </c>
       <c r="D18" s="1"/>
       <c r="E18" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F18" s="1" t="s">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="G18" s="1" t="s">
-        <v>1272</v>
-      </c>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1267</v>
+      </c>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A19" s="1" t="s">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="C19" s="1">
         <v>11</v>
       </c>
       <c r="D19" s="1"/>
       <c r="E19" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>1275</v>
+        <v>1270</v>
       </c>
       <c r="G19" s="1" t="s">
-        <v>1276</v>
-      </c>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1271</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A20" s="1" t="s">
-        <v>1277</v>
+        <v>1272</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>1278</v>
+        <v>1273</v>
       </c>
       <c r="C20" s="1">
         <v>13</v>
       </c>
       <c r="D20" s="1"/>
       <c r="E20" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>1279</v>
+        <v>1274</v>
       </c>
       <c r="G20" s="1" t="s">
-        <v>1280</v>
-      </c>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1275</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A21" s="1" t="s">
-        <v>1281</v>
+        <v>1276</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>1282</v>
+        <v>1277</v>
       </c>
       <c r="C21" s="1">
         <v>13</v>
       </c>
       <c r="D21" s="1"/>
       <c r="E21" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F21" s="1" t="s">
-        <v>1283</v>
+        <v>1278</v>
       </c>
       <c r="G21" s="1" t="s">
-        <v>1284</v>
-      </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1279</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A22" s="1" t="s">
-        <v>1285</v>
+        <v>1280</v>
       </c>
       <c r="B22" s="1" t="s">
-        <v>1286</v>
+        <v>1281</v>
       </c>
       <c r="C22" s="1">
         <v>12</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="G22" s="1" t="s">
-        <v>1288</v>
-      </c>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1283</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" s="1" t="s">
-        <v>1289</v>
+        <v>1284</v>
       </c>
       <c r="B23" s="1" t="s">
-        <v>1290</v>
+        <v>1285</v>
       </c>
       <c r="C23" s="1">
         <v>13</v>
       </c>
       <c r="D23" s="1"/>
       <c r="E23" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>1291</v>
+        <v>1286</v>
       </c>
       <c r="G23" s="1" t="s">
-        <v>1292</v>
-      </c>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1287</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" s="1" t="s">
         <v>897</v>
       </c>
       <c r="B24" s="1" t="s">
-        <v>1293</v>
+        <v>1288</v>
       </c>
       <c r="C24" s="1">
         <v>11</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>1294</v>
+        <v>1289</v>
       </c>
       <c r="G24" s="1" t="s">
-        <v>1295</v>
-      </c>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1290</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A25" s="1" t="s">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="B25" s="1" t="s">
-        <v>1297</v>
+        <v>1292</v>
       </c>
       <c r="C25" s="1">
         <v>13</v>
       </c>
       <c r="D25" s="1"/>
       <c r="E25" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>1298</v>
+        <v>1293</v>
       </c>
       <c r="G25" s="1" t="s">
-        <v>1299</v>
-      </c>
-    </row>
-    <row r="26" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1294</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A26" s="1" t="s">
-        <v>1300</v>
+        <v>1295</v>
       </c>
       <c r="B26" s="1" t="s">
-        <v>1301</v>
+        <v>1296</v>
       </c>
       <c r="C26" s="1">
         <v>11</v>
       </c>
       <c r="D26" s="1"/>
       <c r="E26" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>1302</v>
+        <v>1297</v>
       </c>
       <c r="G26" s="1" t="s">
-        <v>1303</v>
-      </c>
-    </row>
-    <row r="27" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1298</v>
+      </c>
+    </row>
+    <row r="27" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A27" s="1" t="s">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="B27" s="1" t="s">
-        <v>1305</v>
+        <v>1300</v>
       </c>
       <c r="C27" s="1">
         <v>12</v>
       </c>
       <c r="D27" s="1"/>
       <c r="E27" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>1306</v>
+        <v>1301</v>
       </c>
       <c r="G27" s="1" t="s">
-        <v>1307</v>
-      </c>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A28" s="1" t="s">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>1309</v>
+        <v>1304</v>
       </c>
       <c r="C28" s="1">
         <v>13</v>
       </c>
       <c r="D28" s="1"/>
       <c r="E28" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>1310</v>
+        <v>1305</v>
       </c>
       <c r="G28" s="1" t="s">
-        <v>1311</v>
-      </c>
-    </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1306</v>
+      </c>
+    </row>
+    <row r="29" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A29" s="1" t="s">
         <v>941</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>1312</v>
+        <v>1307</v>
       </c>
       <c r="C29" s="1">
         <v>11</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>1313</v>
+        <v>1308</v>
       </c>
       <c r="G29" s="1" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="30" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A30" s="1" t="s">
-        <v>1315</v>
+        <v>1310</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>1316</v>
+        <v>1311</v>
       </c>
       <c r="C30" s="1">
         <v>11</v>
       </c>
       <c r="D30" s="1"/>
       <c r="E30" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>1317</v>
+        <v>1312</v>
       </c>
       <c r="G30" s="1" t="s">
-        <v>1318</v>
-      </c>
-    </row>
-    <row r="31" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1313</v>
+      </c>
+    </row>
+    <row r="31" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A31" s="1" t="s">
-        <v>1319</v>
+        <v>1314</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>1320</v>
+        <v>1315</v>
       </c>
       <c r="C31" s="1">
         <v>11</v>
       </c>
       <c r="D31" s="1"/>
       <c r="E31" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>1321</v>
+        <v>1316</v>
       </c>
       <c r="G31" s="1" t="s">
-        <v>1322</v>
-      </c>
-    </row>
-    <row r="32" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="32" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A32" s="1" t="s">
-        <v>1323</v>
+        <v>1318</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>1324</v>
+        <v>1319</v>
       </c>
       <c r="C32" s="1">
         <v>11</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F32" s="1" t="s">
-        <v>1325</v>
+        <v>1320</v>
       </c>
       <c r="G32" s="1" t="s">
-        <v>1326</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1321</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" s="1" t="s">
-        <v>1327</v>
+        <v>1322</v>
       </c>
       <c r="B33" s="1" t="s">
-        <v>1328</v>
+        <v>1323</v>
       </c>
       <c r="C33" s="1">
         <v>12</v>
       </c>
       <c r="D33" s="1"/>
       <c r="E33" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>1329</v>
+        <v>1324</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" s="1" t="s">
-        <v>1331</v>
+        <v>1326</v>
       </c>
       <c r="B34" s="1" t="s">
-        <v>1332</v>
+        <v>1327</v>
       </c>
       <c r="C34" s="1">
         <v>11</v>
       </c>
       <c r="D34" s="1"/>
       <c r="E34" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>1333</v>
+        <v>1328</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>1334</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1329</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" s="1" t="s">
-        <v>1335</v>
+        <v>1330</v>
       </c>
       <c r="B35" s="1" t="s">
-        <v>1336</v>
+        <v>1331</v>
       </c>
       <c r="C35" s="1">
         <v>13</v>
       </c>
       <c r="D35" s="1"/>
       <c r="E35" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F35" s="1" t="s">
-        <v>1337</v>
+        <v>1332</v>
       </c>
       <c r="G35" s="1" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1333</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" s="1" t="s">
-        <v>1339</v>
+        <v>1334</v>
       </c>
       <c r="B36" s="1" t="s">
-        <v>1340</v>
+        <v>1335</v>
       </c>
       <c r="C36" s="1">
         <v>11</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F36" s="1" t="s">
-        <v>1341</v>
+        <v>1336</v>
       </c>
       <c r="G36" s="1" t="s">
-        <v>1342</v>
-      </c>
-    </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1337</v>
+      </c>
+    </row>
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" s="1" t="s">
-        <v>1343</v>
+        <v>1338</v>
       </c>
       <c r="B37" s="1" t="s">
-        <v>1344</v>
+        <v>1339</v>
       </c>
       <c r="C37" s="1">
         <v>11</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F37" s="1" t="s">
-        <v>1345</v>
+        <v>1340</v>
       </c>
       <c r="G37" s="1" t="s">
-        <v>1346</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1341</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" s="1" t="s">
-        <v>1347</v>
+        <v>1342</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>1348</v>
+        <v>1343</v>
       </c>
       <c r="C38" s="1">
         <v>12</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F38" s="1" t="s">
-        <v>1349</v>
+        <v>1344</v>
       </c>
       <c r="G38" s="1" t="s">
-        <v>1350</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1345</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" s="1" t="s">
-        <v>1351</v>
+        <v>1346</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>1352</v>
+        <v>1347</v>
       </c>
       <c r="C39" s="1">
         <v>12</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F39" s="1" t="s">
-        <v>1353</v>
+        <v>1348</v>
       </c>
       <c r="G39" s="1" t="s">
-        <v>1354</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1349</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" s="1" t="s">
-        <v>1355</v>
+        <v>1350</v>
       </c>
       <c r="B40" s="1" t="s">
-        <v>1356</v>
+        <v>1351</v>
       </c>
       <c r="C40" s="1">
         <v>12</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F40" s="1" t="s">
-        <v>1357</v>
+        <v>1352</v>
       </c>
       <c r="G40" s="1" t="s">
-        <v>1358</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1353</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" s="1" t="s">
-        <v>1359</v>
+        <v>1354</v>
       </c>
       <c r="B41" s="1" t="s">
-        <v>1360</v>
+        <v>1355</v>
       </c>
       <c r="C41" s="1">
         <v>12</v>
       </c>
       <c r="D41" s="1"/>
       <c r="E41" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F41" s="1" t="s">
-        <v>1361</v>
+        <v>1356</v>
       </c>
       <c r="G41" s="1" t="s">
-        <v>1362</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1357</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" s="1" t="s">
-        <v>1363</v>
+        <v>1358</v>
       </c>
       <c r="B42" s="1" t="s">
-        <v>1364</v>
+        <v>1359</v>
       </c>
       <c r="C42" s="1">
         <v>13</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>1365</v>
+        <v>1360</v>
       </c>
       <c r="G42" s="1" t="s">
-        <v>1366</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1361</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" s="1" t="s">
-        <v>1367</v>
+        <v>1362</v>
       </c>
       <c r="B43" s="1" t="s">
-        <v>1368</v>
+        <v>1363</v>
       </c>
       <c r="C43" s="1">
         <v>13</v>
       </c>
       <c r="D43" s="1"/>
       <c r="E43" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F43" s="1" t="s">
-        <v>1369</v>
+        <v>1364</v>
       </c>
       <c r="G43" s="1" t="s">
-        <v>1370</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1365</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" s="1" t="s">
-        <v>1371</v>
+        <v>1366</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="C44" s="1">
         <v>13</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F44" s="1" t="s">
-        <v>1373</v>
+        <v>1368</v>
       </c>
       <c r="G44" s="1" t="s">
-        <v>1374</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1369</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" s="1" t="s">
-        <v>1375</v>
+        <v>1370</v>
       </c>
       <c r="B45" s="1" t="s">
-        <v>1376</v>
+        <v>1371</v>
       </c>
       <c r="C45" s="1">
         <v>13</v>
       </c>
       <c r="D45" s="1"/>
       <c r="E45" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F45" s="1" t="s">
-        <v>1377</v>
+        <v>1372</v>
       </c>
       <c r="G45" s="1" t="s">
-        <v>1378</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1373</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" s="1" t="s">
-        <v>1379</v>
+        <v>1374</v>
       </c>
       <c r="B46" s="1" t="s">
-        <v>1380</v>
+        <v>1375</v>
       </c>
       <c r="C46" s="1">
         <v>13</v>
       </c>
       <c r="D46" s="1"/>
       <c r="E46" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F46" s="1" t="s">
-        <v>1381</v>
+        <v>1376</v>
       </c>
       <c r="G46" s="1" t="s">
-        <v>1382</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1377</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" s="1" t="s">
-        <v>1383</v>
+        <v>1378</v>
       </c>
       <c r="B47" s="1" t="s">
-        <v>1384</v>
+        <v>1379</v>
       </c>
       <c r="C47" s="1">
         <v>11</v>
       </c>
       <c r="D47" s="1"/>
       <c r="E47" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F47" s="1" t="s">
-        <v>1385</v>
+        <v>1380</v>
       </c>
       <c r="G47" s="1" t="s">
-        <v>1386</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1381</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" s="1" t="s">
-        <v>1387</v>
+        <v>1382</v>
       </c>
       <c r="B48" s="1" t="s">
-        <v>1388</v>
+        <v>1383</v>
       </c>
       <c r="C48" s="1">
         <v>12</v>
       </c>
       <c r="D48" s="1"/>
       <c r="E48" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F48" s="1" t="s">
-        <v>1389</v>
+        <v>1384</v>
       </c>
       <c r="G48" s="1" t="s">
-        <v>1390</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1385</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" s="1" t="s">
-        <v>1391</v>
+        <v>1386</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>1392</v>
+        <v>1387</v>
       </c>
       <c r="C49" s="1">
         <v>13</v>
       </c>
       <c r="D49" s="1"/>
       <c r="E49" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>1393</v>
+        <v>1388</v>
       </c>
       <c r="G49" s="1" t="s">
-        <v>1394</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1389</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" s="1" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B50" s="1" t="s">
-        <v>1396</v>
+        <v>1391</v>
       </c>
       <c r="C50" s="1">
         <v>12</v>
       </c>
       <c r="D50" s="1"/>
       <c r="E50" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>1397</v>
+        <v>1392</v>
       </c>
       <c r="G50" s="1" t="s">
-        <v>1398</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1393</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" s="1" t="s">
-        <v>1399</v>
+        <v>1394</v>
       </c>
       <c r="B51" s="1" t="s">
-        <v>1400</v>
+        <v>1395</v>
       </c>
       <c r="C51" s="1">
         <v>13</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>1401</v>
+        <v>1396</v>
       </c>
       <c r="G51" s="1" t="s">
-        <v>1402</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1397</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" s="1" t="s">
-        <v>1403</v>
+        <v>1398</v>
       </c>
       <c r="B52" s="1" t="s">
-        <v>1404</v>
+        <v>1399</v>
       </c>
       <c r="C52" s="1">
         <v>13</v>
       </c>
       <c r="D52" s="1"/>
       <c r="E52" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>1405</v>
+        <v>1400</v>
       </c>
       <c r="G52" s="1" t="s">
-        <v>1406</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1401</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" s="1" t="s">
-        <v>1407</v>
+        <v>1402</v>
       </c>
       <c r="B53" s="1" t="s">
-        <v>1408</v>
+        <v>1403</v>
       </c>
       <c r="C53" s="1">
         <v>11</v>
       </c>
       <c r="D53" s="1"/>
       <c r="E53" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F53" s="1" t="s">
-        <v>1409</v>
+        <v>1404</v>
       </c>
       <c r="G53" s="1" t="s">
-        <v>1410</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1405</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" s="1" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="B54" s="1" t="s">
-        <v>1412</v>
+        <v>1407</v>
       </c>
       <c r="C54" s="1">
         <v>13</v>
       </c>
       <c r="D54" s="1"/>
       <c r="E54" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F54" s="1" t="s">
-        <v>1413</v>
+        <v>1408</v>
       </c>
       <c r="G54" s="1" t="s">
-        <v>1414</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1409</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" s="1" t="s">
-        <v>1415</v>
+        <v>1410</v>
       </c>
       <c r="B55" s="1" t="s">
-        <v>1416</v>
+        <v>1411</v>
       </c>
       <c r="C55" s="1">
         <v>11</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F55" s="1" t="s">
-        <v>1417</v>
+        <v>1412</v>
       </c>
       <c r="G55" s="1" t="s">
-        <v>1418</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" s="1" t="s">
-        <v>1419</v>
+        <v>1414</v>
       </c>
       <c r="B56" s="1" t="s">
-        <v>1420</v>
+        <v>1415</v>
       </c>
       <c r="C56" s="1">
         <v>13</v>
       </c>
       <c r="D56" s="1"/>
       <c r="E56" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>1421</v>
+        <v>1416</v>
       </c>
       <c r="G56" s="1" t="s">
-        <v>1422</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1417</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" s="1" t="s">
-        <v>1423</v>
+        <v>1418</v>
       </c>
       <c r="B57" s="1" t="s">
-        <v>1424</v>
+        <v>1419</v>
       </c>
       <c r="C57" s="1">
         <v>13</v>
       </c>
       <c r="D57" s="1"/>
       <c r="E57" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F57" s="1" t="s">
-        <v>1425</v>
+        <v>1420</v>
       </c>
       <c r="G57" s="1" t="s">
-        <v>1426</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1421</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" s="1" t="s">
-        <v>1427</v>
+        <v>1422</v>
       </c>
       <c r="B58" s="1" t="s">
-        <v>1428</v>
+        <v>1423</v>
       </c>
       <c r="C58" s="1">
         <v>13</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F58" s="1" t="s">
-        <v>1429</v>
+        <v>1424</v>
       </c>
       <c r="G58" s="1" t="s">
-        <v>1430</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1425</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" s="1" t="s">
-        <v>1431</v>
+        <v>1426</v>
       </c>
       <c r="B59" s="1" t="s">
-        <v>1432</v>
+        <v>1427</v>
       </c>
       <c r="C59" s="1">
         <v>12</v>
       </c>
       <c r="D59" s="1"/>
       <c r="E59" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F59" s="1" t="s">
-        <v>1433</v>
+        <v>1428</v>
       </c>
       <c r="G59" s="1" t="s">
-        <v>1434</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1429</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" s="1" t="s">
-        <v>1435</v>
+        <v>1430</v>
       </c>
       <c r="B60" s="1" t="s">
-        <v>1436</v>
+        <v>1431</v>
       </c>
       <c r="C60" s="1">
         <v>13</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>1437</v>
+        <v>1432</v>
       </c>
       <c r="G60" s="1" t="s">
-        <v>1438</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1433</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" s="1" t="s">
-        <v>1439</v>
+        <v>1434</v>
       </c>
       <c r="B61" s="1" t="s">
-        <v>1440</v>
+        <v>1435</v>
       </c>
       <c r="C61" s="1">
         <v>13</v>
       </c>
       <c r="D61" s="1"/>
       <c r="E61" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F61" s="1" t="s">
-        <v>1441</v>
+        <v>1436</v>
       </c>
       <c r="G61" s="1" t="s">
-        <v>1442</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1437</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" s="1" t="s">
-        <v>1443</v>
+        <v>1438</v>
       </c>
       <c r="B62" s="1" t="s">
-        <v>1444</v>
+        <v>1439</v>
       </c>
       <c r="C62" s="1">
         <v>11</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F62" s="1" t="s">
-        <v>1445</v>
+        <v>1440</v>
       </c>
       <c r="G62" s="1" t="s">
-        <v>1446</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1441</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" s="1" t="s">
-        <v>1447</v>
+        <v>1442</v>
       </c>
       <c r="B63" s="1" t="s">
-        <v>1448</v>
+        <v>1443</v>
       </c>
       <c r="C63" s="1">
         <v>11</v>
       </c>
       <c r="D63" s="1"/>
       <c r="E63" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F63" s="1" t="s">
-        <v>1449</v>
+        <v>1444</v>
       </c>
       <c r="G63" s="1" t="s">
-        <v>1450</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1445</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" s="1" t="s">
-        <v>1451</v>
+        <v>1446</v>
       </c>
       <c r="B64" s="1" t="s">
-        <v>1452</v>
+        <v>1447</v>
       </c>
       <c r="C64" s="1">
         <v>13</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="G64" s="1" t="s">
-        <v>1453</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1448</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" s="1" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B65" s="1" t="s">
-        <v>1455</v>
+        <v>1450</v>
       </c>
       <c r="C65" s="1">
         <v>13</v>
       </c>
       <c r="D65" s="1"/>
       <c r="E65" s="1" t="s">
-        <v>1245</v>
+        <v>1240</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>1456</v>
+        <v>1451</v>
       </c>
       <c r="G65" s="1" t="s">
-        <v>1457</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1452</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" s="1" t="s">
-        <v>1458</v>
+        <v>1453</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1459</v>
+        <v>1454</v>
       </c>
       <c r="C66" s="1">
         <v>11</v>
       </c>
       <c r="D66" s="1"/>
       <c r="E66" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>1460</v>
+        <v>1455</v>
       </c>
       <c r="G66" s="1" t="s">
-        <v>1461</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" s="1" t="s">
-        <v>1462</v>
+        <v>1457</v>
       </c>
       <c r="B67" s="1" t="s">
-        <v>1463</v>
+        <v>1458</v>
       </c>
       <c r="C67" s="1">
         <v>13</v>
       </c>
       <c r="D67" s="1"/>
       <c r="E67" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>1464</v>
+        <v>1459</v>
       </c>
       <c r="G67" s="1" t="s">
-        <v>1465</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1460</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" s="1" t="s">
-        <v>1466</v>
+        <v>1461</v>
       </c>
       <c r="B68" s="1" t="s">
-        <v>1467</v>
+        <v>1462</v>
       </c>
       <c r="C68" s="1">
         <v>12</v>
       </c>
       <c r="D68" s="1"/>
       <c r="E68" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>1468</v>
+        <v>1463</v>
       </c>
       <c r="G68" s="1" t="s">
-        <v>1469</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1464</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" s="1" t="s">
-        <v>1470</v>
+        <v>1465</v>
       </c>
       <c r="B69" s="1" t="s">
-        <v>1471</v>
+        <v>1466</v>
       </c>
       <c r="C69" s="1">
         <v>12</v>
       </c>
       <c r="D69" s="1"/>
       <c r="E69" s="1" t="s">
-        <v>1202</v>
+        <v>1197</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>1472</v>
+        <v>1467</v>
       </c>
       <c r="G69" s="1" t="s">
-        <v>1473</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1468</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" s="1" t="s">
-        <v>1474</v>
+        <v>1469</v>
       </c>
       <c r="B70" s="1" t="s">
-        <v>1475</v>
+        <v>1470</v>
       </c>
       <c r="C70" s="1">
         <v>13</v>
       </c>
       <c r="D70" s="1"/>
       <c r="E70" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F70" s="1" t="s">
-        <v>1476</v>
+        <v>1471</v>
       </c>
       <c r="G70" s="1" t="s">
-        <v>1477</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1472</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" s="1" t="s">
         <v>91</v>
       </c>
       <c r="B71" s="1" t="s">
-        <v>1478</v>
+        <v>1473</v>
       </c>
       <c r="C71" s="1">
         <v>11</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="F71" s="1" t="s">
-        <v>1479</v>
+        <v>1474</v>
       </c>
       <c r="G71" s="1" t="s">
-        <v>1480</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1475</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" s="1" t="s">
-        <v>1481</v>
+        <v>1476</v>
       </c>
       <c r="B72" s="1" t="s">
-        <v>1482</v>
+        <v>1477</v>
       </c>
       <c r="C72" s="1">
         <v>12</v>
       </c>
       <c r="D72" s="1"/>
       <c r="E72" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F72" s="1" t="s">
-        <v>1483</v>
+        <v>1478</v>
       </c>
       <c r="G72" s="1" t="s">
-        <v>1484</v>
-      </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1479</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A73" s="1" t="s">
-        <v>1485</v>
+        <v>1480</v>
       </c>
       <c r="B73" s="1" t="s">
-        <v>1486</v>
+        <v>1481</v>
       </c>
       <c r="C73" s="1">
         <v>12</v>
       </c>
       <c r="D73" s="1"/>
       <c r="E73" s="1" t="s">
-        <v>1197</v>
+        <v>1192</v>
       </c>
       <c r="F73" s="1" t="s">
-        <v>1487</v>
+        <v>1482</v>
       </c>
       <c r="G73" s="1" t="s">
-        <v>1488</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1483</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A74" s="1" t="s">
-        <v>1489</v>
+        <v>1484</v>
       </c>
       <c r="B74" s="1" t="s">
-        <v>1490</v>
+        <v>1485</v>
       </c>
       <c r="C74" s="1">
         <v>11</v>
       </c>
       <c r="D74" s="1"/>
       <c r="E74" s="1" t="s">
-        <v>1207</v>
+        <v>1202</v>
       </c>
       <c r="F74" s="1" t="s">
-        <v>1491</v>
+        <v>1486</v>
       </c>
       <c r="G74" s="1" t="s">
-        <v>1492</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1487</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" s="1" t="s">
-        <v>1493</v>
+        <v>1488</v>
       </c>
       <c r="B75" s="1" t="s">
-        <v>1494</v>
+        <v>1489</v>
       </c>
       <c r="C75" s="1">
         <v>12</v>
       </c>
       <c r="D75" s="1"/>
       <c r="E75" s="1" t="s">
-        <v>1222</v>
+        <v>1217</v>
       </c>
       <c r="F75" s="1" t="s">
-        <v>1495</v>
+        <v>1490</v>
       </c>
       <c r="G75" s="1" t="s">
-        <v>1496</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1491</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" s="1" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>1498</v>
+        <v>1493</v>
       </c>
       <c r="C76" s="1">
         <v>13</v>
       </c>
       <c r="D76" s="1"/>
       <c r="E76" s="1" t="s">
-        <v>1227</v>
+        <v>1222</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>1499</v>
+        <v>1494</v>
       </c>
       <c r="G76" s="1" t="s">
-        <v>1500</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1495</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" s="1" t="s">
-        <v>1501</v>
+        <v>1496</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>1502</v>
+        <v>1497</v>
       </c>
       <c r="C77" s="1">
         <v>13</v>
       </c>
       <c r="D77" s="1"/>
       <c r="E77" s="1" t="s">
-        <v>1258</v>
+        <v>1253</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>1503</v>
+        <v>1498</v>
       </c>
       <c r="G77" s="1" t="s">
-        <v>1504</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1499</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" s="1" t="s">
-        <v>1505</v>
+        <v>1500</v>
       </c>
       <c r="B78" s="1" t="s">
-        <v>1506</v>
+        <v>1501</v>
       </c>
       <c r="C78" s="1">
         <v>13</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>1212</v>
+        <v>1207</v>
       </c>
       <c r="F78" s="1" t="s">
-        <v>1507</v>
+        <v>1502</v>
       </c>
       <c r="G78" s="1" t="s">
-        <v>1508</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1503</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" s="1" t="s">
-        <v>1509</v>
+        <v>1504</v>
       </c>
       <c r="B79" s="1" t="s">
-        <v>1510</v>
+        <v>1505</v>
       </c>
       <c r="C79" s="1">
         <v>12</v>
       </c>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>1217</v>
+        <v>1212</v>
       </c>
       <c r="F79" s="1" t="s">
-        <v>1511</v>
+        <v>1506</v>
       </c>
       <c r="G79" s="1" t="s">
-        <v>1512</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1507</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" s="1" t="s">
-        <v>1513</v>
+        <v>1508</v>
       </c>
       <c r="B80" s="1" t="s">
-        <v>1514</v>
+        <v>1509</v>
       </c>
       <c r="C80" s="1">
         <v>13</v>
       </c>
       <c r="D80" s="1"/>
       <c r="E80" s="1" t="s">
-        <v>1236</v>
+        <v>1231</v>
       </c>
       <c r="F80" s="1" t="s">
-        <v>1515</v>
+        <v>1510</v>
       </c>
       <c r="G80" s="1" t="s">
-        <v>1516</v>
+        <v>1511</v>
       </c>
     </row>
   </sheetData>
@@ -15153,14 +15125,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G189"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="5" max="5" width="17.19921875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="19.19921875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9.796875" customWidth="1"/>
+    <col min="5" max="5" width="17.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="9.75" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -15183,12 +15155,12 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>1517</v>
+        <v>1512</v>
       </c>
       <c r="B2" t="s">
-        <v>1518</v>
+        <v>1513</v>
       </c>
       <c r="C2">
         <v>11</v>
@@ -15197,15 +15169,15 @@
         <v>67</v>
       </c>
       <c r="F2" t="s">
-        <v>1519</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1514</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>1520</v>
+        <v>1515</v>
       </c>
       <c r="B3" t="s">
-        <v>1521</v>
+        <v>1516</v>
       </c>
       <c r="C3">
         <v>11</v>
@@ -15214,15 +15186,15 @@
         <v>16</v>
       </c>
       <c r="F3" t="s">
-        <v>1522</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1517</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
-        <v>1523</v>
+        <v>1518</v>
       </c>
       <c r="B4" t="s">
-        <v>1524</v>
+        <v>1519</v>
       </c>
       <c r="C4">
         <v>12</v>
@@ -15231,15 +15203,15 @@
         <v>67</v>
       </c>
       <c r="F4" t="s">
-        <v>1525</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1520</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
-        <v>1526</v>
+        <v>1521</v>
       </c>
       <c r="B5" t="s">
-        <v>1527</v>
+        <v>1522</v>
       </c>
       <c r="C5">
         <v>11</v>
@@ -15248,32 +15220,32 @@
         <v>22</v>
       </c>
       <c r="F5" t="s">
+        <v>1523</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>1524</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1525</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
+      </c>
+      <c r="E6" t="s">
+        <v>11</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1526</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>1527</v>
+      </c>
+      <c r="B7" t="s">
         <v>1528</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A6" t="s">
-        <v>1529</v>
-      </c>
-      <c r="B6" t="s">
-        <v>1530</v>
-      </c>
-      <c r="C6">
-        <v>11</v>
-      </c>
-      <c r="E6" t="s">
-        <v>11</v>
-      </c>
-      <c r="F6" t="s">
-        <v>1531</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A7" t="s">
-        <v>1532</v>
-      </c>
-      <c r="B7" t="s">
-        <v>1533</v>
       </c>
       <c r="C7">
         <v>12</v>
@@ -15282,15 +15254,15 @@
         <v>22</v>
       </c>
       <c r="F7" t="s">
-        <v>1534</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1529</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
-        <v>1535</v>
+        <v>1530</v>
       </c>
       <c r="B8" t="s">
-        <v>1536</v>
+        <v>1531</v>
       </c>
       <c r="C8">
         <v>12</v>
@@ -15299,15 +15271,15 @@
         <v>41</v>
       </c>
       <c r="F8" t="s">
-        <v>1537</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1532</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
-        <v>1538</v>
+        <v>1533</v>
       </c>
       <c r="B9" t="s">
-        <v>1539</v>
+        <v>1534</v>
       </c>
       <c r="C9">
         <v>11</v>
@@ -15316,15 +15288,15 @@
         <v>16</v>
       </c>
       <c r="F9" t="s">
-        <v>1540</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1535</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
-        <v>1541</v>
+        <v>1536</v>
       </c>
       <c r="B10" t="s">
-        <v>1542</v>
+        <v>1537</v>
       </c>
       <c r="C10">
         <v>12</v>
@@ -15333,15 +15305,15 @@
         <v>16</v>
       </c>
       <c r="F10" t="s">
-        <v>1543</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1538</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>733</v>
       </c>
       <c r="B11" t="s">
-        <v>1544</v>
+        <v>1539</v>
       </c>
       <c r="C11">
         <v>12</v>
@@ -15350,15 +15322,15 @@
         <v>72</v>
       </c>
       <c r="F11" t="s">
-        <v>1545</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1540</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
-        <v>1546</v>
+        <v>1541</v>
       </c>
       <c r="B12" t="s">
-        <v>1547</v>
+        <v>1542</v>
       </c>
       <c r="C12">
         <v>12</v>
@@ -15367,15 +15339,15 @@
         <v>72</v>
       </c>
       <c r="F12" t="s">
-        <v>1548</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1543</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>1549</v>
+        <v>1544</v>
       </c>
       <c r="B13" t="s">
-        <v>1550</v>
+        <v>1545</v>
       </c>
       <c r="C13">
         <v>13</v>
@@ -15384,15 +15356,15 @@
         <v>11</v>
       </c>
       <c r="F13" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
-        <v>1552</v>
+        <v>1547</v>
       </c>
       <c r="B14" t="s">
-        <v>1553</v>
+        <v>1548</v>
       </c>
       <c r="C14">
         <v>12</v>
@@ -15401,15 +15373,15 @@
         <v>22</v>
       </c>
       <c r="F14" t="s">
-        <v>1554</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1549</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
-        <v>1555</v>
+        <v>1550</v>
       </c>
       <c r="B15" t="s">
-        <v>1556</v>
+        <v>1551</v>
       </c>
       <c r="C15">
         <v>11</v>
@@ -15418,15 +15390,15 @@
         <v>41</v>
       </c>
       <c r="F15" t="s">
-        <v>1557</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1552</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
-        <v>1558</v>
+        <v>1553</v>
       </c>
       <c r="B16" t="s">
-        <v>1559</v>
+        <v>1554</v>
       </c>
       <c r="C16">
         <v>13</v>
@@ -15435,15 +15407,15 @@
         <v>11</v>
       </c>
       <c r="F16" t="s">
-        <v>1560</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1555</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
-        <v>1561</v>
+        <v>1556</v>
       </c>
       <c r="B17" t="s">
-        <v>1562</v>
+        <v>1557</v>
       </c>
       <c r="C17">
         <v>13</v>
@@ -15452,15 +15424,15 @@
         <v>58</v>
       </c>
       <c r="F17" t="s">
-        <v>1563</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1558</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
-        <v>1564</v>
+        <v>1559</v>
       </c>
       <c r="B18" t="s">
-        <v>1565</v>
+        <v>1560</v>
       </c>
       <c r="C18">
         <v>11</v>
@@ -15469,15 +15441,15 @@
         <v>41</v>
       </c>
       <c r="F18" t="s">
-        <v>1551</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1546</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
-        <v>1566</v>
+        <v>1561</v>
       </c>
       <c r="B19" t="s">
-        <v>1567</v>
+        <v>1562</v>
       </c>
       <c r="C19">
         <v>13</v>
@@ -15486,15 +15458,15 @@
         <v>58</v>
       </c>
       <c r="F19" t="s">
-        <v>1568</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1563</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
-        <v>1569</v>
+        <v>1564</v>
       </c>
       <c r="B20" t="s">
-        <v>1570</v>
+        <v>1565</v>
       </c>
       <c r="C20">
         <v>12</v>
@@ -15503,15 +15475,15 @@
         <v>27</v>
       </c>
       <c r="F20" t="s">
-        <v>1571</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1566</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
-        <v>1572</v>
+        <v>1567</v>
       </c>
       <c r="B21" t="s">
-        <v>1573</v>
+        <v>1568</v>
       </c>
       <c r="C21">
         <v>12</v>
@@ -15520,15 +15492,15 @@
         <v>11</v>
       </c>
       <c r="F21" t="s">
-        <v>1574</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1569</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
-        <v>1575</v>
+        <v>1570</v>
       </c>
       <c r="B22" t="s">
-        <v>1576</v>
+        <v>1571</v>
       </c>
       <c r="C22">
         <v>13</v>
@@ -15540,12 +15512,12 @@
         <v>184</v>
       </c>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>1577</v>
+        <v>1572</v>
       </c>
       <c r="B23" t="s">
-        <v>1578</v>
+        <v>1573</v>
       </c>
       <c r="C23">
         <v>13</v>
@@ -15554,15 +15526,15 @@
         <v>16</v>
       </c>
       <c r="F23" t="s">
-        <v>1579</v>
-      </c>
-    </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1574</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>1580</v>
+        <v>1575</v>
       </c>
       <c r="B24" t="s">
-        <v>1581</v>
+        <v>1576</v>
       </c>
       <c r="C24">
         <v>13</v>
@@ -15571,15 +15543,15 @@
         <v>58</v>
       </c>
       <c r="F24" t="s">
-        <v>1582</v>
-      </c>
-    </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1577</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
-        <v>1583</v>
+        <v>1578</v>
       </c>
       <c r="B25" t="s">
-        <v>1584</v>
+        <v>1579</v>
       </c>
       <c r="C25">
         <v>11</v>
@@ -15588,15 +15560,15 @@
         <v>22</v>
       </c>
       <c r="F25" t="s">
-        <v>1585</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1580</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
-        <v>1586</v>
+        <v>1581</v>
       </c>
       <c r="B26" t="s">
-        <v>1587</v>
+        <v>1582</v>
       </c>
       <c r="C26">
         <v>12</v>
@@ -15605,15 +15577,15 @@
         <v>72</v>
       </c>
       <c r="F26" t="s">
-        <v>1588</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1583</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
-        <v>1497</v>
+        <v>1492</v>
       </c>
       <c r="B27" t="s">
-        <v>1589</v>
+        <v>1584</v>
       </c>
       <c r="C27">
         <v>12</v>
@@ -15622,15 +15594,15 @@
         <v>41</v>
       </c>
       <c r="F27" t="s">
-        <v>1590</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1585</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
-        <v>1591</v>
+        <v>1586</v>
       </c>
       <c r="B28" t="s">
-        <v>1592</v>
+        <v>1587</v>
       </c>
       <c r="C28">
         <v>11</v>
@@ -15639,15 +15611,15 @@
         <v>16</v>
       </c>
       <c r="F28" t="s">
-        <v>1593</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1588</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
-        <v>1594</v>
+        <v>1589</v>
       </c>
       <c r="B29" t="s">
-        <v>1595</v>
+        <v>1590</v>
       </c>
       <c r="C29">
         <v>12</v>
@@ -15656,15 +15628,15 @@
         <v>16</v>
       </c>
       <c r="F29" t="s">
-        <v>1596</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1591</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
-        <v>1454</v>
+        <v>1449</v>
       </c>
       <c r="B30" t="s">
-        <v>1597</v>
+        <v>1592</v>
       </c>
       <c r="C30">
         <v>11</v>
@@ -15673,15 +15645,15 @@
         <v>72</v>
       </c>
       <c r="F30" t="s">
-        <v>1598</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1593</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
-        <v>1599</v>
+        <v>1594</v>
       </c>
       <c r="B31" t="s">
-        <v>1600</v>
+        <v>1595</v>
       </c>
       <c r="C31">
         <v>13</v>
@@ -15690,15 +15662,15 @@
         <v>22</v>
       </c>
       <c r="F31" t="s">
-        <v>1601</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.4">
+        <v>1596</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
-        <v>1602</v>
+        <v>1597</v>
       </c>
       <c r="B32" t="s">
-        <v>1603</v>
+        <v>1598</v>
       </c>
       <c r="C32">
         <v>13</v>
@@ -15707,15 +15679,15 @@
         <v>72</v>
       </c>
       <c r="F32" t="s">
-        <v>1604</v>
-      </c>
-    </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1599</v>
+      </c>
+    </row>
+    <row r="33" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
-        <v>1605</v>
+        <v>1600</v>
       </c>
       <c r="B33" t="s">
-        <v>1606</v>
+        <v>1601</v>
       </c>
       <c r="C33">
         <v>11</v>
@@ -15724,15 +15696,15 @@
         <v>67</v>
       </c>
       <c r="F33" t="s">
-        <v>1607</v>
-      </c>
-    </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1602</v>
+      </c>
+    </row>
+    <row r="34" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
-        <v>1608</v>
+        <v>1603</v>
       </c>
       <c r="B34" t="s">
-        <v>1609</v>
+        <v>1604</v>
       </c>
       <c r="C34">
         <v>11</v>
@@ -15741,15 +15713,15 @@
         <v>22</v>
       </c>
       <c r="F34" t="s">
-        <v>1610</v>
-      </c>
-    </row>
-    <row r="35" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1605</v>
+      </c>
+    </row>
+    <row r="35" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
-        <v>1611</v>
+        <v>1606</v>
       </c>
       <c r="B35" t="s">
-        <v>1612</v>
+        <v>1607</v>
       </c>
       <c r="C35">
         <v>13</v>
@@ -15758,15 +15730,15 @@
         <v>72</v>
       </c>
       <c r="F35" t="s">
-        <v>1613</v>
-      </c>
-    </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1608</v>
+      </c>
+    </row>
+    <row r="36" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="B36" t="s">
-        <v>1615</v>
+        <v>1610</v>
       </c>
       <c r="C36">
         <v>13</v>
@@ -15778,12 +15750,12 @@
         <v>288</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
-        <v>1616</v>
+        <v>1611</v>
       </c>
       <c r="B37" t="s">
-        <v>1617</v>
+        <v>1612</v>
       </c>
       <c r="C37">
         <v>11</v>
@@ -15792,15 +15764,15 @@
         <v>16</v>
       </c>
       <c r="F37" t="s">
-        <v>1618</v>
-      </c>
-    </row>
-    <row r="38" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1613</v>
+      </c>
+    </row>
+    <row r="38" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
-        <v>1619</v>
+        <v>1614</v>
       </c>
       <c r="B38" t="s">
-        <v>1620</v>
+        <v>1615</v>
       </c>
       <c r="C38">
         <v>12</v>
@@ -15812,15 +15784,15 @@
         <v>1134</v>
       </c>
       <c r="G38" t="s">
-        <v>1621</v>
-      </c>
-    </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1616</v>
+      </c>
+    </row>
+    <row r="39" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
-        <v>1622</v>
+        <v>1617</v>
       </c>
       <c r="B39" t="s">
-        <v>1623</v>
+        <v>1618</v>
       </c>
       <c r="C39">
         <v>11</v>
@@ -15832,15 +15804,15 @@
         <v>268</v>
       </c>
       <c r="G39" t="s">
-        <v>1624</v>
-      </c>
-    </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1619</v>
+      </c>
+    </row>
+    <row r="40" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
-        <v>1625</v>
+        <v>1620</v>
       </c>
       <c r="B40" t="s">
-        <v>1626</v>
+        <v>1621</v>
       </c>
       <c r="C40">
         <v>11</v>
@@ -15849,18 +15821,18 @@
         <v>27</v>
       </c>
       <c r="F40" t="s">
-        <v>1627</v>
+        <v>1622</v>
       </c>
       <c r="G40" t="s">
-        <v>1628</v>
-      </c>
-    </row>
-    <row r="41" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1623</v>
+      </c>
+    </row>
+    <row r="41" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
-        <v>1629</v>
+        <v>1624</v>
       </c>
       <c r="B41" t="s">
-        <v>1630</v>
+        <v>1625</v>
       </c>
       <c r="C41">
         <v>13</v>
@@ -15869,18 +15841,18 @@
         <v>27</v>
       </c>
       <c r="F41" t="s">
-        <v>1631</v>
+        <v>1626</v>
       </c>
       <c r="G41" t="s">
-        <v>1632</v>
-      </c>
-    </row>
-    <row r="42" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1627</v>
+      </c>
+    </row>
+    <row r="42" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
-        <v>1633</v>
+        <v>1628</v>
       </c>
       <c r="B42" t="s">
-        <v>1634</v>
+        <v>1629</v>
       </c>
       <c r="C42">
         <v>12</v>
@@ -15889,18 +15861,18 @@
         <v>16</v>
       </c>
       <c r="F42" t="s">
-        <v>1635</v>
+        <v>1630</v>
       </c>
       <c r="G42" t="s">
-        <v>1636</v>
-      </c>
-    </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1631</v>
+      </c>
+    </row>
+    <row r="43" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
-        <v>1637</v>
+        <v>1632</v>
       </c>
       <c r="B43" t="s">
-        <v>1638</v>
+        <v>1633</v>
       </c>
       <c r="C43">
         <v>13</v>
@@ -15909,18 +15881,18 @@
         <v>36</v>
       </c>
       <c r="F43" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="G43" t="s">
-        <v>1640</v>
-      </c>
-    </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1635</v>
+      </c>
+    </row>
+    <row r="44" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
-        <v>1641</v>
+        <v>1636</v>
       </c>
       <c r="B44" t="s">
-        <v>1642</v>
+        <v>1637</v>
       </c>
       <c r="C44">
         <v>13</v>
@@ -15929,18 +15901,18 @@
         <v>11</v>
       </c>
       <c r="F44" t="s">
-        <v>1643</v>
+        <v>1638</v>
       </c>
       <c r="G44" t="s">
-        <v>1644</v>
-      </c>
-    </row>
-    <row r="45" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1639</v>
+      </c>
+    </row>
+    <row r="45" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
-        <v>1645</v>
+        <v>1640</v>
       </c>
       <c r="B45" t="s">
-        <v>1646</v>
+        <v>1641</v>
       </c>
       <c r="C45">
         <v>12</v>
@@ -15949,18 +15921,18 @@
         <v>72</v>
       </c>
       <c r="F45" t="s">
-        <v>1647</v>
+        <v>1642</v>
       </c>
       <c r="G45" t="s">
-        <v>1648</v>
-      </c>
-    </row>
-    <row r="46" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1643</v>
+      </c>
+    </row>
+    <row r="46" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
-        <v>1649</v>
+        <v>1644</v>
       </c>
       <c r="B46" t="s">
-        <v>1650</v>
+        <v>1645</v>
       </c>
       <c r="C46">
         <v>11</v>
@@ -15969,18 +15941,18 @@
         <v>16</v>
       </c>
       <c r="F46" t="s">
-        <v>1651</v>
+        <v>1646</v>
       </c>
       <c r="G46" t="s">
-        <v>1652</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1647</v>
+      </c>
+    </row>
+    <row r="47" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
-        <v>1653</v>
+        <v>1648</v>
       </c>
       <c r="B47" t="s">
-        <v>1654</v>
+        <v>1649</v>
       </c>
       <c r="C47">
         <v>12</v>
@@ -15989,18 +15961,18 @@
         <v>58</v>
       </c>
       <c r="F47" t="s">
-        <v>1655</v>
+        <v>1650</v>
       </c>
       <c r="G47" t="s">
-        <v>1656</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1651</v>
+      </c>
+    </row>
+    <row r="48" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
-        <v>1657</v>
+        <v>1652</v>
       </c>
       <c r="B48" t="s">
-        <v>1658</v>
+        <v>1653</v>
       </c>
       <c r="C48">
         <v>12</v>
@@ -16009,18 +15981,18 @@
         <v>27</v>
       </c>
       <c r="F48" t="s">
-        <v>1659</v>
+        <v>1654</v>
       </c>
       <c r="G48" t="s">
-        <v>1660</v>
-      </c>
-    </row>
-    <row r="49" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="49" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
-        <v>1661</v>
+        <v>1656</v>
       </c>
       <c r="B49" t="s">
-        <v>1662</v>
+        <v>1657</v>
       </c>
       <c r="C49">
         <v>11</v>
@@ -16029,18 +16001,18 @@
         <v>36</v>
       </c>
       <c r="F49" t="s">
-        <v>1663</v>
+        <v>1658</v>
       </c>
       <c r="G49" t="s">
-        <v>1664</v>
-      </c>
-    </row>
-    <row r="50" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1659</v>
+      </c>
+    </row>
+    <row r="50" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
-        <v>1665</v>
+        <v>1660</v>
       </c>
       <c r="B50" t="s">
-        <v>1666</v>
+        <v>1661</v>
       </c>
       <c r="C50">
         <v>12</v>
@@ -16049,18 +16021,18 @@
         <v>41</v>
       </c>
       <c r="F50" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="G50" t="s">
-        <v>1668</v>
-      </c>
-    </row>
-    <row r="51" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1663</v>
+      </c>
+    </row>
+    <row r="51" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
-        <v>1669</v>
+        <v>1664</v>
       </c>
       <c r="B51" t="s">
-        <v>1670</v>
+        <v>1665</v>
       </c>
       <c r="C51">
         <v>11</v>
@@ -16069,18 +16041,18 @@
         <v>27</v>
       </c>
       <c r="F51" t="s">
-        <v>1671</v>
+        <v>1666</v>
       </c>
       <c r="G51" t="s">
-        <v>1672</v>
-      </c>
-    </row>
-    <row r="52" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1667</v>
+      </c>
+    </row>
+    <row r="52" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
-        <v>1614</v>
+        <v>1609</v>
       </c>
       <c r="B52" t="s">
-        <v>1673</v>
+        <v>1668</v>
       </c>
       <c r="C52">
         <v>11</v>
@@ -16092,15 +16064,15 @@
         <v>466</v>
       </c>
       <c r="G52" t="s">
-        <v>1674</v>
-      </c>
-    </row>
-    <row r="53" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1669</v>
+      </c>
+    </row>
+    <row r="53" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
-        <v>1675</v>
+        <v>1670</v>
       </c>
       <c r="B53" t="s">
-        <v>1676</v>
+        <v>1671</v>
       </c>
       <c r="C53">
         <v>11</v>
@@ -16109,18 +16081,18 @@
         <v>72</v>
       </c>
       <c r="F53" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="G53" t="s">
-        <v>1678</v>
-      </c>
-    </row>
-    <row r="54" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="54" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
-        <v>1679</v>
+        <v>1674</v>
       </c>
       <c r="B54" t="s">
-        <v>1680</v>
+        <v>1675</v>
       </c>
       <c r="C54">
         <v>12</v>
@@ -16129,18 +16101,18 @@
         <v>72</v>
       </c>
       <c r="F54" t="s">
-        <v>1681</v>
+        <v>1676</v>
       </c>
       <c r="G54" t="s">
-        <v>1682</v>
-      </c>
-    </row>
-    <row r="55" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1677</v>
+      </c>
+    </row>
+    <row r="55" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
-        <v>1683</v>
+        <v>1678</v>
       </c>
       <c r="B55" t="s">
-        <v>1684</v>
+        <v>1679</v>
       </c>
       <c r="C55">
         <v>12</v>
@@ -16149,18 +16121,18 @@
         <v>36</v>
       </c>
       <c r="F55" t="s">
-        <v>1685</v>
+        <v>1680</v>
       </c>
       <c r="G55" t="s">
-        <v>1686</v>
-      </c>
-    </row>
-    <row r="56" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1681</v>
+      </c>
+    </row>
+    <row r="56" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
-        <v>1687</v>
+        <v>1682</v>
       </c>
       <c r="B56" t="s">
-        <v>1688</v>
+        <v>1683</v>
       </c>
       <c r="C56">
         <v>11</v>
@@ -16169,18 +16141,18 @@
         <v>67</v>
       </c>
       <c r="F56" t="s">
-        <v>1689</v>
+        <v>1684</v>
       </c>
       <c r="G56" t="s">
-        <v>1690</v>
-      </c>
-    </row>
-    <row r="57" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1685</v>
+      </c>
+    </row>
+    <row r="57" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
-        <v>1691</v>
+        <v>1686</v>
       </c>
       <c r="B57" t="s">
-        <v>1692</v>
+        <v>1687</v>
       </c>
       <c r="C57">
         <v>13</v>
@@ -16189,18 +16161,18 @@
         <v>58</v>
       </c>
       <c r="F57" t="s">
-        <v>1693</v>
+        <v>1688</v>
       </c>
       <c r="G57" t="s">
-        <v>1694</v>
-      </c>
-    </row>
-    <row r="58" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1689</v>
+      </c>
+    </row>
+    <row r="58" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
-        <v>1695</v>
+        <v>1690</v>
       </c>
       <c r="B58" t="s">
-        <v>1696</v>
+        <v>1691</v>
       </c>
       <c r="C58">
         <v>11</v>
@@ -16209,18 +16181,18 @@
         <v>22</v>
       </c>
       <c r="F58" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="G58" t="s">
-        <v>1698</v>
-      </c>
-    </row>
-    <row r="59" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1693</v>
+      </c>
+    </row>
+    <row r="59" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
-        <v>1699</v>
+        <v>1694</v>
       </c>
       <c r="B59" t="s">
-        <v>1700</v>
+        <v>1695</v>
       </c>
       <c r="C59">
         <v>11</v>
@@ -16229,18 +16201,18 @@
         <v>58</v>
       </c>
       <c r="F59" t="s">
-        <v>1701</v>
+        <v>1696</v>
       </c>
       <c r="G59" t="s">
-        <v>1702</v>
-      </c>
-    </row>
-    <row r="60" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1697</v>
+      </c>
+    </row>
+    <row r="60" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
-        <v>1703</v>
+        <v>1698</v>
       </c>
       <c r="B60" t="s">
-        <v>1704</v>
+        <v>1699</v>
       </c>
       <c r="C60">
         <v>13</v>
@@ -16249,18 +16221,18 @@
         <v>41</v>
       </c>
       <c r="F60" t="s">
-        <v>1590</v>
+        <v>1585</v>
       </c>
       <c r="G60" t="s">
-        <v>1705</v>
-      </c>
-    </row>
-    <row r="61" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1700</v>
+      </c>
+    </row>
+    <row r="61" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
-        <v>1706</v>
+        <v>1701</v>
       </c>
       <c r="B61" t="s">
-        <v>1707</v>
+        <v>1702</v>
       </c>
       <c r="C61">
         <v>11</v>
@@ -16269,18 +16241,18 @@
         <v>16</v>
       </c>
       <c r="F61" t="s">
-        <v>1708</v>
+        <v>1703</v>
       </c>
       <c r="G61" t="s">
-        <v>1709</v>
-      </c>
-    </row>
-    <row r="62" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1704</v>
+      </c>
+    </row>
+    <row r="62" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
-        <v>1710</v>
+        <v>1705</v>
       </c>
       <c r="B62" t="s">
-        <v>1711</v>
+        <v>1706</v>
       </c>
       <c r="C62">
         <v>13</v>
@@ -16289,18 +16261,18 @@
         <v>72</v>
       </c>
       <c r="F62" t="s">
-        <v>1712</v>
+        <v>1707</v>
       </c>
       <c r="G62" t="s">
-        <v>1713</v>
-      </c>
-    </row>
-    <row r="63" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1708</v>
+      </c>
+    </row>
+    <row r="63" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
-        <v>1714</v>
+        <v>1709</v>
       </c>
       <c r="B63" t="s">
-        <v>1715</v>
+        <v>1710</v>
       </c>
       <c r="C63">
         <v>12</v>
@@ -16309,18 +16281,18 @@
         <v>41</v>
       </c>
       <c r="F63" t="s">
-        <v>1716</v>
+        <v>1711</v>
       </c>
       <c r="G63" t="s">
-        <v>1717</v>
-      </c>
-    </row>
-    <row r="64" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1712</v>
+      </c>
+    </row>
+    <row r="64" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
-        <v>1718</v>
+        <v>1713</v>
       </c>
       <c r="B64" t="s">
-        <v>1719</v>
+        <v>1714</v>
       </c>
       <c r="C64">
         <v>12</v>
@@ -16329,18 +16301,18 @@
         <v>58</v>
       </c>
       <c r="F64" t="s">
-        <v>1720</v>
+        <v>1715</v>
       </c>
       <c r="G64" t="s">
-        <v>1721</v>
-      </c>
-    </row>
-    <row r="65" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1716</v>
+      </c>
+    </row>
+    <row r="65" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
-        <v>1722</v>
+        <v>1717</v>
       </c>
       <c r="B65" t="s">
-        <v>1723</v>
+        <v>1718</v>
       </c>
       <c r="C65">
         <v>13</v>
@@ -16349,18 +16321,18 @@
         <v>41</v>
       </c>
       <c r="F65" t="s">
-        <v>1724</v>
+        <v>1719</v>
       </c>
       <c r="G65" t="s">
-        <v>1725</v>
-      </c>
-    </row>
-    <row r="66" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1720</v>
+      </c>
+    </row>
+    <row r="66" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
-        <v>1726</v>
+        <v>1721</v>
       </c>
       <c r="B66" t="s">
-        <v>1727</v>
+        <v>1722</v>
       </c>
       <c r="C66">
         <v>11</v>
@@ -16372,18 +16344,18 @@
         <v>679</v>
       </c>
       <c r="F66" t="s">
-        <v>1728</v>
+        <v>1723</v>
       </c>
       <c r="G66" t="s">
-        <v>1729</v>
-      </c>
-    </row>
-    <row r="67" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1724</v>
+      </c>
+    </row>
+    <row r="67" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
-        <v>1730</v>
+        <v>1725</v>
       </c>
       <c r="B67" t="s">
-        <v>1731</v>
+        <v>1726</v>
       </c>
       <c r="C67">
         <v>12</v>
@@ -16395,18 +16367,18 @@
         <v>16</v>
       </c>
       <c r="F67" t="s">
-        <v>1732</v>
+        <v>1727</v>
       </c>
       <c r="G67" t="s">
-        <v>1733</v>
-      </c>
-    </row>
-    <row r="68" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1728</v>
+      </c>
+    </row>
+    <row r="68" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
-        <v>1734</v>
+        <v>1729</v>
       </c>
       <c r="B68" t="s">
-        <v>1735</v>
+        <v>1730</v>
       </c>
       <c r="C68">
         <v>12</v>
@@ -16421,15 +16393,15 @@
         <v>212</v>
       </c>
       <c r="G68" t="s">
-        <v>1736</v>
-      </c>
-    </row>
-    <row r="69" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="69" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
-        <v>1737</v>
+        <v>1732</v>
       </c>
       <c r="B69" t="s">
-        <v>1738</v>
+        <v>1733</v>
       </c>
       <c r="C69">
         <v>12</v>
@@ -16444,15 +16416,15 @@
         <v>545</v>
       </c>
       <c r="G69" t="s">
-        <v>1739</v>
-      </c>
-    </row>
-    <row r="70" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1734</v>
+      </c>
+    </row>
+    <row r="70" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
-        <v>1740</v>
+        <v>1735</v>
       </c>
       <c r="B70" t="s">
-        <v>1741</v>
+        <v>1736</v>
       </c>
       <c r="C70">
         <v>12</v>
@@ -16464,18 +16436,18 @@
         <v>11</v>
       </c>
       <c r="F70" t="s">
-        <v>1742</v>
+        <v>1737</v>
       </c>
       <c r="G70" t="s">
-        <v>1743</v>
-      </c>
-    </row>
-    <row r="71" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1738</v>
+      </c>
+    </row>
+    <row r="71" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
-        <v>1744</v>
+        <v>1739</v>
       </c>
       <c r="B71" t="s">
-        <v>1745</v>
+        <v>1740</v>
       </c>
       <c r="C71">
         <v>13</v>
@@ -16487,18 +16459,18 @@
         <v>22</v>
       </c>
       <c r="F71" t="s">
-        <v>1746</v>
+        <v>1741</v>
       </c>
       <c r="G71" t="s">
-        <v>1747</v>
-      </c>
-    </row>
-    <row r="72" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1742</v>
+      </c>
+    </row>
+    <row r="72" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
-        <v>1748</v>
+        <v>1743</v>
       </c>
       <c r="B72" t="s">
-        <v>1749</v>
+        <v>1744</v>
       </c>
       <c r="C72">
         <v>11</v>
@@ -16510,41 +16482,41 @@
         <v>36</v>
       </c>
       <c r="F72" t="s">
-        <v>1639</v>
+        <v>1634</v>
       </c>
       <c r="G72" t="s">
+        <v>1745</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A73" t="s">
+        <v>1746</v>
+      </c>
+      <c r="B73" t="s">
+        <v>1747</v>
+      </c>
+      <c r="C73">
+        <v>11</v>
+      </c>
+      <c r="D73" t="s">
+        <v>10</v>
+      </c>
+      <c r="E73" t="s">
+        <v>11</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1748</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1749</v>
+      </c>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A74" t="s">
         <v>1750</v>
       </c>
-    </row>
-    <row r="73" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A73" t="s">
+      <c r="B74" t="s">
         <v>1751</v>
-      </c>
-      <c r="B73" t="s">
-        <v>1752</v>
-      </c>
-      <c r="C73">
-        <v>11</v>
-      </c>
-      <c r="D73" t="s">
-        <v>10</v>
-      </c>
-      <c r="E73" t="s">
-        <v>11</v>
-      </c>
-      <c r="F73" t="s">
-        <v>1753</v>
-      </c>
-      <c r="G73" t="s">
-        <v>1754</v>
-      </c>
-    </row>
-    <row r="74" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A74" t="s">
-        <v>1755</v>
-      </c>
-      <c r="B74" t="s">
-        <v>1756</v>
       </c>
       <c r="C74">
         <v>12</v>
@@ -16559,15 +16531,15 @@
         <v>141</v>
       </c>
       <c r="G74" t="s">
-        <v>1757</v>
-      </c>
-    </row>
-    <row r="75" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1752</v>
+      </c>
+    </row>
+    <row r="75" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
-        <v>1758</v>
+        <v>1753</v>
       </c>
       <c r="B75" t="s">
-        <v>1759</v>
+        <v>1754</v>
       </c>
       <c r="C75">
         <v>11</v>
@@ -16582,15 +16554,15 @@
         <v>68</v>
       </c>
       <c r="G75" t="s">
-        <v>1760</v>
-      </c>
-    </row>
-    <row r="76" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1755</v>
+      </c>
+    </row>
+    <row r="76" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
-        <v>1761</v>
+        <v>1756</v>
       </c>
       <c r="B76" t="s">
-        <v>1762</v>
+        <v>1757</v>
       </c>
       <c r="C76">
         <v>11</v>
@@ -16602,18 +16574,18 @@
         <v>58</v>
       </c>
       <c r="F76" t="s">
-        <v>1763</v>
+        <v>1758</v>
       </c>
       <c r="G76" t="s">
-        <v>1764</v>
-      </c>
-    </row>
-    <row r="77" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1759</v>
+      </c>
+    </row>
+    <row r="77" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
-        <v>1765</v>
+        <v>1760</v>
       </c>
       <c r="B77" t="s">
-        <v>1766</v>
+        <v>1761</v>
       </c>
       <c r="C77">
         <v>13</v>
@@ -16625,18 +16597,18 @@
         <v>58</v>
       </c>
       <c r="F77" t="s">
-        <v>1767</v>
+        <v>1762</v>
       </c>
       <c r="G77" t="s">
-        <v>1768</v>
-      </c>
-    </row>
-    <row r="78" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1763</v>
+      </c>
+    </row>
+    <row r="78" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
-        <v>1769</v>
+        <v>1764</v>
       </c>
       <c r="B78" t="s">
-        <v>1770</v>
+        <v>1765</v>
       </c>
       <c r="C78">
         <v>13</v>
@@ -16648,18 +16620,18 @@
         <v>22</v>
       </c>
       <c r="F78" t="s">
-        <v>1771</v>
+        <v>1766</v>
       </c>
       <c r="G78" t="s">
-        <v>1772</v>
-      </c>
-    </row>
-    <row r="79" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1767</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
-        <v>1773</v>
+        <v>1768</v>
       </c>
       <c r="B79" t="s">
-        <v>1774</v>
+        <v>1769</v>
       </c>
       <c r="C79">
         <v>12</v>
@@ -16674,15 +16646,15 @@
         <v>696</v>
       </c>
       <c r="G79" t="s">
-        <v>1775</v>
-      </c>
-    </row>
-    <row r="80" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1770</v>
+      </c>
+    </row>
+    <row r="80" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
-        <v>1776</v>
+        <v>1771</v>
       </c>
       <c r="B80" t="s">
-        <v>1777</v>
+        <v>1772</v>
       </c>
       <c r="C80">
         <v>13</v>
@@ -16694,18 +16666,18 @@
         <v>11</v>
       </c>
       <c r="F80" t="s">
-        <v>1778</v>
+        <v>1773</v>
       </c>
       <c r="G80" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="81" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1774</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
-        <v>1780</v>
+        <v>1775</v>
       </c>
       <c r="B81" t="s">
-        <v>1781</v>
+        <v>1776</v>
       </c>
       <c r="C81">
         <v>12</v>
@@ -16717,18 +16689,18 @@
         <v>67</v>
       </c>
       <c r="F81" t="s">
-        <v>1782</v>
+        <v>1777</v>
       </c>
       <c r="G81" t="s">
-        <v>1783</v>
-      </c>
-    </row>
-    <row r="82" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1778</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
-        <v>1784</v>
+        <v>1779</v>
       </c>
       <c r="B82" t="s">
-        <v>1785</v>
+        <v>1780</v>
       </c>
       <c r="C82">
         <v>13</v>
@@ -16740,18 +16712,18 @@
         <v>22</v>
       </c>
       <c r="F82" t="s">
-        <v>1786</v>
+        <v>1781</v>
       </c>
       <c r="G82" t="s">
-        <v>1787</v>
-      </c>
-    </row>
-    <row r="83" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1782</v>
+      </c>
+    </row>
+    <row r="83" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
-        <v>1788</v>
+        <v>1783</v>
       </c>
       <c r="B83" t="s">
-        <v>1789</v>
+        <v>1784</v>
       </c>
       <c r="C83">
         <v>12</v>
@@ -16763,18 +16735,18 @@
         <v>41</v>
       </c>
       <c r="F83" t="s">
-        <v>1790</v>
+        <v>1785</v>
       </c>
       <c r="G83" t="s">
-        <v>1791</v>
-      </c>
-    </row>
-    <row r="84" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1786</v>
+      </c>
+    </row>
+    <row r="84" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
-        <v>1792</v>
+        <v>1787</v>
       </c>
       <c r="B84" t="s">
-        <v>1793</v>
+        <v>1788</v>
       </c>
       <c r="C84">
         <v>12</v>
@@ -16786,18 +16758,18 @@
         <v>58</v>
       </c>
       <c r="F84" t="s">
-        <v>1794</v>
+        <v>1789</v>
       </c>
       <c r="G84" t="s">
-        <v>1795</v>
-      </c>
-    </row>
-    <row r="85" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1790</v>
+      </c>
+    </row>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
-        <v>1796</v>
+        <v>1791</v>
       </c>
       <c r="B85" t="s">
-        <v>1797</v>
+        <v>1792</v>
       </c>
       <c r="C85">
         <v>13</v>
@@ -16809,18 +16781,18 @@
         <v>72</v>
       </c>
       <c r="F85" t="s">
-        <v>1798</v>
+        <v>1793</v>
       </c>
       <c r="G85" t="s">
-        <v>1799</v>
-      </c>
-    </row>
-    <row r="86" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1794</v>
+      </c>
+    </row>
+    <row r="86" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
-        <v>1800</v>
+        <v>1795</v>
       </c>
       <c r="B86" t="s">
-        <v>1801</v>
+        <v>1796</v>
       </c>
       <c r="C86">
         <v>12</v>
@@ -16832,18 +16804,18 @@
         <v>58</v>
       </c>
       <c r="F86" t="s">
-        <v>1802</v>
+        <v>1797</v>
       </c>
       <c r="G86" t="s">
-        <v>1803</v>
-      </c>
-    </row>
-    <row r="87" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1798</v>
+      </c>
+    </row>
+    <row r="87" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
-        <v>1804</v>
+        <v>1799</v>
       </c>
       <c r="B87" t="s">
-        <v>1805</v>
+        <v>1800</v>
       </c>
       <c r="C87">
         <v>13</v>
@@ -16855,18 +16827,18 @@
         <v>679</v>
       </c>
       <c r="F87" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="G87" t="s">
-        <v>1807</v>
-      </c>
-    </row>
-    <row r="88" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1802</v>
+      </c>
+    </row>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
-        <v>1808</v>
+        <v>1803</v>
       </c>
       <c r="B88" t="s">
-        <v>1809</v>
+        <v>1804</v>
       </c>
       <c r="C88">
         <v>12</v>
@@ -16878,18 +16850,18 @@
         <v>41</v>
       </c>
       <c r="F88" t="s">
-        <v>1667</v>
+        <v>1662</v>
       </c>
       <c r="G88" t="s">
-        <v>1810</v>
-      </c>
-    </row>
-    <row r="89" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1805</v>
+      </c>
+    </row>
+    <row r="89" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
-        <v>1811</v>
+        <v>1806</v>
       </c>
       <c r="B89" t="s">
-        <v>1812</v>
+        <v>1807</v>
       </c>
       <c r="C89">
         <v>11</v>
@@ -16901,18 +16873,18 @@
         <v>16</v>
       </c>
       <c r="F89" t="s">
-        <v>1813</v>
+        <v>1808</v>
       </c>
       <c r="G89" t="s">
-        <v>1814</v>
-      </c>
-    </row>
-    <row r="90" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1809</v>
+      </c>
+    </row>
+    <row r="90" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
-        <v>1815</v>
+        <v>1810</v>
       </c>
       <c r="B90" t="s">
-        <v>1816</v>
+        <v>1811</v>
       </c>
       <c r="C90">
         <v>12</v>
@@ -16924,18 +16896,18 @@
         <v>72</v>
       </c>
       <c r="F90" t="s">
-        <v>1817</v>
+        <v>1812</v>
       </c>
       <c r="G90" t="s">
-        <v>1818</v>
-      </c>
-    </row>
-    <row r="91" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1813</v>
+      </c>
+    </row>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
-        <v>1819</v>
+        <v>1814</v>
       </c>
       <c r="B91" t="s">
-        <v>1820</v>
+        <v>1815</v>
       </c>
       <c r="C91">
         <v>13</v>
@@ -16950,15 +16922,15 @@
         <v>560</v>
       </c>
       <c r="G91" t="s">
-        <v>1821</v>
-      </c>
-    </row>
-    <row r="92" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1816</v>
+      </c>
+    </row>
+    <row r="92" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
-        <v>1822</v>
+        <v>1817</v>
       </c>
       <c r="B92" t="s">
-        <v>1823</v>
+        <v>1818</v>
       </c>
       <c r="C92">
         <v>13</v>
@@ -16970,18 +16942,18 @@
         <v>67</v>
       </c>
       <c r="F92" t="s">
-        <v>1824</v>
+        <v>1819</v>
       </c>
       <c r="G92" t="s">
-        <v>1825</v>
-      </c>
-    </row>
-    <row r="93" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1820</v>
+      </c>
+    </row>
+    <row r="93" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
-        <v>1826</v>
+        <v>1821</v>
       </c>
       <c r="B93" t="s">
-        <v>1827</v>
+        <v>1822</v>
       </c>
       <c r="C93">
         <v>12</v>
@@ -16993,18 +16965,18 @@
         <v>679</v>
       </c>
       <c r="F93" t="s">
-        <v>1806</v>
+        <v>1801</v>
       </c>
       <c r="G93" t="s">
-        <v>1828</v>
-      </c>
-    </row>
-    <row r="94" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1823</v>
+      </c>
+    </row>
+    <row r="94" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
-        <v>1829</v>
+        <v>1824</v>
       </c>
       <c r="B94" t="s">
-        <v>1830</v>
+        <v>1825</v>
       </c>
       <c r="C94">
         <v>13</v>
@@ -17016,18 +16988,18 @@
         <v>22</v>
       </c>
       <c r="F94" t="s">
-        <v>1831</v>
+        <v>1826</v>
       </c>
       <c r="G94" t="s">
-        <v>1832</v>
-      </c>
-    </row>
-    <row r="95" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1827</v>
+      </c>
+    </row>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
-        <v>1833</v>
+        <v>1828</v>
       </c>
       <c r="B95" t="s">
-        <v>1834</v>
+        <v>1829</v>
       </c>
       <c r="C95">
         <v>13</v>
@@ -17039,18 +17011,18 @@
         <v>11</v>
       </c>
       <c r="F95" t="s">
-        <v>1835</v>
+        <v>1830</v>
       </c>
       <c r="G95" t="s">
-        <v>1836</v>
-      </c>
-    </row>
-    <row r="96" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1831</v>
+      </c>
+    </row>
+    <row r="96" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
-        <v>1837</v>
+        <v>1832</v>
       </c>
       <c r="B96" t="s">
-        <v>1838</v>
+        <v>1833</v>
       </c>
       <c r="C96">
         <v>12</v>
@@ -17062,18 +17034,18 @@
         <v>22</v>
       </c>
       <c r="F96" t="s">
-        <v>1839</v>
+        <v>1834</v>
       </c>
       <c r="G96" t="s">
-        <v>1840</v>
-      </c>
-    </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1835</v>
+      </c>
+    </row>
+    <row r="97" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
-        <v>1841</v>
+        <v>1836</v>
       </c>
       <c r="B97" t="s">
-        <v>1842</v>
+        <v>1837</v>
       </c>
       <c r="C97">
         <v>12</v>
@@ -17085,18 +17057,18 @@
         <v>36</v>
       </c>
       <c r="F97" t="s">
-        <v>1843</v>
+        <v>1838</v>
       </c>
       <c r="G97" t="s">
-        <v>1844</v>
-      </c>
-    </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1839</v>
+      </c>
+    </row>
+    <row r="98" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
-        <v>1845</v>
+        <v>1840</v>
       </c>
       <c r="B98" t="s">
-        <v>1846</v>
+        <v>1841</v>
       </c>
       <c r="C98">
         <v>12</v>
@@ -17108,18 +17080,18 @@
         <v>22</v>
       </c>
       <c r="F98" t="s">
-        <v>1847</v>
+        <v>1842</v>
       </c>
       <c r="G98" t="s">
-        <v>1848</v>
-      </c>
-    </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1843</v>
+      </c>
+    </row>
+    <row r="99" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
-        <v>1849</v>
+        <v>1844</v>
       </c>
       <c r="B99" t="s">
-        <v>1850</v>
+        <v>1845</v>
       </c>
       <c r="C99">
         <v>12</v>
@@ -17134,15 +17106,15 @@
         <v>50</v>
       </c>
       <c r="G99" t="s">
-        <v>1851</v>
-      </c>
-    </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1846</v>
+      </c>
+    </row>
+    <row r="100" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
-        <v>1852</v>
+        <v>1847</v>
       </c>
       <c r="B100" t="s">
-        <v>1853</v>
+        <v>1848</v>
       </c>
       <c r="C100">
         <v>11</v>
@@ -17154,18 +17126,18 @@
         <v>67</v>
       </c>
       <c r="F100" t="s">
-        <v>1854</v>
+        <v>1849</v>
       </c>
       <c r="G100" t="s">
-        <v>1855</v>
-      </c>
-    </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1850</v>
+      </c>
+    </row>
+    <row r="101" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
-        <v>1856</v>
+        <v>1851</v>
       </c>
       <c r="B101" t="s">
-        <v>1857</v>
+        <v>1852</v>
       </c>
       <c r="C101">
         <v>12</v>
@@ -17177,18 +17149,18 @@
         <v>679</v>
       </c>
       <c r="F101" t="s">
-        <v>1858</v>
+        <v>1853</v>
       </c>
       <c r="G101" t="s">
-        <v>1859</v>
-      </c>
-    </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1854</v>
+      </c>
+    </row>
+    <row r="102" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
-        <v>1860</v>
+        <v>1855</v>
       </c>
       <c r="B102" t="s">
-        <v>1861</v>
+        <v>1856</v>
       </c>
       <c r="C102">
         <v>13</v>
@@ -17200,18 +17172,18 @@
         <v>41</v>
       </c>
       <c r="F102" t="s">
-        <v>1862</v>
+        <v>1857</v>
       </c>
       <c r="G102" t="s">
-        <v>1863</v>
-      </c>
-    </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1858</v>
+      </c>
+    </row>
+    <row r="103" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
-        <v>1864</v>
+        <v>1859</v>
       </c>
       <c r="B103" t="s">
-        <v>1865</v>
+        <v>1860</v>
       </c>
       <c r="C103">
         <v>11</v>
@@ -17223,18 +17195,18 @@
         <v>27</v>
       </c>
       <c r="F103" t="s">
-        <v>1866</v>
+        <v>1861</v>
       </c>
       <c r="G103" t="s">
-        <v>1867</v>
-      </c>
-    </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="104" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
-        <v>1868</v>
+        <v>1863</v>
       </c>
       <c r="B104" t="s">
-        <v>1869</v>
+        <v>1864</v>
       </c>
       <c r="C104">
         <v>13</v>
@@ -17246,18 +17218,18 @@
         <v>67</v>
       </c>
       <c r="F104" t="s">
-        <v>1870</v>
+        <v>1865</v>
       </c>
       <c r="G104" t="s">
-        <v>1871</v>
-      </c>
-    </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1866</v>
+      </c>
+    </row>
+    <row r="105" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
-        <v>1872</v>
+        <v>1867</v>
       </c>
       <c r="B105" t="s">
-        <v>1873</v>
+        <v>1868</v>
       </c>
       <c r="C105">
         <v>12</v>
@@ -17269,18 +17241,18 @@
         <v>36</v>
       </c>
       <c r="F105" t="s">
-        <v>1874</v>
+        <v>1869</v>
       </c>
       <c r="G105" t="s">
-        <v>1875</v>
-      </c>
-    </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1870</v>
+      </c>
+    </row>
+    <row r="106" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
-        <v>1876</v>
+        <v>1871</v>
       </c>
       <c r="B106" t="s">
-        <v>1877</v>
+        <v>1872</v>
       </c>
       <c r="C106">
         <v>12</v>
@@ -17295,15 +17267,15 @@
         <v>607</v>
       </c>
       <c r="G106" t="s">
-        <v>1878</v>
-      </c>
-    </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1873</v>
+      </c>
+    </row>
+    <row r="107" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
-        <v>1395</v>
+        <v>1390</v>
       </c>
       <c r="B107" t="s">
-        <v>1879</v>
+        <v>1874</v>
       </c>
       <c r="C107">
         <v>13</v>
@@ -17315,18 +17287,18 @@
         <v>11</v>
       </c>
       <c r="F107" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="G107" t="s">
-        <v>1881</v>
-      </c>
-    </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1876</v>
+      </c>
+    </row>
+    <row r="108" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
-        <v>1882</v>
+        <v>1877</v>
       </c>
       <c r="B108" t="s">
-        <v>1883</v>
+        <v>1878</v>
       </c>
       <c r="C108">
         <v>11</v>
@@ -17338,18 +17310,18 @@
         <v>22</v>
       </c>
       <c r="F108" t="s">
-        <v>1884</v>
+        <v>1879</v>
       </c>
       <c r="G108" t="s">
-        <v>1885</v>
-      </c>
-    </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1880</v>
+      </c>
+    </row>
+    <row r="109" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
-        <v>1886</v>
+        <v>1881</v>
       </c>
       <c r="B109" t="s">
-        <v>1887</v>
+        <v>1882</v>
       </c>
       <c r="C109">
         <v>13</v>
@@ -17361,18 +17333,18 @@
         <v>41</v>
       </c>
       <c r="F109" t="s">
-        <v>1888</v>
+        <v>1883</v>
       </c>
       <c r="G109" t="s">
-        <v>1889</v>
-      </c>
-    </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1884</v>
+      </c>
+    </row>
+    <row r="110" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
-        <v>1890</v>
+        <v>1885</v>
       </c>
       <c r="B110" t="s">
-        <v>1891</v>
+        <v>1886</v>
       </c>
       <c r="C110">
         <v>11</v>
@@ -17384,18 +17356,18 @@
         <v>41</v>
       </c>
       <c r="F110" t="s">
-        <v>1892</v>
+        <v>1887</v>
       </c>
       <c r="G110" t="s">
-        <v>1893</v>
-      </c>
-    </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1888</v>
+      </c>
+    </row>
+    <row r="111" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
-        <v>1894</v>
+        <v>1889</v>
       </c>
       <c r="B111" t="s">
-        <v>1895</v>
+        <v>1890</v>
       </c>
       <c r="C111">
         <v>11</v>
@@ -17410,15 +17382,15 @@
         <v>482</v>
       </c>
       <c r="G111" t="s">
-        <v>1896</v>
-      </c>
-    </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1891</v>
+      </c>
+    </row>
+    <row r="112" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
-        <v>1897</v>
+        <v>1892</v>
       </c>
       <c r="B112" t="s">
-        <v>1898</v>
+        <v>1893</v>
       </c>
       <c r="C112">
         <v>13</v>
@@ -17430,18 +17402,18 @@
         <v>58</v>
       </c>
       <c r="F112" t="s">
-        <v>1899</v>
+        <v>1894</v>
       </c>
       <c r="G112" t="s">
-        <v>1900</v>
-      </c>
-    </row>
-    <row r="113" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1895</v>
+      </c>
+    </row>
+    <row r="113" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
-        <v>1901</v>
+        <v>1896</v>
       </c>
       <c r="B113" t="s">
-        <v>1902</v>
+        <v>1897</v>
       </c>
       <c r="C113">
         <v>12</v>
@@ -17453,18 +17425,18 @@
         <v>36</v>
       </c>
       <c r="F113" t="s">
-        <v>1903</v>
+        <v>1898</v>
       </c>
       <c r="G113" t="s">
-        <v>1904</v>
-      </c>
-    </row>
-    <row r="114" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1899</v>
+      </c>
+    </row>
+    <row r="114" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
-        <v>1905</v>
+        <v>1900</v>
       </c>
       <c r="B114" t="s">
-        <v>1906</v>
+        <v>1901</v>
       </c>
       <c r="C114">
         <v>11</v>
@@ -17476,18 +17448,18 @@
         <v>67</v>
       </c>
       <c r="F114" t="s">
-        <v>1907</v>
+        <v>1902</v>
       </c>
       <c r="G114" t="s">
-        <v>1908</v>
-      </c>
-    </row>
-    <row r="115" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1903</v>
+      </c>
+    </row>
+    <row r="115" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
-        <v>1909</v>
+        <v>1904</v>
       </c>
       <c r="B115" t="s">
-        <v>1910</v>
+        <v>1905</v>
       </c>
       <c r="C115">
         <v>13</v>
@@ -17499,18 +17471,18 @@
         <v>22</v>
       </c>
       <c r="F115" t="s">
-        <v>1911</v>
+        <v>1906</v>
       </c>
       <c r="G115" t="s">
-        <v>1912</v>
-      </c>
-    </row>
-    <row r="116" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1907</v>
+      </c>
+    </row>
+    <row r="116" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="B116" t="s">
-        <v>1914</v>
+        <v>1909</v>
       </c>
       <c r="C116">
         <v>12</v>
@@ -17522,18 +17494,18 @@
         <v>58</v>
       </c>
       <c r="F116" t="s">
-        <v>1915</v>
+        <v>1910</v>
       </c>
       <c r="G116" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="117" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1911</v>
+      </c>
+    </row>
+    <row r="117" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
-        <v>1917</v>
+        <v>1912</v>
       </c>
       <c r="B117" t="s">
-        <v>1918</v>
+        <v>1913</v>
       </c>
       <c r="C117">
         <v>13</v>
@@ -17545,18 +17517,18 @@
         <v>72</v>
       </c>
       <c r="F117" t="s">
-        <v>1919</v>
+        <v>1914</v>
       </c>
       <c r="G117" t="s">
-        <v>1920</v>
-      </c>
-    </row>
-    <row r="118" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1915</v>
+      </c>
+    </row>
+    <row r="118" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
-        <v>1921</v>
+        <v>1916</v>
       </c>
       <c r="B118" t="s">
-        <v>1922</v>
+        <v>1917</v>
       </c>
       <c r="C118">
         <v>11</v>
@@ -17568,18 +17540,18 @@
         <v>36</v>
       </c>
       <c r="F118" t="s">
-        <v>1923</v>
+        <v>1918</v>
       </c>
       <c r="G118" t="s">
-        <v>1924</v>
-      </c>
-    </row>
-    <row r="119" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1919</v>
+      </c>
+    </row>
+    <row r="119" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
-        <v>1925</v>
+        <v>1920</v>
       </c>
       <c r="B119" t="s">
-        <v>1926</v>
+        <v>1921</v>
       </c>
       <c r="C119">
         <v>13</v>
@@ -17591,18 +17563,18 @@
         <v>67</v>
       </c>
       <c r="F119" t="s">
-        <v>1927</v>
+        <v>1922</v>
       </c>
       <c r="G119" t="s">
-        <v>1928</v>
-      </c>
-    </row>
-    <row r="120" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1923</v>
+      </c>
+    </row>
+    <row r="120" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
-        <v>1929</v>
+        <v>1924</v>
       </c>
       <c r="B120" t="s">
-        <v>1930</v>
+        <v>1925</v>
       </c>
       <c r="C120">
         <v>12</v>
@@ -17614,18 +17586,18 @@
         <v>22</v>
       </c>
       <c r="F120" t="s">
-        <v>1931</v>
+        <v>1926</v>
       </c>
       <c r="G120" t="s">
-        <v>1932</v>
-      </c>
-    </row>
-    <row r="121" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1927</v>
+      </c>
+    </row>
+    <row r="121" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
-        <v>1933</v>
+        <v>1928</v>
       </c>
       <c r="B121" t="s">
-        <v>1934</v>
+        <v>1929</v>
       </c>
       <c r="C121">
         <v>12</v>
@@ -17637,18 +17609,18 @@
         <v>36</v>
       </c>
       <c r="F121" t="s">
-        <v>1935</v>
+        <v>1930</v>
       </c>
       <c r="G121" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="122" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1931</v>
+      </c>
+    </row>
+    <row r="122" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
-        <v>1937</v>
+        <v>1932</v>
       </c>
       <c r="B122" t="s">
-        <v>1938</v>
+        <v>1933</v>
       </c>
       <c r="C122">
         <v>11</v>
@@ -17660,18 +17632,18 @@
         <v>67</v>
       </c>
       <c r="F122" t="s">
-        <v>1939</v>
+        <v>1934</v>
       </c>
       <c r="G122" t="s">
-        <v>1940</v>
-      </c>
-    </row>
-    <row r="123" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1935</v>
+      </c>
+    </row>
+    <row r="123" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
-        <v>1941</v>
+        <v>1936</v>
       </c>
       <c r="B123" t="s">
-        <v>1942</v>
+        <v>1937</v>
       </c>
       <c r="C123">
         <v>13</v>
@@ -17683,18 +17655,18 @@
         <v>679</v>
       </c>
       <c r="F123" t="s">
-        <v>1943</v>
+        <v>1938</v>
       </c>
       <c r="G123" t="s">
-        <v>1944</v>
-      </c>
-    </row>
-    <row r="124" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1939</v>
+      </c>
+    </row>
+    <row r="124" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
-        <v>1945</v>
+        <v>1940</v>
       </c>
       <c r="B124" t="s">
-        <v>1946</v>
+        <v>1941</v>
       </c>
       <c r="C124">
         <v>12</v>
@@ -17706,18 +17678,18 @@
         <v>11</v>
       </c>
       <c r="F124" t="s">
-        <v>1947</v>
+        <v>1942</v>
       </c>
       <c r="G124" t="s">
-        <v>1948</v>
-      </c>
-    </row>
-    <row r="125" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1943</v>
+      </c>
+    </row>
+    <row r="125" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
-        <v>1949</v>
+        <v>1944</v>
       </c>
       <c r="B125" t="s">
-        <v>1950</v>
+        <v>1945</v>
       </c>
       <c r="C125">
         <v>13</v>
@@ -17729,18 +17701,18 @@
         <v>11</v>
       </c>
       <c r="F125" t="s">
-        <v>1951</v>
+        <v>1946</v>
       </c>
       <c r="G125" t="s">
-        <v>1952</v>
-      </c>
-    </row>
-    <row r="126" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1947</v>
+      </c>
+    </row>
+    <row r="126" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
-        <v>1953</v>
+        <v>1948</v>
       </c>
       <c r="B126" t="s">
-        <v>1954</v>
+        <v>1949</v>
       </c>
       <c r="C126">
         <v>13</v>
@@ -17752,18 +17724,18 @@
         <v>22</v>
       </c>
       <c r="F126" t="s">
-        <v>1955</v>
+        <v>1950</v>
       </c>
       <c r="G126" t="s">
-        <v>1956</v>
-      </c>
-    </row>
-    <row r="127" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1951</v>
+      </c>
+    </row>
+    <row r="127" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
-        <v>1957</v>
+        <v>1952</v>
       </c>
       <c r="B127" t="s">
-        <v>1958</v>
+        <v>1953</v>
       </c>
       <c r="C127">
         <v>12</v>
@@ -17775,18 +17747,18 @@
         <v>36</v>
       </c>
       <c r="F127" t="s">
-        <v>1959</v>
+        <v>1954</v>
       </c>
       <c r="G127" t="s">
-        <v>1960</v>
-      </c>
-    </row>
-    <row r="128" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1955</v>
+      </c>
+    </row>
+    <row r="128" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
-        <v>1961</v>
+        <v>1956</v>
       </c>
       <c r="B128" t="s">
-        <v>1962</v>
+        <v>1957</v>
       </c>
       <c r="C128">
         <v>12</v>
@@ -17798,18 +17770,18 @@
         <v>16</v>
       </c>
       <c r="F128" t="s">
-        <v>1963</v>
+        <v>1958</v>
       </c>
       <c r="G128" t="s">
-        <v>1964</v>
-      </c>
-    </row>
-    <row r="129" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1959</v>
+      </c>
+    </row>
+    <row r="129" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
-        <v>1965</v>
+        <v>1960</v>
       </c>
       <c r="B129" t="s">
-        <v>1966</v>
+        <v>1961</v>
       </c>
       <c r="C129">
         <v>11</v>
@@ -17821,18 +17793,18 @@
         <v>67</v>
       </c>
       <c r="F129" t="s">
-        <v>1967</v>
+        <v>1962</v>
       </c>
       <c r="G129" t="s">
-        <v>1968</v>
-      </c>
-    </row>
-    <row r="130" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1963</v>
+      </c>
+    </row>
+    <row r="130" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
-        <v>1969</v>
+        <v>1964</v>
       </c>
       <c r="B130" t="s">
-        <v>1970</v>
+        <v>1965</v>
       </c>
       <c r="C130">
         <v>13</v>
@@ -17844,18 +17816,18 @@
         <v>22</v>
       </c>
       <c r="F130" t="s">
-        <v>1971</v>
+        <v>1966</v>
       </c>
       <c r="G130" t="s">
-        <v>1972</v>
-      </c>
-    </row>
-    <row r="131" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1967</v>
+      </c>
+    </row>
+    <row r="131" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
-        <v>1913</v>
+        <v>1908</v>
       </c>
       <c r="B131" t="s">
-        <v>1973</v>
+        <v>1968</v>
       </c>
       <c r="C131">
         <v>11</v>
@@ -17867,18 +17839,18 @@
         <v>41</v>
       </c>
       <c r="F131" t="s">
-        <v>1974</v>
+        <v>1969</v>
       </c>
       <c r="G131" t="s">
-        <v>1975</v>
-      </c>
-    </row>
-    <row r="132" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1970</v>
+      </c>
+    </row>
+    <row r="132" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
-        <v>1976</v>
+        <v>1971</v>
       </c>
       <c r="B132" t="s">
-        <v>1977</v>
+        <v>1972</v>
       </c>
       <c r="C132">
         <v>13</v>
@@ -17890,18 +17862,18 @@
         <v>11</v>
       </c>
       <c r="F132" t="s">
-        <v>1978</v>
+        <v>1973</v>
       </c>
       <c r="G132" t="s">
-        <v>1979</v>
-      </c>
-    </row>
-    <row r="133" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1974</v>
+      </c>
+    </row>
+    <row r="133" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
-        <v>1980</v>
+        <v>1975</v>
       </c>
       <c r="B133" t="s">
-        <v>1981</v>
+        <v>1976</v>
       </c>
       <c r="C133">
         <v>13</v>
@@ -17913,41 +17885,41 @@
         <v>72</v>
       </c>
       <c r="F133" t="s">
-        <v>1588</v>
+        <v>1583</v>
       </c>
       <c r="G133" t="s">
+        <v>1977</v>
+      </c>
+    </row>
+    <row r="134" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A134" t="s">
+        <v>1978</v>
+      </c>
+      <c r="B134" t="s">
+        <v>1979</v>
+      </c>
+      <c r="C134">
+        <v>11</v>
+      </c>
+      <c r="D134" t="s">
+        <v>10</v>
+      </c>
+      <c r="E134" t="s">
+        <v>11</v>
+      </c>
+      <c r="F134" t="s">
+        <v>1980</v>
+      </c>
+      <c r="G134" t="s">
+        <v>1981</v>
+      </c>
+    </row>
+    <row r="135" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A135" t="s">
         <v>1982</v>
       </c>
-    </row>
-    <row r="134" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A134" t="s">
+      <c r="B135" t="s">
         <v>1983</v>
-      </c>
-      <c r="B134" t="s">
-        <v>1984</v>
-      </c>
-      <c r="C134">
-        <v>11</v>
-      </c>
-      <c r="D134" t="s">
-        <v>10</v>
-      </c>
-      <c r="E134" t="s">
-        <v>11</v>
-      </c>
-      <c r="F134" t="s">
-        <v>1985</v>
-      </c>
-      <c r="G134" t="s">
-        <v>1986</v>
-      </c>
-    </row>
-    <row r="135" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A135" t="s">
-        <v>1987</v>
-      </c>
-      <c r="B135" t="s">
-        <v>1988</v>
       </c>
       <c r="C135">
         <v>13</v>
@@ -17959,18 +17931,18 @@
         <v>11</v>
       </c>
       <c r="F135" t="s">
-        <v>1989</v>
+        <v>1984</v>
       </c>
       <c r="G135" t="s">
-        <v>1990</v>
-      </c>
-    </row>
-    <row r="136" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1985</v>
+      </c>
+    </row>
+    <row r="136" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>484</v>
       </c>
       <c r="B136" t="s">
-        <v>1991</v>
+        <v>1986</v>
       </c>
       <c r="C136">
         <v>13</v>
@@ -17985,15 +17957,15 @@
         <v>587</v>
       </c>
       <c r="G136" t="s">
-        <v>1992</v>
-      </c>
-    </row>
-    <row r="137" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1987</v>
+      </c>
+    </row>
+    <row r="137" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>1011</v>
       </c>
       <c r="B137" t="s">
-        <v>1993</v>
+        <v>1988</v>
       </c>
       <c r="C137">
         <v>12</v>
@@ -18005,18 +17977,18 @@
         <v>27</v>
       </c>
       <c r="F137" t="s">
-        <v>1994</v>
+        <v>1989</v>
       </c>
       <c r="G137" t="s">
-        <v>1995</v>
-      </c>
-    </row>
-    <row r="138" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1990</v>
+      </c>
+    </row>
+    <row r="138" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
-        <v>1996</v>
+        <v>1991</v>
       </c>
       <c r="B138" t="s">
-        <v>1997</v>
+        <v>1992</v>
       </c>
       <c r="C138">
         <v>13</v>
@@ -18031,15 +18003,15 @@
         <v>272</v>
       </c>
       <c r="G138" t="s">
-        <v>1998</v>
-      </c>
-    </row>
-    <row r="139" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1993</v>
+      </c>
+    </row>
+    <row r="139" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
-        <v>1999</v>
+        <v>1994</v>
       </c>
       <c r="B139" t="s">
-        <v>2000</v>
+        <v>1995</v>
       </c>
       <c r="C139">
         <v>13</v>
@@ -18054,15 +18026,15 @@
         <v>1134</v>
       </c>
       <c r="G139" t="s">
-        <v>2001</v>
-      </c>
-    </row>
-    <row r="140" spans="1:7" x14ac:dyDescent="0.4">
+        <v>1996</v>
+      </c>
+    </row>
+    <row r="140" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
-        <v>2002</v>
+        <v>1997</v>
       </c>
       <c r="B140" t="s">
-        <v>2003</v>
+        <v>1998</v>
       </c>
       <c r="C140">
         <v>11</v>
@@ -18074,18 +18046,18 @@
         <v>67</v>
       </c>
       <c r="F140" t="s">
-        <v>2004</v>
+        <v>1999</v>
       </c>
       <c r="G140" t="s">
-        <v>2005</v>
-      </c>
-    </row>
-    <row r="141" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2000</v>
+      </c>
+    </row>
+    <row r="141" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
-        <v>2006</v>
+        <v>2001</v>
       </c>
       <c r="B141" t="s">
-        <v>2007</v>
+        <v>2002</v>
       </c>
       <c r="C141">
         <v>12</v>
@@ -18097,18 +18069,18 @@
         <v>67</v>
       </c>
       <c r="F141" t="s">
-        <v>2008</v>
+        <v>2003</v>
       </c>
       <c r="G141" t="s">
-        <v>2009</v>
-      </c>
-    </row>
-    <row r="142" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2004</v>
+      </c>
+    </row>
+    <row r="142" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
-        <v>2010</v>
+        <v>2005</v>
       </c>
       <c r="B142" t="s">
-        <v>2011</v>
+        <v>2006</v>
       </c>
       <c r="C142">
         <v>11</v>
@@ -18123,15 +18095,15 @@
         <v>376</v>
       </c>
       <c r="G142" t="s">
-        <v>2012</v>
-      </c>
-    </row>
-    <row r="143" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2007</v>
+      </c>
+    </row>
+    <row r="143" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
-        <v>2013</v>
+        <v>2008</v>
       </c>
       <c r="B143" t="s">
-        <v>2014</v>
+        <v>2009</v>
       </c>
       <c r="C143">
         <v>12</v>
@@ -18143,18 +18115,18 @@
         <v>22</v>
       </c>
       <c r="F143" t="s">
-        <v>1697</v>
+        <v>1692</v>
       </c>
       <c r="G143" t="s">
-        <v>2015</v>
-      </c>
-    </row>
-    <row r="144" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2010</v>
+      </c>
+    </row>
+    <row r="144" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
-        <v>2016</v>
+        <v>2011</v>
       </c>
       <c r="B144" t="s">
-        <v>2017</v>
+        <v>2012</v>
       </c>
       <c r="C144">
         <v>13</v>
@@ -18166,18 +18138,18 @@
         <v>72</v>
       </c>
       <c r="F144" t="s">
-        <v>2018</v>
+        <v>2013</v>
       </c>
       <c r="G144" t="s">
-        <v>2019</v>
-      </c>
-    </row>
-    <row r="145" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2014</v>
+      </c>
+    </row>
+    <row r="145" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
-        <v>2020</v>
+        <v>2015</v>
       </c>
       <c r="B145" t="s">
-        <v>2021</v>
+        <v>2016</v>
       </c>
       <c r="C145">
         <v>11</v>
@@ -18192,15 +18164,15 @@
         <v>117</v>
       </c>
       <c r="G145" t="s">
-        <v>2022</v>
-      </c>
-    </row>
-    <row r="146" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2017</v>
+      </c>
+    </row>
+    <row r="146" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
-        <v>2023</v>
+        <v>2018</v>
       </c>
       <c r="B146" t="s">
-        <v>2024</v>
+        <v>2019</v>
       </c>
       <c r="C146">
         <v>12</v>
@@ -18212,18 +18184,18 @@
         <v>72</v>
       </c>
       <c r="F146" t="s">
-        <v>2025</v>
+        <v>2020</v>
       </c>
       <c r="G146" t="s">
-        <v>2026</v>
-      </c>
-    </row>
-    <row r="147" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2021</v>
+      </c>
+    </row>
+    <row r="147" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
-        <v>2027</v>
+        <v>2022</v>
       </c>
       <c r="B147" t="s">
-        <v>2028</v>
+        <v>2023</v>
       </c>
       <c r="C147">
         <v>13</v>
@@ -18235,18 +18207,18 @@
         <v>11</v>
       </c>
       <c r="F147" t="s">
-        <v>2029</v>
+        <v>2024</v>
       </c>
       <c r="G147" t="s">
-        <v>2030</v>
-      </c>
-    </row>
-    <row r="148" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="148" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
-        <v>2031</v>
+        <v>2026</v>
       </c>
       <c r="B148" t="s">
-        <v>2032</v>
+        <v>2027</v>
       </c>
       <c r="C148">
         <v>11</v>
@@ -18258,41 +18230,41 @@
         <v>22</v>
       </c>
       <c r="F148" t="s">
+        <v>2028</v>
+      </c>
+      <c r="G148" t="s">
+        <v>2029</v>
+      </c>
+    </row>
+    <row r="149" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A149" t="s">
+        <v>2030</v>
+      </c>
+      <c r="B149" t="s">
+        <v>2031</v>
+      </c>
+      <c r="C149">
+        <v>11</v>
+      </c>
+      <c r="D149" t="s">
+        <v>10</v>
+      </c>
+      <c r="E149" t="s">
+        <v>11</v>
+      </c>
+      <c r="F149" t="s">
+        <v>2032</v>
+      </c>
+      <c r="G149" t="s">
         <v>2033</v>
       </c>
-      <c r="G148" t="s">
+    </row>
+    <row r="150" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A150" t="s">
         <v>2034</v>
       </c>
-    </row>
-    <row r="149" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A149" t="s">
+      <c r="B150" t="s">
         <v>2035</v>
-      </c>
-      <c r="B149" t="s">
-        <v>2036</v>
-      </c>
-      <c r="C149">
-        <v>11</v>
-      </c>
-      <c r="D149" t="s">
-        <v>10</v>
-      </c>
-      <c r="E149" t="s">
-        <v>11</v>
-      </c>
-      <c r="F149" t="s">
-        <v>2037</v>
-      </c>
-      <c r="G149" t="s">
-        <v>2038</v>
-      </c>
-    </row>
-    <row r="150" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A150" t="s">
-        <v>2039</v>
-      </c>
-      <c r="B150" t="s">
-        <v>2040</v>
       </c>
       <c r="C150">
         <v>11</v>
@@ -18304,18 +18276,18 @@
         <v>27</v>
       </c>
       <c r="F150" t="s">
-        <v>2041</v>
+        <v>2036</v>
       </c>
       <c r="G150" t="s">
-        <v>2042</v>
-      </c>
-    </row>
-    <row r="151" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2037</v>
+      </c>
+    </row>
+    <row r="151" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
-        <v>2043</v>
+        <v>2038</v>
       </c>
       <c r="B151" t="s">
-        <v>2044</v>
+        <v>2039</v>
       </c>
       <c r="C151">
         <v>12</v>
@@ -18327,18 +18299,18 @@
         <v>16</v>
       </c>
       <c r="F151" t="s">
-        <v>2045</v>
+        <v>2040</v>
       </c>
       <c r="G151" t="s">
-        <v>2046</v>
-      </c>
-    </row>
-    <row r="152" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2041</v>
+      </c>
+    </row>
+    <row r="152" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
-        <v>2047</v>
+        <v>2042</v>
       </c>
       <c r="B152" t="s">
-        <v>2048</v>
+        <v>2043</v>
       </c>
       <c r="C152">
         <v>12</v>
@@ -18350,18 +18322,18 @@
         <v>72</v>
       </c>
       <c r="F152" t="s">
-        <v>1677</v>
+        <v>1672</v>
       </c>
       <c r="G152" t="s">
-        <v>2049</v>
-      </c>
-    </row>
-    <row r="153" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2044</v>
+      </c>
+    </row>
+    <row r="153" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
-        <v>2050</v>
+        <v>2045</v>
       </c>
       <c r="B153" t="s">
-        <v>2051</v>
+        <v>2046</v>
       </c>
       <c r="C153">
         <v>12</v>
@@ -18373,18 +18345,18 @@
         <v>16</v>
       </c>
       <c r="F153" t="s">
-        <v>2052</v>
+        <v>2047</v>
       </c>
       <c r="G153" t="s">
-        <v>2053</v>
-      </c>
-    </row>
-    <row r="154" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2048</v>
+      </c>
+    </row>
+    <row r="154" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
-        <v>2054</v>
+        <v>2049</v>
       </c>
       <c r="B154" t="s">
-        <v>2055</v>
+        <v>2050</v>
       </c>
       <c r="C154">
         <v>13</v>
@@ -18396,18 +18368,18 @@
         <v>41</v>
       </c>
       <c r="F154" t="s">
-        <v>2056</v>
+        <v>2051</v>
       </c>
       <c r="G154" t="s">
-        <v>2057</v>
-      </c>
-    </row>
-    <row r="155" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2052</v>
+      </c>
+    </row>
+    <row r="155" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
-        <v>2058</v>
+        <v>2053</v>
       </c>
       <c r="B155" t="s">
-        <v>2059</v>
+        <v>2054</v>
       </c>
       <c r="C155">
         <v>13</v>
@@ -18422,15 +18394,15 @@
         <v>196</v>
       </c>
       <c r="G155" t="s">
-        <v>2060</v>
-      </c>
-    </row>
-    <row r="156" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2055</v>
+      </c>
+    </row>
+    <row r="156" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
-        <v>2061</v>
+        <v>2056</v>
       </c>
       <c r="B156" t="s">
-        <v>2062</v>
+        <v>2057</v>
       </c>
       <c r="C156">
         <v>11</v>
@@ -18442,18 +18414,18 @@
         <v>58</v>
       </c>
       <c r="F156" t="s">
-        <v>2063</v>
+        <v>2058</v>
       </c>
       <c r="G156" t="s">
-        <v>2064</v>
-      </c>
-    </row>
-    <row r="157" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2059</v>
+      </c>
+    </row>
+    <row r="157" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
-        <v>2065</v>
+        <v>2060</v>
       </c>
       <c r="B157" t="s">
-        <v>2066</v>
+        <v>2061</v>
       </c>
       <c r="C157">
         <v>11</v>
@@ -18465,18 +18437,18 @@
         <v>67</v>
       </c>
       <c r="F157" t="s">
-        <v>2067</v>
+        <v>2062</v>
       </c>
       <c r="G157" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="158" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2063</v>
+      </c>
+    </row>
+    <row r="158" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
-        <v>2069</v>
+        <v>2064</v>
       </c>
       <c r="B158" t="s">
-        <v>2070</v>
+        <v>2065</v>
       </c>
       <c r="C158">
         <v>11</v>
@@ -18488,18 +18460,18 @@
         <v>11</v>
       </c>
       <c r="F158" t="s">
-        <v>1880</v>
+        <v>1875</v>
       </c>
       <c r="G158" t="s">
-        <v>2071</v>
-      </c>
-    </row>
-    <row r="159" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2066</v>
+      </c>
+    </row>
+    <row r="159" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
-        <v>2072</v>
+        <v>2067</v>
       </c>
       <c r="B159" t="s">
-        <v>2073</v>
+        <v>2068</v>
       </c>
       <c r="C159">
         <v>12</v>
@@ -18511,18 +18483,18 @@
         <v>58</v>
       </c>
       <c r="F159" t="s">
-        <v>2074</v>
+        <v>2069</v>
       </c>
       <c r="G159" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="160" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2070</v>
+      </c>
+    </row>
+    <row r="160" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
-        <v>2076</v>
+        <v>2071</v>
       </c>
       <c r="B160" t="s">
-        <v>2077</v>
+        <v>2072</v>
       </c>
       <c r="C160">
         <v>12</v>
@@ -18534,18 +18506,18 @@
         <v>36</v>
       </c>
       <c r="F160" t="s">
-        <v>2078</v>
+        <v>2073</v>
       </c>
       <c r="G160" t="s">
-        <v>2079</v>
-      </c>
-    </row>
-    <row r="161" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2074</v>
+      </c>
+    </row>
+    <row r="161" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
-        <v>2080</v>
+        <v>2075</v>
       </c>
       <c r="B161" t="s">
-        <v>2081</v>
+        <v>2076</v>
       </c>
       <c r="C161">
         <v>12</v>
@@ -18557,18 +18529,18 @@
         <v>16</v>
       </c>
       <c r="F161" t="s">
-        <v>2082</v>
+        <v>2077</v>
       </c>
       <c r="G161" t="s">
-        <v>2083</v>
-      </c>
-    </row>
-    <row r="162" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2078</v>
+      </c>
+    </row>
+    <row r="162" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
-        <v>2084</v>
+        <v>2079</v>
       </c>
       <c r="B162" t="s">
-        <v>2085</v>
+        <v>2080</v>
       </c>
       <c r="C162">
         <v>12</v>
@@ -18580,18 +18552,18 @@
         <v>41</v>
       </c>
       <c r="F162" t="s">
-        <v>2086</v>
+        <v>2081</v>
       </c>
       <c r="G162" t="s">
-        <v>2087</v>
-      </c>
-    </row>
-    <row r="163" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2082</v>
+      </c>
+    </row>
+    <row r="163" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
-        <v>2088</v>
+        <v>2083</v>
       </c>
       <c r="B163" t="s">
-        <v>2089</v>
+        <v>2084</v>
       </c>
       <c r="C163">
         <v>12</v>
@@ -18603,18 +18575,18 @@
         <v>41</v>
       </c>
       <c r="F163" t="s">
-        <v>2090</v>
+        <v>2085</v>
       </c>
       <c r="G163" t="s">
-        <v>2091</v>
-      </c>
-    </row>
-    <row r="164" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2086</v>
+      </c>
+    </row>
+    <row r="164" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
-        <v>2092</v>
+        <v>2087</v>
       </c>
       <c r="B164" t="s">
-        <v>2093</v>
+        <v>2088</v>
       </c>
       <c r="C164">
         <v>13</v>
@@ -18629,15 +18601,15 @@
         <v>595</v>
       </c>
       <c r="G164" t="s">
-        <v>2094</v>
-      </c>
-    </row>
-    <row r="165" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2089</v>
+      </c>
+    </row>
+    <row r="165" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
-        <v>2095</v>
+        <v>2090</v>
       </c>
       <c r="B165" t="s">
-        <v>2096</v>
+        <v>2091</v>
       </c>
       <c r="C165">
         <v>11</v>
@@ -18649,18 +18621,18 @@
         <v>22</v>
       </c>
       <c r="F165" t="s">
-        <v>2097</v>
+        <v>2092</v>
       </c>
       <c r="G165" t="s">
-        <v>2098</v>
-      </c>
-    </row>
-    <row r="166" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2093</v>
+      </c>
+    </row>
+    <row r="166" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
-        <v>1411</v>
+        <v>1406</v>
       </c>
       <c r="B166" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="C166">
         <v>12</v>
@@ -18672,18 +18644,18 @@
         <v>41</v>
       </c>
       <c r="F166" t="s">
-        <v>2100</v>
+        <v>2095</v>
       </c>
       <c r="G166" t="s">
-        <v>2101</v>
-      </c>
-    </row>
-    <row r="167" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="167" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="B167" t="s">
-        <v>2103</v>
+        <v>2098</v>
       </c>
       <c r="C167">
         <v>13</v>
@@ -18695,18 +18667,18 @@
         <v>72</v>
       </c>
       <c r="F167" t="s">
-        <v>2104</v>
+        <v>2099</v>
       </c>
       <c r="G167" t="s">
-        <v>2105</v>
-      </c>
-    </row>
-    <row r="168" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2100</v>
+      </c>
+    </row>
+    <row r="168" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
-        <v>2106</v>
+        <v>2101</v>
       </c>
       <c r="B168" t="s">
-        <v>2107</v>
+        <v>2102</v>
       </c>
       <c r="C168">
         <v>12</v>
@@ -18718,18 +18690,18 @@
         <v>11</v>
       </c>
       <c r="F168" t="s">
-        <v>2108</v>
+        <v>2103</v>
       </c>
       <c r="G168" t="s">
-        <v>2109</v>
-      </c>
-    </row>
-    <row r="169" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="169" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
-        <v>2110</v>
+        <v>2105</v>
       </c>
       <c r="B169" t="s">
-        <v>2111</v>
+        <v>2106</v>
       </c>
       <c r="C169">
         <v>11</v>
@@ -18741,18 +18713,18 @@
         <v>72</v>
       </c>
       <c r="F169" t="s">
-        <v>2112</v>
+        <v>2107</v>
       </c>
       <c r="G169" t="s">
-        <v>2113</v>
-      </c>
-    </row>
-    <row r="170" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2108</v>
+      </c>
+    </row>
+    <row r="170" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
-        <v>2114</v>
+        <v>2109</v>
       </c>
       <c r="B170" t="s">
-        <v>2115</v>
+        <v>2110</v>
       </c>
       <c r="C170">
         <v>13</v>
@@ -18764,18 +18736,18 @@
         <v>41</v>
       </c>
       <c r="F170" t="s">
-        <v>2116</v>
+        <v>2111</v>
       </c>
       <c r="G170" t="s">
-        <v>2117</v>
-      </c>
-    </row>
-    <row r="171" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2112</v>
+      </c>
+    </row>
+    <row r="171" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
-        <v>2118</v>
+        <v>2113</v>
       </c>
       <c r="B171" t="s">
-        <v>2119</v>
+        <v>2114</v>
       </c>
       <c r="C171">
         <v>12</v>
@@ -18787,18 +18759,18 @@
         <v>58</v>
       </c>
       <c r="F171" t="s">
-        <v>2120</v>
+        <v>2115</v>
       </c>
       <c r="G171" t="s">
-        <v>2121</v>
-      </c>
-    </row>
-    <row r="172" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2116</v>
+      </c>
+    </row>
+    <row r="172" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
-        <v>2122</v>
+        <v>2117</v>
       </c>
       <c r="B172" t="s">
-        <v>2123</v>
+        <v>2118</v>
       </c>
       <c r="C172">
         <v>12</v>
@@ -18810,18 +18782,18 @@
         <v>41</v>
       </c>
       <c r="F172" t="s">
-        <v>2124</v>
+        <v>2119</v>
       </c>
       <c r="G172" t="s">
-        <v>2125</v>
-      </c>
-    </row>
-    <row r="173" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="173" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
-        <v>2126</v>
+        <v>2121</v>
       </c>
       <c r="B173" t="s">
-        <v>2127</v>
+        <v>2122</v>
       </c>
       <c r="C173">
         <v>12</v>
@@ -18833,18 +18805,18 @@
         <v>27</v>
       </c>
       <c r="F173" t="s">
-        <v>2128</v>
+        <v>2123</v>
       </c>
       <c r="G173" t="s">
-        <v>2129</v>
-      </c>
-    </row>
-    <row r="174" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2124</v>
+      </c>
+    </row>
+    <row r="174" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
-        <v>2130</v>
+        <v>2125</v>
       </c>
       <c r="B174" t="s">
-        <v>2131</v>
+        <v>2126</v>
       </c>
       <c r="C174">
         <v>11</v>
@@ -18859,15 +18831,15 @@
         <v>46</v>
       </c>
       <c r="G174" t="s">
-        <v>2132</v>
-      </c>
-    </row>
-    <row r="175" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2127</v>
+      </c>
+    </row>
+    <row r="175" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
-        <v>2133</v>
+        <v>2128</v>
       </c>
       <c r="B175" t="s">
-        <v>2134</v>
+        <v>2129</v>
       </c>
       <c r="C175">
         <v>12</v>
@@ -18879,18 +18851,18 @@
         <v>67</v>
       </c>
       <c r="F175" t="s">
-        <v>2135</v>
+        <v>2130</v>
       </c>
       <c r="G175" t="s">
-        <v>2136</v>
-      </c>
-    </row>
-    <row r="176" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2131</v>
+      </c>
+    </row>
+    <row r="176" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
-        <v>2137</v>
+        <v>2132</v>
       </c>
       <c r="B176" t="s">
-        <v>2138</v>
+        <v>2133</v>
       </c>
       <c r="C176">
         <v>13</v>
@@ -18905,15 +18877,15 @@
         <v>595</v>
       </c>
       <c r="G176" t="s">
-        <v>2139</v>
-      </c>
-    </row>
-    <row r="177" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2134</v>
+      </c>
+    </row>
+    <row r="177" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
-        <v>2140</v>
+        <v>2135</v>
       </c>
       <c r="B177" t="s">
-        <v>2141</v>
+        <v>2136</v>
       </c>
       <c r="C177">
         <v>13</v>
@@ -18925,18 +18897,18 @@
         <v>67</v>
       </c>
       <c r="F177" t="s">
-        <v>2142</v>
+        <v>2137</v>
       </c>
       <c r="G177" t="s">
-        <v>2143</v>
-      </c>
-    </row>
-    <row r="178" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2138</v>
+      </c>
+    </row>
+    <row r="178" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
-        <v>2144</v>
+        <v>2139</v>
       </c>
       <c r="B178" t="s">
-        <v>2145</v>
+        <v>2140</v>
       </c>
       <c r="C178">
         <v>13</v>
@@ -18948,18 +18920,18 @@
         <v>27</v>
       </c>
       <c r="F178" t="s">
-        <v>2146</v>
+        <v>2141</v>
       </c>
       <c r="G178" t="s">
-        <v>2147</v>
-      </c>
-    </row>
-    <row r="179" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2142</v>
+      </c>
+    </row>
+    <row r="179" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
-        <v>2148</v>
+        <v>2143</v>
       </c>
       <c r="B179" t="s">
-        <v>2149</v>
+        <v>2144</v>
       </c>
       <c r="C179">
         <v>13</v>
@@ -18971,18 +18943,18 @@
         <v>27</v>
       </c>
       <c r="F179" t="s">
-        <v>2150</v>
+        <v>2145</v>
       </c>
       <c r="G179" t="s">
-        <v>2151</v>
-      </c>
-    </row>
-    <row r="180" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2146</v>
+      </c>
+    </row>
+    <row r="180" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
-        <v>2152</v>
+        <v>2147</v>
       </c>
       <c r="B180" t="s">
-        <v>2153</v>
+        <v>2148</v>
       </c>
       <c r="C180">
         <v>13</v>
@@ -18994,41 +18966,41 @@
         <v>22</v>
       </c>
       <c r="F180" t="s">
+        <v>2149</v>
+      </c>
+      <c r="G180" t="s">
+        <v>2150</v>
+      </c>
+    </row>
+    <row r="181" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A181" t="s">
+        <v>2151</v>
+      </c>
+      <c r="B181" t="s">
+        <v>2152</v>
+      </c>
+      <c r="C181">
+        <v>11</v>
+      </c>
+      <c r="D181" t="s">
+        <v>10</v>
+      </c>
+      <c r="E181" t="s">
+        <v>11</v>
+      </c>
+      <c r="F181" t="s">
+        <v>2153</v>
+      </c>
+      <c r="G181" t="s">
         <v>2154</v>
       </c>
-      <c r="G180" t="s">
+    </row>
+    <row r="182" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A182" t="s">
         <v>2155</v>
       </c>
-    </row>
-    <row r="181" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A181" t="s">
+      <c r="B182" t="s">
         <v>2156</v>
-      </c>
-      <c r="B181" t="s">
-        <v>2157</v>
-      </c>
-      <c r="C181">
-        <v>11</v>
-      </c>
-      <c r="D181" t="s">
-        <v>10</v>
-      </c>
-      <c r="E181" t="s">
-        <v>11</v>
-      </c>
-      <c r="F181" t="s">
-        <v>2158</v>
-      </c>
-      <c r="G181" t="s">
-        <v>2159</v>
-      </c>
-    </row>
-    <row r="182" spans="1:7" x14ac:dyDescent="0.4">
-      <c r="A182" t="s">
-        <v>2160</v>
-      </c>
-      <c r="B182" t="s">
-        <v>2161</v>
       </c>
       <c r="C182">
         <v>11</v>
@@ -19040,18 +19012,18 @@
         <v>22</v>
       </c>
       <c r="F182" t="s">
-        <v>2033</v>
+        <v>2028</v>
       </c>
       <c r="G182" t="s">
-        <v>2162</v>
-      </c>
-    </row>
-    <row r="183" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2157</v>
+      </c>
+    </row>
+    <row r="183" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
-        <v>2163</v>
+        <v>2158</v>
       </c>
       <c r="B183" t="s">
-        <v>2164</v>
+        <v>2159</v>
       </c>
       <c r="C183">
         <v>12</v>
@@ -19063,18 +19035,18 @@
         <v>36</v>
       </c>
       <c r="F183" t="s">
-        <v>2165</v>
+        <v>2160</v>
       </c>
       <c r="G183" t="s">
-        <v>2166</v>
-      </c>
-    </row>
-    <row r="184" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2161</v>
+      </c>
+    </row>
+    <row r="184" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
-        <v>2167</v>
+        <v>2162</v>
       </c>
       <c r="B184" t="s">
-        <v>2168</v>
+        <v>2163</v>
       </c>
       <c r="C184">
         <v>12</v>
@@ -19086,18 +19058,18 @@
         <v>22</v>
       </c>
       <c r="F184" t="s">
-        <v>2169</v>
+        <v>2164</v>
       </c>
       <c r="G184" t="s">
-        <v>2170</v>
-      </c>
-    </row>
-    <row r="185" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2165</v>
+      </c>
+    </row>
+    <row r="185" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
-        <v>2171</v>
+        <v>2166</v>
       </c>
       <c r="B185" t="s">
-        <v>2172</v>
+        <v>2167</v>
       </c>
       <c r="C185">
         <v>13</v>
@@ -19109,18 +19081,18 @@
         <v>72</v>
       </c>
       <c r="F185" t="s">
-        <v>2173</v>
+        <v>2168</v>
       </c>
       <c r="G185" t="s">
-        <v>2174</v>
-      </c>
-    </row>
-    <row r="186" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2169</v>
+      </c>
+    </row>
+    <row r="186" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
-        <v>2175</v>
+        <v>2170</v>
       </c>
       <c r="B186" t="s">
-        <v>2176</v>
+        <v>2171</v>
       </c>
       <c r="C186">
         <v>13</v>
@@ -19132,18 +19104,18 @@
         <v>36</v>
       </c>
       <c r="F186" t="s">
-        <v>2177</v>
+        <v>2172</v>
       </c>
       <c r="G186" t="s">
-        <v>2178</v>
-      </c>
-    </row>
-    <row r="187" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2173</v>
+      </c>
+    </row>
+    <row r="187" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
-        <v>2179</v>
+        <v>2174</v>
       </c>
       <c r="B187" t="s">
-        <v>2180</v>
+        <v>2175</v>
       </c>
       <c r="C187">
         <v>11</v>
@@ -19155,18 +19127,18 @@
         <v>41</v>
       </c>
       <c r="F187" t="s">
-        <v>2181</v>
+        <v>2176</v>
       </c>
       <c r="G187" t="s">
-        <v>2182</v>
-      </c>
-    </row>
-    <row r="188" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2177</v>
+      </c>
+    </row>
+    <row r="188" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
-        <v>2183</v>
+        <v>2178</v>
       </c>
       <c r="B188" t="s">
-        <v>2184</v>
+        <v>2179</v>
       </c>
       <c r="C188">
         <v>11</v>
@@ -19178,18 +19150,18 @@
         <v>36</v>
       </c>
       <c r="F188" t="s">
-        <v>2185</v>
+        <v>2180</v>
       </c>
       <c r="G188" t="s">
-        <v>2186</v>
-      </c>
-    </row>
-    <row r="189" spans="1:7" x14ac:dyDescent="0.4">
+        <v>2181</v>
+      </c>
+    </row>
+    <row r="189" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
-        <v>2187</v>
+        <v>2182</v>
       </c>
       <c r="B189" t="s">
-        <v>2188</v>
+        <v>2183</v>
       </c>
       <c r="C189">
         <v>13</v>
@@ -19201,10 +19173,10 @@
         <v>16</v>
       </c>
       <c r="F189" t="s">
-        <v>2189</v>
+        <v>2184</v>
       </c>
       <c r="G189" t="s">
-        <v>2190</v>
+        <v>2185</v>
       </c>
     </row>
   </sheetData>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H28"/>
+  <dimension ref="A1:H70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
@@ -1544,6 +1544,1686 @@
         </is>
       </c>
     </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>박시아</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>snapchatnegotia</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 49 105동 402호</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>권민영</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-09-30 09:18:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>엄서진</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>artthoughtful7</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>대구 북구 공항로 84 102동 104호</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>김윤정</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-09-30 09:19:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>유주은</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>gopeace</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>11</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 203동 104호</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>이지예</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-09-30 09:31:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>한정아</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>allystudent</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>13</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>대구 북구 구암서로 41 305동 106호</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>한성일</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-09-30 09:46:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>윤상우</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>inclusionfood5</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>12</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>대구 북구 공항로 16 105동 104호</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>이현진</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-09-30 09:59:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>이정안</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>fashion5</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>11</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 49 105동 505호</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>홍현아</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-09-30 10:10:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>라시유</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>writersuccess</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 89 203동 206호</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>라성하</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-09-30 10:21:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>이서영</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>superbookworm</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>13</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>대구 북구 동북로 241 203동 203호</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>김은아</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-09-30 10:33:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>이은성</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>lovesejong</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>대구도남초등학교</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>대구 북구 구리로 254 203동 208호</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>이준호</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-09-30 10:34:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>김유현</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>basketballdevel</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>11</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>대구 북구 읍내동 794 103동 108호</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>양소라</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-09-30 10:48:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>신설하</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>happyproducer8</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>11</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>대구 북구 한강로 17 103동 208호</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>신재원</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-09-30 11:18:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>박도율</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>tiktokdeveloper</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>11</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>대구사수초등학교</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 89 202동 406호</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>박형진</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-09-30 11:32:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>김단우</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>counselorgirl8</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>대구관문초등학교</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>대구 북구 매전로4길 9 212동 105호</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>이지혜</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-09-30 11:46:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>오희진</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>teenbrave2</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>11</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>대구 북구 한강로 17 103동 208호</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>오동인</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-09-30 11:59:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>신하린</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>friendshipnight</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>13</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 101동 402호</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>남혜진</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-09-30 12:10:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>조다빈</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>justicesupporte</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>12</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 103동 207호</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>박지선</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-09-30 12:23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>조민겸</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>starrysaettrave</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>대구 북구 읍내동 794 103동 106호</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>김경희</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-09-30 12:37:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>최지현</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>noobstarrysaet0</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>11</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>대구사수초등학교</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 89 202동 301호</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>정유미</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025-09-30 13:00:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>정하라</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>imaginationcomm</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>13</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 97 103동 206호</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>황혜영</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-09-30 13:12:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>최태린</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>bakingsaetsky</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>대구연경초등학교</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>대구 북구 연경중앙로11길 19 103동 104호</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>최동현</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-09-30 13:24:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>지연주</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>patient04</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>대구관문초등학교</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>대구 북구 매전로4길 31 203동 102호</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>지재욱</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-09-30 13:36:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>박재은</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>supporter1</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>12</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>대구 북구 대천로 101 101동 508호</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>신소희</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2025-09-30 13:47:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>신동건</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>kpoplearner8</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>11</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>대구도남초등학교</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>대구 북구 도남길 148-51 102동 401호</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>이민서</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2025-09-30 14:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>김다예</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>teammate05</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>13</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 156 103동 403호</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>김형수</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2025-09-30 14:11:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>장나영</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>starrysaetleade</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>13</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 205동 105호</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>이은주</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2025-09-30 14:22:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>윤진서</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>communityachiev</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>13</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>대구관문초등학교</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>대구 북구 매전로4길 9 212동 505호</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>신지원</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2025-09-30 14:35:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>손찬희</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>periodtfoodie6</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>대구사수초등학교</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 89 202동 301호</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>손형민</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2025-09-30 14:49:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>김리안</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>gratitudecrazy</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>11</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>대구 북구 읍내동 794 102동 505호</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>김성열</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2025-09-30 15:03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>원도형</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>dancebookworm4</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>12</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>대구관문초등학교</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>대구 북구 매전로4길 31 203동 501호</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>원민철</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2025-09-30 15:18:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>심설</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>ally13</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>13</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 205동 304호</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>심기훈</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-09-30 15:31:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>지도겸</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>tiktokinfluence</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 101동 502호</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>김혜원</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2025-09-30 15:41:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>김한별</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>hero2</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>11</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 156 101동 107호</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>이윤지</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2025-09-30 15:56:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>문예린</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>mollyhealth</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>13</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>대구 북구 읍내동 794 103동 309호</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>문준영</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025-09-30 16:07:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>김라윤</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>fashionistaspor</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 102동 401호</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>김지영</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2025-09-30 16:21:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>최승아</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>innovation7</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>12</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 202동 304호</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>최동호</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2025-09-30 16:36:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>김유성</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>ninjastrategist</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>13</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>대구동변초등학교</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>대구 북구 동변로 55 102동 408호</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>김동욱</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2025-09-30 16:46:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>박시후</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>friend69</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>11</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>대구관문초등학교</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>대구 북구 매전로 50-42 202동 108호</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>우소정</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:00:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>김성현</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>doctor2</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>11</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>대구 북구 동북로 241 203동 406호</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>김재영</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:14:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>박누리</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>sunshineresourc</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>대구도남초등학교</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 국우동 1079 103동 409호</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>박준철</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>박율</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>patientscientis</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>대구삼영초등학교</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>대구 북구 내곡로 49 104동 201호</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>정민희</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:38:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>고세령</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>traveler9</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>11</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 100 202동 204호</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>김은정</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2025-09-30 17:49:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>신유민</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>naruto62</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>12</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 103동 405호</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>신동원</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2025-09-30 18:02:12</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H70"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
@@ -3224,6 +3224,46 @@
         </is>
       </c>
     </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>양든</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>friendlyorganiz</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 102동 404호</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>임지연</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2025-10-01 08:48:22</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -419,7 +419,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
@@ -3264,6 +3264,926 @@
         </is>
       </c>
     </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>김해준</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>learningqueen6</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 103동 209호</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>우미영</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025-10-01 09:18:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>김희서</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>justicerush6</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>11</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>대구동변초등학교</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>대구 북구 동변로 50 103동 502호</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>김동윤</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025-10-01 09:29:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>강하임</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>nevertbh8</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 203동 103호</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>박민주</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2025-10-01 09:43:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>박은수</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>photographymedi</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>대구칠곡초등학교</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>대구 북구 학정동로 40 203동 105호</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>박민식</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-10-01 09:54:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>윤율희</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>success0</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>11</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>대구칠성초등학교</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>대구 북구 호암로 20 107동 306호</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>윤성철</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025-10-01 10:08:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>라서온</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>basketballrepor</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>12</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>대구칠성초등학교</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>대구 북구 칠성남로 101 110동 409호</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>라성수</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2025-10-01 10:23:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>배시하</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>empathywarrior1</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>12</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>대구사수초등학교</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>대구 북구 한강로 17 102동 509호</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>김미정</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2025-10-01 10:37:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>박가온</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>motivator2</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>12</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>대구 북구 공항로 84 104동 207호</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>정미소</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2025-10-01 10:50:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>박혜나</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>daygercommunica</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>11</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>대구연경초등학교</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>대구 동구 동화천로 369 102동 303호</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>박준성</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2025-10-01 11:03:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>박하나</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>guitar1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>13</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>대구 북구 국우동 1079 102동 303호</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>박민호</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2025-10-01 11:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>박다니엘</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>ghostingsmash</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>12</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>대구칠성초등학교</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>대구 북구 칠성남로 101 108동 101호</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>이윤아</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2025-10-01 11:27:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>조경민</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>therapistadvent</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>대구학남초등학교</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 102동 502호</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>조성규</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2025-10-01 11:39:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>한담</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>wisdomrespect</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>12</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>대구도남초등학교</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>대구광역시 북구 국우동 1079 103동 208호</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>이미선</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2025-10-01 11:50:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>장수정</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>linguistsejong7</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>13</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>대구운암초등학교</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>대구 북구 대천로 101 103동 107호</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>장성진</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2025-10-01 12:03:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>정우현</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>friendlyfamily</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>13</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>대구 북구 동북로 241 202동 105호</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>이유나</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2025-10-01 12:14:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>김이랑</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>shiningwhiz2</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>12</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 156 101동 509호</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>김지안</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2025-10-01 12:29:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>황로하</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>volunteerguide0</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>13</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>대구운암초등학교</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 156 103동 506호</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>한지현</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2025-10-01 12:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>이연아</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>squad3</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>12</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>대구 북구 국우동 1079 102동 501호</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>안지수</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2025-10-01 12:52:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>황도하</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>bookwormchill6</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>12</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>대구복현초등학교</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>대구 북구 동북로 241 203동 503호</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>유유리</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2025-10-01 13:07:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>강슬</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>historylunatic</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>12</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>대구 북구 학남로 60 103동 504호</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>고소미</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2025-10-01 13:18:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>이시연</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>compassionbaker</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>11</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>대구태암초등학교</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>대구 북구 동천로 156 102동 107호</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>이재현</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2025-10-01 13:33:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>장혜리</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>dreamer2</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>대구동평초등학교</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>대구 북구 대천로 101 101동 201호</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>장형원</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2025-10-01 13:44:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>권정후</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>athletesuccess4</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>11</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>대구학정초등학교</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>대구 북구 학정로110길 29 103동 305호</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>권준규</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2025-10-01 13:58:33</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KJG\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\EnozAce\Documents\GitHub\enoz_kjg\파이썬\코딩교실 매크로\1.코딩교실준비\2.추가인원 수강신청\1.추가인원 가입 수강신청\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF6C97B3-7227-4CAC-9064-18F6A416F2D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C02EDFEB-3B06-4735-AFA7-36D7398A323F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2472" yWindow="732" windowWidth="17280" windowHeight="8964" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="32310" yWindow="3510" windowWidth="28860" windowHeight="15465" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" r:id="rId1"/>
@@ -1798,9 +1798,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H92"/>
-  <sheetFormatPr defaultRowHeight="17.399999999999999" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -1826,7 +1826,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>8</v>
       </c>
@@ -1852,7 +1852,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>15</v>
       </c>
@@ -1878,7 +1878,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>22</v>
       </c>
@@ -1904,7 +1904,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>28</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>34</v>
       </c>
@@ -1956,7 +1956,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>39</v>
       </c>
@@ -1982,7 +1982,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>45</v>
       </c>
@@ -2008,7 +2008,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>51</v>
       </c>
@@ -2034,7 +2034,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>57</v>
       </c>
@@ -2060,7 +2060,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>62</v>
       </c>
@@ -2086,7 +2086,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>68</v>
       </c>
@@ -2112,7 +2112,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="13" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>74</v>
       </c>
@@ -2138,7 +2138,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="14" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>80</v>
       </c>
@@ -2164,7 +2164,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>85</v>
       </c>
@@ -2190,7 +2190,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>90</v>
       </c>
@@ -2216,7 +2216,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>96</v>
       </c>
@@ -2242,7 +2242,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>101</v>
       </c>
@@ -2268,7 +2268,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>107</v>
       </c>
@@ -2294,7 +2294,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>112</v>
       </c>
@@ -2320,7 +2320,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>117</v>
       </c>
@@ -2346,7 +2346,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>122</v>
       </c>
@@ -2372,7 +2372,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>127</v>
       </c>
@@ -2398,7 +2398,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>132</v>
       </c>
@@ -2424,7 +2424,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>137</v>
       </c>
@@ -2450,7 +2450,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>142</v>
       </c>
@@ -2476,7 +2476,7 @@
         <v>146</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>147</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>152</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>153</v>
       </c>
@@ -2528,7 +2528,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>158</v>
       </c>
@@ -2554,7 +2554,7 @@
         <v>163</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>164</v>
       </c>
@@ -2580,7 +2580,7 @@
         <v>168</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>169</v>
       </c>
@@ -2606,7 +2606,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>174</v>
       </c>
@@ -2632,7 +2632,7 @@
         <v>178</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>179</v>
       </c>
@@ -2658,7 +2658,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>184</v>
       </c>
@@ -2684,7 +2684,7 @@
         <v>188</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>189</v>
       </c>
@@ -2710,7 +2710,7 @@
         <v>193</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>194</v>
       </c>
@@ -2736,7 +2736,7 @@
         <v>198</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>199</v>
       </c>
@@ -2762,7 +2762,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>204</v>
       </c>
@@ -2788,7 +2788,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>209</v>
       </c>
@@ -2814,7 +2814,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>214</v>
       </c>
@@ -2840,7 +2840,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>218</v>
       </c>
@@ -2866,7 +2866,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>223</v>
       </c>
@@ -2892,7 +2892,7 @@
         <v>227</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>228</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>232</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>233</v>
       </c>
@@ -2944,7 +2944,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>238</v>
       </c>
@@ -2970,7 +2970,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>243</v>
       </c>
@@ -2996,7 +2996,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>248</v>
       </c>
@@ -3022,7 +3022,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>253</v>
       </c>
@@ -3048,7 +3048,7 @@
         <v>257</v>
       </c>
     </row>
-    <row r="49" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="49" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>258</v>
       </c>
@@ -3074,7 +3074,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="50" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="50" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>263</v>
       </c>
@@ -3100,7 +3100,7 @@
         <v>267</v>
       </c>
     </row>
-    <row r="51" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="51" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>268</v>
       </c>
@@ -3126,7 +3126,7 @@
         <v>272</v>
       </c>
     </row>
-    <row r="52" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="52" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>273</v>
       </c>
@@ -3152,7 +3152,7 @@
         <v>277</v>
       </c>
     </row>
-    <row r="53" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="53" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>278</v>
       </c>
@@ -3178,7 +3178,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="54" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="54" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>282</v>
       </c>
@@ -3204,7 +3204,7 @@
         <v>286</v>
       </c>
     </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="55" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>287</v>
       </c>
@@ -3230,7 +3230,7 @@
         <v>291</v>
       </c>
     </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="56" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>292</v>
       </c>
@@ -3256,7 +3256,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="57" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="57" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>297</v>
       </c>
@@ -3282,7 +3282,7 @@
         <v>301</v>
       </c>
     </row>
-    <row r="58" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="58" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>302</v>
       </c>
@@ -3308,7 +3308,7 @@
         <v>306</v>
       </c>
     </row>
-    <row r="59" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="59" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>307</v>
       </c>
@@ -3334,7 +3334,7 @@
         <v>311</v>
       </c>
     </row>
-    <row r="60" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="60" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>312</v>
       </c>
@@ -3360,7 +3360,7 @@
         <v>316</v>
       </c>
     </row>
-    <row r="61" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="61" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>317</v>
       </c>
@@ -3386,7 +3386,7 @@
         <v>321</v>
       </c>
     </row>
-    <row r="62" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>322</v>
       </c>
@@ -3412,7 +3412,7 @@
         <v>326</v>
       </c>
     </row>
-    <row r="63" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="63" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>327</v>
       </c>
@@ -3438,7 +3438,7 @@
         <v>331</v>
       </c>
     </row>
-    <row r="64" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="64" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>332</v>
       </c>
@@ -3464,7 +3464,7 @@
         <v>336</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>337</v>
       </c>
@@ -3490,7 +3490,7 @@
         <v>341</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>342</v>
       </c>
@@ -3516,7 +3516,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>347</v>
       </c>
@@ -3542,7 +3542,7 @@
         <v>351</v>
       </c>
     </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="68" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>352</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="69" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="69" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>357</v>
       </c>
@@ -3594,7 +3594,7 @@
         <v>361</v>
       </c>
     </row>
-    <row r="70" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="70" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>362</v>
       </c>
@@ -3620,7 +3620,7 @@
         <v>366</v>
       </c>
     </row>
-    <row r="71" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="71" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>367</v>
       </c>
@@ -3646,7 +3646,7 @@
         <v>371</v>
       </c>
     </row>
-    <row r="72" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="72" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>372</v>
       </c>
@@ -3672,7 +3672,7 @@
         <v>376</v>
       </c>
     </row>
-    <row r="73" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="73" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>377</v>
       </c>
@@ -3698,7 +3698,7 @@
         <v>381</v>
       </c>
     </row>
-    <row r="74" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="74" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>382</v>
       </c>
@@ -3724,7 +3724,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="75" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>387</v>
       </c>
@@ -3750,7 +3750,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="76" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>392</v>
       </c>
@@ -3776,7 +3776,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="77" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="77" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>397</v>
       </c>
@@ -3802,7 +3802,7 @@
         <v>401</v>
       </c>
     </row>
-    <row r="78" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="78" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>402</v>
       </c>
@@ -3828,7 +3828,7 @@
         <v>406</v>
       </c>
     </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="79" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>407</v>
       </c>
@@ -3854,7 +3854,7 @@
         <v>411</v>
       </c>
     </row>
-    <row r="80" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="80" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>412</v>
       </c>
@@ -3880,7 +3880,7 @@
         <v>416</v>
       </c>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>417</v>
       </c>
@@ -3906,7 +3906,7 @@
         <v>421</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>422</v>
       </c>
@@ -3932,7 +3932,7 @@
         <v>426</v>
       </c>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>427</v>
       </c>
@@ -3958,7 +3958,7 @@
         <v>431</v>
       </c>
     </row>
-    <row r="84" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="84" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>432</v>
       </c>
@@ -3984,7 +3984,7 @@
         <v>436</v>
       </c>
     </row>
-    <row r="85" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="85" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>437</v>
       </c>
@@ -4010,7 +4010,7 @@
         <v>441</v>
       </c>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>442</v>
       </c>
@@ -4036,7 +4036,7 @@
         <v>446</v>
       </c>
     </row>
-    <row r="87" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="87" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>447</v>
       </c>
@@ -4062,7 +4062,7 @@
         <v>451</v>
       </c>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>452</v>
       </c>
@@ -4088,7 +4088,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="89" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>457</v>
       </c>
@@ -4114,7 +4114,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="90" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="90" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>462</v>
       </c>
@@ -4140,7 +4140,7 @@
         <v>466</v>
       </c>
     </row>
-    <row r="91" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="91" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>467</v>
       </c>
@@ -4166,7 +4166,7 @@
         <v>471</v>
       </c>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.4">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>472</v>
       </c>

--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -7,6 +7,7 @@
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="PH" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1"/>
@@ -419,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H108"/>
+  <dimension ref="A1:H99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
@@ -4384,368 +4385,1744 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>박희찬</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>justiceeditor4</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>12</v>
-      </c>
-      <c r="D100" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>대구관문초등학교</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>대구 북구 매전로4길 31 203동 308호</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>박지은</t>
-        </is>
-      </c>
-      <c r="H100" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:02:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>윤지연</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>champlove4</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>11</v>
-      </c>
-      <c r="D101" t="inlineStr">
-        <is>
-          <t>화목</t>
-        </is>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>대구칠곡초등학교</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>대구 북구 학정동로 40 201동 208호</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>김은아</t>
-        </is>
-      </c>
-      <c r="H101" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:15:53</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>윤유리</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>ghosting5</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>13</v>
-      </c>
-      <c r="D102" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>대구삼영초등학교</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>대구 북구 내곡로 49 104동 102호</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>윤현우</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:27:32</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>박서준</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>laughterfashion</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>11</v>
-      </c>
-      <c r="D103" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>대구태암초등학교</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>대구 북구 학남로 60 102동 408호</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>김은진</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:34:27</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>김성윤</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>facilitatorscie</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>13</v>
-      </c>
-      <c r="D104" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>대구학정초등학교</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>대구 북구 학정로110길 29 101동 406호</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>김형석</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:40:10</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>배은비</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>imaginativeinst</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>12</v>
-      </c>
-      <c r="D105" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>대구동변초등학교</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>대구 북구 동변로 55 103동 507호</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>이혜미</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:49:07</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>이지민</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>curioussloshed1</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>11</v>
-      </c>
-      <c r="D106" t="inlineStr">
-        <is>
-          <t>월수</t>
-        </is>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>대구태암초등학교</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>대구 북구 동천로 156 101동 505호</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>이성찬</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>2025-10-01 19:58:06</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>김예진</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>expertyoutube7</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>12</v>
-      </c>
-      <c r="D107" t="inlineStr">
-        <is>
-          <t>화목</t>
-        </is>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>대구관문초등학교</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>대구 북구 매전로 50-42 202동 203호</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>김형일</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>2025-10-01 20:06:46</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>장라원</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>friendlychampio</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>12</v>
-      </c>
-      <c r="D108" t="inlineStr">
-        <is>
-          <t>화목</t>
-        </is>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>대구동변초등학교</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>대구 북구 동변로 50 101동 109호</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>장형종</t>
-        </is>
-      </c>
-      <c r="H108" t="inlineStr">
-        <is>
-          <t>2025-10-01 20:13:01</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H43"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>이름</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>아이디</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>나이</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>요일</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>학교</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>주소</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>부모이름</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>가입일시</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>유서율</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>baking07</t>
+        </is>
+      </c>
+      <c r="C2" t="n">
+        <v>13</v>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로827번길 9 102동 101호</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>이현희</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>2025-10-02 09:34:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>이보경</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>bakerchef</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>11</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>창포초등학교</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1075번길 10 103동 208호</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>김혜미</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2025-10-02 09:44:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>김채훈</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>versatilestarry</t>
+        </is>
+      </c>
+      <c r="C4" t="n">
+        <v>11</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>달전초등학교</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 이인리 927-61 108동 506호</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>김성찬</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:05:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>송태환</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>technologyequal</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>12</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로 127 202동 203호</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>송성욱</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:14:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>한인서</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>counselorversat</t>
+        </is>
+      </c>
+      <c r="C6" t="n">
+        <v>13</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 문덕로12번길 6 나동 105호</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>한형철</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:24:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>문율아</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>honestyspeciali</t>
+        </is>
+      </c>
+      <c r="C7" t="n">
+        <v>11</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 301호</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>문현우</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:30:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>강형준</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>peacehistory</t>
+        </is>
+      </c>
+      <c r="C8" t="n">
+        <v>11</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창동로 129 중해마루힐 111동 103호</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>김민솔</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:37:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>이민정</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>btswarrior</t>
+        </is>
+      </c>
+      <c r="C9" t="n">
+        <v>11</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 101호</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>이형종</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:47:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>남환</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>freetraveler3</t>
+        </is>
+      </c>
+      <c r="C10" t="n">
+        <v>11</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 503호</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>남민준</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2025-10-02 10:55:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>김정빈</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>teenbookworm</t>
+        </is>
+      </c>
+      <c r="C11" t="n">
+        <v>12</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로489번길 9 106동 404호</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>김현준</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:04:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>신이수</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>criticgenius</t>
+        </is>
+      </c>
+      <c r="C12" t="n">
+        <v>13</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로 127 202동 102호</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>선혜정</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:11:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>김윤호</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>perseveranceres</t>
+        </is>
+      </c>
+      <c r="C13" t="n">
+        <v>11</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 405호</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>장은솔</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:18:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>김진아</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>nightwhiz</t>
+        </is>
+      </c>
+      <c r="C14" t="n">
+        <v>11</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 205동 407호</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>김성훈</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:24:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>정로이</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>respectcool5</t>
+        </is>
+      </c>
+      <c r="C15" t="n">
+        <v>13</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 66-11 102동 402호</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>최현영</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:30:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>이유이</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>fashionistadeve</t>
+        </is>
+      </c>
+      <c r="C16" t="n">
+        <v>13</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>문덕초등학교</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 해병로 405 청호하이츠 102동 209호</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>이성현</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:36:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>전윤수</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>tiktok22</t>
+        </is>
+      </c>
+      <c r="C17" t="n">
+        <v>13</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 이인로 56 포항역삼구트리니엔 108동 104호</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>유지은</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:43:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>라하선</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>successreporter</t>
+        </is>
+      </c>
+      <c r="C18" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 정몽주로861번길 19 라동 104호</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>박미연</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:51:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>유수안</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>speakereducator</t>
+        </is>
+      </c>
+      <c r="C19" t="n">
+        <v>11</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>달전초등학교</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 지곡로 294 220동 302호</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>이민선</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>2025-10-02 11:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>김효린</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>loyaltyhero4</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>11</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼호로 391 116동 206호</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>이민아</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:03:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>노로운</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>throwdownrespon</t>
+        </is>
+      </c>
+      <c r="C21" t="n">
+        <v>11</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 409호</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>김혜림</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:09:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>이가은</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>educatorsupport</t>
+        </is>
+      </c>
+      <c r="C22" t="n">
+        <v>12</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 66-11 102동 206호</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>이형우</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:19:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>김진영</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>gamerrocket5</t>
+        </is>
+      </c>
+      <c r="C23" t="n">
+        <v>12</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 101호</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>김민상</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:27:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>김한결</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>bruhscience1</t>
+        </is>
+      </c>
+      <c r="C24" t="n">
+        <v>12</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창동로 129 중해마루힐 111동 504호</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>염은서</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:33:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>정우찬</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>explorationstyl</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>13</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 중성로32번길 30-1 1동 505호</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>김소윤</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:42:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>이아인</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>creatordope</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 204호</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>이성민</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>임미나</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>couragekpop</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>12</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 환호공원길 53-4 103동 109호</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>정은영</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>2025-10-02 12:59:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>손호</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>sciencebookworm</t>
+        </is>
+      </c>
+      <c r="C28" t="n">
+        <v>13</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1123번길 14 105동 102호</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>변지아</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:08:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>윤유찬</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>persistentsumme</t>
+        </is>
+      </c>
+      <c r="C29" t="n">
+        <v>12</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 이인로 56 포항역삼구트리니엔 108동 308호</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>윤형범</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:16:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>오다연</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>ultra07</t>
+        </is>
+      </c>
+      <c r="C30" t="n">
+        <v>11</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>달전초등학교</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 이인리 927-61 108동 301호</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>정현주</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:24:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>최민솔</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>equalitynaruto</t>
+        </is>
+      </c>
+      <c r="C31" t="n">
+        <v>13</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 102호</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>송민경</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>이우성</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>historycollabor</t>
+        </is>
+      </c>
+      <c r="C32" t="n">
+        <v>11</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E32" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1123번길 14 105동 308호</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>전은아</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:40:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>노인아</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>whiz4</t>
+        </is>
+      </c>
+      <c r="C33" t="n">
+        <v>11</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 508호</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>공소진</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:46:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>이태민</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>curioushelpful0</t>
+        </is>
+      </c>
+      <c r="C34" t="n">
+        <v>13</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 209호</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>박소영</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>2025-10-02 13:55:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>손유준</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>hyperhealth</t>
+        </is>
+      </c>
+      <c r="C35" t="n">
+        <v>11</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 66-11 102동 405호</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>손민규</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:02:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>박아론</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>megaartist2</t>
+        </is>
+      </c>
+      <c r="C36" t="n">
+        <v>11</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창동로 129 중해마루힐 111동 203호</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>이은진</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:07:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>전서아</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>reporterenglish</t>
+        </is>
+      </c>
+      <c r="C37" t="n">
+        <v>13</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼호로 391 116동 201호</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>전동규</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:15:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>박태준</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>leader66</t>
+        </is>
+      </c>
+      <c r="C38" t="n">
+        <v>12</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 107호</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>박형태</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:24:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>백솔</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>supporterlingui</t>
+        </is>
+      </c>
+      <c r="C39" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 206동 502호</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>천민지</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:32:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>이연서</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>strategistthera</t>
+        </is>
+      </c>
+      <c r="C40" t="n">
+        <v>13</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1123번길 14 105동 306호</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>김예은</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:42:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>오봄</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>requestiongener</t>
+        </is>
+      </c>
+      <c r="C41" t="n">
+        <v>12</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 두호로 66 107동 107호</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>정혜선</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:48:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>김다엘</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>entrepreneurgam</t>
+        </is>
+      </c>
+      <c r="C42" t="n">
+        <v>13</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새마을로 2 103동 301호</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>김유리</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:56:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>이규빈</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>healthbasic</t>
+        </is>
+      </c>
+      <c r="C43" t="n">
+        <v>12</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로18번길 6 1동 201호</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>류미경</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>2025-10-02 14:56:55</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
+++ b/파이썬/코딩교실 매크로/1.코딩교실준비/2.추가인원 수강신청/1.추가인원 가입 수강신청/추가인원 가입 현황.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2472" yWindow="732" windowWidth="17280" windowHeight="8964" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="2928" yWindow="564" windowWidth="17280" windowHeight="8964" tabRatio="600" firstSheet="0" activeTab="1" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="BG" sheetId="1" state="visible" r:id="rId1"/>
@@ -4397,8 +4397,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H43"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:H126"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="17.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -6119,6 +6119,3326 @@
       <c r="H43" t="inlineStr">
         <is>
           <t>2025-10-02 14:56:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>이세연</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>loyaltyinventor</t>
+        </is>
+      </c>
+      <c r="C44" t="n">
+        <v>11</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로489번길 9 106동 502호</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>이민재</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:05:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>유도준</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>starrysaetrespo</t>
+        </is>
+      </c>
+      <c r="C45" t="n">
+        <v>12</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로827번길 9 102동 209호</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>정지은</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>박하빈</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>snatchedrespect</t>
+        </is>
+      </c>
+      <c r="C46" t="n">
+        <v>12</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 501호</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>박형일</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:33:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>한민희</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>happyhistory7</t>
+        </is>
+      </c>
+      <c r="C47" t="n">
+        <v>12</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 중원로 16 103동 506호</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>한민석</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>2025-10-13 10:48:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>윤은준</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>artisthelpful</t>
+        </is>
+      </c>
+      <c r="C48" t="n">
+        <v>13</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 206동 209호</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>윤동진</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>2025-10-13 11:00:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>최수민</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>organizedtravel</t>
+        </is>
+      </c>
+      <c r="C49" t="n">
+        <v>11</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 306호</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>노유라</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>2025-10-13 11:13:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>구아랑</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>explorationmemo</t>
+        </is>
+      </c>
+      <c r="C50" t="n">
+        <v>11</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 402호</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>안현아</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>2025-10-13 11:25:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>조아연</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>justice11</t>
+        </is>
+      </c>
+      <c r="C51" t="n">
+        <v>12</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 302호</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>이지영</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>2025-10-13 11:38:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>김태규</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>sea73</t>
+        </is>
+      </c>
+      <c r="C52" t="n">
+        <v>11</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우미길 90 101동 105호</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>강지예</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>2025-10-13 11:52:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>김여진</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>basketball3</t>
+        </is>
+      </c>
+      <c r="C53" t="n">
+        <v>13</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1123번길 14 105동 205호</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>김형도</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:06:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>김연우</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>pianodeveloper</t>
+        </is>
+      </c>
+      <c r="C54" t="n">
+        <v>12</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 중원로 16 103동 201호</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>강소라</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>김성준</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>gotraveler</t>
+        </is>
+      </c>
+      <c r="C55" t="n">
+        <v>13</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>달전초등학교</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 이인리 927-61 108동 206호</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>김형준</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:31:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>김주안</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>boyorganizer</t>
+        </is>
+      </c>
+      <c r="C56" t="n">
+        <v>13</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 66-11 102동 107호</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>김재훈</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:43:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>김은하</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>charmingbts</t>
+        </is>
+      </c>
+      <c r="C57" t="n">
+        <v>11</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 206동 404호</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>윤지연</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>2025-10-13 12:58:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>김해리</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>historyfriendsh</t>
+        </is>
+      </c>
+      <c r="C58" t="n">
+        <v>11</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 407호</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>김동일</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:10:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>이현민</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>violincomedian8</t>
+        </is>
+      </c>
+      <c r="C59" t="n">
+        <v>12</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 201호</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>이동민</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:21:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>송루아</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>happiness9</t>
+        </is>
+      </c>
+      <c r="C60" t="n">
+        <v>13</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 509호</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>이소연</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:35:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>최인호</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>integrity9</t>
+        </is>
+      </c>
+      <c r="C61" t="n">
+        <v>12</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창동로 129 중해마루힐 111동 401호</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>김미소</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:49:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>노지영</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>pioneerchampion</t>
+        </is>
+      </c>
+      <c r="C62" t="n">
+        <v>13</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 창흥로 67 307동 305호</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>권은아</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>2025-10-13 13:53:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>김준호</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>confidentfoodie</t>
+        </is>
+      </c>
+      <c r="C63" t="n">
+        <v>13</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로827번길 9 102동 408호</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>김준혁</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:04:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>송태희</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>respecttbh</t>
+        </is>
+      </c>
+      <c r="C64" t="n">
+        <v>13</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 407호</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>오지아</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:14:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>변서영</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>soccer26</t>
+        </is>
+      </c>
+      <c r="C65" t="n">
+        <v>11</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로489번길 9 106동 409호</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>변성범</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:30:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>이시율</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>mindfulnesssupp</t>
+        </is>
+      </c>
+      <c r="C66" t="n">
+        <v>12</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 문덕로12번길 6 나동 502호</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>장유미</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:42:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>오유아</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>kindnesslearner</t>
+        </is>
+      </c>
+      <c r="C67" t="n">
+        <v>13</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 중성로32번길 30-1 가동 106호</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>이유진</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>2025-10-13 14:57:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>신윤진</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>englishsejong5</t>
+        </is>
+      </c>
+      <c r="C68" t="n">
+        <v>13</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로 127 202동 203호</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>신동석</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:09:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>김루희</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>basketballwarri</t>
+        </is>
+      </c>
+      <c r="C69" t="n">
+        <v>13</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 두호로 66 107동 103호</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>장민희</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:21:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>주예주</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>boypromoter</t>
+        </is>
+      </c>
+      <c r="C70" t="n">
+        <v>13</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 66-11 102동 301호</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>주준일</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:33:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>원현아</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>mathematicianfi</t>
+        </is>
+      </c>
+      <c r="C71" t="n">
+        <v>13</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>창포초등학교</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1075번길 10 103동 107호</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>김소희</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:45:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>홍은솔</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>narutotbh2</t>
+        </is>
+      </c>
+      <c r="C72" t="n">
+        <v>11</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 환호공원길 53-4 103동 507호</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>홍동훈</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>2025-10-13 15:57:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>조정우</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>flex1</t>
+        </is>
+      </c>
+      <c r="C73" t="n">
+        <v>12</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 해병로 125 105동 209호</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>조형석</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:08:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>오하늘</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>motivatedsquad</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>11</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 306호</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>오재현</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:23:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>이여울</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>photography3</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>11</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 30 가동 106호</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>손현영</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:35:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>추세인</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>liquid2</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>13</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 남성리 587-1 104동 503호</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>추재훈</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:57:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>박하유</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>couragecooking</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>13</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>문덕초등학교</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 문덕로12번길 29 103동 409호</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>박동현</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>2025-10-13 16:58:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>강지원</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>volunteerkpop9</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>13</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 307호</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>강형찬</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:08:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>조서원</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>athletevoluntee</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>11</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 206호</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>조준수</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:17:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>최예슬</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>patientflex</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>11</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창동로 129 중해마루힐 111동 105호</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>최형수</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:26:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>허가인</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>allyvolunteer</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>11</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 506호</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>고윤아</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:37:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>김진호</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>curator4</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>11</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 108호</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>김형준</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:47:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>오세희</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>inventorenviron</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>11</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우미길 90 101동 101호</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>오동윤</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>2025-10-13 17:55:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>양연준</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>friendship6</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>13</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새마을로 2 103동 304호</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>양민상</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:03:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>김이엘</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>lifeguitar</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>11</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로88번길 10 101동 505호</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>김동하</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:04:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>황시온</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>minecraftfitnes</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>12</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 환호공원길 53-4 103동 401호</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>김예은</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:34:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>권서빈</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>imaginative26</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>13</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>문덕초등학교</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 냉천로 340 1동 202호</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>권현우</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:42:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>김소희</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>geniusindepende</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>12</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 206동 503호</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>김성찬</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>2025-10-13 18:51:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>김채현</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>facilitator16</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>11</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 인덕로 71 3동 304호</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>김경희</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>2025-10-13 19:01:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>송은설</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>curatoroptimist</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>12</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 중흥로161번길 24-8 경동하이츠13차 B동 109호</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>김현정</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>2025-10-14 15:39:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>송보나</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>lovehistory3</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>12</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 정몽주로 702 103동 202호</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>송현준</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>2025-10-14 15:41:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>양하율</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>mathematicianru</t>
+        </is>
+      </c>
+      <c r="C92" t="n">
+        <v>12</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우미길 90 101동 102호</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>최수진</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>2025-10-14 15:49:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>엄서준</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>herosea</t>
+        </is>
+      </c>
+      <c r="C93" t="n">
+        <v>11</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새마을로 2 103동 504호</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>박윤영</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>2025-10-14 15:55:18</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>손경준</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>optimisthappy</t>
+        </is>
+      </c>
+      <c r="C94" t="n">
+        <v>12</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로 127 202동 107호</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>왕미연</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>2025-10-14 15:56:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>이민건</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>bruhfitness5</t>
+        </is>
+      </c>
+      <c r="C95" t="n">
+        <v>11</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 창흥로 67 307동 408호</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>류지수</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:05:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>신유라</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>sustainabilityf</t>
+        </is>
+      </c>
+      <c r="C96" t="n">
+        <v>11</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 305호</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>성혜나</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:14:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>박이서</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>hyper20</t>
+        </is>
+      </c>
+      <c r="C97" t="n">
+        <v>11</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>문덕초등학교</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 문덕로12번길 29 103동 307호</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>박민식</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:23:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>오윤</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>violincommunity</t>
+        </is>
+      </c>
+      <c r="C98" t="n">
+        <v>11</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E98" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 정몽주로 702 103동 409호</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>오동철</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:24:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" t="inlineStr">
+        <is>
+          <t>강우진</t>
+        </is>
+      </c>
+      <c r="B99" t="inlineStr">
+        <is>
+          <t>kindboy0</t>
+        </is>
+      </c>
+      <c r="C99" t="n">
+        <v>13</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E99" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 206동 407호</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>강민철</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:31:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" t="inlineStr">
+        <is>
+          <t>조혜원</t>
+        </is>
+      </c>
+      <c r="B100" t="inlineStr">
+        <is>
+          <t>peacetiktok4</t>
+        </is>
+      </c>
+      <c r="C100" t="n">
+        <v>11</v>
+      </c>
+      <c r="D100" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E100" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용흥동 포항우방타운 110동 108호</t>
+        </is>
+      </c>
+      <c r="G100" t="inlineStr">
+        <is>
+          <t>조준호</t>
+        </is>
+      </c>
+      <c r="H100" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:39:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" t="inlineStr">
+        <is>
+          <t>권민영</t>
+        </is>
+      </c>
+      <c r="B101" t="inlineStr">
+        <is>
+          <t>imaginationanim</t>
+        </is>
+      </c>
+      <c r="C101" t="n">
+        <v>12</v>
+      </c>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E101" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 남성리 587-1 104동 207호</t>
+        </is>
+      </c>
+      <c r="G101" t="inlineStr">
+        <is>
+          <t>김민솔</t>
+        </is>
+      </c>
+      <c r="H101" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:47:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>이정훈</t>
+        </is>
+      </c>
+      <c r="B102" t="inlineStr">
+        <is>
+          <t>editor21</t>
+        </is>
+      </c>
+      <c r="C102" t="n">
+        <v>13</v>
+      </c>
+      <c r="D102" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E102" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F102" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 정몽주로861번길 19 라동 209호</t>
+        </is>
+      </c>
+      <c r="G102" t="inlineStr">
+        <is>
+          <t>박미란</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:48:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>장준</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>megaachievement</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E103" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 중성로32번길 30-1 가동 309호</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>오현진</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>2025-10-14 16:57:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>주라율</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>photographerher</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E104" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로18번길 6 1동 507호</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>오지안</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>2025-10-14 17:07:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>윤해솔</t>
+        </is>
+      </c>
+      <c r="B105" t="inlineStr">
+        <is>
+          <t>explorer22</t>
+        </is>
+      </c>
+      <c r="C105" t="n">
+        <v>11</v>
+      </c>
+      <c r="D105" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E105" t="inlineStr">
+        <is>
+          <t>포항동부초등학교</t>
+        </is>
+      </c>
+      <c r="F105" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼흥로32번길 5 103동 202호</t>
+        </is>
+      </c>
+      <c r="G105" t="inlineStr">
+        <is>
+          <t>윤성일</t>
+        </is>
+      </c>
+      <c r="H105" t="inlineStr">
+        <is>
+          <t>2025-10-14 17:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>김휘</t>
+        </is>
+      </c>
+      <c r="B106" t="inlineStr">
+        <is>
+          <t>adventurerkpop9</t>
+        </is>
+      </c>
+      <c r="C106" t="n">
+        <v>11</v>
+      </c>
+      <c r="D106" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E106" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F106" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 301호</t>
+        </is>
+      </c>
+      <c r="G106" t="inlineStr">
+        <is>
+          <t>오민선</t>
+        </is>
+      </c>
+      <c r="H106" t="inlineStr">
+        <is>
+          <t>2025-10-14 17:26:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>김세린</t>
+        </is>
+      </c>
+      <c r="B107" t="inlineStr">
+        <is>
+          <t>wisdomliquid4</t>
+        </is>
+      </c>
+      <c r="C107" t="n">
+        <v>12</v>
+      </c>
+      <c r="D107" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E107" t="inlineStr">
+        <is>
+          <t>상대초등학교</t>
+        </is>
+      </c>
+      <c r="F107" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 대해로79번길 14-10 성경빌라 가동 304호</t>
+        </is>
+      </c>
+      <c r="G107" t="inlineStr">
+        <is>
+          <t>김동훈</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>2025-10-14 17:35:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>박시훈</t>
+        </is>
+      </c>
+      <c r="B108" t="inlineStr">
+        <is>
+          <t>resilience9</t>
+        </is>
+      </c>
+      <c r="C108" t="n">
+        <v>11</v>
+      </c>
+      <c r="D108" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E108" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F108" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼호로 391 116동 201호</t>
+        </is>
+      </c>
+      <c r="G108" t="inlineStr">
+        <is>
+          <t>박동원</t>
+        </is>
+      </c>
+      <c r="H108" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:17:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>이이진</t>
+        </is>
+      </c>
+      <c r="B109" t="inlineStr">
+        <is>
+          <t>adventureblackp</t>
+        </is>
+      </c>
+      <c r="C109" t="n">
+        <v>12</v>
+      </c>
+      <c r="D109" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E109" t="inlineStr">
+        <is>
+          <t>구정초등학교</t>
+        </is>
+      </c>
+      <c r="F109" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 정몽주로 702 103동 204호</t>
+        </is>
+      </c>
+      <c r="G109" t="inlineStr">
+        <is>
+          <t>남민경</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:27:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>김하람</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>kindpokemon</t>
+        </is>
+      </c>
+      <c r="C110" t="n">
+        <v>13</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>장량초등학교</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 용두산길 62 102동 509호</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>김형석</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:37:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>백지안</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>moneyeditor3</t>
+        </is>
+      </c>
+      <c r="C111" t="n">
+        <v>12</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로489번길 9 106동 101호</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>백동인</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:47:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>정하운</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>goatleader0</t>
+        </is>
+      </c>
+      <c r="C112" t="n">
+        <v>13</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 문덕로12번길 6 나동 304호</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>남민지</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>2025-10-15 13:55:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="113" ht="16.8" customHeight="1">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>김나연</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>lifeinnovator</t>
+        </is>
+      </c>
+      <c r="C113" t="n">
+        <v>11</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 성실로 50 205동 207호</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>김민재</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>2025-10-15 14:05:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>이찬</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>counselorknowle</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>11</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>흥해남산초등학교</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 중성로32번길 30-1 1동 109호</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>이성범</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>2025-10-15 14:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>유지희</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>compassionthoug</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>11</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>포항대흥초등학교</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우미길 90 101동 107호</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>유재석</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:06:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>구다솜</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>crazyhelpful</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>11</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>포항해맞이초등학교</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 삼호로 391 204동 405호</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>구성규</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:13:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>김승훈</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>starrysaetbrave</t>
+        </is>
+      </c>
+      <c r="C117" t="n">
+        <v>11</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 107호</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>손소영</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:23:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>김아민</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>wiselegend</t>
+        </is>
+      </c>
+      <c r="C118" t="n">
+        <v>12</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 해병로 125 105동 109호</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>배혜진</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:33:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>김가율</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>yeeseoloyalty</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>13</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>포항원동초등학교</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 오천읍 해병로489번길 9 106동 507호</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>김동일</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:43:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>안미소</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>familyequality</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>13</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 정몽주로861번길 19 라동 508호</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>안성수</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>2025-10-15 15:53:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>김재호</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>skillfulsports</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>12</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>포항중앙초등학교</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 우창로 20 205동 401호</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>김성훈</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>2025-10-15 16:02:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>양소미</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>determinedwhiz3</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>11</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>창포초등학교</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 대곡로 21 창포아이파크2차아파트 204동 203호</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>안윤미</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>2025-10-15 16:11:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>김세윤</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>honestytea3</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>13</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 이인로 56 포항역삼구트리니엔 108동 203호</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>최미영</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:15:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>이은호</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>dancercritic4</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>12</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>인덕초등학교</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>경북 포항시 남구 해병로 125 105동 108호</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>이정훈</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:26:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>이지혜</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>neverhelpful</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>13</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>화목</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>장성초등학교</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 새천년대로1123번길 14 105동 203호</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>권윤지</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>김로아</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>mollykpop4</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>11</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>월수</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>학천초등학교</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>경북 포항시 북구 흥해읍 도음로877번길 9 105동 304호</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>김혜원</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>2025-10-15 17:29:00</t>
         </is>
       </c>
     </row>
